--- a/data/proteomics/volume_size_across_compartment_Rosemary_NH4_limitation_v2.xlsx
+++ b/data/proteomics/volume_size_across_compartment_Rosemary_NH4_limitation_v2.xlsx
@@ -8,14 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A35DFD-DFB5-2A41-9809-C53E4C779ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB29863-CEE2-8D40-867B-A3F060C55351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="26880" windowHeight="15220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$A$140</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="164">
   <si>
     <t>compartment</t>
   </si>
@@ -1931,16 +1936,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>787400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11018,7 +11023,7 @@
         <v>0.74652733067627874</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:M2" si="0">H2/C2</f>
+        <f t="shared" ref="L2" si="0">H2/C2</f>
         <v>0.45752737359624945</v>
       </c>
       <c r="M2">
@@ -11052,7 +11057,7 @@
         <v>0.17596856724843041</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K19" si="1">G3/B3</f>
+        <f t="shared" ref="K3:K18" si="1">G3/B3</f>
         <v>0.73596974668197945</v>
       </c>
       <c r="L3">
@@ -11676,4 +11681,9421 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6DD68D5-A363-574C-A4F1-9F5610A100A3}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S140"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="43.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="19" width="29.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>0.52168090071337803</v>
+      </c>
+      <c r="C2">
+        <v>0.47696846799627352</v>
+      </c>
+      <c r="D2">
+        <v>0.49557603499405062</v>
+      </c>
+      <c r="E2">
+        <v>0.39311051923590351</v>
+      </c>
+      <c r="F2">
+        <v>0.41260246092852981</v>
+      </c>
+      <c r="G2">
+        <v>0.57716777966309829</v>
+      </c>
+      <c r="H2">
+        <v>0.5979680544289937</v>
+      </c>
+      <c r="I2">
+        <v>0.51453161426750382</v>
+      </c>
+      <c r="J2">
+        <v>0.52371269284754085</v>
+      </c>
+      <c r="K2">
+        <v>0.55962137944422863</v>
+      </c>
+      <c r="L2">
+        <v>0.55616942624912469</v>
+      </c>
+      <c r="M2">
+        <v>0.5643625727006305</v>
+      </c>
+      <c r="N2">
+        <v>1.003591251627264</v>
+      </c>
+      <c r="O2">
+        <v>1.0070385249961189</v>
+      </c>
+      <c r="P2">
+        <v>0.94317449424856026</v>
+      </c>
+      <c r="Q2">
+        <v>1.2689549979590189</v>
+      </c>
+      <c r="R2">
+        <v>1.349875761704193</v>
+      </c>
+      <c r="S2">
+        <v>1.3362065324613479</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>1.3153460701366929E-3</v>
+      </c>
+      <c r="C3">
+        <v>1.2510874325635561E-3</v>
+      </c>
+      <c r="D3">
+        <v>1.129289074246759E-3</v>
+      </c>
+      <c r="E3">
+        <v>1.0021405535975191E-3</v>
+      </c>
+      <c r="F3">
+        <v>1.041135671339215E-3</v>
+      </c>
+      <c r="G3">
+        <v>9.3333249674703634E-4</v>
+      </c>
+      <c r="H3">
+        <v>1.311823358583556E-3</v>
+      </c>
+      <c r="I3">
+        <v>1.083998113460815E-3</v>
+      </c>
+      <c r="J3">
+        <v>1.206541460260438E-3</v>
+      </c>
+      <c r="K3">
+        <v>1.28250273665894E-3</v>
+      </c>
+      <c r="L3">
+        <v>1.256820027737965E-3</v>
+      </c>
+      <c r="M3">
+        <v>1.3881221783130051E-3</v>
+      </c>
+      <c r="N3">
+        <v>1.77001969155968E-3</v>
+      </c>
+      <c r="O3">
+        <v>1.8214138483895971E-3</v>
+      </c>
+      <c r="P3">
+        <v>1.7631683978265951E-3</v>
+      </c>
+      <c r="Q3">
+        <v>2.047922642367514E-3</v>
+      </c>
+      <c r="R3">
+        <v>2.1065674051327292E-3</v>
+      </c>
+      <c r="S3">
+        <v>1.9654586075582401E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>8.7416873195713827E-4</v>
+      </c>
+      <c r="C4">
+        <v>8.0745994098694804E-4</v>
+      </c>
+      <c r="D4">
+        <v>8.5814656883098357E-4</v>
+      </c>
+      <c r="E4">
+        <v>8.1454031589881285E-4</v>
+      </c>
+      <c r="F4">
+        <v>8.5174424469599359E-4</v>
+      </c>
+      <c r="G4">
+        <v>8.7259421370951848E-4</v>
+      </c>
+      <c r="H4">
+        <v>1.235246266824287E-3</v>
+      </c>
+      <c r="I4">
+        <v>1.0263393106025431E-3</v>
+      </c>
+      <c r="J4">
+        <v>1.0143544942661071E-3</v>
+      </c>
+      <c r="K4">
+        <v>1.183436165546782E-3</v>
+      </c>
+      <c r="L4">
+        <v>1.223654975188363E-3</v>
+      </c>
+      <c r="M4">
+        <v>1.211053360348398E-3</v>
+      </c>
+      <c r="N4">
+        <v>1.9882424908955732E-3</v>
+      </c>
+      <c r="O4">
+        <v>2.0221797053222431E-3</v>
+      </c>
+      <c r="P4">
+        <v>2.0456564963340618E-3</v>
+      </c>
+      <c r="Q4">
+        <v>2.3907342758811611E-3</v>
+      </c>
+      <c r="R4">
+        <v>2.8464180742778589E-3</v>
+      </c>
+      <c r="S4">
+        <v>2.6965120956042791E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>1.109261458155498E-2</v>
+      </c>
+      <c r="C5">
+        <v>1.02663792252816E-2</v>
+      </c>
+      <c r="D5">
+        <v>1.038853667089347E-2</v>
+      </c>
+      <c r="E5">
+        <v>1.055764997198671E-2</v>
+      </c>
+      <c r="F5">
+        <v>1.0847245597843211E-2</v>
+      </c>
+      <c r="G5">
+        <v>1.428209835529225E-2</v>
+      </c>
+      <c r="H5">
+        <v>1.7969457909468269E-2</v>
+      </c>
+      <c r="I5">
+        <v>1.526523209082209E-2</v>
+      </c>
+      <c r="J5">
+        <v>1.5552716025541031E-2</v>
+      </c>
+      <c r="K5">
+        <v>1.8716860347803909E-2</v>
+      </c>
+      <c r="L5">
+        <v>1.8629273637774731E-2</v>
+      </c>
+      <c r="M5">
+        <v>1.82065533222684E-2</v>
+      </c>
+      <c r="N5">
+        <v>3.2024411299395997E-2</v>
+      </c>
+      <c r="O5">
+        <v>3.3679281296891253E-2</v>
+      </c>
+      <c r="P5">
+        <v>2.9711216543955261E-2</v>
+      </c>
+      <c r="Q5">
+        <v>3.6488792158002423E-2</v>
+      </c>
+      <c r="R5">
+        <v>3.7749644825005008E-2</v>
+      </c>
+      <c r="S5">
+        <v>3.8005764170014812E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>0.30597973817177743</v>
+      </c>
+      <c r="C6">
+        <v>0.28100773693804809</v>
+      </c>
+      <c r="D6">
+        <v>0.29472827685478048</v>
+      </c>
+      <c r="E6">
+        <v>0.23147733026061459</v>
+      </c>
+      <c r="F6">
+        <v>0.2455508140171152</v>
+      </c>
+      <c r="G6">
+        <v>0.32930331440883248</v>
+      </c>
+      <c r="H6">
+        <v>0.34581182183169817</v>
+      </c>
+      <c r="I6">
+        <v>0.30233640462425487</v>
+      </c>
+      <c r="J6">
+        <v>0.30055884840654862</v>
+      </c>
+      <c r="K6">
+        <v>0.30900078724685959</v>
+      </c>
+      <c r="L6">
+        <v>0.31228971371028241</v>
+      </c>
+      <c r="M6">
+        <v>0.31348340269863589</v>
+      </c>
+      <c r="N6">
+        <v>0.56398577843565423</v>
+      </c>
+      <c r="O6">
+        <v>0.5678304997106749</v>
+      </c>
+      <c r="P6">
+        <v>0.54872438177973015</v>
+      </c>
+      <c r="Q6">
+        <v>0.75892027472114709</v>
+      </c>
+      <c r="R6">
+        <v>0.82016412113016712</v>
+      </c>
+      <c r="S6">
+        <v>0.77419796013118791</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.67442031443780781</v>
+      </c>
+      <c r="C7">
+        <v>0.61520960606633124</v>
+      </c>
+      <c r="D7">
+        <v>0.62987423996521164</v>
+      </c>
+      <c r="E7">
+        <v>0.52211228625007611</v>
+      </c>
+      <c r="F7">
+        <v>0.55279457618101979</v>
+      </c>
+      <c r="G7">
+        <v>0.75230275314614692</v>
+      </c>
+      <c r="H7">
+        <v>0.80052203884857087</v>
+      </c>
+      <c r="I7">
+        <v>0.6830876819151378</v>
+      </c>
+      <c r="J7">
+        <v>0.69221686090539314</v>
+      </c>
+      <c r="K7">
+        <v>0.80091064711627802</v>
+      </c>
+      <c r="L7">
+        <v>0.77743592967316522</v>
+      </c>
+      <c r="M7">
+        <v>0.76554413113374953</v>
+      </c>
+      <c r="N7">
+        <v>1.566262375120504</v>
+      </c>
+      <c r="O7">
+        <v>1.5659609377606869</v>
+      </c>
+      <c r="P7">
+        <v>1.522733603813841</v>
+      </c>
+      <c r="Q7">
+        <v>2.152409749044963</v>
+      </c>
+      <c r="R7">
+        <v>2.2577487354393582</v>
+      </c>
+      <c r="S7">
+        <v>2.2221502610264028</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <v>0.324474652658578</v>
+      </c>
+      <c r="C8">
+        <v>0.28664237377279689</v>
+      </c>
+      <c r="D8">
+        <v>0.27883279813046569</v>
+      </c>
+      <c r="E8">
+        <v>0.24678451999742981</v>
+      </c>
+      <c r="F8">
+        <v>0.25513844542106812</v>
+      </c>
+      <c r="G8">
+        <v>0.38691904509735209</v>
+      </c>
+      <c r="H8">
+        <v>0.3807188592851361</v>
+      </c>
+      <c r="I8">
+        <v>0.3304304344291123</v>
+      </c>
+      <c r="J8">
+        <v>0.33080450937127592</v>
+      </c>
+      <c r="K8">
+        <v>0.32362353458857029</v>
+      </c>
+      <c r="L8">
+        <v>0.32928633625512371</v>
+      </c>
+      <c r="M8">
+        <v>0.32153221743800159</v>
+      </c>
+      <c r="N8">
+        <v>0.62172495972392128</v>
+      </c>
+      <c r="O8">
+        <v>0.61761707681017519</v>
+      </c>
+      <c r="P8">
+        <v>0.60953706938270669</v>
+      </c>
+      <c r="Q8">
+        <v>0.85997701213800837</v>
+      </c>
+      <c r="R8">
+        <v>0.95616978915339124</v>
+      </c>
+      <c r="S8">
+        <v>0.88592345149530627</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9">
+        <v>0.10183449707543719</v>
+      </c>
+      <c r="C9">
+        <v>9.5005500765825521E-2</v>
+      </c>
+      <c r="D9">
+        <v>8.6628164838528546E-2</v>
+      </c>
+      <c r="E9">
+        <v>7.6217569793132281E-2</v>
+      </c>
+      <c r="F9">
+        <v>8.0597380539462068E-2</v>
+      </c>
+      <c r="G9">
+        <v>0.1157248510346111</v>
+      </c>
+      <c r="H9">
+        <v>0.1105201273561455</v>
+      </c>
+      <c r="I9">
+        <v>9.6649410024441482E-2</v>
+      </c>
+      <c r="J9">
+        <v>0.10015433620251719</v>
+      </c>
+      <c r="K9">
+        <v>8.9830191002160664E-2</v>
+      </c>
+      <c r="L9">
+        <v>8.9571511937425061E-2</v>
+      </c>
+      <c r="M9">
+        <v>7.70039807701417E-2</v>
+      </c>
+      <c r="N9">
+        <v>0.17965456496580601</v>
+      </c>
+      <c r="O9">
+        <v>0.1713563778754203</v>
+      </c>
+      <c r="P9">
+        <v>0.1912716087407241</v>
+      </c>
+      <c r="Q9">
+        <v>0.27226669812674548</v>
+      </c>
+      <c r="R9">
+        <v>0.29981687882794739</v>
+      </c>
+      <c r="S9">
+        <v>0.26664625122750951</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10">
+        <v>2.6597233662811571E-2</v>
+      </c>
+      <c r="C10">
+        <v>2.3611947597992781E-2</v>
+      </c>
+      <c r="D10">
+        <v>2.4761167959351928E-2</v>
+      </c>
+      <c r="E10">
+        <v>2.6717515913466289E-2</v>
+      </c>
+      <c r="F10">
+        <v>2.7480597704362481E-2</v>
+      </c>
+      <c r="G10">
+        <v>2.9881091553176128E-2</v>
+      </c>
+      <c r="H10">
+        <v>4.3629219982038538E-2</v>
+      </c>
+      <c r="I10">
+        <v>3.7751539479471588E-2</v>
+      </c>
+      <c r="J10">
+        <v>3.9339314619605138E-2</v>
+      </c>
+      <c r="K10">
+        <v>4.3459187008200208E-2</v>
+      </c>
+      <c r="L10">
+        <v>4.0964696074900123E-2</v>
+      </c>
+      <c r="M10">
+        <v>4.5195927571712771E-2</v>
+      </c>
+      <c r="N10">
+        <v>6.1257479242017181E-2</v>
+      </c>
+      <c r="O10">
+        <v>6.0364468796990867E-2</v>
+      </c>
+      <c r="P10">
+        <v>6.252328238732191E-2</v>
+      </c>
+      <c r="Q10">
+        <v>7.2588575653336554E-2</v>
+      </c>
+      <c r="R10">
+        <v>7.0606692028063606E-2</v>
+      </c>
+      <c r="S10">
+        <v>7.7747889202745141E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11">
+        <v>0.1431501181995877</v>
+      </c>
+      <c r="C11">
+        <v>0.1267119253387865</v>
+      </c>
+      <c r="D11">
+        <v>0.1099763394444485</v>
+      </c>
+      <c r="E11">
+        <v>9.8083457300997032E-2</v>
+      </c>
+      <c r="F11">
+        <v>0.10054213429827839</v>
+      </c>
+      <c r="G11">
+        <v>0.1804269187246885</v>
+      </c>
+      <c r="H11">
+        <v>0.1563110051080617</v>
+      </c>
+      <c r="I11">
+        <v>0.13451315661417959</v>
+      </c>
+      <c r="J11">
+        <v>0.13739297388876001</v>
+      </c>
+      <c r="K11">
+        <v>0.1200863018213852</v>
+      </c>
+      <c r="L11">
+        <v>0.1251488878169221</v>
+      </c>
+      <c r="M11">
+        <v>0.1075962030299378</v>
+      </c>
+      <c r="N11">
+        <v>0.24727399940893799</v>
+      </c>
+      <c r="O11">
+        <v>0.24777742148800189</v>
+      </c>
+      <c r="P11">
+        <v>0.25130410152073163</v>
+      </c>
+      <c r="Q11">
+        <v>0.35828740225691241</v>
+      </c>
+      <c r="R11">
+        <v>0.43630558280501441</v>
+      </c>
+      <c r="S11">
+        <v>0.36936226800580291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12">
+        <v>3.6615730162034982E-2</v>
+      </c>
+      <c r="C12">
+        <v>3.3193412918249392E-2</v>
+      </c>
+      <c r="D12">
+        <v>3.2736380178983469E-2</v>
+      </c>
+      <c r="E12">
+        <v>3.0387933749704749E-2</v>
+      </c>
+      <c r="F12">
+        <v>3.3558868644769868E-2</v>
+      </c>
+      <c r="G12">
+        <v>3.2913557350441242E-2</v>
+      </c>
+      <c r="H12">
+        <v>4.993554413072919E-2</v>
+      </c>
+      <c r="I12">
+        <v>4.2289869960422041E-2</v>
+      </c>
+      <c r="J12">
+        <v>4.4756711427342569E-2</v>
+      </c>
+      <c r="K12">
+        <v>5.1509442010587908E-2</v>
+      </c>
+      <c r="L12">
+        <v>4.7974256232255208E-2</v>
+      </c>
+      <c r="M12">
+        <v>5.1283408509693831E-2</v>
+      </c>
+      <c r="N12">
+        <v>7.9734199897988384E-2</v>
+      </c>
+      <c r="O12">
+        <v>8.1249026272581862E-2</v>
+      </c>
+      <c r="P12">
+        <v>7.7871747016744708E-2</v>
+      </c>
+      <c r="Q12">
+        <v>9.2430110712261745E-2</v>
+      </c>
+      <c r="R12">
+        <v>9.9377429848346632E-2</v>
+      </c>
+      <c r="S12">
+        <v>0.1030537358957393</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13">
+        <v>5.049118025665233E-3</v>
+      </c>
+      <c r="C13">
+        <v>4.3944901355913793E-3</v>
+      </c>
+      <c r="D13">
+        <v>4.5450894398999381E-3</v>
+      </c>
+      <c r="E13">
+        <v>4.7052286589753496E-3</v>
+      </c>
+      <c r="F13">
+        <v>5.4667966791803971E-3</v>
+      </c>
+      <c r="G13">
+        <v>4.1119551599476997E-3</v>
+      </c>
+      <c r="H13">
+        <v>8.3317491845484766E-3</v>
+      </c>
+      <c r="I13">
+        <v>6.7054738851576772E-3</v>
+      </c>
+      <c r="J13">
+        <v>7.5611355824115331E-3</v>
+      </c>
+      <c r="K13">
+        <v>8.7188855980094241E-3</v>
+      </c>
+      <c r="L13">
+        <v>7.6074910393393591E-3</v>
+      </c>
+      <c r="M13">
+        <v>8.7644170562388088E-3</v>
+      </c>
+      <c r="N13">
+        <v>1.16590875381931E-2</v>
+      </c>
+      <c r="O13">
+        <v>1.08334924713361E-2</v>
+      </c>
+      <c r="P13">
+        <v>1.129449410935769E-2</v>
+      </c>
+      <c r="Q13">
+        <v>1.02387998648556E-2</v>
+      </c>
+      <c r="R13">
+        <v>1.0872558231931201E-2</v>
+      </c>
+      <c r="S13">
+        <v>1.2229813671697599E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14">
+        <v>2.5286537114969761E-2</v>
+      </c>
+      <c r="C14">
+        <v>2.4886146757268642E-2</v>
+      </c>
+      <c r="D14">
+        <v>2.8513908403849861E-2</v>
+      </c>
+      <c r="E14">
+        <v>1.8644122851725731E-2</v>
+      </c>
+      <c r="F14">
+        <v>2.153176724016596E-2</v>
+      </c>
+      <c r="G14">
+        <v>2.6855518822424249E-2</v>
+      </c>
+      <c r="H14">
+        <v>3.2083484293142353E-2</v>
+      </c>
+      <c r="I14">
+        <v>2.7138951568141521E-2</v>
+      </c>
+      <c r="J14">
+        <v>2.6609293023922492E-2</v>
+      </c>
+      <c r="K14">
+        <v>2.9503215972636158E-2</v>
+      </c>
+      <c r="L14">
+        <v>2.7966460713460029E-2</v>
+      </c>
+      <c r="M14">
+        <v>3.046264675507623E-2</v>
+      </c>
+      <c r="N14">
+        <v>4.1810810724656672E-2</v>
+      </c>
+      <c r="O14">
+        <v>4.2915103696636522E-2</v>
+      </c>
+      <c r="P14">
+        <v>3.743347230456872E-2</v>
+      </c>
+      <c r="Q14">
+        <v>4.4664037270640618E-2</v>
+      </c>
+      <c r="R14">
+        <v>4.753633934426417E-2</v>
+      </c>
+      <c r="S14">
+        <v>4.8805563210103382E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15">
+        <v>3.8128165992862839E-3</v>
+      </c>
+      <c r="C15">
+        <v>3.7057921893978618E-3</v>
+      </c>
+      <c r="D15">
+        <v>3.9230220577348429E-3</v>
+      </c>
+      <c r="E15">
+        <v>3.0976627929918E-3</v>
+      </c>
+      <c r="F15">
+        <v>3.3908361613397839E-3</v>
+      </c>
+      <c r="G15">
+        <v>7.0420503155666373E-3</v>
+      </c>
+      <c r="H15">
+        <v>7.1655063167931094E-3</v>
+      </c>
+      <c r="I15">
+        <v>6.2077070330024652E-3</v>
+      </c>
+      <c r="J15">
+        <v>5.6617796952316782E-3</v>
+      </c>
+      <c r="K15">
+        <v>5.9481380298195457E-3</v>
+      </c>
+      <c r="L15">
+        <v>5.491708360268059E-3</v>
+      </c>
+      <c r="M15">
+        <v>6.1061696923507816E-3</v>
+      </c>
+      <c r="N15">
+        <v>9.0287011247454953E-3</v>
+      </c>
+      <c r="O15">
+        <v>1.05713992162711E-2</v>
+      </c>
+      <c r="P15">
+        <v>8.2575185472999035E-3</v>
+      </c>
+      <c r="Q15">
+        <v>1.0806448585672869E-2</v>
+      </c>
+      <c r="R15">
+        <v>1.112388698845449E-2</v>
+      </c>
+      <c r="S15">
+        <v>1.160788558270744E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16">
+        <v>5.7126008418277334E-3</v>
+      </c>
+      <c r="C16">
+        <v>5.4216181312761683E-3</v>
+      </c>
+      <c r="D16">
+        <v>5.1244116324737684E-3</v>
+      </c>
+      <c r="E16">
+        <v>5.4356084538281094E-3</v>
+      </c>
+      <c r="F16">
+        <v>5.5524600557088563E-3</v>
+      </c>
+      <c r="G16">
+        <v>4.7328305389872797E-3</v>
+      </c>
+      <c r="H16">
+        <v>8.2753982151466277E-3</v>
+      </c>
+      <c r="I16">
+        <v>6.7748193093014417E-3</v>
+      </c>
+      <c r="J16">
+        <v>7.2446221971518643E-3</v>
+      </c>
+      <c r="K16">
+        <v>8.8613634551802621E-3</v>
+      </c>
+      <c r="L16">
+        <v>8.5438990320700799E-3</v>
+      </c>
+      <c r="M16">
+        <v>9.004211516962006E-3</v>
+      </c>
+      <c r="N16">
+        <v>1.338165463131712E-2</v>
+      </c>
+      <c r="O16">
+        <v>1.3063213303705429E-2</v>
+      </c>
+      <c r="P16">
+        <v>1.286004652863197E-2</v>
+      </c>
+      <c r="Q16">
+        <v>1.5409507754745949E-2</v>
+      </c>
+      <c r="R16">
+        <v>1.580657355591384E-2</v>
+      </c>
+      <c r="S16">
+        <v>1.7044021580984729E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17">
+        <v>8.435572441337278E-3</v>
+      </c>
+      <c r="C17">
+        <v>6.7516802998516612E-3</v>
+      </c>
+      <c r="D17">
+        <v>7.0789751161425898E-3</v>
+      </c>
+      <c r="E17">
+        <v>6.7901319717498304E-3</v>
+      </c>
+      <c r="F17">
+        <v>7.8677962090515328E-3</v>
+      </c>
+      <c r="G17">
+        <v>6.8181474318680059E-3</v>
+      </c>
+      <c r="H17">
+        <v>1.2230842406464619E-2</v>
+      </c>
+      <c r="I17">
+        <v>1.000420164235807E-2</v>
+      </c>
+      <c r="J17">
+        <v>9.0080850307955197E-3</v>
+      </c>
+      <c r="K17">
+        <v>1.2267547847315119E-2</v>
+      </c>
+      <c r="L17">
+        <v>1.0940783693845329E-2</v>
+      </c>
+      <c r="M17">
+        <v>1.2257392012258349E-2</v>
+      </c>
+      <c r="N17">
+        <v>1.2652382795486739E-2</v>
+      </c>
+      <c r="O17">
+        <v>1.631006091967923E-2</v>
+      </c>
+      <c r="P17">
+        <v>1.5546056194377249E-2</v>
+      </c>
+      <c r="Q17">
+        <v>1.6502045376877099E-2</v>
+      </c>
+      <c r="R17">
+        <v>1.6573241034040578E-2</v>
+      </c>
+      <c r="S17">
+        <v>1.830828423212106E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18">
+        <v>7.4433956726780203E-3</v>
+      </c>
+      <c r="C18">
+        <v>6.5466005329380796E-3</v>
+      </c>
+      <c r="D18">
+        <v>6.3133952725797672E-3</v>
+      </c>
+      <c r="E18">
+        <v>6.0379525647388174E-3</v>
+      </c>
+      <c r="F18">
+        <v>6.6288723114520378E-3</v>
+      </c>
+      <c r="G18">
+        <v>6.0302871120524173E-3</v>
+      </c>
+      <c r="H18">
+        <v>9.793894302960111E-3</v>
+      </c>
+      <c r="I18">
+        <v>8.080082426028673E-3</v>
+      </c>
+      <c r="J18">
+        <v>9.0674615850175489E-3</v>
+      </c>
+      <c r="K18">
+        <v>1.016044041851465E-2</v>
+      </c>
+      <c r="L18">
+        <v>9.722657632836848E-3</v>
+      </c>
+      <c r="M18">
+        <v>1.0083334869383309E-2</v>
+      </c>
+      <c r="N18">
+        <v>1.6553925234170739E-2</v>
+      </c>
+      <c r="O18">
+        <v>1.674171959952258E-2</v>
+      </c>
+      <c r="P18">
+        <v>1.6046772017487481E-2</v>
+      </c>
+      <c r="Q18">
+        <v>2.0214824377013951E-2</v>
+      </c>
+      <c r="R18">
+        <v>2.408388022697338E-2</v>
+      </c>
+      <c r="S18">
+        <v>2.4844649462093471E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19">
+        <v>5.0266697364469851E-3</v>
+      </c>
+      <c r="C19">
+        <v>4.5199917878337584E-3</v>
+      </c>
+      <c r="D19">
+        <v>4.6504161665670276E-3</v>
+      </c>
+      <c r="E19">
+        <v>4.6320070547016456E-3</v>
+      </c>
+      <c r="F19">
+        <v>4.8068055869547096E-3</v>
+      </c>
+      <c r="G19">
+        <v>5.0019735992843251E-3</v>
+      </c>
+      <c r="H19">
+        <v>7.2790323927404777E-3</v>
+      </c>
+      <c r="I19">
+        <v>6.3977708082863906E-3</v>
+      </c>
+      <c r="J19">
+        <v>6.3884019985686854E-3</v>
+      </c>
+      <c r="K19">
+        <v>7.5309720419573789E-3</v>
+      </c>
+      <c r="L19">
+        <v>7.2633575969650822E-3</v>
+      </c>
+      <c r="M19">
+        <v>7.6180700801189638E-3</v>
+      </c>
+      <c r="N19">
+        <v>1.146869679137489E-2</v>
+      </c>
+      <c r="O19">
+        <v>1.1710692227630321E-2</v>
+      </c>
+      <c r="P19">
+        <v>1.1456777561593729E-2</v>
+      </c>
+      <c r="Q19">
+        <v>1.444466999713029E-2</v>
+      </c>
+      <c r="R19">
+        <v>1.486261021990095E-2</v>
+      </c>
+      <c r="S19">
+        <v>1.505131658364077E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20">
+        <v>1.4390086759201859E-2</v>
+      </c>
+      <c r="C20">
+        <v>1.254529804881725E-2</v>
+      </c>
+      <c r="D20">
+        <v>1.395444048221669E-2</v>
+      </c>
+      <c r="E20">
+        <v>1.286564209019561E-2</v>
+      </c>
+      <c r="F20">
+        <v>1.394436266123397E-2</v>
+      </c>
+      <c r="G20">
+        <v>1.7764498217008949E-2</v>
+      </c>
+      <c r="H20">
+        <v>2.080394931722172E-2</v>
+      </c>
+      <c r="I20">
+        <v>1.792844159990109E-2</v>
+      </c>
+      <c r="J20">
+        <v>1.8323114768975621E-2</v>
+      </c>
+      <c r="K20">
+        <v>2.239033721602807E-2</v>
+      </c>
+      <c r="L20">
+        <v>2.2512526021556491E-2</v>
+      </c>
+      <c r="M20">
+        <v>2.0285045305072139E-2</v>
+      </c>
+      <c r="N20">
+        <v>4.3610990941221499E-2</v>
+      </c>
+      <c r="O20">
+        <v>4.2654967366544783E-2</v>
+      </c>
+      <c r="P20">
+        <v>4.084420843985978E-2</v>
+      </c>
+      <c r="Q20">
+        <v>5.264107071099635E-2</v>
+      </c>
+      <c r="R20">
+        <v>4.8932220069569557E-2</v>
+      </c>
+      <c r="S20">
+        <v>5.6011165358524052E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21">
+        <v>3.0730118733010781E-5</v>
+      </c>
+      <c r="C21">
+        <v>2.4653054888002051E-5</v>
+      </c>
+      <c r="D21">
+        <v>2.1877973559695921E-5</v>
+      </c>
+      <c r="E21">
+        <v>2.392284112993527E-5</v>
+      </c>
+      <c r="F21">
+        <v>2.3219242756340809E-5</v>
+      </c>
+      <c r="G21">
+        <v>2.5703931792249371E-5</v>
+      </c>
+      <c r="H21">
+        <v>4.5656952218429999E-5</v>
+      </c>
+      <c r="I21">
+        <v>3.9252596764147053E-5</v>
+      </c>
+      <c r="J21">
+        <v>3.9615008133186073E-5</v>
+      </c>
+      <c r="K21">
+        <v>4.5468822434618081E-5</v>
+      </c>
+      <c r="L21">
+        <v>4.7513476518550703E-5</v>
+      </c>
+      <c r="M21">
+        <v>4.4540728317792039E-5</v>
+      </c>
+      <c r="N21">
+        <v>7.3565377496052841E-5</v>
+      </c>
+      <c r="O21">
+        <v>7.3926334371425469E-5</v>
+      </c>
+      <c r="P21">
+        <v>7.7247490197707391E-5</v>
+      </c>
+      <c r="Q21">
+        <v>1.012162775132576E-4</v>
+      </c>
+      <c r="R21">
+        <v>1.060724866472324E-4</v>
+      </c>
+      <c r="S21">
+        <v>9.2747337167669298E-5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22">
+        <v>1.9339698159685219E-3</v>
+      </c>
+      <c r="C22">
+        <v>1.726444550205355E-3</v>
+      </c>
+      <c r="D22">
+        <v>1.7568120249692239E-3</v>
+      </c>
+      <c r="E22">
+        <v>1.6764278039707271E-3</v>
+      </c>
+      <c r="F22">
+        <v>1.7560698133790721E-3</v>
+      </c>
+      <c r="G22">
+        <v>1.731485853245787E-3</v>
+      </c>
+      <c r="H22">
+        <v>2.6091436810420439E-3</v>
+      </c>
+      <c r="I22">
+        <v>2.327622918269023E-3</v>
+      </c>
+      <c r="J22">
+        <v>2.335238073920165E-3</v>
+      </c>
+      <c r="K22">
+        <v>2.72976496231476E-3</v>
+      </c>
+      <c r="L22">
+        <v>2.6412044953540879E-3</v>
+      </c>
+      <c r="M22">
+        <v>2.8721232495236629E-3</v>
+      </c>
+      <c r="N22">
+        <v>4.1553336415746482E-3</v>
+      </c>
+      <c r="O22">
+        <v>4.3143406498813621E-3</v>
+      </c>
+      <c r="P22">
+        <v>4.0059010679025587E-3</v>
+      </c>
+      <c r="Q22">
+        <v>5.1058647860750218E-3</v>
+      </c>
+      <c r="R22">
+        <v>5.0518988041301973E-3</v>
+      </c>
+      <c r="S22">
+        <v>5.3795307988317442E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23">
+        <v>6.5448959278972846E-2</v>
+      </c>
+      <c r="C23">
+        <v>5.3442265260817419E-2</v>
+      </c>
+      <c r="D23">
+        <v>4.83543742059898E-2</v>
+      </c>
+      <c r="E23">
+        <v>4.2127228444845087E-2</v>
+      </c>
+      <c r="F23">
+        <v>4.0646359187736313E-2</v>
+      </c>
+      <c r="G23">
+        <v>0.10180170200708211</v>
+      </c>
+      <c r="H23">
+        <v>8.2920557083839233E-2</v>
+      </c>
+      <c r="I23">
+        <v>6.9282225196765551E-2</v>
+      </c>
+      <c r="J23">
+        <v>6.5038271894280422E-2</v>
+      </c>
+      <c r="K23">
+        <v>6.0038127597530022E-2</v>
+      </c>
+      <c r="L23">
+        <v>6.6023942518207687E-2</v>
+      </c>
+      <c r="M23">
+        <v>6.0671016906859242E-2</v>
+      </c>
+      <c r="N23">
+        <v>0.1245721472587214</v>
+      </c>
+      <c r="O23">
+        <v>0.12913450384629249</v>
+      </c>
+      <c r="P23">
+        <v>0.12105406111017861</v>
+      </c>
+      <c r="Q23">
+        <v>0.16884419504690329</v>
+      </c>
+      <c r="R23">
+        <v>0.21714137472509731</v>
+      </c>
+      <c r="S23">
+        <v>0.18222311692682569</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24">
+        <v>2.9607358867976742E-4</v>
+      </c>
+      <c r="C24">
+        <v>3.0561654625169929E-4</v>
+      </c>
+      <c r="D24">
+        <v>3.6508380902797508E-4</v>
+      </c>
+      <c r="E24">
+        <v>3.1939233816720089E-4</v>
+      </c>
+      <c r="F24">
+        <v>2.9496606536018501E-4</v>
+      </c>
+      <c r="G24">
+        <v>4.172351128721647E-4</v>
+      </c>
+      <c r="H24">
+        <v>5.6700299839898029E-4</v>
+      </c>
+      <c r="I24">
+        <v>4.7308726665161362E-4</v>
+      </c>
+      <c r="J24">
+        <v>4.583174489436459E-4</v>
+      </c>
+      <c r="K24">
+        <v>5.2910028644206778E-4</v>
+      </c>
+      <c r="L24">
+        <v>5.646461396192719E-4</v>
+      </c>
+      <c r="M24">
+        <v>5.2727542541564185E-4</v>
+      </c>
+      <c r="N24">
+        <v>1.001765132372118E-3</v>
+      </c>
+      <c r="O24">
+        <v>1.0024647092024049E-3</v>
+      </c>
+      <c r="P24">
+        <v>9.9963451557499839E-4</v>
+      </c>
+      <c r="Q24">
+        <v>1.130360403149471E-3</v>
+      </c>
+      <c r="R24">
+        <v>1.257474704243687E-3</v>
+      </c>
+      <c r="S24">
+        <v>1.255203598807323E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25">
+        <v>3.9816899629995907E-3</v>
+      </c>
+      <c r="C25">
+        <v>3.6356224548318569E-3</v>
+      </c>
+      <c r="D25">
+        <v>3.7783460578624441E-3</v>
+      </c>
+      <c r="E25">
+        <v>3.4197807779066921E-3</v>
+      </c>
+      <c r="F25">
+        <v>3.7020960249158248E-3</v>
+      </c>
+      <c r="G25">
+        <v>5.1333700300097082E-3</v>
+      </c>
+      <c r="H25">
+        <v>5.2936158949742776E-3</v>
+      </c>
+      <c r="I25">
+        <v>4.605492990943174E-3</v>
+      </c>
+      <c r="J25">
+        <v>4.8806051785642082E-3</v>
+      </c>
+      <c r="K25">
+        <v>5.7172188483922397E-3</v>
+      </c>
+      <c r="L25">
+        <v>5.5861696867243651E-3</v>
+      </c>
+      <c r="M25">
+        <v>5.6155933045174211E-3</v>
+      </c>
+      <c r="N25">
+        <v>9.8973391726068401E-3</v>
+      </c>
+      <c r="O25">
+        <v>9.7461453703039103E-3</v>
+      </c>
+      <c r="P25">
+        <v>8.9912490729539257E-3</v>
+      </c>
+      <c r="Q25">
+        <v>1.1086357019808479E-2</v>
+      </c>
+      <c r="R25">
+        <v>1.1368590012109469E-2</v>
+      </c>
+      <c r="S25">
+        <v>1.2630475395293311E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26">
+        <v>3.572379925020588E-3</v>
+      </c>
+      <c r="C26">
+        <v>3.2908621277222411E-3</v>
+      </c>
+      <c r="D26">
+        <v>3.175276113531484E-3</v>
+      </c>
+      <c r="E26">
+        <v>3.4803378476092901E-3</v>
+      </c>
+      <c r="F26">
+        <v>3.5086165088936191E-3</v>
+      </c>
+      <c r="G26">
+        <v>2.8706524056610339E-3</v>
+      </c>
+      <c r="H26">
+        <v>5.3339849819719551E-3</v>
+      </c>
+      <c r="I26">
+        <v>4.3430372448871732E-3</v>
+      </c>
+      <c r="J26">
+        <v>4.8693625923623687E-3</v>
+      </c>
+      <c r="K26">
+        <v>5.7311372346447566E-3</v>
+      </c>
+      <c r="L26">
+        <v>5.3369400104544664E-3</v>
+      </c>
+      <c r="M26">
+        <v>5.624705573409332E-3</v>
+      </c>
+      <c r="N26">
+        <v>8.1187247339197105E-3</v>
+      </c>
+      <c r="O26">
+        <v>7.8945290868691741E-3</v>
+      </c>
+      <c r="P26">
+        <v>8.1270069226796089E-3</v>
+      </c>
+      <c r="Q26">
+        <v>9.3818684131330814E-3</v>
+      </c>
+      <c r="R26">
+        <v>1.0061478725950651E-2</v>
+      </c>
+      <c r="S26">
+        <v>1.12525675673088E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27">
+        <v>2.3631906161993271E-2</v>
+      </c>
+      <c r="C27">
+        <v>2.0344676478983699E-2</v>
+      </c>
+      <c r="D27">
+        <v>2.206476918498531E-2</v>
+      </c>
+      <c r="E27">
+        <v>2.1333828317238328E-2</v>
+      </c>
+      <c r="F27">
+        <v>2.1547355316053458E-2</v>
+      </c>
+      <c r="G27">
+        <v>2.928489587149747E-2</v>
+      </c>
+      <c r="H27">
+        <v>3.493389407902206E-2</v>
+      </c>
+      <c r="I27">
+        <v>2.9728424072488512E-2</v>
+      </c>
+      <c r="J27">
+        <v>2.890109739348919E-2</v>
+      </c>
+      <c r="K27">
+        <v>3.9889124843425112E-2</v>
+      </c>
+      <c r="L27">
+        <v>3.8287914786261437E-2</v>
+      </c>
+      <c r="M27">
+        <v>3.8836271076579401E-2</v>
+      </c>
+      <c r="N27">
+        <v>8.9641759564404566E-2</v>
+      </c>
+      <c r="O27">
+        <v>9.5041292270298033E-2</v>
+      </c>
+      <c r="P27">
+        <v>8.8076530872782888E-2</v>
+      </c>
+      <c r="Q27">
+        <v>0.1329163296625813</v>
+      </c>
+      <c r="R27">
+        <v>0.14458939137103921</v>
+      </c>
+      <c r="S27">
+        <v>0.14071054934979699</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28">
+        <v>9.601396901303173E-4</v>
+      </c>
+      <c r="C28">
+        <v>8.9178782935141253E-4</v>
+      </c>
+      <c r="D28">
+        <v>1.0058872842320871E-3</v>
+      </c>
+      <c r="E28">
+        <v>8.748548515545569E-4</v>
+      </c>
+      <c r="F28">
+        <v>9.1190714432707264E-4</v>
+      </c>
+      <c r="G28">
+        <v>8.7598442389746596E-4</v>
+      </c>
+      <c r="H28">
+        <v>1.2378889513963739E-3</v>
+      </c>
+      <c r="I28">
+        <v>1.0612817118930079E-3</v>
+      </c>
+      <c r="J28">
+        <v>1.091706714391585E-3</v>
+      </c>
+      <c r="K28">
+        <v>1.22532468596344E-3</v>
+      </c>
+      <c r="L28">
+        <v>1.2546218742088399E-3</v>
+      </c>
+      <c r="M28">
+        <v>1.249500659015432E-3</v>
+      </c>
+      <c r="N28">
+        <v>2.0787878279435192E-3</v>
+      </c>
+      <c r="O28">
+        <v>1.9779476606494122E-3</v>
+      </c>
+      <c r="P28">
+        <v>1.918595285612787E-3</v>
+      </c>
+      <c r="Q28">
+        <v>2.265381791223839E-3</v>
+      </c>
+      <c r="R28">
+        <v>2.2922316201684141E-3</v>
+      </c>
+      <c r="S28">
+        <v>2.4430638039817818E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29">
+        <v>4.1784683712305287E-2</v>
+      </c>
+      <c r="C29">
+        <v>4.0299214823080361E-2</v>
+      </c>
+      <c r="D29">
+        <v>4.2841216895741489E-2</v>
+      </c>
+      <c r="E29">
+        <v>3.4342798181441189E-2</v>
+      </c>
+      <c r="F29">
+        <v>3.9724044053207987E-2</v>
+      </c>
+      <c r="G29">
+        <v>3.3181929130573259E-2</v>
+      </c>
+      <c r="H29">
+        <v>4.7288055869059362E-2</v>
+      </c>
+      <c r="I29">
+        <v>4.0191076532389167E-2</v>
+      </c>
+      <c r="J29">
+        <v>4.3745622721353287E-2</v>
+      </c>
+      <c r="K29">
+        <v>4.906111308521012E-2</v>
+      </c>
+      <c r="L29">
+        <v>4.6261344409665027E-2</v>
+      </c>
+      <c r="M29">
+        <v>4.9687026947242668E-2</v>
+      </c>
+      <c r="N29">
+        <v>7.3006939161326709E-2</v>
+      </c>
+      <c r="O29">
+        <v>7.4317379367692282E-2</v>
+      </c>
+      <c r="P29">
+        <v>7.129962323660162E-2</v>
+      </c>
+      <c r="Q29">
+        <v>8.3110221787514094E-2</v>
+      </c>
+      <c r="R29">
+        <v>8.415552651775414E-2</v>
+      </c>
+      <c r="S29">
+        <v>9.2938408757419766E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30">
+        <v>6.5362178116251039E-5</v>
+      </c>
+      <c r="C30">
+        <v>5.6965485663412109E-5</v>
+      </c>
+      <c r="D30">
+        <v>6.323983187398732E-5</v>
+      </c>
+      <c r="E30">
+        <v>5.1359376098513438E-5</v>
+      </c>
+      <c r="F30">
+        <v>6.0753290344262697E-5</v>
+      </c>
+      <c r="G30">
+        <v>6.2475882493593502E-5</v>
+      </c>
+      <c r="H30">
+        <v>6.9415106835508456E-5</v>
+      </c>
+      <c r="I30">
+        <v>6.3264550876010819E-5</v>
+      </c>
+      <c r="J30">
+        <v>5.6135165805079007E-5</v>
+      </c>
+      <c r="K30">
+        <v>6.3515509647171745E-5</v>
+      </c>
+      <c r="L30">
+        <v>7.1360175739494905E-5</v>
+      </c>
+      <c r="M30">
+        <v>6.729598909199773E-5</v>
+      </c>
+      <c r="N30">
+        <v>1.13364247847944E-4</v>
+      </c>
+      <c r="O30">
+        <v>1.179424405421455E-4</v>
+      </c>
+      <c r="P30">
+        <v>9.9698442624793757E-5</v>
+      </c>
+      <c r="Q30">
+        <v>1.534338339133495E-4</v>
+      </c>
+      <c r="R30">
+        <v>1.01795351198165E-4</v>
+      </c>
+      <c r="S30">
+        <v>1.039169637903396E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31">
+        <v>1.584164524315908E-5</v>
+      </c>
+      <c r="C31">
+        <v>1.5468241098484749E-5</v>
+      </c>
+      <c r="D31">
+        <v>1.7204597385666128E-5</v>
+      </c>
+      <c r="E31">
+        <v>1.3860746283147549E-5</v>
+      </c>
+      <c r="F31">
+        <v>1.319922812486902E-5</v>
+      </c>
+      <c r="G31">
+        <v>1.4205195757246851E-5</v>
+      </c>
+      <c r="H31">
+        <v>1.8317974979946601E-5</v>
+      </c>
+      <c r="I31">
+        <v>1.6563922587039809E-5</v>
+      </c>
+      <c r="J31">
+        <v>1.6861425176598979E-5</v>
+      </c>
+      <c r="K31">
+        <v>1.8889765552421611E-5</v>
+      </c>
+      <c r="L31">
+        <v>1.8536328121137222E-5</v>
+      </c>
+      <c r="M31">
+        <v>2.0602958359230299E-5</v>
+      </c>
+      <c r="N31">
+        <v>2.7694055918040041E-5</v>
+      </c>
+      <c r="O31">
+        <v>3.0207152562207839E-5</v>
+      </c>
+      <c r="P31">
+        <v>2.8122341726704259E-5</v>
+      </c>
+      <c r="Q31">
+        <v>3.3317264992463512E-5</v>
+      </c>
+      <c r="R31">
+        <v>2.959878246107162E-5</v>
+      </c>
+      <c r="S31">
+        <v>3.6754027816040528E-5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32">
+        <v>5.9673049592233338E-2</v>
+      </c>
+      <c r="C32">
+        <v>5.5161225887082888E-2</v>
+      </c>
+      <c r="D32">
+        <v>7.0660632467169124E-2</v>
+      </c>
+      <c r="E32">
+        <v>5.101571986852791E-2</v>
+      </c>
+      <c r="F32">
+        <v>5.4128444370192021E-2</v>
+      </c>
+      <c r="G32">
+        <v>7.5754948140673684E-2</v>
+      </c>
+      <c r="H32">
+        <v>7.8304833926385348E-2</v>
+      </c>
+      <c r="I32">
+        <v>6.7695073432117586E-2</v>
+      </c>
+      <c r="J32">
+        <v>6.8151476563625926E-2</v>
+      </c>
+      <c r="K32">
+        <v>8.2073550113305513E-2</v>
+      </c>
+      <c r="L32">
+        <v>8.3171560844040843E-2</v>
+      </c>
+      <c r="M32">
+        <v>7.779299447583217E-2</v>
+      </c>
+      <c r="N32">
+        <v>0.16866332025223499</v>
+      </c>
+      <c r="O32">
+        <v>0.16055821910462459</v>
+      </c>
+      <c r="P32">
+        <v>0.1637301235937188</v>
+      </c>
+      <c r="Q32">
+        <v>0.23700107639562151</v>
+      </c>
+      <c r="R32">
+        <v>0.24747411702710609</v>
+      </c>
+      <c r="S32">
+        <v>0.23522196452025179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33">
+        <v>3.9281415525559527E-2</v>
+      </c>
+      <c r="C33">
+        <v>3.4902588588395587E-2</v>
+      </c>
+      <c r="D33">
+        <v>4.3190325053759311E-2</v>
+      </c>
+      <c r="E33">
+        <v>3.6433905190692562E-2</v>
+      </c>
+      <c r="F33">
+        <v>3.7770871683273782E-2</v>
+      </c>
+      <c r="G33">
+        <v>4.5847393592958592E-2</v>
+      </c>
+      <c r="H33">
+        <v>5.0225457298055602E-2</v>
+      </c>
+      <c r="I33">
+        <v>4.6993652118224753E-2</v>
+      </c>
+      <c r="J33">
+        <v>4.3911105205912487E-2</v>
+      </c>
+      <c r="K33">
+        <v>4.0604551533334067E-2</v>
+      </c>
+      <c r="L33">
+        <v>4.222617339125119E-2</v>
+      </c>
+      <c r="M33">
+        <v>4.9896172355252677E-2</v>
+      </c>
+      <c r="N33">
+        <v>7.5444282756787426E-2</v>
+      </c>
+      <c r="O33">
+        <v>7.8764176381949269E-2</v>
+      </c>
+      <c r="P33">
+        <v>6.8539239692100545E-2</v>
+      </c>
+      <c r="Q33">
+        <v>8.3899406509916327E-2</v>
+      </c>
+      <c r="R33">
+        <v>8.4326169085986308E-2</v>
+      </c>
+      <c r="S33">
+        <v>8.6880009926717697E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34">
+        <v>2.1025811242308089E-3</v>
+      </c>
+      <c r="C34">
+        <v>1.836922371714553E-3</v>
+      </c>
+      <c r="D34">
+        <v>1.8629623217095721E-3</v>
+      </c>
+      <c r="E34">
+        <v>1.6542089778586689E-3</v>
+      </c>
+      <c r="F34">
+        <v>1.777972575455846E-3</v>
+      </c>
+      <c r="G34">
+        <v>2.0841778770934929E-3</v>
+      </c>
+      <c r="H34">
+        <v>2.9332872485250371E-3</v>
+      </c>
+      <c r="I34">
+        <v>2.488780392150594E-3</v>
+      </c>
+      <c r="J34">
+        <v>2.5214259278997959E-3</v>
+      </c>
+      <c r="K34">
+        <v>2.942290564688174E-3</v>
+      </c>
+      <c r="L34">
+        <v>2.8098418623285441E-3</v>
+      </c>
+      <c r="M34">
+        <v>2.826058497224958E-3</v>
+      </c>
+      <c r="N34">
+        <v>5.2176851850961291E-3</v>
+      </c>
+      <c r="O34">
+        <v>5.0316210949219583E-3</v>
+      </c>
+      <c r="P34">
+        <v>4.6334274688973626E-3</v>
+      </c>
+      <c r="Q34">
+        <v>6.726304927452114E-3</v>
+      </c>
+      <c r="R34">
+        <v>6.8650833666141784E-3</v>
+      </c>
+      <c r="S34">
+        <v>6.71213655136438E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35">
+        <v>1.2583644939613331E-3</v>
+      </c>
+      <c r="C35">
+        <v>1.212593833794354E-3</v>
+      </c>
+      <c r="D35">
+        <v>1.150248558398665E-3</v>
+      </c>
+      <c r="E35">
+        <v>1.053261662288855E-3</v>
+      </c>
+      <c r="F35">
+        <v>1.0824368296500481E-3</v>
+      </c>
+      <c r="G35">
+        <v>1.740256428863384E-3</v>
+      </c>
+      <c r="H35">
+        <v>2.0277882709426038E-3</v>
+      </c>
+      <c r="I35">
+        <v>1.660266100919626E-3</v>
+      </c>
+      <c r="J35">
+        <v>1.698886023457268E-3</v>
+      </c>
+      <c r="K35">
+        <v>1.895458316071565E-3</v>
+      </c>
+      <c r="L35">
+        <v>1.8303524167249459E-3</v>
+      </c>
+      <c r="M35">
+        <v>1.780555778188278E-3</v>
+      </c>
+      <c r="N35">
+        <v>3.6114743681895699E-3</v>
+      </c>
+      <c r="O35">
+        <v>3.6450041309488159E-3</v>
+      </c>
+      <c r="P35">
+        <v>3.193086741053776E-3</v>
+      </c>
+      <c r="Q35">
+        <v>3.850733355482474E-3</v>
+      </c>
+      <c r="R35">
+        <v>4.3428923804234064E-3</v>
+      </c>
+      <c r="S35">
+        <v>4.5197995447907131E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36">
+        <v>3.1407706007878069E-3</v>
+      </c>
+      <c r="C36">
+        <v>2.8197052114094902E-3</v>
+      </c>
+      <c r="D36">
+        <v>2.880650284996926E-3</v>
+      </c>
+      <c r="E36">
+        <v>2.697690983706071E-3</v>
+      </c>
+      <c r="F36">
+        <v>2.7407126462664299E-3</v>
+      </c>
+      <c r="G36">
+        <v>2.4189281812121411E-3</v>
+      </c>
+      <c r="H36">
+        <v>4.1103868442495858E-3</v>
+      </c>
+      <c r="I36">
+        <v>3.570742073707008E-3</v>
+      </c>
+      <c r="J36">
+        <v>3.6133815404497381E-3</v>
+      </c>
+      <c r="K36">
+        <v>4.0999414304114697E-3</v>
+      </c>
+      <c r="L36">
+        <v>3.8515703716466652E-3</v>
+      </c>
+      <c r="M36">
+        <v>4.0276169561370371E-3</v>
+      </c>
+      <c r="N36">
+        <v>6.8724969224053011E-3</v>
+      </c>
+      <c r="O36">
+        <v>7.3754294346404566E-3</v>
+      </c>
+      <c r="P36">
+        <v>7.3027510472318084E-3</v>
+      </c>
+      <c r="Q36">
+        <v>8.3510258218908156E-3</v>
+      </c>
+      <c r="R36">
+        <v>9.213512599590204E-3</v>
+      </c>
+      <c r="S36">
+        <v>9.510761419686169E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37">
+        <v>1.8742438631994419E-2</v>
+      </c>
+      <c r="C37">
+        <v>1.5865953704056301E-2</v>
+      </c>
+      <c r="D37">
+        <v>1.7482081766865259E-2</v>
+      </c>
+      <c r="E37">
+        <v>1.531651260788678E-2</v>
+      </c>
+      <c r="F37">
+        <v>1.621275922863314E-2</v>
+      </c>
+      <c r="G37">
+        <v>2.471438054811493E-2</v>
+      </c>
+      <c r="H37">
+        <v>2.7881432825503549E-2</v>
+      </c>
+      <c r="I37">
+        <v>2.458181700655486E-2</v>
+      </c>
+      <c r="J37">
+        <v>2.5084232730665131E-2</v>
+      </c>
+      <c r="K37">
+        <v>2.812580771048365E-2</v>
+      </c>
+      <c r="L37">
+        <v>2.7449934178464551E-2</v>
+      </c>
+      <c r="M37">
+        <v>2.720057921792603E-2</v>
+      </c>
+      <c r="N37">
+        <v>4.1703386457619937E-2</v>
+      </c>
+      <c r="O37">
+        <v>4.3479850045011398E-2</v>
+      </c>
+      <c r="P37">
+        <v>3.8404776537416453E-2</v>
+      </c>
+      <c r="Q37">
+        <v>4.6940305922004009E-2</v>
+      </c>
+      <c r="R37">
+        <v>4.3066271277535498E-2</v>
+      </c>
+      <c r="S37">
+        <v>4.9721049303481417E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38">
+        <v>1.1199798115865201E-3</v>
+      </c>
+      <c r="C38">
+        <v>1.0482018304517401E-3</v>
+      </c>
+      <c r="D38">
+        <v>1.1114130959858509E-3</v>
+      </c>
+      <c r="E38">
+        <v>9.1818904181362778E-4</v>
+      </c>
+      <c r="F38">
+        <v>9.3411747423177976E-4</v>
+      </c>
+      <c r="G38">
+        <v>8.915528447191773E-4</v>
+      </c>
+      <c r="H38">
+        <v>1.3111873958523629E-3</v>
+      </c>
+      <c r="I38">
+        <v>1.093542379639255E-3</v>
+      </c>
+      <c r="J38">
+        <v>1.116495912943925E-3</v>
+      </c>
+      <c r="K38">
+        <v>1.325207601121408E-3</v>
+      </c>
+      <c r="L38">
+        <v>1.2721446820349511E-3</v>
+      </c>
+      <c r="M38">
+        <v>1.3334827767604101E-3</v>
+      </c>
+      <c r="N38">
+        <v>2.016445597492914E-3</v>
+      </c>
+      <c r="O38">
+        <v>2.1410532140265712E-3</v>
+      </c>
+      <c r="P38">
+        <v>2.1496056878763021E-3</v>
+      </c>
+      <c r="Q38">
+        <v>2.5223718828097622E-3</v>
+      </c>
+      <c r="R38">
+        <v>2.549028021010989E-3</v>
+      </c>
+      <c r="S38">
+        <v>2.6147124316860271E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39">
+        <v>4.7182416699867598E-4</v>
+      </c>
+      <c r="C39">
+        <v>4.6095011071894932E-4</v>
+      </c>
+      <c r="D39">
+        <v>5.1116749479884478E-4</v>
+      </c>
+      <c r="E39">
+        <v>4.1536527263981508E-4</v>
+      </c>
+      <c r="F39">
+        <v>3.8862560769321598E-4</v>
+      </c>
+      <c r="G39">
+        <v>4.0013794837689731E-4</v>
+      </c>
+      <c r="H39">
+        <v>5.6989916514396969E-4</v>
+      </c>
+      <c r="I39">
+        <v>4.7295485803416958E-4</v>
+      </c>
+      <c r="J39">
+        <v>4.676195310665344E-4</v>
+      </c>
+      <c r="K39">
+        <v>5.7387532937831071E-4</v>
+      </c>
+      <c r="L39">
+        <v>5.4754293410500757E-4</v>
+      </c>
+      <c r="M39">
+        <v>5.8193667999292223E-4</v>
+      </c>
+      <c r="N39">
+        <v>8.3560767911098005E-4</v>
+      </c>
+      <c r="O39">
+        <v>9.0757429215064902E-4</v>
+      </c>
+      <c r="P39">
+        <v>8.8153894544291066E-4</v>
+      </c>
+      <c r="Q39">
+        <v>1.057564227427745E-3</v>
+      </c>
+      <c r="R39">
+        <v>9.7770328484481669E-4</v>
+      </c>
+      <c r="S39">
+        <v>1.1072043662357059E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40">
+        <v>3.6390575700491761E-4</v>
+      </c>
+      <c r="C40">
+        <v>2.8015908145394329E-4</v>
+      </c>
+      <c r="D40">
+        <v>3.0293471503505941E-4</v>
+      </c>
+      <c r="E40">
+        <v>2.6864083419161162E-4</v>
+      </c>
+      <c r="F40">
+        <v>2.9127006191111262E-4</v>
+      </c>
+      <c r="G40">
+        <v>3.2994082155844169E-4</v>
+      </c>
+      <c r="H40">
+        <v>4.538768502562573E-4</v>
+      </c>
+      <c r="I40">
+        <v>3.9799168441350541E-4</v>
+      </c>
+      <c r="J40">
+        <v>3.7970945053433639E-4</v>
+      </c>
+      <c r="K40">
+        <v>4.6142027813000669E-4</v>
+      </c>
+      <c r="L40">
+        <v>4.2900588575763059E-4</v>
+      </c>
+      <c r="M40">
+        <v>4.4448424155524172E-4</v>
+      </c>
+      <c r="N40">
+        <v>7.1941555042573304E-4</v>
+      </c>
+      <c r="O40">
+        <v>7.0486676875198358E-4</v>
+      </c>
+      <c r="P40">
+        <v>7.6141444618018793E-4</v>
+      </c>
+      <c r="Q40">
+        <v>9.6063431160237458E-4</v>
+      </c>
+      <c r="R40">
+        <v>9.3782546057167128E-4</v>
+      </c>
+      <c r="S40">
+        <v>9.6067943982541923E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41">
+        <v>7.1767250098676307E-4</v>
+      </c>
+      <c r="C41">
+        <v>5.8216372524495319E-4</v>
+      </c>
+      <c r="D41">
+        <v>6.0931548790788155E-4</v>
+      </c>
+      <c r="E41">
+        <v>5.7793596702596507E-4</v>
+      </c>
+      <c r="F41">
+        <v>5.915019507909177E-4</v>
+      </c>
+      <c r="G41">
+        <v>9.4765080486306462E-4</v>
+      </c>
+      <c r="H41">
+        <v>8.8244108987272838E-4</v>
+      </c>
+      <c r="I41">
+        <v>7.4734566575935287E-4</v>
+      </c>
+      <c r="J41">
+        <v>7.6781545518068896E-4</v>
+      </c>
+      <c r="K41">
+        <v>1.036935394352837E-3</v>
+      </c>
+      <c r="L41">
+        <v>8.7525407433901433E-4</v>
+      </c>
+      <c r="M41">
+        <v>8.6904637268575232E-4</v>
+      </c>
+      <c r="N41">
+        <v>1.4103653321055789E-3</v>
+      </c>
+      <c r="O41">
+        <v>1.490115268707816E-3</v>
+      </c>
+      <c r="P41">
+        <v>1.3297959049325841E-3</v>
+      </c>
+      <c r="Q41">
+        <v>1.7182405281997699E-3</v>
+      </c>
+      <c r="R41">
+        <v>1.635874904768214E-3</v>
+      </c>
+      <c r="S41">
+        <v>1.667701275330164E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42">
+        <v>6.4935723513182681E-4</v>
+      </c>
+      <c r="C42">
+        <v>4.9120973869564604E-4</v>
+      </c>
+      <c r="D42">
+        <v>5.201759213330667E-4</v>
+      </c>
+      <c r="E42">
+        <v>4.8946245953323619E-4</v>
+      </c>
+      <c r="F42">
+        <v>5.1377202142020666E-4</v>
+      </c>
+      <c r="G42">
+        <v>6.999381801553095E-4</v>
+      </c>
+      <c r="H42">
+        <v>7.344291052171246E-4</v>
+      </c>
+      <c r="I42">
+        <v>6.1024846155245042E-4</v>
+      </c>
+      <c r="J42">
+        <v>6.2980003026964619E-4</v>
+      </c>
+      <c r="K42">
+        <v>8.7918055171631372E-4</v>
+      </c>
+      <c r="L42">
+        <v>7.0818280347237079E-4</v>
+      </c>
+      <c r="M42">
+        <v>7.6394279764526612E-4</v>
+      </c>
+      <c r="N42">
+        <v>1.006194746172734E-3</v>
+      </c>
+      <c r="O42">
+        <v>1.073022021595317E-3</v>
+      </c>
+      <c r="P42">
+        <v>1.0391903365340701E-3</v>
+      </c>
+      <c r="Q42">
+        <v>1.2351773842469551E-3</v>
+      </c>
+      <c r="R42">
+        <v>1.210571453382412E-3</v>
+      </c>
+      <c r="S42">
+        <v>1.215611748998546E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43">
+        <v>1.430730308687968E-3</v>
+      </c>
+      <c r="C43">
+        <v>1.2598386100167479E-3</v>
+      </c>
+      <c r="D43">
+        <v>1.338310871670054E-3</v>
+      </c>
+      <c r="E43">
+        <v>1.2612263725924021E-3</v>
+      </c>
+      <c r="F43">
+        <v>1.3815439219651399E-3</v>
+      </c>
+      <c r="G43">
+        <v>1.7568123649820771E-3</v>
+      </c>
+      <c r="H43">
+        <v>2.1844953040473371E-3</v>
+      </c>
+      <c r="I43">
+        <v>1.766939356805425E-3</v>
+      </c>
+      <c r="J43">
+        <v>1.9634813929459952E-3</v>
+      </c>
+      <c r="K43">
+        <v>2.2377635936136151E-3</v>
+      </c>
+      <c r="L43">
+        <v>2.1391231136564008E-3</v>
+      </c>
+      <c r="M43">
+        <v>2.2271614548867191E-3</v>
+      </c>
+      <c r="N43">
+        <v>3.8790696522526332E-3</v>
+      </c>
+      <c r="O43">
+        <v>3.863080667579023E-3</v>
+      </c>
+      <c r="P43">
+        <v>3.9487390657586344E-3</v>
+      </c>
+      <c r="Q43">
+        <v>4.2772897227513007E-3</v>
+      </c>
+      <c r="R43">
+        <v>4.8082717165282918E-3</v>
+      </c>
+      <c r="S43">
+        <v>5.0718154557086769E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44">
+        <v>7.8630103875604127E-3</v>
+      </c>
+      <c r="C44">
+        <v>6.7948206464345604E-3</v>
+      </c>
+      <c r="D44">
+        <v>6.3540376845877128E-3</v>
+      </c>
+      <c r="E44">
+        <v>6.2483998030561207E-3</v>
+      </c>
+      <c r="F44">
+        <v>6.8179883880623527E-3</v>
+      </c>
+      <c r="G44">
+        <v>6.8906923908908192E-3</v>
+      </c>
+      <c r="H44">
+        <v>1.0350799399101321E-2</v>
+      </c>
+      <c r="I44">
+        <v>8.9750199690271648E-3</v>
+      </c>
+      <c r="J44">
+        <v>9.2873849099614474E-3</v>
+      </c>
+      <c r="K44">
+        <v>1.0836070019408801E-2</v>
+      </c>
+      <c r="L44">
+        <v>1.0193491918969649E-2</v>
+      </c>
+      <c r="M44">
+        <v>1.049926516432096E-2</v>
+      </c>
+      <c r="N44">
+        <v>1.8996108779040791E-2</v>
+      </c>
+      <c r="O44">
+        <v>2.0000633247695122E-2</v>
+      </c>
+      <c r="P44">
+        <v>1.9333862389126742E-2</v>
+      </c>
+      <c r="Q44">
+        <v>2.244486932264942E-2</v>
+      </c>
+      <c r="R44">
+        <v>2.5000265094045869E-2</v>
+      </c>
+      <c r="S44">
+        <v>2.6039269284904111E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45">
+        <v>1.767306540755206E-4</v>
+      </c>
+      <c r="C45">
+        <v>1.5108262859206301E-4</v>
+      </c>
+      <c r="D45">
+        <v>1.5682577460802429E-4</v>
+      </c>
+      <c r="E45">
+        <v>1.410147061403566E-4</v>
+      </c>
+      <c r="F45">
+        <v>1.3918170602130131E-4</v>
+      </c>
+      <c r="G45">
+        <v>1.5002203350318819E-4</v>
+      </c>
+      <c r="H45">
+        <v>2.3395877604584099E-4</v>
+      </c>
+      <c r="I45">
+        <v>1.984333018344373E-4</v>
+      </c>
+      <c r="J45">
+        <v>2.2083584487625981E-4</v>
+      </c>
+      <c r="K45">
+        <v>2.4705910559725159E-4</v>
+      </c>
+      <c r="L45">
+        <v>2.1394074445419889E-4</v>
+      </c>
+      <c r="M45">
+        <v>2.2268159833646541E-4</v>
+      </c>
+      <c r="N45">
+        <v>4.1335502587073249E-4</v>
+      </c>
+      <c r="O45">
+        <v>4.0182428521585241E-4</v>
+      </c>
+      <c r="P45">
+        <v>4.057646388478497E-4</v>
+      </c>
+      <c r="Q45">
+        <v>4.8163417211123422E-4</v>
+      </c>
+      <c r="R45">
+        <v>5.6984061139775442E-4</v>
+      </c>
+      <c r="S45">
+        <v>5.5594829812635087E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46">
+        <v>8.2755882571622586E-5</v>
+      </c>
+      <c r="C46">
+        <v>8.0777181939488854E-5</v>
+      </c>
+      <c r="D46">
+        <v>9.1181361618371132E-5</v>
+      </c>
+      <c r="E46">
+        <v>7.6567820065647673E-5</v>
+      </c>
+      <c r="F46">
+        <v>7.4144697062222925E-5</v>
+      </c>
+      <c r="G46">
+        <v>9.4992808687027866E-5</v>
+      </c>
+      <c r="H46">
+        <v>1.2135773336617691E-4</v>
+      </c>
+      <c r="I46">
+        <v>1.068885442734451E-4</v>
+      </c>
+      <c r="J46">
+        <v>1.097264641272879E-4</v>
+      </c>
+      <c r="K46">
+        <v>1.169523120820766E-4</v>
+      </c>
+      <c r="L46">
+        <v>1.137642823858088E-4</v>
+      </c>
+      <c r="M46">
+        <v>1.257164349663787E-4</v>
+      </c>
+      <c r="N46">
+        <v>1.8017833145710199E-4</v>
+      </c>
+      <c r="O46">
+        <v>1.5847457389556939E-4</v>
+      </c>
+      <c r="P46">
+        <v>1.412767395292943E-4</v>
+      </c>
+      <c r="Q46">
+        <v>1.5445123215233271E-4</v>
+      </c>
+      <c r="R46">
+        <v>1.6135177576074349E-4</v>
+      </c>
+      <c r="S46">
+        <v>2.072032203985273E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47">
+        <v>4.8462995946080002E-4</v>
+      </c>
+      <c r="C47">
+        <v>5.6228949686204131E-4</v>
+      </c>
+      <c r="D47">
+        <v>4.3488587865835293E-4</v>
+      </c>
+      <c r="E47">
+        <v>4.0082328022747672E-4</v>
+      </c>
+      <c r="F47">
+        <v>4.1284781978506659E-4</v>
+      </c>
+      <c r="G47">
+        <v>4.5085540710861858E-4</v>
+      </c>
+      <c r="H47">
+        <v>5.99712825669642E-4</v>
+      </c>
+      <c r="I47">
+        <v>4.9718224036668997E-4</v>
+      </c>
+      <c r="J47">
+        <v>4.2380000299435569E-4</v>
+      </c>
+      <c r="K47">
+        <v>5.6928909549666836E-4</v>
+      </c>
+      <c r="L47">
+        <v>5.5009313887433952E-4</v>
+      </c>
+      <c r="M47">
+        <v>5.9101725563555005E-4</v>
+      </c>
+      <c r="N47">
+        <v>8.0088647972143933E-4</v>
+      </c>
+      <c r="O47">
+        <v>8.0840344084570658E-4</v>
+      </c>
+      <c r="P47">
+        <v>8.0247238577983086E-4</v>
+      </c>
+      <c r="Q47">
+        <v>8.7487766512548922E-4</v>
+      </c>
+      <c r="R47">
+        <v>9.8281411499864932E-4</v>
+      </c>
+      <c r="S47">
+        <v>9.9475240833718699E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48">
+        <v>5.1969526537232044E-3</v>
+      </c>
+      <c r="C48">
+        <v>4.3178103068700754E-3</v>
+      </c>
+      <c r="D48">
+        <v>4.0874204863403686E-3</v>
+      </c>
+      <c r="E48">
+        <v>3.1902529932834631E-3</v>
+      </c>
+      <c r="F48">
+        <v>3.8740301052419129E-3</v>
+      </c>
+      <c r="G48">
+        <v>4.060990896287202E-3</v>
+      </c>
+      <c r="H48">
+        <v>5.4172380238092076E-3</v>
+      </c>
+      <c r="I48">
+        <v>4.527036907750805E-3</v>
+      </c>
+      <c r="J48">
+        <v>5.2703172675125781E-3</v>
+      </c>
+      <c r="K48">
+        <v>5.4994791807240232E-3</v>
+      </c>
+      <c r="L48">
+        <v>5.520992334913803E-3</v>
+      </c>
+      <c r="M48">
+        <v>5.5625902736904584E-3</v>
+      </c>
+      <c r="N48">
+        <v>9.6828784219461211E-3</v>
+      </c>
+      <c r="O48">
+        <v>1.027431101665551E-2</v>
+      </c>
+      <c r="P48">
+        <v>8.8252098876770713E-3</v>
+      </c>
+      <c r="Q48">
+        <v>1.162301002694829E-2</v>
+      </c>
+      <c r="R48">
+        <v>1.45546920430163E-2</v>
+      </c>
+      <c r="S48">
+        <v>1.4290294534299711E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49">
+        <v>3.1090584147638119E-3</v>
+      </c>
+      <c r="C49">
+        <v>2.8031572268415101E-3</v>
+      </c>
+      <c r="D49">
+        <v>2.6104543943644902E-3</v>
+      </c>
+      <c r="E49">
+        <v>2.8548369967367E-3</v>
+      </c>
+      <c r="F49">
+        <v>2.7385328988694889E-3</v>
+      </c>
+      <c r="G49">
+        <v>3.779994689824148E-3</v>
+      </c>
+      <c r="H49">
+        <v>5.6477273764580444E-3</v>
+      </c>
+      <c r="I49">
+        <v>4.6962606960169748E-3</v>
+      </c>
+      <c r="J49">
+        <v>4.5084629751851804E-3</v>
+      </c>
+      <c r="K49">
+        <v>5.6811897681848704E-3</v>
+      </c>
+      <c r="L49">
+        <v>5.0980652438319179E-3</v>
+      </c>
+      <c r="M49">
+        <v>5.7699291126990038E-3</v>
+      </c>
+      <c r="N49">
+        <v>9.192019145626406E-3</v>
+      </c>
+      <c r="O49">
+        <v>1.1189107699514939E-2</v>
+      </c>
+      <c r="P49">
+        <v>9.3644177175258251E-3</v>
+      </c>
+      <c r="Q49">
+        <v>1.112603541101898E-2</v>
+      </c>
+      <c r="R49">
+        <v>1.0527156177249541E-2</v>
+      </c>
+      <c r="S49">
+        <v>1.194250628113043E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50">
+        <v>3.0128059723786389E-4</v>
+      </c>
+      <c r="C50">
+        <v>2.5550881213140119E-4</v>
+      </c>
+      <c r="D50">
+        <v>2.7437450325904839E-4</v>
+      </c>
+      <c r="E50">
+        <v>2.347281228901373E-4</v>
+      </c>
+      <c r="F50">
+        <v>2.4890355186552862E-4</v>
+      </c>
+      <c r="G50">
+        <v>3.0905776676118472E-4</v>
+      </c>
+      <c r="H50">
+        <v>3.8446109782471708E-4</v>
+      </c>
+      <c r="I50">
+        <v>3.4519938756275042E-4</v>
+      </c>
+      <c r="J50">
+        <v>3.3359327323885339E-4</v>
+      </c>
+      <c r="K50">
+        <v>4.266752941893008E-4</v>
+      </c>
+      <c r="L50">
+        <v>4.2404896920190759E-4</v>
+      </c>
+      <c r="M50">
+        <v>4.0893351183909411E-4</v>
+      </c>
+      <c r="N50">
+        <v>7.9618646590210167E-4</v>
+      </c>
+      <c r="O50">
+        <v>8.0951121069815159E-4</v>
+      </c>
+      <c r="P50">
+        <v>8.0807183116656911E-4</v>
+      </c>
+      <c r="Q50">
+        <v>9.9938408605938648E-4</v>
+      </c>
+      <c r="R50">
+        <v>1.0799282890860569E-3</v>
+      </c>
+      <c r="S50">
+        <v>1.0778053986923049E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51">
+        <v>2.9634350179405199E-2</v>
+      </c>
+      <c r="C51">
+        <v>2.600229489078499E-2</v>
+      </c>
+      <c r="D51">
+        <v>2.588499389940942E-2</v>
+      </c>
+      <c r="E51">
+        <v>2.5689076140034569E-2</v>
+      </c>
+      <c r="F51">
+        <v>2.5648739143889401E-2</v>
+      </c>
+      <c r="G51">
+        <v>3.4278051677180198E-2</v>
+      </c>
+      <c r="H51">
+        <v>4.4173153818362683E-2</v>
+      </c>
+      <c r="I51">
+        <v>3.7550907354700187E-2</v>
+      </c>
+      <c r="J51">
+        <v>3.7011109463904082E-2</v>
+      </c>
+      <c r="K51">
+        <v>5.2445555685911797E-2</v>
+      </c>
+      <c r="L51">
+        <v>5.0251887992168169E-2</v>
+      </c>
+      <c r="M51">
+        <v>4.7020212213486547E-2</v>
+      </c>
+      <c r="N51">
+        <v>0.1234318284247891</v>
+      </c>
+      <c r="O51">
+        <v>0.12344016514138539</v>
+      </c>
+      <c r="P51">
+        <v>0.122887891811818</v>
+      </c>
+      <c r="Q51">
+        <v>0.18932450259815359</v>
+      </c>
+      <c r="R51">
+        <v>0.2041678729973968</v>
+      </c>
+      <c r="S51">
+        <v>0.1951052889672891</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52">
+        <v>7.2834734508432717E-4</v>
+      </c>
+      <c r="C52">
+        <v>6.6129437813740289E-4</v>
+      </c>
+      <c r="D52">
+        <v>6.6568653500800618E-4</v>
+      </c>
+      <c r="E52">
+        <v>6.5671428055525413E-4</v>
+      </c>
+      <c r="F52">
+        <v>6.9680504616984225E-4</v>
+      </c>
+      <c r="G52">
+        <v>8.6065099314287232E-4</v>
+      </c>
+      <c r="H52">
+        <v>1.149160480263709E-3</v>
+      </c>
+      <c r="I52">
+        <v>9.883780819457857E-4</v>
+      </c>
+      <c r="J52">
+        <v>1.001755666038917E-3</v>
+      </c>
+      <c r="K52">
+        <v>1.157303261830061E-3</v>
+      </c>
+      <c r="L52">
+        <v>1.129441734019896E-3</v>
+      </c>
+      <c r="M52">
+        <v>1.2110402125334321E-3</v>
+      </c>
+      <c r="N52">
+        <v>1.8741821645289619E-3</v>
+      </c>
+      <c r="O52">
+        <v>1.8794198886239971E-3</v>
+      </c>
+      <c r="P52">
+        <v>1.6530894483973351E-3</v>
+      </c>
+      <c r="Q52">
+        <v>1.950279422570903E-3</v>
+      </c>
+      <c r="R52">
+        <v>1.9495106175573429E-3</v>
+      </c>
+      <c r="S52">
+        <v>2.2234371779933041E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53">
+        <v>1.3034555432303159E-4</v>
+      </c>
+      <c r="C53">
+        <v>1.2574308063965551E-4</v>
+      </c>
+      <c r="D53">
+        <v>1.2453913773975391E-4</v>
+      </c>
+      <c r="E53">
+        <v>1.041910531878411E-4</v>
+      </c>
+      <c r="F53">
+        <v>1.091240028472694E-4</v>
+      </c>
+      <c r="G53">
+        <v>1.113836012675937E-4</v>
+      </c>
+      <c r="H53">
+        <v>1.4230725594194821E-4</v>
+      </c>
+      <c r="I53">
+        <v>1.157727660977516E-4</v>
+      </c>
+      <c r="J53">
+        <v>1.2256554829897151E-4</v>
+      </c>
+      <c r="K53">
+        <v>1.390022797621929E-4</v>
+      </c>
+      <c r="L53">
+        <v>1.3867563201716771E-4</v>
+      </c>
+      <c r="M53">
+        <v>1.4591365990878461E-4</v>
+      </c>
+      <c r="N53">
+        <v>2.0147204412167109E-4</v>
+      </c>
+      <c r="O53">
+        <v>2.1720325049637721E-4</v>
+      </c>
+      <c r="P53">
+        <v>1.9910317713342271E-4</v>
+      </c>
+      <c r="Q53">
+        <v>2.2125942165229491E-4</v>
+      </c>
+      <c r="R53">
+        <v>2.2979910873422349E-4</v>
+      </c>
+      <c r="S53">
+        <v>2.4619859813210671E-4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54">
+        <v>5.8572904728547419E-2</v>
+      </c>
+      <c r="C54">
+        <v>5.3240049025310779E-2</v>
+      </c>
+      <c r="D54">
+        <v>5.4314227906562387E-2</v>
+      </c>
+      <c r="E54">
+        <v>3.979857311804829E-2</v>
+      </c>
+      <c r="F54">
+        <v>4.5758875130469577E-2</v>
+      </c>
+      <c r="G54">
+        <v>5.338083677483068E-2</v>
+      </c>
+      <c r="H54">
+        <v>5.9360392044956363E-2</v>
+      </c>
+      <c r="I54">
+        <v>4.8038644275973923E-2</v>
+      </c>
+      <c r="J54">
+        <v>4.8426441278487921E-2</v>
+      </c>
+      <c r="K54">
+        <v>5.1882561599134687E-2</v>
+      </c>
+      <c r="L54">
+        <v>5.3062512311843182E-2</v>
+      </c>
+      <c r="M54">
+        <v>5.516057509214907E-2</v>
+      </c>
+      <c r="N54">
+        <v>0.1260878639115785</v>
+      </c>
+      <c r="O54">
+        <v>0.1163750790886096</v>
+      </c>
+      <c r="P54">
+        <v>0.11590659522057779</v>
+      </c>
+      <c r="Q54">
+        <v>0.1726253688074165</v>
+      </c>
+      <c r="R54">
+        <v>0.18571529211419369</v>
+      </c>
+      <c r="S54">
+        <v>0.1847289625567464</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55">
+        <v>9.2884825321610572E-3</v>
+      </c>
+      <c r="C55">
+        <v>8.1250548190742716E-3</v>
+      </c>
+      <c r="D55">
+        <v>8.6063802810145279E-3</v>
+      </c>
+      <c r="E55">
+        <v>8.3723087878476068E-3</v>
+      </c>
+      <c r="F55">
+        <v>8.8890105981806796E-3</v>
+      </c>
+      <c r="G55">
+        <v>1.228029484102317E-2</v>
+      </c>
+      <c r="H55">
+        <v>1.3637383851340879E-2</v>
+      </c>
+      <c r="I55">
+        <v>1.179019247795603E-2</v>
+      </c>
+      <c r="J55">
+        <v>1.193460362511037E-2</v>
+      </c>
+      <c r="K55">
+        <v>1.245426450093501E-2</v>
+      </c>
+      <c r="L55">
+        <v>1.246312469582261E-2</v>
+      </c>
+      <c r="M55">
+        <v>1.231265745520274E-2</v>
+      </c>
+      <c r="N55">
+        <v>1.9995583218504712E-2</v>
+      </c>
+      <c r="O55">
+        <v>1.95788241244408E-2</v>
+      </c>
+      <c r="P55">
+        <v>1.8799229719396789E-2</v>
+      </c>
+      <c r="Q55">
+        <v>2.4037075485859261E-2</v>
+      </c>
+      <c r="R55">
+        <v>2.5088094102810491E-2</v>
+      </c>
+      <c r="S55">
+        <v>2.5074128367365431E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56">
+        <v>2.4991808429704141E-2</v>
+      </c>
+      <c r="C56">
+        <v>2.2243922628609889E-2</v>
+      </c>
+      <c r="D56">
+        <v>2.3071353863392301E-2</v>
+      </c>
+      <c r="E56">
+        <v>2.6120513226405798E-2</v>
+      </c>
+      <c r="F56">
+        <v>2.7326699989203951E-2</v>
+      </c>
+      <c r="G56">
+        <v>2.7882369798495839E-2</v>
+      </c>
+      <c r="H56">
+        <v>4.449728198721576E-2</v>
+      </c>
+      <c r="I56">
+        <v>3.7676808388305248E-2</v>
+      </c>
+      <c r="J56">
+        <v>4.0244007164825249E-2</v>
+      </c>
+      <c r="K56">
+        <v>4.8651576400129043E-2</v>
+      </c>
+      <c r="L56">
+        <v>4.6579510518485252E-2</v>
+      </c>
+      <c r="M56">
+        <v>4.9783148664481081E-2</v>
+      </c>
+      <c r="N56">
+        <v>7.8210568386407012E-2</v>
+      </c>
+      <c r="O56">
+        <v>7.5412595633913893E-2</v>
+      </c>
+      <c r="P56">
+        <v>6.7289491685300781E-2</v>
+      </c>
+      <c r="Q56">
+        <v>7.821861225092322E-2</v>
+      </c>
+      <c r="R56">
+        <v>8.5912136833612845E-2</v>
+      </c>
+      <c r="S56">
+        <v>9.4083804794127757E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57">
+        <v>5.7707796517620746E-4</v>
+      </c>
+      <c r="C57">
+        <v>5.0819945160221068E-4</v>
+      </c>
+      <c r="D57">
+        <v>6.3061696913379597E-4</v>
+      </c>
+      <c r="E57">
+        <v>5.0075451614375085E-4</v>
+      </c>
+      <c r="F57">
+        <v>5.3498988072719087E-4</v>
+      </c>
+      <c r="G57">
+        <v>5.3051493275968378E-4</v>
+      </c>
+      <c r="H57">
+        <v>6.9706572951142118E-4</v>
+      </c>
+      <c r="I57">
+        <v>6.6844146246997636E-4</v>
+      </c>
+      <c r="J57">
+        <v>6.2766599441813141E-4</v>
+      </c>
+      <c r="K57">
+        <v>7.0521139000494291E-4</v>
+      </c>
+      <c r="L57">
+        <v>7.4398835532091517E-4</v>
+      </c>
+      <c r="M57">
+        <v>7.2545735830400191E-4</v>
+      </c>
+      <c r="N57">
+        <v>1.1910584250900821E-3</v>
+      </c>
+      <c r="O57">
+        <v>1.096560622799685E-3</v>
+      </c>
+      <c r="P57">
+        <v>1.2325402076005501E-3</v>
+      </c>
+      <c r="Q57">
+        <v>1.354393455237624E-3</v>
+      </c>
+      <c r="R57">
+        <v>1.5458747684309461E-3</v>
+      </c>
+      <c r="S57">
+        <v>1.6173954522136129E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58">
+        <v>9.4493444001396583E-4</v>
+      </c>
+      <c r="C58">
+        <v>8.7575579713060174E-4</v>
+      </c>
+      <c r="D58">
+        <v>8.9176370309611524E-4</v>
+      </c>
+      <c r="E58">
+        <v>8.3080970299110257E-4</v>
+      </c>
+      <c r="F58">
+        <v>9.1072202422412204E-4</v>
+      </c>
+      <c r="G58">
+        <v>7.0025334145244148E-4</v>
+      </c>
+      <c r="H58">
+        <v>1.203245227154371E-3</v>
+      </c>
+      <c r="I58">
+        <v>1.013346273851311E-3</v>
+      </c>
+      <c r="J58">
+        <v>1.04786785590268E-3</v>
+      </c>
+      <c r="K58">
+        <v>1.240191814229775E-3</v>
+      </c>
+      <c r="L58">
+        <v>1.1755238308420791E-3</v>
+      </c>
+      <c r="M58">
+        <v>1.289292632663305E-3</v>
+      </c>
+      <c r="N58">
+        <v>1.8661204631396199E-3</v>
+      </c>
+      <c r="O58">
+        <v>1.8249650799390829E-3</v>
+      </c>
+      <c r="P58">
+        <v>1.9148092300542781E-3</v>
+      </c>
+      <c r="Q58">
+        <v>2.0287722081192791E-3</v>
+      </c>
+      <c r="R58">
+        <v>2.296044901218367E-3</v>
+      </c>
+      <c r="S58">
+        <v>2.2764354201817139E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59">
+        <v>1.1801212614847231E-3</v>
+      </c>
+      <c r="C59">
+        <v>8.4423680348145135E-4</v>
+      </c>
+      <c r="D59">
+        <v>1.075644154997986E-3</v>
+      </c>
+      <c r="E59">
+        <v>7.9957860604178523E-4</v>
+      </c>
+      <c r="F59">
+        <v>1.0976256300074089E-3</v>
+      </c>
+      <c r="G59">
+        <v>1.5060468335925761E-3</v>
+      </c>
+      <c r="H59">
+        <v>1.57532677408374E-3</v>
+      </c>
+      <c r="I59">
+        <v>1.5116031963143171E-3</v>
+      </c>
+      <c r="J59">
+        <v>1.3710252151338609E-3</v>
+      </c>
+      <c r="K59">
+        <v>1.6269693341490271E-3</v>
+      </c>
+      <c r="L59">
+        <v>1.6342805701449791E-3</v>
+      </c>
+      <c r="M59">
+        <v>1.578499231619382E-3</v>
+      </c>
+      <c r="N59">
+        <v>2.4677855464692771E-3</v>
+      </c>
+      <c r="O59">
+        <v>2.6362098875120569E-3</v>
+      </c>
+      <c r="P59">
+        <v>2.4405767005679741E-3</v>
+      </c>
+      <c r="Q59">
+        <v>3.241969737141661E-3</v>
+      </c>
+      <c r="R59">
+        <v>2.6413973873942462E-3</v>
+      </c>
+      <c r="S59">
+        <v>3.035403841779181E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60">
+        <v>1.55169832957358E-2</v>
+      </c>
+      <c r="C60">
+        <v>1.35323781106296E-2</v>
+      </c>
+      <c r="D60">
+        <v>1.553110070443481E-2</v>
+      </c>
+      <c r="E60">
+        <v>1.739372341958241E-2</v>
+      </c>
+      <c r="F60">
+        <v>1.6721553242357499E-2</v>
+      </c>
+      <c r="G60">
+        <v>2.169225338579572E-2</v>
+      </c>
+      <c r="H60">
+        <v>2.8947184079150499E-2</v>
+      </c>
+      <c r="I60">
+        <v>2.555353229455078E-2</v>
+      </c>
+      <c r="J60">
+        <v>2.5457782218779149E-2</v>
+      </c>
+      <c r="K60">
+        <v>2.8353239710428909E-2</v>
+      </c>
+      <c r="L60">
+        <v>2.738291211541331E-2</v>
+      </c>
+      <c r="M60">
+        <v>3.0195921170955729E-2</v>
+      </c>
+      <c r="N60">
+        <v>4.1584862487304648E-2</v>
+      </c>
+      <c r="O60">
+        <v>4.0543026907140373E-2</v>
+      </c>
+      <c r="P60">
+        <v>4.2875974460481851E-2</v>
+      </c>
+      <c r="Q60">
+        <v>5.1201310459050769E-2</v>
+      </c>
+      <c r="R60">
+        <v>5.2163721759982823E-2</v>
+      </c>
+      <c r="S60">
+        <v>5.4464482159938959E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61">
+        <v>6.0611971063976905E-4</v>
+      </c>
+      <c r="C61">
+        <v>6.515413288554953E-4</v>
+      </c>
+      <c r="D61">
+        <v>4.9782985750381229E-4</v>
+      </c>
+      <c r="E61">
+        <v>4.904757399292254E-4</v>
+      </c>
+      <c r="F61">
+        <v>4.9704551422311623E-4</v>
+      </c>
+      <c r="G61">
+        <v>6.3170344130103711E-4</v>
+      </c>
+      <c r="H61">
+        <v>7.9882325539146833E-4</v>
+      </c>
+      <c r="I61">
+        <v>6.7650666513797313E-4</v>
+      </c>
+      <c r="J61">
+        <v>5.9480155449079925E-4</v>
+      </c>
+      <c r="K61">
+        <v>7.3422098227454127E-4</v>
+      </c>
+      <c r="L61">
+        <v>7.0981367184209184E-4</v>
+      </c>
+      <c r="M61">
+        <v>7.3182631256667641E-4</v>
+      </c>
+      <c r="N61">
+        <v>1.0772141132579379E-3</v>
+      </c>
+      <c r="O61">
+        <v>1.1849292715275231E-3</v>
+      </c>
+      <c r="P61">
+        <v>1.184529465228846E-3</v>
+      </c>
+      <c r="Q61">
+        <v>1.486466088547341E-3</v>
+      </c>
+      <c r="R61">
+        <v>1.608054909930285E-3</v>
+      </c>
+      <c r="S61">
+        <v>1.4849575327044249E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62">
+        <v>2.1944170513650459E-4</v>
+      </c>
+      <c r="C62">
+        <v>1.329227050572132E-5</v>
+      </c>
+      <c r="D62">
+        <v>2.1977222169739541E-4</v>
+      </c>
+      <c r="E62">
+        <v>5.2219711500206641E-6</v>
+      </c>
+      <c r="F62">
+        <v>2.2583858441529869E-4</v>
+      </c>
+      <c r="G62">
+        <v>1.7598806228676759E-4</v>
+      </c>
+      <c r="H62">
+        <v>6.8269653967690181E-6</v>
+      </c>
+      <c r="I62">
+        <v>2.4279746501232419E-4</v>
+      </c>
+      <c r="J62">
+        <v>1.7244417682309081E-5</v>
+      </c>
+      <c r="K62">
+        <v>2.1510073625286431E-4</v>
+      </c>
+      <c r="L62">
+        <v>2.0119221390586291E-4</v>
+      </c>
+      <c r="M62">
+        <v>2.8185834481320529E-4</v>
+      </c>
+      <c r="N62">
+        <v>1.8530456119239878E-5</v>
+      </c>
+      <c r="O62">
+        <v>2.212541883989433E-4</v>
+      </c>
+      <c r="P62">
+        <v>7.1052985304173813E-6</v>
+      </c>
+      <c r="Q62">
+        <v>2.8102747280070651E-4</v>
+      </c>
+      <c r="R62">
+        <v>8.2521880310023334E-6</v>
+      </c>
+      <c r="S62">
+        <v>4.1989674742003592E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63">
+        <v>2.6108034194159122E-2</v>
+      </c>
+      <c r="C63">
+        <v>2.5809798206189741E-2</v>
+      </c>
+      <c r="D63">
+        <v>2.577269670636673E-2</v>
+      </c>
+      <c r="E63">
+        <v>1.7201240940908521E-2</v>
+      </c>
+      <c r="F63">
+        <v>2.137908684559435E-2</v>
+      </c>
+      <c r="G63">
+        <v>2.450173205316751E-2</v>
+      </c>
+      <c r="H63">
+        <v>2.467820436928057E-2</v>
+      </c>
+      <c r="I63">
+        <v>2.21043419180963E-2</v>
+      </c>
+      <c r="J63">
+        <v>2.200739363839194E-2</v>
+      </c>
+      <c r="K63">
+        <v>1.951875879589951E-2</v>
+      </c>
+      <c r="L63">
+        <v>2.0247980308641542E-2</v>
+      </c>
+      <c r="M63">
+        <v>2.2895156887605739E-2</v>
+      </c>
+      <c r="N63">
+        <v>2.4983662141162849E-2</v>
+      </c>
+      <c r="O63">
+        <v>2.4871440769260459E-2</v>
+      </c>
+      <c r="P63">
+        <v>2.1470238661894001E-2</v>
+      </c>
+      <c r="Q63">
+        <v>2.849296838107104E-2</v>
+      </c>
+      <c r="R63">
+        <v>2.8534462577476691E-2</v>
+      </c>
+      <c r="S63">
+        <v>2.5961458987112131E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64">
+        <v>6.7203132088341662E-5</v>
+      </c>
+      <c r="C64">
+        <v>5.9136455321203312E-5</v>
+      </c>
+      <c r="D64">
+        <v>7.3614419860574588E-5</v>
+      </c>
+      <c r="E64">
+        <v>6.7607151541604018E-5</v>
+      </c>
+      <c r="F64">
+        <v>7.3953042776780587E-5</v>
+      </c>
+      <c r="G64">
+        <v>8.4775395607023378E-5</v>
+      </c>
+      <c r="H64">
+        <v>1.083870505709137E-4</v>
+      </c>
+      <c r="I64">
+        <v>9.4755185043177311E-5</v>
+      </c>
+      <c r="J64">
+        <v>9.330011942754319E-5</v>
+      </c>
+      <c r="K64">
+        <v>1.179808655334539E-4</v>
+      </c>
+      <c r="L64">
+        <v>1.163481268553569E-4</v>
+      </c>
+      <c r="M64">
+        <v>1.202272452395045E-4</v>
+      </c>
+      <c r="N64">
+        <v>2.5004413139013677E-4</v>
+      </c>
+      <c r="O64">
+        <v>2.5415455567386758E-4</v>
+      </c>
+      <c r="P64">
+        <v>2.1332799488574041E-4</v>
+      </c>
+      <c r="Q64">
+        <v>2.787787574952359E-4</v>
+      </c>
+      <c r="R64">
+        <v>3.2741371509558927E-4</v>
+      </c>
+      <c r="S64">
+        <v>3.1606175764276029E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65">
+        <v>4.5385002377759012E-2</v>
+      </c>
+      <c r="C65">
+        <v>4.3389610153184932E-2</v>
+      </c>
+      <c r="D65">
+        <v>4.3306865200237903E-2</v>
+      </c>
+      <c r="E65">
+        <v>2.3553116262926391E-2</v>
+      </c>
+      <c r="F65">
+        <v>2.5415275794820971E-2</v>
+      </c>
+      <c r="G65">
+        <v>4.0918835045379021E-2</v>
+      </c>
+      <c r="H65">
+        <v>3.864147426126141E-2</v>
+      </c>
+      <c r="I65">
+        <v>3.3566725955240372E-2</v>
+      </c>
+      <c r="J65">
+        <v>3.4854245935760031E-2</v>
+      </c>
+      <c r="K65">
+        <v>4.0656877600203048E-2</v>
+      </c>
+      <c r="L65">
+        <v>3.8899454695712793E-2</v>
+      </c>
+      <c r="M65">
+        <v>3.9690318092233522E-2</v>
+      </c>
+      <c r="N65">
+        <v>7.1152008473109651E-2</v>
+      </c>
+      <c r="O65">
+        <v>7.2011560990568046E-2</v>
+      </c>
+      <c r="P65">
+        <v>6.1528666863547861E-2</v>
+      </c>
+      <c r="Q65">
+        <v>8.6675594127511871E-2</v>
+      </c>
+      <c r="R65">
+        <v>8.0398412386930102E-2</v>
+      </c>
+      <c r="S65">
+        <v>8.7609422898526204E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66">
+        <v>1.7507380481664541E-3</v>
+      </c>
+      <c r="C66">
+        <v>1.5376075696494039E-3</v>
+      </c>
+      <c r="D66">
+        <v>1.5810621756649681E-3</v>
+      </c>
+      <c r="E66">
+        <v>1.4301826196817329E-3</v>
+      </c>
+      <c r="F66">
+        <v>1.574889555060237E-3</v>
+      </c>
+      <c r="G66">
+        <v>2.098101915306448E-3</v>
+      </c>
+      <c r="H66">
+        <v>2.552324109944716E-3</v>
+      </c>
+      <c r="I66">
+        <v>2.1672872622783999E-3</v>
+      </c>
+      <c r="J66">
+        <v>2.1690689744174761E-3</v>
+      </c>
+      <c r="K66">
+        <v>2.346664005244008E-3</v>
+      </c>
+      <c r="L66">
+        <v>2.374642599413692E-3</v>
+      </c>
+      <c r="M66">
+        <v>2.3670722646465512E-3</v>
+      </c>
+      <c r="N66">
+        <v>4.1342996673953414E-3</v>
+      </c>
+      <c r="O66">
+        <v>3.9559700735441522E-3</v>
+      </c>
+      <c r="P66">
+        <v>4.062988145373158E-3</v>
+      </c>
+      <c r="Q66">
+        <v>4.8588575921543302E-3</v>
+      </c>
+      <c r="R66">
+        <v>4.7459257988651136E-3</v>
+      </c>
+      <c r="S66">
+        <v>4.6314583254743972E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67">
+        <v>9.3865918613219492E-5</v>
+      </c>
+      <c r="C67">
+        <v>8.6270376945797505E-5</v>
+      </c>
+      <c r="D67">
+        <v>8.3519781091093671E-5</v>
+      </c>
+      <c r="E67">
+        <v>7.4232478855921824E-5</v>
+      </c>
+      <c r="F67">
+        <v>7.9814211931711091E-5</v>
+      </c>
+      <c r="G67">
+        <v>7.2766163654898296E-5</v>
+      </c>
+      <c r="H67">
+        <v>9.1406838597558445E-5</v>
+      </c>
+      <c r="I67">
+        <v>7.6873159962819826E-5</v>
+      </c>
+      <c r="J67">
+        <v>8.5042740416851247E-5</v>
+      </c>
+      <c r="K67">
+        <v>8.9060583593061955E-5</v>
+      </c>
+      <c r="L67">
+        <v>8.1836698001765037E-5</v>
+      </c>
+      <c r="M67">
+        <v>9.2992896470505827E-5</v>
+      </c>
+      <c r="N67">
+        <v>1.170291077615545E-4</v>
+      </c>
+      <c r="O67">
+        <v>1.2548516184964249E-4</v>
+      </c>
+      <c r="P67">
+        <v>1.121694308682754E-4</v>
+      </c>
+      <c r="Q67">
+        <v>1.3389267337155509E-4</v>
+      </c>
+      <c r="R67">
+        <v>1.2835088950972329E-4</v>
+      </c>
+      <c r="S67">
+        <v>1.3112503454960439E-4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>85</v>
+      </c>
+      <c r="B68">
+        <v>2.8962248061748148E-4</v>
+      </c>
+      <c r="C68">
+        <v>2.7081954411402429E-4</v>
+      </c>
+      <c r="D68">
+        <v>2.6417791681213222E-4</v>
+      </c>
+      <c r="E68">
+        <v>2.5259926692929063E-4</v>
+      </c>
+      <c r="F68">
+        <v>2.5035702820524889E-4</v>
+      </c>
+      <c r="G68">
+        <v>2.914410848531309E-4</v>
+      </c>
+      <c r="H68">
+        <v>4.1646412625729592E-4</v>
+      </c>
+      <c r="I68">
+        <v>3.3113260451805528E-4</v>
+      </c>
+      <c r="J68">
+        <v>3.7349193668925989E-4</v>
+      </c>
+      <c r="K68">
+        <v>4.0380444979079918E-4</v>
+      </c>
+      <c r="L68">
+        <v>4.0112824763389923E-4</v>
+      </c>
+      <c r="M68">
+        <v>4.1226432053980788E-4</v>
+      </c>
+      <c r="N68">
+        <v>6.6997750716386948E-4</v>
+      </c>
+      <c r="O68">
+        <v>6.6172442415516881E-4</v>
+      </c>
+      <c r="P68">
+        <v>6.0287188094852685E-4</v>
+      </c>
+      <c r="Q68">
+        <v>7.3497403732652989E-4</v>
+      </c>
+      <c r="R68">
+        <v>7.2811998760617745E-4</v>
+      </c>
+      <c r="S68">
+        <v>7.9178760593874738E-4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>86</v>
+      </c>
+      <c r="B69">
+        <v>4.6332819572115998E-4</v>
+      </c>
+      <c r="C69">
+        <v>3.8783460356192552E-4</v>
+      </c>
+      <c r="D69">
+        <v>3.6911622047056868E-4</v>
+      </c>
+      <c r="E69">
+        <v>3.8589663617785648E-4</v>
+      </c>
+      <c r="F69">
+        <v>3.9146055590534118E-4</v>
+      </c>
+      <c r="G69">
+        <v>5.7184857057434603E-4</v>
+      </c>
+      <c r="H69">
+        <v>7.1699781036210818E-4</v>
+      </c>
+      <c r="I69">
+        <v>6.173166494182951E-4</v>
+      </c>
+      <c r="J69">
+        <v>5.8952331960059751E-4</v>
+      </c>
+      <c r="K69">
+        <v>6.7859799830715902E-4</v>
+      </c>
+      <c r="L69">
+        <v>6.7652525133533197E-4</v>
+      </c>
+      <c r="M69">
+        <v>6.7893348683338778E-4</v>
+      </c>
+      <c r="N69">
+        <v>1.19829761041941E-3</v>
+      </c>
+      <c r="O69">
+        <v>1.3202691568389179E-3</v>
+      </c>
+      <c r="P69">
+        <v>1.22225495870886E-3</v>
+      </c>
+      <c r="Q69">
+        <v>1.741458081799373E-3</v>
+      </c>
+      <c r="R69">
+        <v>1.938964157824213E-3</v>
+      </c>
+      <c r="S69">
+        <v>1.688690018318423E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70">
+        <v>4.8070147233054771E-4</v>
+      </c>
+      <c r="C70">
+        <v>4.9002959417704243E-4</v>
+      </c>
+      <c r="D70">
+        <v>4.7875621343000571E-4</v>
+      </c>
+      <c r="E70">
+        <v>2.8178156296279128E-4</v>
+      </c>
+      <c r="F70">
+        <v>3.2732227213544911E-4</v>
+      </c>
+      <c r="G70">
+        <v>1.9579747522259551E-4</v>
+      </c>
+      <c r="H70">
+        <v>2.9490410003243001E-4</v>
+      </c>
+      <c r="I70">
+        <v>2.2291466840091331E-4</v>
+      </c>
+      <c r="J70">
+        <v>2.6958854216880981E-4</v>
+      </c>
+      <c r="K70">
+        <v>2.7248732047784898E-4</v>
+      </c>
+      <c r="L70">
+        <v>2.386874083180412E-4</v>
+      </c>
+      <c r="M70">
+        <v>2.8350359763391751E-4</v>
+      </c>
+      <c r="N70">
+        <v>2.7828584274680439E-4</v>
+      </c>
+      <c r="O70">
+        <v>2.4939372856838243E-4</v>
+      </c>
+      <c r="P70">
+        <v>2.5875632209515107E-4</v>
+      </c>
+      <c r="Q70">
+        <v>2.2215089848510249E-4</v>
+      </c>
+      <c r="R70">
+        <v>2.7629519555147678E-4</v>
+      </c>
+      <c r="S70">
+        <v>3.0963180316446261E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>88</v>
+      </c>
+      <c r="B71">
+        <v>2.9625330768823489E-2</v>
+      </c>
+      <c r="C71">
+        <v>2.8215880429381699E-2</v>
+      </c>
+      <c r="D71">
+        <v>3.3413237358895287E-2</v>
+      </c>
+      <c r="E71">
+        <v>2.583514108216511E-2</v>
+      </c>
+      <c r="F71">
+        <v>2.7162034812638011E-2</v>
+      </c>
+      <c r="G71">
+        <v>3.1117016738587341E-2</v>
+      </c>
+      <c r="H71">
+        <v>4.0983889792453709E-2</v>
+      </c>
+      <c r="I71">
+        <v>3.548762131640576E-2</v>
+      </c>
+      <c r="J71">
+        <v>3.5188856714781107E-2</v>
+      </c>
+      <c r="K71">
+        <v>3.8326142077478607E-2</v>
+      </c>
+      <c r="L71">
+        <v>3.6317674263504247E-2</v>
+      </c>
+      <c r="M71">
+        <v>4.1079347166555681E-2</v>
+      </c>
+      <c r="N71">
+        <v>5.0987961332092338E-2</v>
+      </c>
+      <c r="O71">
+        <v>4.9503866916413182E-2</v>
+      </c>
+      <c r="P71">
+        <v>5.0309689732823487E-2</v>
+      </c>
+      <c r="Q71">
+        <v>5.9417867762002648E-2</v>
+      </c>
+      <c r="R71">
+        <v>6.1704271678242877E-2</v>
+      </c>
+      <c r="S71">
+        <v>6.3453940636552228E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>89</v>
+      </c>
+      <c r="B72">
+        <v>5.9115883410060296E-3</v>
+      </c>
+      <c r="C72">
+        <v>5.4728751324707413E-3</v>
+      </c>
+      <c r="D72">
+        <v>5.5117641385662858E-3</v>
+      </c>
+      <c r="E72">
+        <v>5.0850267909183667E-3</v>
+      </c>
+      <c r="F72">
+        <v>4.9987694764851353E-3</v>
+      </c>
+      <c r="G72">
+        <v>5.5082544991327748E-3</v>
+      </c>
+      <c r="H72">
+        <v>8.0016418333028819E-3</v>
+      </c>
+      <c r="I72">
+        <v>6.5808105488166114E-3</v>
+      </c>
+      <c r="J72">
+        <v>7.1343389085886926E-3</v>
+      </c>
+      <c r="K72">
+        <v>8.6945225671189834E-3</v>
+      </c>
+      <c r="L72">
+        <v>7.8936797417141491E-3</v>
+      </c>
+      <c r="M72">
+        <v>7.8316752282819469E-3</v>
+      </c>
+      <c r="N72">
+        <v>1.693006799742993E-2</v>
+      </c>
+      <c r="O72">
+        <v>1.7697268108481511E-2</v>
+      </c>
+      <c r="P72">
+        <v>1.4718560792153459E-2</v>
+      </c>
+      <c r="Q72">
+        <v>2.098053184294878E-2</v>
+      </c>
+      <c r="R72">
+        <v>1.786028529217654E-2</v>
+      </c>
+      <c r="S72">
+        <v>2.28535014861386E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B73">
+        <v>4.229517190642719E-3</v>
+      </c>
+      <c r="C73">
+        <v>3.9489266649271916E-3</v>
+      </c>
+      <c r="D73">
+        <v>3.863875210915713E-3</v>
+      </c>
+      <c r="E73">
+        <v>3.4725953784951399E-3</v>
+      </c>
+      <c r="F73">
+        <v>3.6790935832060759E-3</v>
+      </c>
+      <c r="G73">
+        <v>4.6415698778313778E-3</v>
+      </c>
+      <c r="H73">
+        <v>5.6318654924810184E-3</v>
+      </c>
+      <c r="I73">
+        <v>4.5792184040454676E-3</v>
+      </c>
+      <c r="J73">
+        <v>4.9982694258997786E-3</v>
+      </c>
+      <c r="K73">
+        <v>5.7182465013887861E-3</v>
+      </c>
+      <c r="L73">
+        <v>5.5616179569513572E-3</v>
+      </c>
+      <c r="M73">
+        <v>5.6000361129927038E-3</v>
+      </c>
+      <c r="N73">
+        <v>8.1973630187266444E-3</v>
+      </c>
+      <c r="O73">
+        <v>8.8044741242745816E-3</v>
+      </c>
+      <c r="P73">
+        <v>7.8830306484106681E-3</v>
+      </c>
+      <c r="Q73">
+        <v>9.5477627313022145E-3</v>
+      </c>
+      <c r="R73">
+        <v>9.4719619143424864E-3</v>
+      </c>
+      <c r="S73">
+        <v>9.6745814386925665E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74">
+        <v>3.858859539032478E-3</v>
+      </c>
+      <c r="C74">
+        <v>3.5625138835151471E-3</v>
+      </c>
+      <c r="D74">
+        <v>3.7634205443742908E-3</v>
+      </c>
+      <c r="E74">
+        <v>3.1223411697679769E-3</v>
+      </c>
+      <c r="F74">
+        <v>3.257769407621171E-3</v>
+      </c>
+      <c r="G74">
+        <v>5.3722017799392842E-3</v>
+      </c>
+      <c r="H74">
+        <v>5.3257131629443188E-3</v>
+      </c>
+      <c r="I74">
+        <v>4.5938608999729217E-3</v>
+      </c>
+      <c r="J74">
+        <v>4.332786695136967E-3</v>
+      </c>
+      <c r="K74">
+        <v>5.0559642788742696E-3</v>
+      </c>
+      <c r="L74">
+        <v>5.1126689789655283E-3</v>
+      </c>
+      <c r="M74">
+        <v>5.3414841487392506E-3</v>
+      </c>
+      <c r="N74">
+        <v>9.2080511925708413E-3</v>
+      </c>
+      <c r="O74">
+        <v>9.1702674494142222E-3</v>
+      </c>
+      <c r="P74">
+        <v>8.048153330755899E-3</v>
+      </c>
+      <c r="Q74">
+        <v>1.0712961488589769E-2</v>
+      </c>
+      <c r="R74">
+        <v>1.0113985230607719E-2</v>
+      </c>
+      <c r="S74">
+        <v>1.128563330941134E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75">
+        <v>1.148246810327173E-5</v>
+      </c>
+      <c r="C75">
+        <v>9.9881974606902785E-6</v>
+      </c>
+      <c r="D75">
+        <v>1.130601136845054E-5</v>
+      </c>
+      <c r="E75">
+        <v>9.9254823353811649E-6</v>
+      </c>
+      <c r="F75">
+        <v>1.029138615817551E-5</v>
+      </c>
+      <c r="G75">
+        <v>1.390998153609936E-5</v>
+      </c>
+      <c r="H75">
+        <v>1.4250640306020341E-5</v>
+      </c>
+      <c r="I75">
+        <v>1.1646793075177019E-5</v>
+      </c>
+      <c r="J75">
+        <v>1.185876698370858E-5</v>
+      </c>
+      <c r="K75">
+        <v>1.6089088540472461E-5</v>
+      </c>
+      <c r="L75">
+        <v>1.276131308713029E-5</v>
+      </c>
+      <c r="M75">
+        <v>1.4373592611302671E-5</v>
+      </c>
+      <c r="N75">
+        <v>1.680213938880364E-5</v>
+      </c>
+      <c r="O75">
+        <v>1.6928364041612279E-5</v>
+      </c>
+      <c r="P75">
+        <v>2.0010189678224411E-5</v>
+      </c>
+      <c r="Q75">
+        <v>1.7840076639379822E-5</v>
+      </c>
+      <c r="R75">
+        <v>2.312921799998797E-5</v>
+      </c>
+      <c r="S75">
+        <v>2.570642314378748E-5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76">
+        <v>2.8557482116111049E-3</v>
+      </c>
+      <c r="C76">
+        <v>2.5171848971318879E-3</v>
+      </c>
+      <c r="D76">
+        <v>2.3987828108606112E-3</v>
+      </c>
+      <c r="E76">
+        <v>2.3310379726741571E-3</v>
+      </c>
+      <c r="F76">
+        <v>2.3384509021023561E-3</v>
+      </c>
+      <c r="G76">
+        <v>2.0886088023573958E-3</v>
+      </c>
+      <c r="H76">
+        <v>3.6984901117166858E-3</v>
+      </c>
+      <c r="I76">
+        <v>3.1348670852894261E-3</v>
+      </c>
+      <c r="J76">
+        <v>3.2295481066935468E-3</v>
+      </c>
+      <c r="K76">
+        <v>3.641234053210944E-3</v>
+      </c>
+      <c r="L76">
+        <v>3.361145959178447E-3</v>
+      </c>
+      <c r="M76">
+        <v>3.5574146012131141E-3</v>
+      </c>
+      <c r="N76">
+        <v>5.8575016151071364E-3</v>
+      </c>
+      <c r="O76">
+        <v>6.3565556756171697E-3</v>
+      </c>
+      <c r="P76">
+        <v>6.1163348001484841E-3</v>
+      </c>
+      <c r="Q76">
+        <v>7.2161084068886701E-3</v>
+      </c>
+      <c r="R76">
+        <v>7.819969584078804E-3</v>
+      </c>
+      <c r="S76">
+        <v>8.1002644096940767E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77">
+        <v>7.6581631877021563E-5</v>
+      </c>
+      <c r="C77">
+        <v>7.6195841721188258E-5</v>
+      </c>
+      <c r="D77">
+        <v>6.9050810991637965E-5</v>
+      </c>
+      <c r="E77">
+        <v>7.9758221480572656E-5</v>
+      </c>
+      <c r="F77">
+        <v>8.5073425573411489E-5</v>
+      </c>
+      <c r="G77">
+        <v>7.1489726487167956E-5</v>
+      </c>
+      <c r="H77">
+        <v>1.4193185380610839E-4</v>
+      </c>
+      <c r="I77">
+        <v>1.22616533372272E-4</v>
+      </c>
+      <c r="J77">
+        <v>1.247333527118988E-4</v>
+      </c>
+      <c r="K77">
+        <v>1.526781063375047E-4</v>
+      </c>
+      <c r="L77">
+        <v>1.5876055965552801E-4</v>
+      </c>
+      <c r="M77">
+        <v>1.4611185142480979E-4</v>
+      </c>
+      <c r="N77">
+        <v>2.7114302511031612E-4</v>
+      </c>
+      <c r="O77">
+        <v>2.8527594932213602E-4</v>
+      </c>
+      <c r="P77">
+        <v>3.2515089661901261E-4</v>
+      </c>
+      <c r="Q77">
+        <v>3.6980020297853561E-4</v>
+      </c>
+      <c r="R77">
+        <v>4.2308120382416123E-4</v>
+      </c>
+      <c r="S77">
+        <v>3.6447494348777591E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B78">
+        <v>9.3570859958915717E-3</v>
+      </c>
+      <c r="C78">
+        <v>9.4966454068929774E-3</v>
+      </c>
+      <c r="D78">
+        <v>8.9138646309628502E-3</v>
+      </c>
+      <c r="E78">
+        <v>8.7703974113607225E-3</v>
+      </c>
+      <c r="F78">
+        <v>1.1250654435804371E-2</v>
+      </c>
+      <c r="G78">
+        <v>6.6952837999655892E-3</v>
+      </c>
+      <c r="H78">
+        <v>8.945065471986478E-3</v>
+      </c>
+      <c r="I78">
+        <v>8.1375275157715005E-3</v>
+      </c>
+      <c r="J78">
+        <v>1.0031110284412731E-2</v>
+      </c>
+      <c r="K78">
+        <v>1.057113352576566E-2</v>
+      </c>
+      <c r="L78">
+        <v>9.9711256908431353E-3</v>
+      </c>
+      <c r="M78">
+        <v>1.140890492811091E-2</v>
+      </c>
+      <c r="N78">
+        <v>1.2014342281334439E-2</v>
+      </c>
+      <c r="O78">
+        <v>1.2374531094674261E-2</v>
+      </c>
+      <c r="P78">
+        <v>1.2645704367438299E-2</v>
+      </c>
+      <c r="Q78">
+        <v>1.204081478853229E-2</v>
+      </c>
+      <c r="R78">
+        <v>8.6320832000524386E-3</v>
+      </c>
+      <c r="S78">
+        <v>1.1791854604107499E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B79">
+        <v>1.4277396973762959E-4</v>
+      </c>
+      <c r="C79">
+        <v>1.3923545916613871E-4</v>
+      </c>
+      <c r="D79">
+        <v>1.3573388864413229E-4</v>
+      </c>
+      <c r="E79">
+        <v>1.2040160989150359E-4</v>
+      </c>
+      <c r="F79">
+        <v>1.199724246250904E-4</v>
+      </c>
+      <c r="G79">
+        <v>8.9778851003809745E-5</v>
+      </c>
+      <c r="H79">
+        <v>1.6754991123949271E-4</v>
+      </c>
+      <c r="I79">
+        <v>1.46816694857466E-4</v>
+      </c>
+      <c r="J79">
+        <v>1.5572588603715939E-4</v>
+      </c>
+      <c r="K79">
+        <v>1.7480096758174641E-4</v>
+      </c>
+      <c r="L79">
+        <v>1.647637236993874E-4</v>
+      </c>
+      <c r="M79">
+        <v>1.881050905005304E-4</v>
+      </c>
+      <c r="N79">
+        <v>2.6944944772384032E-4</v>
+      </c>
+      <c r="O79">
+        <v>2.6854596908240988E-4</v>
+      </c>
+      <c r="P79">
+        <v>2.6052088634172048E-4</v>
+      </c>
+      <c r="Q79">
+        <v>3.050483196752891E-4</v>
+      </c>
+      <c r="R79">
+        <v>3.0158315093917957E-4</v>
+      </c>
+      <c r="S79">
+        <v>3.0808334993690341E-4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>97</v>
+      </c>
+      <c r="B80">
+        <v>3.4526688794505299E-4</v>
+      </c>
+      <c r="C80">
+        <v>2.7293455800550033E-4</v>
+      </c>
+      <c r="D80">
+        <v>2.7435950577572881E-4</v>
+      </c>
+      <c r="E80">
+        <v>2.773450507326296E-4</v>
+      </c>
+      <c r="F80">
+        <v>2.925014035649998E-4</v>
+      </c>
+      <c r="G80">
+        <v>3.5391000939497582E-4</v>
+      </c>
+      <c r="H80">
+        <v>4.8316776450394008E-4</v>
+      </c>
+      <c r="I80">
+        <v>4.1652245571028359E-4</v>
+      </c>
+      <c r="J80">
+        <v>3.9601542685010181E-4</v>
+      </c>
+      <c r="K80">
+        <v>4.5714550912356378E-4</v>
+      </c>
+      <c r="L80">
+        <v>4.4944017087003888E-4</v>
+      </c>
+      <c r="M80">
+        <v>4.4868998870851648E-4</v>
+      </c>
+      <c r="N80">
+        <v>7.3534071666686086E-4</v>
+      </c>
+      <c r="O80">
+        <v>8.6530601617875694E-4</v>
+      </c>
+      <c r="P80">
+        <v>9.0676645064832458E-4</v>
+      </c>
+      <c r="Q80">
+        <v>1.1637781433265369E-3</v>
+      </c>
+      <c r="R80">
+        <v>1.240566338360461E-3</v>
+      </c>
+      <c r="S80">
+        <v>1.1630448504656981E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81">
+        <v>1.617649677853665E-4</v>
+      </c>
+      <c r="C81">
+        <v>1.5687111436426369E-4</v>
+      </c>
+      <c r="D81">
+        <v>1.587643346957275E-4</v>
+      </c>
+      <c r="E81">
+        <v>1.188043199283739E-4</v>
+      </c>
+      <c r="F81">
+        <v>1.2679169017121021E-4</v>
+      </c>
+      <c r="G81">
+        <v>1.4661131390452731E-4</v>
+      </c>
+      <c r="H81">
+        <v>1.655952826083399E-4</v>
+      </c>
+      <c r="I81">
+        <v>1.425239076559735E-4</v>
+      </c>
+      <c r="J81">
+        <v>1.485275694328215E-4</v>
+      </c>
+      <c r="K81">
+        <v>1.6460505924596581E-4</v>
+      </c>
+      <c r="L81">
+        <v>1.633215648078686E-4</v>
+      </c>
+      <c r="M81">
+        <v>1.8015672297491789E-4</v>
+      </c>
+      <c r="N81">
+        <v>2.5847830873170603E-4</v>
+      </c>
+      <c r="O81">
+        <v>2.7256683211108568E-4</v>
+      </c>
+      <c r="P81">
+        <v>2.16434770140497E-4</v>
+      </c>
+      <c r="Q81">
+        <v>2.9929094083632271E-4</v>
+      </c>
+      <c r="R81">
+        <v>2.886783249889444E-4</v>
+      </c>
+      <c r="S81">
+        <v>3.1298692392101192E-4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82">
+        <v>1.486532462203562E-4</v>
+      </c>
+      <c r="C82">
+        <v>1.377593145533877E-4</v>
+      </c>
+      <c r="D82">
+        <v>1.369372478776535E-4</v>
+      </c>
+      <c r="E82">
+        <v>1.5429389922227871E-4</v>
+      </c>
+      <c r="F82">
+        <v>1.644339608186677E-4</v>
+      </c>
+      <c r="G82">
+        <v>1.7307825655773709E-4</v>
+      </c>
+      <c r="H82">
+        <v>2.6745286633148452E-4</v>
+      </c>
+      <c r="I82">
+        <v>2.1681629862259209E-4</v>
+      </c>
+      <c r="J82">
+        <v>2.3195172975765409E-4</v>
+      </c>
+      <c r="K82">
+        <v>3.6134113814419871E-4</v>
+      </c>
+      <c r="L82">
+        <v>2.9317007049637462E-4</v>
+      </c>
+      <c r="M82">
+        <v>3.1063998292790772E-4</v>
+      </c>
+      <c r="N82">
+        <v>5.7910936523761366E-4</v>
+      </c>
+      <c r="O82">
+        <v>6.5298195735146467E-4</v>
+      </c>
+      <c r="P82">
+        <v>4.7151927272539191E-4</v>
+      </c>
+      <c r="Q82">
+        <v>5.7463448404955291E-4</v>
+      </c>
+      <c r="R82">
+        <v>5.5647597620965723E-4</v>
+      </c>
+      <c r="S82">
+        <v>6.4008476390022733E-4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83">
+        <v>4.96574561415585E-3</v>
+      </c>
+      <c r="C83">
+        <v>4.506007106331803E-3</v>
+      </c>
+      <c r="D83">
+        <v>4.454924966412116E-3</v>
+      </c>
+      <c r="E83">
+        <v>5.2851771439534649E-3</v>
+      </c>
+      <c r="F83">
+        <v>5.4119439685071796E-3</v>
+      </c>
+      <c r="G83">
+        <v>8.7657067731571389E-3</v>
+      </c>
+      <c r="H83">
+        <v>1.0398519845651891E-2</v>
+      </c>
+      <c r="I83">
+        <v>8.8556476523815476E-3</v>
+      </c>
+      <c r="J83">
+        <v>8.8623217156401386E-3</v>
+      </c>
+      <c r="K83">
+        <v>1.1346519002304999E-2</v>
+      </c>
+      <c r="L83">
+        <v>1.1513870632284311E-2</v>
+      </c>
+      <c r="M83">
+        <v>1.065989658846777E-2</v>
+      </c>
+      <c r="N83">
+        <v>2.108879396683409E-2</v>
+      </c>
+      <c r="O83">
+        <v>2.2700460344559859E-2</v>
+      </c>
+      <c r="P83">
+        <v>1.9038635164962799E-2</v>
+      </c>
+      <c r="Q83">
+        <v>2.4405286746247659E-2</v>
+      </c>
+      <c r="R83">
+        <v>2.5609527489713329E-2</v>
+      </c>
+      <c r="S83">
+        <v>2.5868629249101761E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>101</v>
+      </c>
+      <c r="B84">
+        <v>8.8546859624652203E-4</v>
+      </c>
+      <c r="C84">
+        <v>8.2577457202059662E-4</v>
+      </c>
+      <c r="D84">
+        <v>9.5777435969685216E-4</v>
+      </c>
+      <c r="E84">
+        <v>8.997746952792311E-4</v>
+      </c>
+      <c r="F84">
+        <v>9.6940558277604065E-4</v>
+      </c>
+      <c r="G84">
+        <v>1.6504013756396959E-3</v>
+      </c>
+      <c r="H84">
+        <v>1.7259315349459829E-3</v>
+      </c>
+      <c r="I84">
+        <v>1.5620458600046989E-3</v>
+      </c>
+      <c r="J84">
+        <v>1.4679612636091419E-3</v>
+      </c>
+      <c r="K84">
+        <v>1.8675502170905839E-3</v>
+      </c>
+      <c r="L84">
+        <v>1.88682300385407E-3</v>
+      </c>
+      <c r="M84">
+        <v>1.808521550999375E-3</v>
+      </c>
+      <c r="N84">
+        <v>4.0542321828822524E-3</v>
+      </c>
+      <c r="O84">
+        <v>3.9416050718533704E-3</v>
+      </c>
+      <c r="P84">
+        <v>3.484121236049804E-3</v>
+      </c>
+      <c r="Q84">
+        <v>4.415170932562623E-3</v>
+      </c>
+      <c r="R84">
+        <v>5.3161696293557966E-3</v>
+      </c>
+      <c r="S84">
+        <v>5.0452504995903589E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>102</v>
+      </c>
+      <c r="B85">
+        <v>3.9160265814264707E-3</v>
+      </c>
+      <c r="C85">
+        <v>3.3377548848523078E-3</v>
+      </c>
+      <c r="D85">
+        <v>3.4558157237340112E-3</v>
+      </c>
+      <c r="E85">
+        <v>3.5558582133289E-3</v>
+      </c>
+      <c r="F85">
+        <v>4.3104014912440829E-3</v>
+      </c>
+      <c r="G85">
+        <v>3.1002327970720378E-3</v>
+      </c>
+      <c r="H85">
+        <v>6.6143087411107016E-3</v>
+      </c>
+      <c r="I85">
+        <v>5.2613316343825579E-3</v>
+      </c>
+      <c r="J85">
+        <v>5.9105228682727086E-3</v>
+      </c>
+      <c r="K85">
+        <v>6.7692888667309874E-3</v>
+      </c>
+      <c r="L85">
+        <v>5.69626224108662E-3</v>
+      </c>
+      <c r="M85">
+        <v>6.911721816082953E-3</v>
+      </c>
+      <c r="N85">
+        <v>8.2600939509449248E-3</v>
+      </c>
+      <c r="O85">
+        <v>7.7450105634238502E-3</v>
+      </c>
+      <c r="P85">
+        <v>7.8840437773232824E-3</v>
+      </c>
+      <c r="Q85">
+        <v>6.9630511695064467E-3</v>
+      </c>
+      <c r="R85">
+        <v>6.668479741154326E-3</v>
+      </c>
+      <c r="S85">
+        <v>8.3819175469876054E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86">
+        <v>4.9722359486858926E-4</v>
+      </c>
+      <c r="C86">
+        <v>4.6662539659841098E-4</v>
+      </c>
+      <c r="D86">
+        <v>4.5835492889850061E-4</v>
+      </c>
+      <c r="E86">
+        <v>4.1953125673061447E-4</v>
+      </c>
+      <c r="F86">
+        <v>4.4085403263520808E-4</v>
+      </c>
+      <c r="G86">
+        <v>5.1279734693337922E-4</v>
+      </c>
+      <c r="H86">
+        <v>7.0021073995131522E-4</v>
+      </c>
+      <c r="I86">
+        <v>6.1879111987323172E-4</v>
+      </c>
+      <c r="J86">
+        <v>5.9570524405736652E-4</v>
+      </c>
+      <c r="K86">
+        <v>6.785816912652623E-4</v>
+      </c>
+      <c r="L86">
+        <v>6.7258336985115039E-4</v>
+      </c>
+      <c r="M86">
+        <v>7.3014423920909704E-4</v>
+      </c>
+      <c r="N86">
+        <v>1.03293147444857E-3</v>
+      </c>
+      <c r="O86">
+        <v>1.1360871846443079E-3</v>
+      </c>
+      <c r="P86">
+        <v>1.020336973867775E-3</v>
+      </c>
+      <c r="Q86">
+        <v>1.2945803040570569E-3</v>
+      </c>
+      <c r="R86">
+        <v>1.3278650913824859E-3</v>
+      </c>
+      <c r="S86">
+        <v>1.3233897945096179E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>104</v>
+      </c>
+      <c r="B87">
+        <v>7.0031199210304795E-5</v>
+      </c>
+      <c r="C87">
+        <v>6.2882520117145288E-5</v>
+      </c>
+      <c r="D87">
+        <v>7.0264231959284818E-5</v>
+      </c>
+      <c r="E87">
+        <v>7.626206349932255E-5</v>
+      </c>
+      <c r="F87">
+        <v>4.8526290869256513E-5</v>
+      </c>
+      <c r="G87">
+        <v>9.6924300285762939E-5</v>
+      </c>
+      <c r="H87">
+        <v>1.928226945098727E-4</v>
+      </c>
+      <c r="I87">
+        <v>1.2860335012640441E-4</v>
+      </c>
+      <c r="J87">
+        <v>1.666346887758861E-4</v>
+      </c>
+      <c r="K87">
+        <v>1.7260321314542079E-4</v>
+      </c>
+      <c r="L87">
+        <v>1.630007142854011E-4</v>
+      </c>
+      <c r="M87">
+        <v>1.005205700139525E-4</v>
+      </c>
+      <c r="N87">
+        <v>3.5554377693076651E-4</v>
+      </c>
+      <c r="O87">
+        <v>3.6194514748446449E-4</v>
+      </c>
+      <c r="P87">
+        <v>3.7533657935626748E-4</v>
+      </c>
+      <c r="Q87">
+        <v>4.9301258057897035E-4</v>
+      </c>
+      <c r="R87">
+        <v>6.701027410692227E-4</v>
+      </c>
+      <c r="S87">
+        <v>7.0173632386985889E-4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>105</v>
+      </c>
+      <c r="B88">
+        <v>8.7078352061999102E-3</v>
+      </c>
+      <c r="C88">
+        <v>8.1169644100704142E-3</v>
+      </c>
+      <c r="D88">
+        <v>9.3758027677012003E-3</v>
+      </c>
+      <c r="E88">
+        <v>7.9866505052137993E-3</v>
+      </c>
+      <c r="F88">
+        <v>9.3181470377374179E-3</v>
+      </c>
+      <c r="G88">
+        <v>7.9177725540595795E-3</v>
+      </c>
+      <c r="H88">
+        <v>1.284959218027198E-2</v>
+      </c>
+      <c r="I88">
+        <v>9.4342300349553113E-3</v>
+      </c>
+      <c r="J88">
+        <v>1.0637757615151519E-2</v>
+      </c>
+      <c r="K88">
+        <v>1.167694885098295E-2</v>
+      </c>
+      <c r="L88">
+        <v>1.103391372804787E-2</v>
+      </c>
+      <c r="M88">
+        <v>1.293271768370928E-2</v>
+      </c>
+      <c r="N88">
+        <v>1.652174056199739E-2</v>
+      </c>
+      <c r="O88">
+        <v>1.5647841421619652E-2</v>
+      </c>
+      <c r="P88">
+        <v>1.404559347814416E-2</v>
+      </c>
+      <c r="Q88">
+        <v>1.358692305246828E-2</v>
+      </c>
+      <c r="R88">
+        <v>1.249148247625341E-2</v>
+      </c>
+      <c r="S88">
+        <v>1.5872136038720189E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>106</v>
+      </c>
+      <c r="B89">
+        <v>9.1952597086549613E-6</v>
+      </c>
+      <c r="C89">
+        <v>9.1751788969027825E-6</v>
+      </c>
+      <c r="D89">
+        <v>1.0968475741430531E-5</v>
+      </c>
+      <c r="E89">
+        <v>9.3484480873598355E-6</v>
+      </c>
+      <c r="F89">
+        <v>1.064073614330079E-5</v>
+      </c>
+      <c r="G89">
+        <v>9.1756089298329633E-6</v>
+      </c>
+      <c r="H89">
+        <v>1.27404148053122E-5</v>
+      </c>
+      <c r="I89">
+        <v>1.13747873812535E-5</v>
+      </c>
+      <c r="J89">
+        <v>1.189401372313864E-5</v>
+      </c>
+      <c r="K89">
+        <v>1.3308579877501291E-5</v>
+      </c>
+      <c r="L89">
+        <v>1.393565560172643E-5</v>
+      </c>
+      <c r="M89">
+        <v>1.456764323879005E-5</v>
+      </c>
+      <c r="N89">
+        <v>2.0018389472823669E-5</v>
+      </c>
+      <c r="O89">
+        <v>2.4410576431090301E-5</v>
+      </c>
+      <c r="P89">
+        <v>2.2068009104018012E-5</v>
+      </c>
+      <c r="Q89">
+        <v>2.960799561498168E-5</v>
+      </c>
+      <c r="R89">
+        <v>2.4622239487724891E-5</v>
+      </c>
+      <c r="S89">
+        <v>2.475381785406305E-5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>107</v>
+      </c>
+      <c r="B90">
+        <v>5.3921095070184953E-4</v>
+      </c>
+      <c r="C90">
+        <v>4.7172565515764861E-4</v>
+      </c>
+      <c r="D90">
+        <v>5.995721524307948E-4</v>
+      </c>
+      <c r="E90">
+        <v>4.6777766435629768E-4</v>
+      </c>
+      <c r="F90">
+        <v>4.9893086413135661E-4</v>
+      </c>
+      <c r="G90">
+        <v>5.0152348224131364E-4</v>
+      </c>
+      <c r="H90">
+        <v>6.4963225937203874E-4</v>
+      </c>
+      <c r="I90">
+        <v>6.2909274559330491E-4</v>
+      </c>
+      <c r="J90">
+        <v>5.8504554725965477E-4</v>
+      </c>
+      <c r="K90">
+        <v>6.5510021207001361E-4</v>
+      </c>
+      <c r="L90">
+        <v>6.9543018215554534E-4</v>
+      </c>
+      <c r="M90">
+        <v>6.7901156965051565E-4</v>
+      </c>
+      <c r="N90">
+        <v>1.1144253980926451E-3</v>
+      </c>
+      <c r="O90">
+        <v>1.0276388199419481E-3</v>
+      </c>
+      <c r="P90">
+        <v>1.150661058439015E-3</v>
+      </c>
+      <c r="Q90">
+        <v>1.2201413572187679E-3</v>
+      </c>
+      <c r="R90">
+        <v>1.4545596724012289E-3</v>
+      </c>
+      <c r="S90">
+        <v>1.5224709274627439E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>108</v>
+      </c>
+      <c r="B91">
+        <v>3.3035028573789593E-5</v>
+      </c>
+      <c r="C91">
+        <v>2.7948632919935971E-5</v>
+      </c>
+      <c r="D91">
+        <v>3.0467554998747872E-5</v>
+      </c>
+      <c r="E91">
+        <v>2.635200530601555E-5</v>
+      </c>
+      <c r="F91">
+        <v>3.0019540336260061E-5</v>
+      </c>
+      <c r="G91">
+        <v>2.4044222430871009E-5</v>
+      </c>
+      <c r="H91">
+        <v>3.6690419539880351E-5</v>
+      </c>
+      <c r="I91">
+        <v>3.0261338569320221E-5</v>
+      </c>
+      <c r="J91">
+        <v>3.2031487547492449E-5</v>
+      </c>
+      <c r="K91">
+        <v>4.2341308358795292E-5</v>
+      </c>
+      <c r="L91">
+        <v>4.0959232909865011E-5</v>
+      </c>
+      <c r="M91">
+        <v>4.3194903560704312E-5</v>
+      </c>
+      <c r="N91">
+        <v>5.659683737635366E-5</v>
+      </c>
+      <c r="O91">
+        <v>6.3705765454660608E-5</v>
+      </c>
+      <c r="P91">
+        <v>5.5506766771933728E-5</v>
+      </c>
+      <c r="Q91">
+        <v>7.6314638017724673E-5</v>
+      </c>
+      <c r="R91">
+        <v>6.8476820727709061E-5</v>
+      </c>
+      <c r="S91">
+        <v>6.3173923315524745E-5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>109</v>
+      </c>
+      <c r="B92">
+        <v>2.4200941782001321E-4</v>
+      </c>
+      <c r="C92">
+        <v>2.1703113989494661E-4</v>
+      </c>
+      <c r="D92">
+        <v>2.212119913315144E-4</v>
+      </c>
+      <c r="E92">
+        <v>2.006251282465114E-4</v>
+      </c>
+      <c r="F92">
+        <v>2.2142566113164471E-4</v>
+      </c>
+      <c r="G92">
+        <v>1.9014507779356691E-4</v>
+      </c>
+      <c r="H92">
+        <v>3.030550909208249E-4</v>
+      </c>
+      <c r="I92">
+        <v>2.7517864300599892E-4</v>
+      </c>
+      <c r="J92">
+        <v>2.8475801519462477E-4</v>
+      </c>
+      <c r="K92">
+        <v>3.5636576264283721E-4</v>
+      </c>
+      <c r="L92">
+        <v>3.5685668238635951E-4</v>
+      </c>
+      <c r="M92">
+        <v>3.5570535723167539E-4</v>
+      </c>
+      <c r="N92">
+        <v>6.2159362610415803E-4</v>
+      </c>
+      <c r="O92">
+        <v>5.4663913268502759E-4</v>
+      </c>
+      <c r="P92">
+        <v>5.7429085619195737E-4</v>
+      </c>
+      <c r="Q92">
+        <v>7.8061005778058332E-4</v>
+      </c>
+      <c r="R92">
+        <v>6.8923875829583097E-4</v>
+      </c>
+      <c r="S92">
+        <v>7.7789573988055636E-4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>110</v>
+      </c>
+      <c r="B93">
+        <v>1.7699845348805739E-3</v>
+      </c>
+      <c r="C93">
+        <v>1.5165671302306239E-3</v>
+      </c>
+      <c r="D93">
+        <v>1.713695849464001E-3</v>
+      </c>
+      <c r="E93">
+        <v>1.179689774217329E-3</v>
+      </c>
+      <c r="F93">
+        <v>1.253641833911199E-3</v>
+      </c>
+      <c r="G93">
+        <v>2.3786659555999189E-3</v>
+      </c>
+      <c r="H93">
+        <v>2.0889334136448951E-3</v>
+      </c>
+      <c r="I93">
+        <v>1.702575045562483E-3</v>
+      </c>
+      <c r="J93">
+        <v>1.6477390579983471E-3</v>
+      </c>
+      <c r="K93">
+        <v>1.7839166503995391E-3</v>
+      </c>
+      <c r="L93">
+        <v>1.7232759506168921E-3</v>
+      </c>
+      <c r="M93">
+        <v>1.8801670037391859E-3</v>
+      </c>
+      <c r="N93">
+        <v>2.8324071058655172E-3</v>
+      </c>
+      <c r="O93">
+        <v>2.5326011505283361E-3</v>
+      </c>
+      <c r="P93">
+        <v>1.41227680002631E-3</v>
+      </c>
+      <c r="Q93">
+        <v>3.3632333799994089E-3</v>
+      </c>
+      <c r="R93">
+        <v>5.6311477179957518E-3</v>
+      </c>
+      <c r="S93">
+        <v>4.2260009802180063E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>111</v>
+      </c>
+      <c r="B94">
+        <v>1.134123193772568E-3</v>
+      </c>
+      <c r="C94">
+        <v>1.161229336365994E-3</v>
+      </c>
+      <c r="D94">
+        <v>1.042945306637311E-3</v>
+      </c>
+      <c r="E94">
+        <v>8.2071809845682625E-4</v>
+      </c>
+      <c r="F94">
+        <v>9.4707537713696621E-4</v>
+      </c>
+      <c r="G94">
+        <v>6.359212337559353E-4</v>
+      </c>
+      <c r="H94">
+        <v>1.155123068489884E-3</v>
+      </c>
+      <c r="I94">
+        <v>9.5793768964227163E-4</v>
+      </c>
+      <c r="J94">
+        <v>1.072934180125793E-3</v>
+      </c>
+      <c r="K94">
+        <v>1.224632033595759E-3</v>
+      </c>
+      <c r="L94">
+        <v>1.070383143853177E-3</v>
+      </c>
+      <c r="M94">
+        <v>1.2238105854458399E-3</v>
+      </c>
+      <c r="N94">
+        <v>1.8143839053657159E-3</v>
+      </c>
+      <c r="O94">
+        <v>1.7760954548932449E-3</v>
+      </c>
+      <c r="P94">
+        <v>1.523972816235017E-3</v>
+      </c>
+      <c r="Q94">
+        <v>2.0046381736502231E-3</v>
+      </c>
+      <c r="R94">
+        <v>1.7116497374590649E-3</v>
+      </c>
+      <c r="S94">
+        <v>1.8797704078648129E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>112</v>
+      </c>
+      <c r="B95">
+        <v>1.30233544006055E-3</v>
+      </c>
+      <c r="C95">
+        <v>1.193257756353494E-3</v>
+      </c>
+      <c r="D95">
+        <v>1.2884837291992309E-3</v>
+      </c>
+      <c r="E95">
+        <v>1.030243915419249E-3</v>
+      </c>
+      <c r="F95">
+        <v>1.1368151100976821E-3</v>
+      </c>
+      <c r="G95">
+        <v>1.434695428067531E-3</v>
+      </c>
+      <c r="H95">
+        <v>1.5308474245238071E-3</v>
+      </c>
+      <c r="I95">
+        <v>1.320725973201811E-3</v>
+      </c>
+      <c r="J95">
+        <v>1.3965764413782331E-3</v>
+      </c>
+      <c r="K95">
+        <v>1.5380370865675621E-3</v>
+      </c>
+      <c r="L95">
+        <v>1.434886353309807E-3</v>
+      </c>
+      <c r="M95">
+        <v>1.498229809092603E-3</v>
+      </c>
+      <c r="N95">
+        <v>1.8662310375981549E-3</v>
+      </c>
+      <c r="O95">
+        <v>2.0967305389425462E-3</v>
+      </c>
+      <c r="P95">
+        <v>1.606839614141372E-3</v>
+      </c>
+      <c r="Q95">
+        <v>2.0151018490135461E-3</v>
+      </c>
+      <c r="R95">
+        <v>1.6982966461465609E-3</v>
+      </c>
+      <c r="S95">
+        <v>1.8248227196781259E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>113</v>
+      </c>
+      <c r="B96">
+        <v>5.4843235980178815E-4</v>
+      </c>
+      <c r="C96">
+        <v>4.4684247947503051E-4</v>
+      </c>
+      <c r="D96">
+        <v>4.3804950688343148E-4</v>
+      </c>
+      <c r="E96">
+        <v>4.4136829763437042E-4</v>
+      </c>
+      <c r="F96">
+        <v>4.9711255786095716E-4</v>
+      </c>
+      <c r="G96">
+        <v>7.2223008779870529E-4</v>
+      </c>
+      <c r="H96">
+        <v>8.2458187331732157E-4</v>
+      </c>
+      <c r="I96">
+        <v>7.6353284400686118E-4</v>
+      </c>
+      <c r="J96">
+        <v>7.7198171877534071E-4</v>
+      </c>
+      <c r="K96">
+        <v>9.0357278689207705E-4</v>
+      </c>
+      <c r="L96">
+        <v>8.7643074494005364E-4</v>
+      </c>
+      <c r="M96">
+        <v>9.1905827752364626E-4</v>
+      </c>
+      <c r="N96">
+        <v>1.705439855194314E-3</v>
+      </c>
+      <c r="O96">
+        <v>1.5161985846744101E-3</v>
+      </c>
+      <c r="P96">
+        <v>1.4865497290158581E-3</v>
+      </c>
+      <c r="Q96">
+        <v>1.9586219221177032E-3</v>
+      </c>
+      <c r="R96">
+        <v>1.9705134693159352E-3</v>
+      </c>
+      <c r="S96">
+        <v>1.9179540799085331E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>114</v>
+      </c>
+      <c r="B97">
+        <v>7.7011671699601741E-5</v>
+      </c>
+      <c r="C97">
+        <v>8.1040756558044237E-5</v>
+      </c>
+      <c r="D97">
+        <v>7.2565480444186937E-5</v>
+      </c>
+      <c r="E97">
+        <v>7.6226866348544795E-5</v>
+      </c>
+      <c r="F97">
+        <v>8.0646275352032719E-5</v>
+      </c>
+      <c r="G97">
+        <v>7.2609253287471233E-5</v>
+      </c>
+      <c r="H97">
+        <v>1.198853899255664E-4</v>
+      </c>
+      <c r="I97">
+        <v>1.035829637691105E-4</v>
+      </c>
+      <c r="J97">
+        <v>1.054507779651953E-4</v>
+      </c>
+      <c r="K97">
+        <v>1.487846301531955E-4</v>
+      </c>
+      <c r="L97">
+        <v>1.364525827404441E-4</v>
+      </c>
+      <c r="M97">
+        <v>1.4205507218482491E-4</v>
+      </c>
+      <c r="N97">
+        <v>2.333204634745349E-4</v>
+      </c>
+      <c r="O97">
+        <v>2.7745112275712078E-4</v>
+      </c>
+      <c r="P97">
+        <v>2.628762557856181E-4</v>
+      </c>
+      <c r="Q97">
+        <v>3.1321742958851252E-4</v>
+      </c>
+      <c r="R97">
+        <v>3.230218731935015E-4</v>
+      </c>
+      <c r="S97">
+        <v>3.3479339542375922E-4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>115</v>
+      </c>
+      <c r="B98">
+        <v>1.8083507784866481E-4</v>
+      </c>
+      <c r="C98">
+        <v>1.7189248130515441E-4</v>
+      </c>
+      <c r="D98">
+        <v>1.6495596606281779E-4</v>
+      </c>
+      <c r="E98">
+        <v>1.841309052624612E-4</v>
+      </c>
+      <c r="F98">
+        <v>1.787952269374826E-4</v>
+      </c>
+      <c r="G98">
+        <v>2.1564671321801861E-4</v>
+      </c>
+      <c r="H98">
+        <v>2.9417280332523689E-4</v>
+      </c>
+      <c r="I98">
+        <v>2.3746539276499741E-4</v>
+      </c>
+      <c r="J98">
+        <v>2.5109974404614362E-4</v>
+      </c>
+      <c r="K98">
+        <v>3.1894462164406108E-4</v>
+      </c>
+      <c r="L98">
+        <v>3.1045857325147927E-4</v>
+      </c>
+      <c r="M98">
+        <v>3.2192047966484398E-4</v>
+      </c>
+      <c r="N98">
+        <v>5.5640449436893894E-4</v>
+      </c>
+      <c r="O98">
+        <v>5.8533604499938063E-4</v>
+      </c>
+      <c r="P98">
+        <v>5.265538925808735E-4</v>
+      </c>
+      <c r="Q98">
+        <v>6.5185652273189718E-4</v>
+      </c>
+      <c r="R98">
+        <v>6.1514907005351198E-4</v>
+      </c>
+      <c r="S98">
+        <v>6.6680335719709145E-4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>116</v>
+      </c>
+      <c r="B99">
+        <v>8.7047113649730735E-5</v>
+      </c>
+      <c r="C99">
+        <v>7.5790909258581274E-5</v>
+      </c>
+      <c r="D99">
+        <v>9.6569375243712449E-5</v>
+      </c>
+      <c r="E99">
+        <v>9.3655827433051977E-5</v>
+      </c>
+      <c r="F99">
+        <v>9.62005825567072E-5</v>
+      </c>
+      <c r="G99">
+        <v>1.166353899263836E-4</v>
+      </c>
+      <c r="H99">
+        <v>1.6564405049783489E-4</v>
+      </c>
+      <c r="I99">
+        <v>1.4971152327546841E-4</v>
+      </c>
+      <c r="J99">
+        <v>1.3860150788378179E-4</v>
+      </c>
+      <c r="K99">
+        <v>1.6439567935335649E-4</v>
+      </c>
+      <c r="L99">
+        <v>1.584900834957547E-4</v>
+      </c>
+      <c r="M99">
+        <v>1.700094306754787E-4</v>
+      </c>
+      <c r="N99">
+        <v>2.8743460840515898E-4</v>
+      </c>
+      <c r="O99">
+        <v>2.9001778995653101E-4</v>
+      </c>
+      <c r="P99">
+        <v>2.757623812084135E-4</v>
+      </c>
+      <c r="Q99">
+        <v>3.5036326302645448E-4</v>
+      </c>
+      <c r="R99">
+        <v>3.2688196580709419E-4</v>
+      </c>
+      <c r="S99">
+        <v>3.3445108874967231E-4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>117</v>
+      </c>
+      <c r="B100">
+        <v>4.2317711389895299E-4</v>
+      </c>
+      <c r="C100">
+        <v>3.7934655816961678E-4</v>
+      </c>
+      <c r="D100">
+        <v>4.2423725322306052E-4</v>
+      </c>
+      <c r="E100">
+        <v>3.563266228121634E-4</v>
+      </c>
+      <c r="F100">
+        <v>3.5453823265224128E-4</v>
+      </c>
+      <c r="G100">
+        <v>4.3776293258557491E-4</v>
+      </c>
+      <c r="H100">
+        <v>5.5215663289179522E-4</v>
+      </c>
+      <c r="I100">
+        <v>4.6842351701602693E-4</v>
+      </c>
+      <c r="J100">
+        <v>4.6549112582748282E-4</v>
+      </c>
+      <c r="K100">
+        <v>5.4123327921252117E-4</v>
+      </c>
+      <c r="L100">
+        <v>5.2365293951448422E-4</v>
+      </c>
+      <c r="M100">
+        <v>5.6532040238161448E-4</v>
+      </c>
+      <c r="N100">
+        <v>8.8299345789956418E-4</v>
+      </c>
+      <c r="O100">
+        <v>8.7593703554712408E-4</v>
+      </c>
+      <c r="P100">
+        <v>8.4452210144180505E-4</v>
+      </c>
+      <c r="Q100">
+        <v>9.8154538339924368E-4</v>
+      </c>
+      <c r="R100">
+        <v>9.8038762434054334E-4</v>
+      </c>
+      <c r="S100">
+        <v>1.103597424587455E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>118</v>
+      </c>
+      <c r="B101">
+        <v>5.1480979914610386E-4</v>
+      </c>
+      <c r="C101">
+        <v>5.0593538809680079E-4</v>
+      </c>
+      <c r="D101">
+        <v>4.6846850647362149E-4</v>
+      </c>
+      <c r="E101">
+        <v>3.725797737103704E-4</v>
+      </c>
+      <c r="F101">
+        <v>4.4465899371137318E-4</v>
+      </c>
+      <c r="G101">
+        <v>3.9362415744694478E-4</v>
+      </c>
+      <c r="H101">
+        <v>6.7652322333771676E-4</v>
+      </c>
+      <c r="I101">
+        <v>5.2812839953910384E-4</v>
+      </c>
+      <c r="J101">
+        <v>6.2131074114068726E-4</v>
+      </c>
+      <c r="K101">
+        <v>6.8389319657417033E-4</v>
+      </c>
+      <c r="L101">
+        <v>7.2186655135080013E-4</v>
+      </c>
+      <c r="M101">
+        <v>6.3425063114644353E-4</v>
+      </c>
+      <c r="N101">
+        <v>1.106891036127439E-3</v>
+      </c>
+      <c r="O101">
+        <v>1.11112954806538E-3</v>
+      </c>
+      <c r="P101">
+        <v>9.4674964246346566E-4</v>
+      </c>
+      <c r="Q101">
+        <v>1.2779892239067269E-3</v>
+      </c>
+      <c r="R101">
+        <v>1.3236449405414439E-3</v>
+      </c>
+      <c r="S101">
+        <v>1.4347708927683819E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>119</v>
+      </c>
+      <c r="B102">
+        <v>4.7566131648397996E-3</v>
+      </c>
+      <c r="C102">
+        <v>4.100540129250224E-3</v>
+      </c>
+      <c r="D102">
+        <v>4.1348071548991359E-3</v>
+      </c>
+      <c r="E102">
+        <v>3.5091219280714851E-3</v>
+      </c>
+      <c r="F102">
+        <v>3.605887649468792E-3</v>
+      </c>
+      <c r="G102">
+        <v>4.8174428434211714E-3</v>
+      </c>
+      <c r="H102">
+        <v>5.6705023178300219E-3</v>
+      </c>
+      <c r="I102">
+        <v>5.2127499956454168E-3</v>
+      </c>
+      <c r="J102">
+        <v>5.1066292473690199E-3</v>
+      </c>
+      <c r="K102">
+        <v>5.65070780874631E-3</v>
+      </c>
+      <c r="L102">
+        <v>5.3950450188603961E-3</v>
+      </c>
+      <c r="M102">
+        <v>5.3724242976642871E-3</v>
+      </c>
+      <c r="N102">
+        <v>1.0059453115924891E-2</v>
+      </c>
+      <c r="O102">
+        <v>9.6726490913453533E-3</v>
+      </c>
+      <c r="P102">
+        <v>7.200974759195216E-3</v>
+      </c>
+      <c r="Q102">
+        <v>1.2711293147648061E-2</v>
+      </c>
+      <c r="R102">
+        <v>1.22613345897595E-2</v>
+      </c>
+      <c r="S102">
+        <v>1.272834218487214E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>120</v>
+      </c>
+      <c r="B103">
+        <v>1.3514290565692461E-4</v>
+      </c>
+      <c r="C103">
+        <v>1.3049625011092261E-4</v>
+      </c>
+      <c r="D103">
+        <v>1.285912148456921E-4</v>
+      </c>
+      <c r="E103">
+        <v>1.2892011393773401E-4</v>
+      </c>
+      <c r="F103">
+        <v>1.1837539872284749E-4</v>
+      </c>
+      <c r="G103">
+        <v>1.6382194591313089E-4</v>
+      </c>
+      <c r="H103">
+        <v>1.8763868136030339E-4</v>
+      </c>
+      <c r="I103">
+        <v>1.6342035449368419E-4</v>
+      </c>
+      <c r="J103">
+        <v>1.6462204275075859E-4</v>
+      </c>
+      <c r="K103">
+        <v>1.8950882517797371E-4</v>
+      </c>
+      <c r="L103">
+        <v>1.9355762194173169E-4</v>
+      </c>
+      <c r="M103">
+        <v>1.9641415554577399E-4</v>
+      </c>
+      <c r="N103">
+        <v>2.9219016493698031E-4</v>
+      </c>
+      <c r="O103">
+        <v>2.8282994005068249E-4</v>
+      </c>
+      <c r="P103">
+        <v>2.9287547046792769E-4</v>
+      </c>
+      <c r="Q103">
+        <v>3.7787381348159017E-4</v>
+      </c>
+      <c r="R103">
+        <v>3.4832572660930611E-4</v>
+      </c>
+      <c r="S103">
+        <v>3.3190821922789003E-4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>121</v>
+      </c>
+      <c r="B104">
+        <v>2.8710128548389802E-4</v>
+      </c>
+      <c r="C104">
+        <v>2.7692639537944168E-4</v>
+      </c>
+      <c r="D104">
+        <v>2.6690343133718188E-4</v>
+      </c>
+      <c r="E104">
+        <v>2.678779259221557E-4</v>
+      </c>
+      <c r="F104">
+        <v>2.7659625716330182E-4</v>
+      </c>
+      <c r="G104">
+        <v>2.3067451616485589E-4</v>
+      </c>
+      <c r="H104">
+        <v>3.7452473897445172E-4</v>
+      </c>
+      <c r="I104">
+        <v>3.1875535148669478E-4</v>
+      </c>
+      <c r="J104">
+        <v>3.3251553081898601E-4</v>
+      </c>
+      <c r="K104">
+        <v>3.8198441642891482E-4</v>
+      </c>
+      <c r="L104">
+        <v>3.6730726451383113E-4</v>
+      </c>
+      <c r="M104">
+        <v>4.0501026971667518E-4</v>
+      </c>
+      <c r="N104">
+        <v>5.819078942641007E-4</v>
+      </c>
+      <c r="O104">
+        <v>5.8074311750991238E-4</v>
+      </c>
+      <c r="P104">
+        <v>5.5141871925139805E-4</v>
+      </c>
+      <c r="Q104">
+        <v>6.1493880129453061E-4</v>
+      </c>
+      <c r="R104">
+        <v>6.1685794298133457E-4</v>
+      </c>
+      <c r="S104">
+        <v>7.1038828634939434E-4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>122</v>
+      </c>
+      <c r="B105">
+        <v>3.2811952607373349E-4</v>
+      </c>
+      <c r="C105">
+        <v>2.9923348642611579E-4</v>
+      </c>
+      <c r="D105">
+        <v>2.7511705171906801E-4</v>
+      </c>
+      <c r="E105">
+        <v>2.7112041032806132E-4</v>
+      </c>
+      <c r="F105">
+        <v>2.8430572613661828E-4</v>
+      </c>
+      <c r="G105">
+        <v>2.9373503899622448E-4</v>
+      </c>
+      <c r="H105">
+        <v>4.3097437912306691E-4</v>
+      </c>
+      <c r="I105">
+        <v>3.7765267797664918E-4</v>
+      </c>
+      <c r="J105">
+        <v>3.6737303960406639E-4</v>
+      </c>
+      <c r="K105">
+        <v>4.0798862531970267E-4</v>
+      </c>
+      <c r="L105">
+        <v>4.1097819110799E-4</v>
+      </c>
+      <c r="M105">
+        <v>4.3528139240607962E-4</v>
+      </c>
+      <c r="N105">
+        <v>6.138876562689627E-4</v>
+      </c>
+      <c r="O105">
+        <v>6.8593802797452588E-4</v>
+      </c>
+      <c r="P105">
+        <v>6.0790439150937552E-4</v>
+      </c>
+      <c r="Q105">
+        <v>7.8029100601808806E-4</v>
+      </c>
+      <c r="R105">
+        <v>7.4476114057588604E-4</v>
+      </c>
+      <c r="S105">
+        <v>7.3182240237149834E-4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>123</v>
+      </c>
+      <c r="B106">
+        <v>5.3128720066249863E-4</v>
+      </c>
+      <c r="C106">
+        <v>5.0258841518911442E-4</v>
+      </c>
+      <c r="D106">
+        <v>5.8039588122110795E-4</v>
+      </c>
+      <c r="E106">
+        <v>4.6858740948851598E-4</v>
+      </c>
+      <c r="F106">
+        <v>5.2231904042855627E-4</v>
+      </c>
+      <c r="G106">
+        <v>5.7449336699337734E-4</v>
+      </c>
+      <c r="H106">
+        <v>7.480583065481391E-4</v>
+      </c>
+      <c r="I106">
+        <v>6.3573536474020539E-4</v>
+      </c>
+      <c r="J106">
+        <v>6.3613505588319273E-4</v>
+      </c>
+      <c r="K106">
+        <v>6.975126028247367E-4</v>
+      </c>
+      <c r="L106">
+        <v>7.0857698440787817E-4</v>
+      </c>
+      <c r="M106">
+        <v>7.5586267392877232E-4</v>
+      </c>
+      <c r="N106">
+        <v>1.081714880550847E-3</v>
+      </c>
+      <c r="O106">
+        <v>1.089525753269407E-3</v>
+      </c>
+      <c r="P106">
+        <v>8.8641010255868639E-4</v>
+      </c>
+      <c r="Q106">
+        <v>1.128909238842096E-3</v>
+      </c>
+      <c r="R106">
+        <v>1.170028775511967E-3</v>
+      </c>
+      <c r="S106">
+        <v>1.2877234543541009E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>124</v>
+      </c>
+      <c r="B107">
+        <v>1.203949576113875E-4</v>
+      </c>
+      <c r="C107">
+        <v>1.039714513592692E-4</v>
+      </c>
+      <c r="D107">
+        <v>8.2757645083107232E-5</v>
+      </c>
+      <c r="E107">
+        <v>1.105674924716778E-4</v>
+      </c>
+      <c r="F107">
+        <v>1.2128043078502501E-4</v>
+      </c>
+      <c r="G107">
+        <v>1.4933413653482429E-4</v>
+      </c>
+      <c r="H107">
+        <v>1.6221955428856929E-4</v>
+      </c>
+      <c r="I107">
+        <v>1.4680252514204061E-4</v>
+      </c>
+      <c r="J107">
+        <v>1.4523678842174079E-4</v>
+      </c>
+      <c r="K107">
+        <v>1.3707284869462439E-4</v>
+      </c>
+      <c r="L107">
+        <v>1.5587584438282829E-4</v>
+      </c>
+      <c r="M107">
+        <v>1.4546530847388061E-4</v>
+      </c>
+      <c r="N107">
+        <v>2.8081563357467879E-4</v>
+      </c>
+      <c r="O107">
+        <v>2.0668940790855139E-4</v>
+      </c>
+      <c r="P107">
+        <v>2.3499947238359481E-4</v>
+      </c>
+      <c r="Q107">
+        <v>3.5554664450070621E-4</v>
+      </c>
+      <c r="R107">
+        <v>4.0211374662741279E-4</v>
+      </c>
+      <c r="S107">
+        <v>4.0686296700183041E-4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>125</v>
+      </c>
+      <c r="B108">
+        <v>1.5950224850504529E-3</v>
+      </c>
+      <c r="C108">
+        <v>1.448896167443553E-3</v>
+      </c>
+      <c r="D108">
+        <v>1.5113763267409631E-3</v>
+      </c>
+      <c r="E108">
+        <v>1.3785964326466899E-3</v>
+      </c>
+      <c r="F108">
+        <v>1.4448301319098451E-3</v>
+      </c>
+      <c r="G108">
+        <v>1.663990918669541E-3</v>
+      </c>
+      <c r="H108">
+        <v>2.0597011719534078E-3</v>
+      </c>
+      <c r="I108">
+        <v>1.825634799248105E-3</v>
+      </c>
+      <c r="J108">
+        <v>1.842983141750746E-3</v>
+      </c>
+      <c r="K108">
+        <v>2.0486848474252162E-3</v>
+      </c>
+      <c r="L108">
+        <v>2.0129450573906161E-3</v>
+      </c>
+      <c r="M108">
+        <v>2.1593795180762602E-3</v>
+      </c>
+      <c r="N108">
+        <v>3.1725117474970632E-3</v>
+      </c>
+      <c r="O108">
+        <v>3.3579618042955009E-3</v>
+      </c>
+      <c r="P108">
+        <v>3.082666717881192E-3</v>
+      </c>
+      <c r="Q108">
+        <v>3.779187269129662E-3</v>
+      </c>
+      <c r="R108">
+        <v>3.4096923030713122E-3</v>
+      </c>
+      <c r="S108">
+        <v>3.8338161213044108E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>126</v>
+      </c>
+      <c r="B109">
+        <v>9.7706918923129229E-6</v>
+      </c>
+      <c r="C109">
+        <v>8.241874902276118E-6</v>
+      </c>
+      <c r="D109">
+        <v>9.5396085654374059E-6</v>
+      </c>
+      <c r="E109">
+        <v>8.3295924134206782E-6</v>
+      </c>
+      <c r="F109">
+        <v>9.2311960777453931E-6</v>
+      </c>
+      <c r="G109">
+        <v>1.305576092584286E-5</v>
+      </c>
+      <c r="H109">
+        <v>1.2696390127142859E-5</v>
+      </c>
+      <c r="I109">
+        <v>1.2128110512312139E-5</v>
+      </c>
+      <c r="J109">
+        <v>1.1157134444065479E-5</v>
+      </c>
+      <c r="K109">
+        <v>1.3673704382304519E-5</v>
+      </c>
+      <c r="L109">
+        <v>1.425078236490984E-5</v>
+      </c>
+      <c r="M109">
+        <v>1.5147187732003849E-5</v>
+      </c>
+      <c r="N109">
+        <v>2.159804105669607E-5</v>
+      </c>
+      <c r="O109">
+        <v>2.1093432316942349E-5</v>
+      </c>
+      <c r="P109">
+        <v>2.1505286239100559E-5</v>
+      </c>
+      <c r="Q109">
+        <v>2.4281161590872089E-5</v>
+      </c>
+      <c r="R109">
+        <v>2.64564187490477E-5</v>
+      </c>
+      <c r="S109">
+        <v>2.4874088873697541E-5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>127</v>
+      </c>
+      <c r="B110">
+        <v>5.0901745672510702E-4</v>
+      </c>
+      <c r="C110">
+        <v>4.6526490405817452E-4</v>
+      </c>
+      <c r="D110">
+        <v>3.9875667132224497E-4</v>
+      </c>
+      <c r="E110">
+        <v>4.1118267393727942E-4</v>
+      </c>
+      <c r="F110">
+        <v>4.7200309287190648E-4</v>
+      </c>
+      <c r="G110">
+        <v>4.3090745888594412E-4</v>
+      </c>
+      <c r="H110">
+        <v>6.9500392347776141E-4</v>
+      </c>
+      <c r="I110">
+        <v>5.7740966724813443E-4</v>
+      </c>
+      <c r="J110">
+        <v>5.979045856166987E-4</v>
+      </c>
+      <c r="K110">
+        <v>6.7162446099283365E-4</v>
+      </c>
+      <c r="L110">
+        <v>6.4780140135734616E-4</v>
+      </c>
+      <c r="M110">
+        <v>6.70611704854507E-4</v>
+      </c>
+      <c r="N110">
+        <v>1.055216403329197E-3</v>
+      </c>
+      <c r="O110">
+        <v>1.1617925433550359E-3</v>
+      </c>
+      <c r="P110">
+        <v>8.6455082985592742E-4</v>
+      </c>
+      <c r="Q110">
+        <v>1.2999911859745709E-3</v>
+      </c>
+      <c r="R110">
+        <v>1.671388765973478E-3</v>
+      </c>
+      <c r="S110">
+        <v>1.341532783650808E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>128</v>
+      </c>
+      <c r="B111">
+        <v>7.1478484056441234E-3</v>
+      </c>
+      <c r="C111">
+        <v>6.5300139233089053E-3</v>
+      </c>
+      <c r="D111">
+        <v>6.7372602564795634E-3</v>
+      </c>
+      <c r="E111">
+        <v>5.6525383250498502E-3</v>
+      </c>
+      <c r="F111">
+        <v>6.0644546862061851E-3</v>
+      </c>
+      <c r="G111">
+        <v>7.2146536787583114E-3</v>
+      </c>
+      <c r="H111">
+        <v>8.7912391778323957E-3</v>
+      </c>
+      <c r="I111">
+        <v>7.3651349611875876E-3</v>
+      </c>
+      <c r="J111">
+        <v>7.6960003666602782E-3</v>
+      </c>
+      <c r="K111">
+        <v>8.5311126333929219E-3</v>
+      </c>
+      <c r="L111">
+        <v>8.1304927928106223E-3</v>
+      </c>
+      <c r="M111">
+        <v>8.2621686820142093E-3</v>
+      </c>
+      <c r="N111">
+        <v>1.3063997659121151E-2</v>
+      </c>
+      <c r="O111">
+        <v>1.2914008791226519E-2</v>
+      </c>
+      <c r="P111">
+        <v>1.2483193113333631E-2</v>
+      </c>
+      <c r="Q111">
+        <v>1.471718044272287E-2</v>
+      </c>
+      <c r="R111">
+        <v>1.596738982076322E-2</v>
+      </c>
+      <c r="S111">
+        <v>1.5928557324436349E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>129</v>
+      </c>
+      <c r="B112">
+        <v>5.4625157128379315E-4</v>
+      </c>
+      <c r="C112">
+        <v>4.7741974662588761E-4</v>
+      </c>
+      <c r="D112">
+        <v>6.0434277192834157E-4</v>
+      </c>
+      <c r="E112">
+        <v>4.7404706112101261E-4</v>
+      </c>
+      <c r="F112">
+        <v>5.0400434781297716E-4</v>
+      </c>
+      <c r="G112">
+        <v>5.0867514655238307E-4</v>
+      </c>
+      <c r="H112">
+        <v>6.5988738820815774E-4</v>
+      </c>
+      <c r="I112">
+        <v>6.3629501447667208E-4</v>
+      </c>
+      <c r="J112">
+        <v>5.9487137303933604E-4</v>
+      </c>
+      <c r="K112">
+        <v>6.6761437353523884E-4</v>
+      </c>
+      <c r="L112">
+        <v>7.0442722655693021E-4</v>
+      </c>
+      <c r="M112">
+        <v>6.8775947399953312E-4</v>
+      </c>
+      <c r="N112">
+        <v>1.135036464211664E-3</v>
+      </c>
+      <c r="O112">
+        <v>1.0456983338291231E-3</v>
+      </c>
+      <c r="P112">
+        <v>1.1711919054685561E-3</v>
+      </c>
+      <c r="Q112">
+        <v>1.241955291913951E-3</v>
+      </c>
+      <c r="R112">
+        <v>1.478240500317576E-3</v>
+      </c>
+      <c r="S112">
+        <v>1.5431670165025619E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+      <c r="B113">
+        <v>1.143145728668973E-4</v>
+      </c>
+      <c r="C113">
+        <v>7.7217582351932657E-5</v>
+      </c>
+      <c r="D113">
+        <v>8.2808652185807093E-5</v>
+      </c>
+      <c r="E113">
+        <v>7.5652647795902627E-5</v>
+      </c>
+      <c r="F113">
+        <v>7.4876900293444185E-5</v>
+      </c>
+      <c r="G113">
+        <v>1.284485656628661E-4</v>
+      </c>
+      <c r="H113">
+        <v>1.2625299138675829E-4</v>
+      </c>
+      <c r="I113">
+        <v>1.0953783566056971E-4</v>
+      </c>
+      <c r="J113">
+        <v>1.05489422563694E-4</v>
+      </c>
+      <c r="K113">
+        <v>1.289065496134771E-4</v>
+      </c>
+      <c r="L113">
+        <v>1.2275559351192339E-4</v>
+      </c>
+      <c r="M113">
+        <v>1.3725660855120161E-4</v>
+      </c>
+      <c r="N113">
+        <v>2.164514147711673E-4</v>
+      </c>
+      <c r="O113">
+        <v>2.333809984158051E-4</v>
+      </c>
+      <c r="P113">
+        <v>2.3352137466604359E-4</v>
+      </c>
+      <c r="Q113">
+        <v>2.8328164603902162E-4</v>
+      </c>
+      <c r="R113">
+        <v>3.1862816596628358E-4</v>
+      </c>
+      <c r="S113">
+        <v>2.8267715981240951E-4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>131</v>
+      </c>
+      <c r="B114">
+        <v>5.4181758242213369E-5</v>
+      </c>
+      <c r="C114">
+        <v>5.6639314023145687E-5</v>
+      </c>
+      <c r="D114">
+        <v>4.6361194053736227E-5</v>
+      </c>
+      <c r="E114">
+        <v>5.2613952802405123E-5</v>
+      </c>
+      <c r="F114">
+        <v>5.0427609414766443E-5</v>
+      </c>
+      <c r="G114">
+        <v>8.5853002788222675E-5</v>
+      </c>
+      <c r="H114">
+        <v>7.8644220162705329E-5</v>
+      </c>
+      <c r="I114">
+        <v>6.5916639197101821E-5</v>
+      </c>
+      <c r="J114">
+        <v>7.2832015638326608E-5</v>
+      </c>
+      <c r="K114">
+        <v>8.1579363114530089E-5</v>
+      </c>
+      <c r="L114">
+        <v>8.8463802095211942E-5</v>
+      </c>
+      <c r="M114">
+        <v>7.0644028326222684E-5</v>
+      </c>
+      <c r="N114">
+        <v>1.3849918547976831E-4</v>
+      </c>
+      <c r="O114">
+        <v>1.5769491516989069E-4</v>
+      </c>
+      <c r="P114">
+        <v>1.4732464098466639E-4</v>
+      </c>
+      <c r="Q114">
+        <v>1.925872067486655E-4</v>
+      </c>
+      <c r="R114">
+        <v>1.6660263906690599E-4</v>
+      </c>
+      <c r="S114">
+        <v>1.5580417885246729E-4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>132</v>
+      </c>
+      <c r="B115">
+        <v>1.1326665690705689E-3</v>
+      </c>
+      <c r="C115">
+        <v>1.019757750993301E-3</v>
+      </c>
+      <c r="D115">
+        <v>1.0375362738766539E-3</v>
+      </c>
+      <c r="E115">
+        <v>9.9906195723479E-4</v>
+      </c>
+      <c r="F115">
+        <v>1.0387479810507749E-3</v>
+      </c>
+      <c r="G115">
+        <v>1.116355106711436E-3</v>
+      </c>
+      <c r="H115">
+        <v>1.577495159852656E-3</v>
+      </c>
+      <c r="I115">
+        <v>1.3807781664898261E-3</v>
+      </c>
+      <c r="J115">
+        <v>1.4037851105817959E-3</v>
+      </c>
+      <c r="K115">
+        <v>1.7625560400176619E-3</v>
+      </c>
+      <c r="L115">
+        <v>1.7381212545511081E-3</v>
+      </c>
+      <c r="M115">
+        <v>1.657815401135914E-3</v>
+      </c>
+      <c r="N115">
+        <v>2.9572253689159481E-3</v>
+      </c>
+      <c r="O115">
+        <v>2.8690721863427939E-3</v>
+      </c>
+      <c r="P115">
+        <v>2.937099464458933E-3</v>
+      </c>
+      <c r="Q115">
+        <v>3.714974991880551E-3</v>
+      </c>
+      <c r="R115">
+        <v>3.7884285332224002E-3</v>
+      </c>
+      <c r="S115">
+        <v>3.717374288917422E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>133</v>
+      </c>
+      <c r="B116">
+        <v>3.4461813256063319E-4</v>
+      </c>
+      <c r="C116">
+        <v>3.0855336458250648E-4</v>
+      </c>
+      <c r="D116">
+        <v>3.239574441846765E-4</v>
+      </c>
+      <c r="E116">
+        <v>2.8920756296001279E-4</v>
+      </c>
+      <c r="F116">
+        <v>3.1134334829585277E-4</v>
+      </c>
+      <c r="G116">
+        <v>3.2269647782476562E-4</v>
+      </c>
+      <c r="H116">
+        <v>4.1507052824110458E-4</v>
+      </c>
+      <c r="I116">
+        <v>3.4512143651928691E-4</v>
+      </c>
+      <c r="J116">
+        <v>3.6944610864428172E-4</v>
+      </c>
+      <c r="K116">
+        <v>3.9195849043365048E-4</v>
+      </c>
+      <c r="L116">
+        <v>3.9255754840670679E-4</v>
+      </c>
+      <c r="M116">
+        <v>4.2358622553520921E-4</v>
+      </c>
+      <c r="N116">
+        <v>6.1710080206566907E-4</v>
+      </c>
+      <c r="O116">
+        <v>6.2031908757696058E-4</v>
+      </c>
+      <c r="P116">
+        <v>5.9246306841495284E-4</v>
+      </c>
+      <c r="Q116">
+        <v>6.4925162226339543E-4</v>
+      </c>
+      <c r="R116">
+        <v>6.5946078505836148E-4</v>
+      </c>
+      <c r="S116">
+        <v>7.6694081865805197E-4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>134</v>
+      </c>
+      <c r="B117">
+        <v>1.4669756690477439E-4</v>
+      </c>
+      <c r="C117">
+        <v>1.315343693578179E-4</v>
+      </c>
+      <c r="D117">
+        <v>1.290269449638574E-4</v>
+      </c>
+      <c r="E117">
+        <v>1.453750515334986E-4</v>
+      </c>
+      <c r="F117">
+        <v>1.133677673913557E-4</v>
+      </c>
+      <c r="G117">
+        <v>1.71288110198191E-4</v>
+      </c>
+      <c r="H117">
+        <v>3.0066221451343012E-4</v>
+      </c>
+      <c r="I117">
+        <v>2.2059866368693079E-4</v>
+      </c>
+      <c r="J117">
+        <v>2.5985057802253598E-4</v>
+      </c>
+      <c r="K117">
+        <v>2.8309546412934588E-4</v>
+      </c>
+      <c r="L117">
+        <v>2.6663948481997442E-4</v>
+      </c>
+      <c r="M117">
+        <v>2.0620962735515321E-4</v>
+      </c>
+      <c r="N117">
+        <v>5.4740477435639143E-4</v>
+      </c>
+      <c r="O117">
+        <v>5.7242829056759835E-4</v>
+      </c>
+      <c r="P117">
+        <v>5.3934799419127404E-4</v>
+      </c>
+      <c r="Q117">
+        <v>7.1969593652906156E-4</v>
+      </c>
+      <c r="R117">
+        <v>8.8133534813557204E-4</v>
+      </c>
+      <c r="S117">
+        <v>9.4337170427396969E-4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>135</v>
+      </c>
+      <c r="B118">
+        <v>3.3586886913879931E-5</v>
+      </c>
+      <c r="C118">
+        <v>2.9927897191506669E-5</v>
+      </c>
+      <c r="D118">
+        <v>2.6073394668930311E-5</v>
+      </c>
+      <c r="E118">
+        <v>3.1024082285193463E-5</v>
+      </c>
+      <c r="F118">
+        <v>2.9980093292523789E-5</v>
+      </c>
+      <c r="G118">
+        <v>2.9091579389926339E-5</v>
+      </c>
+      <c r="H118">
+        <v>5.1255734698266847E-5</v>
+      </c>
+      <c r="I118">
+        <v>4.6026464795558788E-5</v>
+      </c>
+      <c r="J118">
+        <v>4.0556846601664521E-5</v>
+      </c>
+      <c r="K118">
+        <v>5.0242650453658828E-5</v>
+      </c>
+      <c r="L118">
+        <v>5.2635634509626203E-5</v>
+      </c>
+      <c r="M118">
+        <v>5.554544091376503E-5</v>
+      </c>
+      <c r="N118">
+        <v>8.468338967294795E-5</v>
+      </c>
+      <c r="O118">
+        <v>9.5329597985942266E-5</v>
+      </c>
+      <c r="P118">
+        <v>9.547683253804422E-5</v>
+      </c>
+      <c r="Q118">
+        <v>1.2260061108136311E-4</v>
+      </c>
+      <c r="R118">
+        <v>1.214700098049173E-4</v>
+      </c>
+      <c r="S118">
+        <v>1.195122512838769E-4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>136</v>
+      </c>
+      <c r="B119">
+        <v>8.3745118924219994E-4</v>
+      </c>
+      <c r="C119">
+        <v>7.0570245688831353E-4</v>
+      </c>
+      <c r="D119">
+        <v>7.7604143245975322E-4</v>
+      </c>
+      <c r="E119">
+        <v>8.8544740320338044E-4</v>
+      </c>
+      <c r="F119">
+        <v>9.3850910902534162E-4</v>
+      </c>
+      <c r="G119">
+        <v>9.0413653149136821E-4</v>
+      </c>
+      <c r="H119">
+        <v>1.5792050107242021E-3</v>
+      </c>
+      <c r="I119">
+        <v>1.3480837001302269E-3</v>
+      </c>
+      <c r="J119">
+        <v>1.4087102998618919E-3</v>
+      </c>
+      <c r="K119">
+        <v>1.6685970865115351E-3</v>
+      </c>
+      <c r="L119">
+        <v>1.5338446573517561E-3</v>
+      </c>
+      <c r="M119">
+        <v>1.706667776595202E-3</v>
+      </c>
+      <c r="N119">
+        <v>2.4851023134130892E-3</v>
+      </c>
+      <c r="O119">
+        <v>2.623259402998681E-3</v>
+      </c>
+      <c r="P119">
+        <v>2.269209269573315E-3</v>
+      </c>
+      <c r="Q119">
+        <v>2.8327861472374079E-3</v>
+      </c>
+      <c r="R119">
+        <v>2.8254592718456009E-3</v>
+      </c>
+      <c r="S119">
+        <v>2.9021723199663531E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>137</v>
+      </c>
+      <c r="B120">
+        <v>8.2944359410616633E-2</v>
+      </c>
+      <c r="C120">
+        <v>7.2447150714786829E-2</v>
+      </c>
+      <c r="D120">
+        <v>7.6718159585829476E-2</v>
+      </c>
+      <c r="E120">
+        <v>7.3021671946587846E-2</v>
+      </c>
+      <c r="F120">
+        <v>7.399650220444437E-2</v>
+      </c>
+      <c r="G120">
+        <v>0.10521702638307109</v>
+      </c>
+      <c r="H120">
+        <v>0.12800732064373921</v>
+      </c>
+      <c r="I120">
+        <v>0.1078033815440137</v>
+      </c>
+      <c r="J120">
+        <v>0.10569348083240961</v>
+      </c>
+      <c r="K120">
+        <v>0.15254218592106911</v>
+      </c>
+      <c r="L120">
+        <v>0.1478156520677521</v>
+      </c>
+      <c r="M120">
+        <v>0.13727698121645049</v>
+      </c>
+      <c r="N120">
+        <v>0.36315573183213362</v>
+      </c>
+      <c r="O120">
+        <v>0.36227284678400451</v>
+      </c>
+      <c r="P120">
+        <v>0.33669209652558141</v>
+      </c>
+      <c r="Q120">
+        <v>0.54447083120770301</v>
+      </c>
+      <c r="R120">
+        <v>0.57592399260549165</v>
+      </c>
+      <c r="S120">
+        <v>0.56458439642178349</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>138</v>
+      </c>
+      <c r="B121">
+        <v>1.225452987870022E-5</v>
+      </c>
+      <c r="C121">
+        <v>1.1190804218148989E-5</v>
+      </c>
+      <c r="D121">
+        <v>1.2145759568192711E-5</v>
+      </c>
+      <c r="E121">
+        <v>9.2446681868973088E-6</v>
+      </c>
+      <c r="F121">
+        <v>1.010052961079917E-5</v>
+      </c>
+      <c r="G121">
+        <v>8.6347898100798769E-6</v>
+      </c>
+      <c r="H121">
+        <v>1.090745231513085E-5</v>
+      </c>
+      <c r="I121">
+        <v>9.286063710145072E-6</v>
+      </c>
+      <c r="J121">
+        <v>9.5493896814119855E-6</v>
+      </c>
+      <c r="K121">
+        <v>1.094977697136307E-5</v>
+      </c>
+      <c r="L121">
+        <v>1.047187094180236E-5</v>
+      </c>
+      <c r="M121">
+        <v>1.092816160895563E-5</v>
+      </c>
+      <c r="N121">
+        <v>1.555856698893301E-5</v>
+      </c>
+      <c r="O121">
+        <v>1.358268738093174E-5</v>
+      </c>
+      <c r="P121">
+        <v>1.202007901535453E-5</v>
+      </c>
+      <c r="Q121">
+        <v>1.3936332460881939E-5</v>
+      </c>
+      <c r="R121">
+        <v>1.2606931902799521E-5</v>
+      </c>
+      <c r="S121">
+        <v>1.829730388315628E-5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>139</v>
+      </c>
+      <c r="B122">
+        <v>1.00288895246451E-4</v>
+      </c>
+      <c r="C122">
+        <v>1.0057660957142861E-4</v>
+      </c>
+      <c r="D122">
+        <v>9.683241931202645E-5</v>
+      </c>
+      <c r="E122">
+        <v>9.3369426711524236E-5</v>
+      </c>
+      <c r="F122">
+        <v>9.7003817776785816E-5</v>
+      </c>
+      <c r="G122">
+        <v>6.4441754358427519E-5</v>
+      </c>
+      <c r="H122">
+        <v>1.208756126330559E-4</v>
+      </c>
+      <c r="I122">
+        <v>1.1144330251123719E-4</v>
+      </c>
+      <c r="J122">
+        <v>1.201324446959018E-4</v>
+      </c>
+      <c r="K122">
+        <v>1.254752240059063E-4</v>
+      </c>
+      <c r="L122">
+        <v>1.1330824368197771E-4</v>
+      </c>
+      <c r="M122">
+        <v>1.4145808641273221E-4</v>
+      </c>
+      <c r="N122">
+        <v>1.6345995403153749E-4</v>
+      </c>
+      <c r="O122">
+        <v>1.7725070005039981E-4</v>
+      </c>
+      <c r="P122">
+        <v>1.2907227195833811E-4</v>
+      </c>
+      <c r="Q122">
+        <v>1.607574998805713E-4</v>
+      </c>
+      <c r="R122">
+        <v>1.4319215446883011E-4</v>
+      </c>
+      <c r="S122">
+        <v>1.7430741134038551E-4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>140</v>
+      </c>
+      <c r="B123">
+        <v>3.715124763617004E-3</v>
+      </c>
+      <c r="C123">
+        <v>3.4332977281511662E-3</v>
+      </c>
+      <c r="D123">
+        <v>3.533748019788137E-3</v>
+      </c>
+      <c r="E123">
+        <v>2.9488225269910899E-3</v>
+      </c>
+      <c r="F123">
+        <v>3.054973716370517E-3</v>
+      </c>
+      <c r="G123">
+        <v>3.577567405704181E-3</v>
+      </c>
+      <c r="H123">
+        <v>4.7374359516524581E-3</v>
+      </c>
+      <c r="I123">
+        <v>4.2137651238308843E-3</v>
+      </c>
+      <c r="J123">
+        <v>4.1917377740844806E-3</v>
+      </c>
+      <c r="K123">
+        <v>5.0151834977322333E-3</v>
+      </c>
+      <c r="L123">
+        <v>4.4800072756396806E-3</v>
+      </c>
+      <c r="M123">
+        <v>4.9096549297802201E-3</v>
+      </c>
+      <c r="N123">
+        <v>8.1996273259348548E-3</v>
+      </c>
+      <c r="O123">
+        <v>8.4526976008969766E-3</v>
+      </c>
+      <c r="P123">
+        <v>9.3836362656202228E-3</v>
+      </c>
+      <c r="Q123">
+        <v>1.070648995193655E-2</v>
+      </c>
+      <c r="R123">
+        <v>1.2663049044324149E-2</v>
+      </c>
+      <c r="S123">
+        <v>1.162691771050473E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>141</v>
+      </c>
+      <c r="B124">
+        <v>1.781397279129719E-3</v>
+      </c>
+      <c r="C124">
+        <v>1.531857366799119E-3</v>
+      </c>
+      <c r="D124">
+        <v>1.573491160544317E-3</v>
+      </c>
+      <c r="E124">
+        <v>1.5335753900190851E-3</v>
+      </c>
+      <c r="F124">
+        <v>1.729816681530589E-3</v>
+      </c>
+      <c r="G124">
+        <v>1.516743856500941E-3</v>
+      </c>
+      <c r="H124">
+        <v>2.0953959079946598E-3</v>
+      </c>
+      <c r="I124">
+        <v>1.7811824527973229E-3</v>
+      </c>
+      <c r="J124">
+        <v>2.0975738349048529E-3</v>
+      </c>
+      <c r="K124">
+        <v>2.227931083909796E-3</v>
+      </c>
+      <c r="L124">
+        <v>2.34336773060925E-3</v>
+      </c>
+      <c r="M124">
+        <v>2.344325229694611E-3</v>
+      </c>
+      <c r="N124">
+        <v>3.602182383823798E-3</v>
+      </c>
+      <c r="O124">
+        <v>3.846416694744855E-3</v>
+      </c>
+      <c r="P124">
+        <v>2.9741458767430801E-3</v>
+      </c>
+      <c r="Q124">
+        <v>3.818410215955781E-3</v>
+      </c>
+      <c r="R124">
+        <v>3.737322428167282E-3</v>
+      </c>
+      <c r="S124">
+        <v>3.679845014185681E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>142</v>
+      </c>
+      <c r="B125">
+        <v>3.9653704576772314E-3</v>
+      </c>
+      <c r="C125">
+        <v>3.64061851595127E-3</v>
+      </c>
+      <c r="D125">
+        <v>3.3349639841934349E-3</v>
+      </c>
+      <c r="E125">
+        <v>3.582132138181014E-3</v>
+      </c>
+      <c r="F125">
+        <v>3.5287913816990481E-3</v>
+      </c>
+      <c r="G125">
+        <v>2.5281956614552148E-3</v>
+      </c>
+      <c r="H125">
+        <v>5.3025729909860816E-3</v>
+      </c>
+      <c r="I125">
+        <v>4.2171268439820031E-3</v>
+      </c>
+      <c r="J125">
+        <v>4.8235222905952599E-3</v>
+      </c>
+      <c r="K125">
+        <v>5.4117992577943893E-3</v>
+      </c>
+      <c r="L125">
+        <v>4.8884200281058814E-3</v>
+      </c>
+      <c r="M125">
+        <v>5.347422089636877E-3</v>
+      </c>
+      <c r="N125">
+        <v>7.7232296122019643E-3</v>
+      </c>
+      <c r="O125">
+        <v>8.0975238015342007E-3</v>
+      </c>
+      <c r="P125">
+        <v>7.8430687931750794E-3</v>
+      </c>
+      <c r="Q125">
+        <v>8.4854052303741431E-3</v>
+      </c>
+      <c r="R125">
+        <v>9.0471237903183253E-3</v>
+      </c>
+      <c r="S125">
+        <v>1.085191680118776E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>143</v>
+      </c>
+      <c r="B126">
+        <v>9.3256513230090306E-5</v>
+      </c>
+      <c r="C126">
+        <v>7.61832913938599E-5</v>
+      </c>
+      <c r="D126">
+        <v>6.9848823146390635E-5</v>
+      </c>
+      <c r="E126">
+        <v>8.0993548072392146E-5</v>
+      </c>
+      <c r="F126">
+        <v>8.3661115824362699E-5</v>
+      </c>
+      <c r="G126">
+        <v>8.7002798628372721E-5</v>
+      </c>
+      <c r="H126">
+        <v>1.2337935715819851E-4</v>
+      </c>
+      <c r="I126">
+        <v>1.15975608572482E-4</v>
+      </c>
+      <c r="J126">
+        <v>1.061844388401645E-4</v>
+      </c>
+      <c r="K126">
+        <v>1.317374609259157E-4</v>
+      </c>
+      <c r="L126">
+        <v>1.2978294102927791E-4</v>
+      </c>
+      <c r="M126">
+        <v>1.2894445299043469E-4</v>
+      </c>
+      <c r="N126">
+        <v>2.3071002775497539E-4</v>
+      </c>
+      <c r="O126">
+        <v>1.442337197691567E-4</v>
+      </c>
+      <c r="P126">
+        <v>2.3128749303008651E-4</v>
+      </c>
+      <c r="Q126">
+        <v>2.2228428728073319E-4</v>
+      </c>
+      <c r="R126">
+        <v>2.9825640153162788E-4</v>
+      </c>
+      <c r="S126">
+        <v>3.204777730060202E-4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>144</v>
+      </c>
+      <c r="B127">
+        <v>3.341776578469771E-4</v>
+      </c>
+      <c r="C127">
+        <v>2.947399868782469E-4</v>
+      </c>
+      <c r="D127">
+        <v>2.587802709785501E-4</v>
+      </c>
+      <c r="E127">
+        <v>3.1912286249740799E-4</v>
+      </c>
+      <c r="F127">
+        <v>3.2282984927882821E-4</v>
+      </c>
+      <c r="G127">
+        <v>3.0975591307494063E-4</v>
+      </c>
+      <c r="H127">
+        <v>5.3291650628100012E-4</v>
+      </c>
+      <c r="I127">
+        <v>4.4788975168097358E-4</v>
+      </c>
+      <c r="J127">
+        <v>4.8085078307283651E-4</v>
+      </c>
+      <c r="K127">
+        <v>5.7664765229441793E-4</v>
+      </c>
+      <c r="L127">
+        <v>5.4771584171010184E-4</v>
+      </c>
+      <c r="M127">
+        <v>5.624510555085067E-4</v>
+      </c>
+      <c r="N127">
+        <v>1.0315054455993849E-3</v>
+      </c>
+      <c r="O127">
+        <v>1.0339171562569419E-3</v>
+      </c>
+      <c r="P127">
+        <v>1.1399745690002089E-3</v>
+      </c>
+      <c r="Q127">
+        <v>1.354100336958297E-3</v>
+      </c>
+      <c r="R127">
+        <v>1.4324235789407341E-3</v>
+      </c>
+      <c r="S127">
+        <v>1.441582478889107E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>145</v>
+      </c>
+      <c r="B128">
+        <v>8.6334080652937268E-4</v>
+      </c>
+      <c r="C128">
+        <v>8.1069366298877578E-4</v>
+      </c>
+      <c r="D128">
+        <v>7.7854036485493867E-4</v>
+      </c>
+      <c r="E128">
+        <v>7.3671762096233343E-4</v>
+      </c>
+      <c r="F128">
+        <v>7.9498612842932091E-4</v>
+      </c>
+      <c r="G128">
+        <v>5.7881219597834591E-4</v>
+      </c>
+      <c r="H128">
+        <v>1.0906628046981951E-3</v>
+      </c>
+      <c r="I128">
+        <v>8.4395562000550458E-4</v>
+      </c>
+      <c r="J128">
+        <v>9.6372697027518152E-4</v>
+      </c>
+      <c r="K128">
+        <v>1.0431868858570149E-3</v>
+      </c>
+      <c r="L128">
+        <v>9.6947685859524963E-4</v>
+      </c>
+      <c r="M128">
+        <v>1.034777643129529E-3</v>
+      </c>
+      <c r="N128">
+        <v>1.5123083351784811E-3</v>
+      </c>
+      <c r="O128">
+        <v>1.4308121536250891E-3</v>
+      </c>
+      <c r="P128">
+        <v>1.55835384566596E-3</v>
+      </c>
+      <c r="Q128">
+        <v>1.71836626738802E-3</v>
+      </c>
+      <c r="R128">
+        <v>1.864406120364269E-3</v>
+      </c>
+      <c r="S128">
+        <v>1.6657749589537581E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>146</v>
+      </c>
+      <c r="B129">
+        <v>2.8366719883606088E-4</v>
+      </c>
+      <c r="C129">
+        <v>2.3643553986381729E-4</v>
+      </c>
+      <c r="D129">
+        <v>2.384822229516347E-4</v>
+      </c>
+      <c r="E129">
+        <v>2.1546268793467001E-4</v>
+      </c>
+      <c r="F129">
+        <v>2.1671037768236669E-4</v>
+      </c>
+      <c r="G129">
+        <v>2.843712783910105E-4</v>
+      </c>
+      <c r="H129">
+        <v>3.7811425383149953E-4</v>
+      </c>
+      <c r="I129">
+        <v>3.2353933199825242E-4</v>
+      </c>
+      <c r="J129">
+        <v>3.1563637278111723E-4</v>
+      </c>
+      <c r="K129">
+        <v>3.7652013963950681E-4</v>
+      </c>
+      <c r="L129">
+        <v>3.5421305586305141E-4</v>
+      </c>
+      <c r="M129">
+        <v>3.6354522667744982E-4</v>
+      </c>
+      <c r="N129">
+        <v>6.1404763769060252E-4</v>
+      </c>
+      <c r="O129">
+        <v>6.1039480642264545E-4</v>
+      </c>
+      <c r="P129">
+        <v>6.7601582056811581E-4</v>
+      </c>
+      <c r="Q129">
+        <v>8.6611381384340842E-4</v>
+      </c>
+      <c r="R129">
+        <v>8.7634014497180786E-4</v>
+      </c>
+      <c r="S129">
+        <v>8.2951745767352418E-4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>147</v>
+      </c>
+      <c r="B130">
+        <v>2.2782618340639051E-4</v>
+      </c>
+      <c r="C130">
+        <v>2.10385091236766E-4</v>
+      </c>
+      <c r="D130">
+        <v>2.034279880858614E-4</v>
+      </c>
+      <c r="E130">
+        <v>1.8378951314697149E-4</v>
+      </c>
+      <c r="F130">
+        <v>1.8895676616462959E-4</v>
+      </c>
+      <c r="G130">
+        <v>1.811583334806758E-4</v>
+      </c>
+      <c r="H130">
+        <v>2.828623328330711E-4</v>
+      </c>
+      <c r="I130">
+        <v>2.4223485128856619E-4</v>
+      </c>
+      <c r="J130">
+        <v>2.6420832653212902E-4</v>
+      </c>
+      <c r="K130">
+        <v>2.6485965353100421E-4</v>
+      </c>
+      <c r="L130">
+        <v>2.6742839344641298E-4</v>
+      </c>
+      <c r="M130">
+        <v>2.8323516125040128E-4</v>
+      </c>
+      <c r="N130">
+        <v>5.0321800956595452E-4</v>
+      </c>
+      <c r="O130">
+        <v>5.1433328136760929E-4</v>
+      </c>
+      <c r="P130">
+        <v>4.8150630074088129E-4</v>
+      </c>
+      <c r="Q130">
+        <v>6.1950557945073036E-4</v>
+      </c>
+      <c r="R130">
+        <v>5.930251422931644E-4</v>
+      </c>
+      <c r="S130">
+        <v>6.1818300834059331E-4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>148</v>
+      </c>
+      <c r="B131">
+        <v>4.0982827154034467E-4</v>
+      </c>
+      <c r="C131">
+        <v>3.719655846756468E-4</v>
+      </c>
+      <c r="D131">
+        <v>3.9116757952542872E-4</v>
+      </c>
+      <c r="E131">
+        <v>3.877323243535501E-4</v>
+      </c>
+      <c r="F131">
+        <v>4.0713515636497439E-4</v>
+      </c>
+      <c r="G131">
+        <v>3.9545445005425309E-4</v>
+      </c>
+      <c r="H131">
+        <v>5.9704260263382695E-4</v>
+      </c>
+      <c r="I131">
+        <v>5.0769603944311932E-4</v>
+      </c>
+      <c r="J131">
+        <v>5.2261028253934572E-4</v>
+      </c>
+      <c r="K131">
+        <v>6.4970510651338902E-4</v>
+      </c>
+      <c r="L131">
+        <v>6.3318566303486006E-4</v>
+      </c>
+      <c r="M131">
+        <v>6.6533814055127019E-4</v>
+      </c>
+      <c r="N131">
+        <v>1.0498498945965449E-3</v>
+      </c>
+      <c r="O131">
+        <v>1.027326335436446E-3</v>
+      </c>
+      <c r="P131">
+        <v>1.04423979471078E-3</v>
+      </c>
+      <c r="Q131">
+        <v>1.2790036257961999E-3</v>
+      </c>
+      <c r="R131">
+        <v>1.236341242380846E-3</v>
+      </c>
+      <c r="S131">
+        <v>1.338845458055433E-3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>149</v>
+      </c>
+      <c r="B132">
+        <v>2.7811718787483871E-4</v>
+      </c>
+      <c r="C132">
+        <v>2.3092684029839099E-4</v>
+      </c>
+      <c r="D132">
+        <v>2.226626465898547E-4</v>
+      </c>
+      <c r="E132">
+        <v>2.378977726442645E-4</v>
+      </c>
+      <c r="F132">
+        <v>2.4740342975893649E-4</v>
+      </c>
+      <c r="G132">
+        <v>2.5932643015439349E-4</v>
+      </c>
+      <c r="H132">
+        <v>3.8333254088729839E-4</v>
+      </c>
+      <c r="I132">
+        <v>3.17217455294705E-4</v>
+      </c>
+      <c r="J132">
+        <v>3.2461456573767999E-4</v>
+      </c>
+      <c r="K132">
+        <v>3.8946807384256381E-4</v>
+      </c>
+      <c r="L132">
+        <v>3.7114999924135452E-4</v>
+      </c>
+      <c r="M132">
+        <v>3.8728431391114361E-4</v>
+      </c>
+      <c r="N132">
+        <v>6.0761358111364897E-4</v>
+      </c>
+      <c r="O132">
+        <v>6.2770661717196654E-4</v>
+      </c>
+      <c r="P132">
+        <v>6.321351751211766E-4</v>
+      </c>
+      <c r="Q132">
+        <v>7.4063363906825544E-4</v>
+      </c>
+      <c r="R132">
+        <v>7.8909017912577562E-4</v>
+      </c>
+      <c r="S132">
+        <v>7.755771346502321E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>150</v>
+      </c>
+      <c r="B133">
+        <v>4.2488003348059378E-3</v>
+      </c>
+      <c r="C133">
+        <v>3.8157286279405728E-3</v>
+      </c>
+      <c r="D133">
+        <v>4.5304460310715104E-3</v>
+      </c>
+      <c r="E133">
+        <v>4.9464115913869927E-3</v>
+      </c>
+      <c r="F133">
+        <v>5.3668168748338971E-3</v>
+      </c>
+      <c r="G133">
+        <v>5.1074043693214843E-3</v>
+      </c>
+      <c r="H133">
+        <v>8.4177933335237865E-3</v>
+      </c>
+      <c r="I133">
+        <v>7.2891897826938747E-3</v>
+      </c>
+      <c r="J133">
+        <v>7.044396425886384E-3</v>
+      </c>
+      <c r="K133">
+        <v>9.2440101884671971E-3</v>
+      </c>
+      <c r="L133">
+        <v>9.6894820600032256E-3</v>
+      </c>
+      <c r="M133">
+        <v>8.8469140229833192E-3</v>
+      </c>
+      <c r="N133">
+        <v>2.0566362707440139E-2</v>
+      </c>
+      <c r="O133">
+        <v>1.9355072415818471E-2</v>
+      </c>
+      <c r="P133">
+        <v>1.9216683831520261E-2</v>
+      </c>
+      <c r="Q133">
+        <v>2.8675846267073681E-2</v>
+      </c>
+      <c r="R133">
+        <v>2.8975871165406241E-2</v>
+      </c>
+      <c r="S133">
+        <v>2.8980314402255011E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>151</v>
+      </c>
+      <c r="B134">
+        <v>1.173979354843232E-5</v>
+      </c>
+      <c r="C134">
+        <v>9.4785458356402564E-6</v>
+      </c>
+      <c r="D134">
+        <v>1.2294893513667211E-5</v>
+      </c>
+      <c r="E134">
+        <v>1.0448607894307139E-5</v>
+      </c>
+      <c r="F134">
+        <v>1.104254080964704E-5</v>
+      </c>
+      <c r="G134">
+        <v>1.454756455273593E-5</v>
+      </c>
+      <c r="H134">
+        <v>1.3321943724241499E-5</v>
+      </c>
+      <c r="I134">
+        <v>1.179705885810155E-5</v>
+      </c>
+      <c r="J134">
+        <v>9.5778474159045174E-6</v>
+      </c>
+      <c r="K134">
+        <v>1.4632779914639E-5</v>
+      </c>
+      <c r="L134">
+        <v>1.409286831441157E-5</v>
+      </c>
+      <c r="M134">
+        <v>1.4497125769451489E-5</v>
+      </c>
+      <c r="N134">
+        <v>1.2638121297079811E-5</v>
+      </c>
+      <c r="O134">
+        <v>1.870845080668713E-5</v>
+      </c>
+      <c r="P134">
+        <v>1.436072701599588E-5</v>
+      </c>
+      <c r="Q134">
+        <v>1.8277526586591489E-5</v>
+      </c>
+      <c r="R134">
+        <v>1.5439149678209059E-5</v>
+      </c>
+      <c r="S134">
+        <v>2.074225799857105E-5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>152</v>
+      </c>
+      <c r="B135">
+        <v>1.092823207897459E-4</v>
+      </c>
+      <c r="C135">
+        <v>1.026220412002501E-4</v>
+      </c>
+      <c r="D135">
+        <v>9.7979217585098991E-5</v>
+      </c>
+      <c r="E135">
+        <v>6.8777962204096668E-5</v>
+      </c>
+      <c r="F135">
+        <v>7.8202724080188489E-5</v>
+      </c>
+      <c r="G135">
+        <v>7.7226651678441254E-5</v>
+      </c>
+      <c r="H135">
+        <v>1.0451994260091591E-4</v>
+      </c>
+      <c r="I135">
+        <v>9.0034864213575023E-5</v>
+      </c>
+      <c r="J135">
+        <v>9.0229223877313057E-5</v>
+      </c>
+      <c r="K135">
+        <v>1.1850089579105039E-4</v>
+      </c>
+      <c r="L135">
+        <v>1.246362068096556E-4</v>
+      </c>
+      <c r="M135">
+        <v>1.2583806094050969E-4</v>
+      </c>
+      <c r="N135">
+        <v>2.211602638222907E-4</v>
+      </c>
+      <c r="O135">
+        <v>2.379470581590378E-4</v>
+      </c>
+      <c r="P135">
+        <v>2.3696604704452029E-4</v>
+      </c>
+      <c r="Q135">
+        <v>2.9081113724047103E-4</v>
+      </c>
+      <c r="R135">
+        <v>2.8681331340860009E-4</v>
+      </c>
+      <c r="S135">
+        <v>3.034399261225309E-4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>153</v>
+      </c>
+      <c r="B136">
+        <v>4.4115170747673821E-6</v>
+      </c>
+      <c r="C136">
+        <v>4.3404155232204586E-6</v>
+      </c>
+      <c r="D136">
+        <v>4.5876429270864858E-6</v>
+      </c>
+      <c r="E136">
+        <v>4.4296199552101222E-6</v>
+      </c>
+      <c r="F136">
+        <v>4.7980169049193246E-6</v>
+      </c>
+      <c r="G136">
+        <v>3.6983978692801318E-6</v>
+      </c>
+      <c r="H136">
+        <v>5.5057538739818744E-6</v>
+      </c>
+      <c r="I136">
+        <v>4.7002858489251091E-6</v>
+      </c>
+      <c r="J136">
+        <v>5.6630551204188721E-6</v>
+      </c>
+      <c r="K136">
+        <v>6.6174324548547009E-6</v>
+      </c>
+      <c r="L136">
+        <v>6.75146802114764E-6</v>
+      </c>
+      <c r="M136">
+        <v>6.6562768019499654E-6</v>
+      </c>
+      <c r="N136">
+        <v>6.7283630309850271E-6</v>
+      </c>
+      <c r="O136">
+        <v>6.8037930946803899E-6</v>
+      </c>
+      <c r="P136">
+        <v>6.0484904861765727E-6</v>
+      </c>
+      <c r="Q136">
+        <v>7.0706808299156677E-6</v>
+      </c>
+      <c r="R136">
+        <v>6.455003576773288E-6</v>
+      </c>
+      <c r="S136">
+        <v>6.9920219300034541E-6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>154</v>
+      </c>
+      <c r="B137">
+        <v>6.6180208424452386E-5</v>
+      </c>
+      <c r="C137">
+        <v>5.9878976068953918E-5</v>
+      </c>
+      <c r="D137">
+        <v>7.5927921959235945E-5</v>
+      </c>
+      <c r="E137">
+        <v>9.0677983181120596E-5</v>
+      </c>
+      <c r="F137">
+        <v>9.2639803895478917E-5</v>
+      </c>
+      <c r="G137">
+        <v>9.2532815283591846E-5</v>
+      </c>
+      <c r="H137">
+        <v>1.1656425050547191E-4</v>
+      </c>
+      <c r="I137">
+        <v>8.3991939146263675E-5</v>
+      </c>
+      <c r="J137">
+        <v>1.1280281226917639E-4</v>
+      </c>
+      <c r="K137">
+        <v>1.364520097070643E-4</v>
+      </c>
+      <c r="L137">
+        <v>1.4016814165093949E-4</v>
+      </c>
+      <c r="M137">
+        <v>1.3365763004376859E-4</v>
+      </c>
+      <c r="N137">
+        <v>1.8188465171130319E-4</v>
+      </c>
+      <c r="O137">
+        <v>1.871961942871278E-4</v>
+      </c>
+      <c r="P137">
+        <v>1.5316276848694591E-4</v>
+      </c>
+      <c r="Q137">
+        <v>1.7787931320195949E-4</v>
+      </c>
+      <c r="R137">
+        <v>1.665894922312595E-4</v>
+      </c>
+      <c r="S137">
+        <v>1.7308683112520271E-4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>155</v>
+      </c>
+      <c r="B138">
+        <v>3.9841403854096622E-5</v>
+      </c>
+      <c r="C138">
+        <v>3.7159613330394313E-5</v>
+      </c>
+      <c r="D138">
+        <v>2.9174197402952419E-5</v>
+      </c>
+      <c r="E138">
+        <v>3.7628486993437512E-5</v>
+      </c>
+      <c r="F138">
+        <v>3.9242750581337529E-5</v>
+      </c>
+      <c r="G138">
+        <v>3.2884047543355401E-5</v>
+      </c>
+      <c r="H138">
+        <v>5.6151260116449483E-5</v>
+      </c>
+      <c r="I138">
+        <v>4.201461271103691E-5</v>
+      </c>
+      <c r="J138">
+        <v>4.8684079877076792E-5</v>
+      </c>
+      <c r="K138">
+        <v>5.7265250215326501E-5</v>
+      </c>
+      <c r="L138">
+        <v>4.1884885939222212E-5</v>
+      </c>
+      <c r="M138">
+        <v>5.4248597358138133E-5</v>
+      </c>
+      <c r="N138">
+        <v>8.5782135191215969E-5</v>
+      </c>
+      <c r="O138">
+        <v>6.4576942834703539E-5</v>
+      </c>
+      <c r="P138">
+        <v>9.0235529624522508E-5</v>
+      </c>
+      <c r="Q138">
+        <v>6.844233423362837E-5</v>
+      </c>
+      <c r="R138">
+        <v>1.00618567093765E-4</v>
+      </c>
+      <c r="S138">
+        <v>9.1515998322152858E-5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>156</v>
+      </c>
+      <c r="B139">
+        <v>2.7690786211844259E-5</v>
+      </c>
+      <c r="C139">
+        <v>2.6811936429250411E-5</v>
+      </c>
+      <c r="D139">
+        <v>1.9263022092519469E-5</v>
+      </c>
+      <c r="E139">
+        <v>2.616333229675459E-5</v>
+      </c>
+      <c r="F139">
+        <v>2.827222748311832E-5</v>
+      </c>
+      <c r="G139">
+        <v>2.7021572002865999E-5</v>
+      </c>
+      <c r="H139">
+        <v>4.0850956226853013E-5</v>
+      </c>
+      <c r="I139">
+        <v>3.1647021321238392E-5</v>
+      </c>
+      <c r="J139">
+        <v>3.464555468065137E-5</v>
+      </c>
+      <c r="K139">
+        <v>3.9724249830173931E-5</v>
+      </c>
+      <c r="L139">
+        <v>2.912079709059454E-5</v>
+      </c>
+      <c r="M139">
+        <v>4.0592521269578392E-5</v>
+      </c>
+      <c r="N139">
+        <v>6.8802203464586186E-5</v>
+      </c>
+      <c r="O139">
+        <v>5.0832786307435793E-5</v>
+      </c>
+      <c r="P139">
+        <v>7.0539631198708626E-5</v>
+      </c>
+      <c r="Q139">
+        <v>5.2359140519580473E-5</v>
+      </c>
+      <c r="R139">
+        <v>7.7885557788469334E-5</v>
+      </c>
+      <c r="S139">
+        <v>7.8296052402549758E-5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>157</v>
+      </c>
+      <c r="B140">
+        <v>4.4426095450382032E-5</v>
+      </c>
+      <c r="C140">
+        <v>4.049293762888767E-5</v>
+      </c>
+      <c r="D140">
+        <v>4.1630068378187897E-5</v>
+      </c>
+      <c r="E140">
+        <v>3.9465910647490652E-5</v>
+      </c>
+      <c r="F140">
+        <v>4.4054861953987802E-5</v>
+      </c>
+      <c r="G140">
+        <v>3.0658791583254772E-5</v>
+      </c>
+      <c r="H140">
+        <v>5.2426341425023198E-5</v>
+      </c>
+      <c r="I140">
+        <v>4.094135358458079E-5</v>
+      </c>
+      <c r="J140">
+        <v>4.4969047348937158E-5</v>
+      </c>
+      <c r="K140">
+        <v>5.0364201016834682E-5</v>
+      </c>
+      <c r="L140">
+        <v>4.937816962250103E-5</v>
+      </c>
+      <c r="M140">
+        <v>5.3672963740818348E-5</v>
+      </c>
+      <c r="N140">
+        <v>7.5924682841530038E-5</v>
+      </c>
+      <c r="O140">
+        <v>7.4298781387981065E-5</v>
+      </c>
+      <c r="P140">
+        <v>7.5153261263979571E-5</v>
+      </c>
+      <c r="Q140">
+        <v>8.5516143744751087E-5</v>
+      </c>
+      <c r="R140">
+        <v>8.819103225592033E-5</v>
+      </c>
+      <c r="S140">
+        <v>7.9341975933633127E-5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A140" xr:uid="{F6DD68D5-A363-574C-A4F1-9F5610A100A3}">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter val="*mito*"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6BC16A1-B539-D349-B8D2-1AE75E54CCEA}">
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.52168090071337803</v>
+      </c>
+      <c r="C2">
+        <v>2.5286537114969761E-2</v>
+      </c>
+      <c r="D2">
+        <v>3.9281415525559527E-2</v>
+      </c>
+      <c r="E2">
+        <v>1.8742438631994419E-2</v>
+      </c>
+      <c r="F2">
+        <v>2.4991808429704141E-2</v>
+      </c>
+      <c r="G2">
+        <v>4.5385002377759012E-2</v>
+      </c>
+      <c r="H2">
+        <v>1.486532462203562E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0.47696846799627352</v>
+      </c>
+      <c r="C3">
+        <v>2.4886146757268642E-2</v>
+      </c>
+      <c r="D3">
+        <v>3.4902588588395587E-2</v>
+      </c>
+      <c r="E3">
+        <v>1.5865953704056301E-2</v>
+      </c>
+      <c r="F3">
+        <v>2.2243922628609889E-2</v>
+      </c>
+      <c r="G3">
+        <v>4.3389610153184932E-2</v>
+      </c>
+      <c r="H3">
+        <v>1.377593145533877E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0.49557603499405062</v>
+      </c>
+      <c r="C4">
+        <v>2.8513908403849861E-2</v>
+      </c>
+      <c r="D4">
+        <v>4.3190325053759311E-2</v>
+      </c>
+      <c r="E4">
+        <v>1.7482081766865259E-2</v>
+      </c>
+      <c r="F4">
+        <v>2.3071353863392301E-2</v>
+      </c>
+      <c r="G4">
+        <v>4.3306865200237903E-2</v>
+      </c>
+      <c r="H4">
+        <v>1.369372478776535E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0.39311051923590351</v>
+      </c>
+      <c r="C5">
+        <v>1.8644122851725731E-2</v>
+      </c>
+      <c r="D5">
+        <v>3.6433905190692562E-2</v>
+      </c>
+      <c r="E5">
+        <v>1.531651260788678E-2</v>
+      </c>
+      <c r="F5">
+        <v>2.6120513226405798E-2</v>
+      </c>
+      <c r="G5">
+        <v>2.3553116262926391E-2</v>
+      </c>
+      <c r="H5">
+        <v>1.5429389922227871E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0.41260246092852981</v>
+      </c>
+      <c r="C6">
+        <v>2.153176724016596E-2</v>
+      </c>
+      <c r="D6">
+        <v>3.7770871683273782E-2</v>
+      </c>
+      <c r="E6">
+        <v>1.621275922863314E-2</v>
+      </c>
+      <c r="F6">
+        <v>2.7326699989203951E-2</v>
+      </c>
+      <c r="G6">
+        <v>2.5415275794820971E-2</v>
+      </c>
+      <c r="H6">
+        <v>1.644339608186677E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>0.57716777966309829</v>
+      </c>
+      <c r="C7">
+        <v>2.6855518822424249E-2</v>
+      </c>
+      <c r="D7">
+        <v>4.5847393592958592E-2</v>
+      </c>
+      <c r="E7">
+        <v>2.471438054811493E-2</v>
+      </c>
+      <c r="F7">
+        <v>2.7882369798495839E-2</v>
+      </c>
+      <c r="G7">
+        <v>4.0918835045379021E-2</v>
+      </c>
+      <c r="H7">
+        <v>1.7307825655773709E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0.5979680544289937</v>
+      </c>
+      <c r="C8">
+        <v>3.2083484293142353E-2</v>
+      </c>
+      <c r="D8">
+        <v>5.0225457298055602E-2</v>
+      </c>
+      <c r="E8">
+        <v>2.7881432825503549E-2</v>
+      </c>
+      <c r="F8">
+        <v>4.449728198721576E-2</v>
+      </c>
+      <c r="G8">
+        <v>3.864147426126141E-2</v>
+      </c>
+      <c r="H8">
+        <v>2.6745286633148452E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0.51453161426750382</v>
+      </c>
+      <c r="C9">
+        <v>2.7138951568141521E-2</v>
+      </c>
+      <c r="D9">
+        <v>4.6993652118224753E-2</v>
+      </c>
+      <c r="E9">
+        <v>2.458181700655486E-2</v>
+      </c>
+      <c r="F9">
+        <v>3.7676808388305248E-2</v>
+      </c>
+      <c r="G9">
+        <v>3.3566725955240372E-2</v>
+      </c>
+      <c r="H9">
+        <v>2.1681629862259209E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>0.52371269284754085</v>
+      </c>
+      <c r="C10">
+        <v>2.6609293023922492E-2</v>
+      </c>
+      <c r="D10">
+        <v>4.3911105205912487E-2</v>
+      </c>
+      <c r="E10">
+        <v>2.5084232730665131E-2</v>
+      </c>
+      <c r="F10">
+        <v>4.0244007164825249E-2</v>
+      </c>
+      <c r="G10">
+        <v>3.4854245935760031E-2</v>
+      </c>
+      <c r="H10">
+        <v>2.3195172975765409E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>0.55962137944422863</v>
+      </c>
+      <c r="C11">
+        <v>2.9503215972636158E-2</v>
+      </c>
+      <c r="D11">
+        <v>4.0604551533334067E-2</v>
+      </c>
+      <c r="E11">
+        <v>2.812580771048365E-2</v>
+      </c>
+      <c r="F11">
+        <v>4.8651576400129043E-2</v>
+      </c>
+      <c r="G11">
+        <v>4.0656877600203048E-2</v>
+      </c>
+      <c r="H11">
+        <v>3.6134113814419871E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>0.55616942624912469</v>
+      </c>
+      <c r="C12">
+        <v>2.7966460713460029E-2</v>
+      </c>
+      <c r="D12">
+        <v>4.222617339125119E-2</v>
+      </c>
+      <c r="E12">
+        <v>2.7449934178464551E-2</v>
+      </c>
+      <c r="F12">
+        <v>4.6579510518485252E-2</v>
+      </c>
+      <c r="G12">
+        <v>3.8899454695712793E-2</v>
+      </c>
+      <c r="H12">
+        <v>2.9317007049637462E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.5643625727006305</v>
+      </c>
+      <c r="C13">
+        <v>3.046264675507623E-2</v>
+      </c>
+      <c r="D13">
+        <v>4.9896172355252677E-2</v>
+      </c>
+      <c r="E13">
+        <v>2.720057921792603E-2</v>
+      </c>
+      <c r="F13">
+        <v>4.9783148664481081E-2</v>
+      </c>
+      <c r="G13">
+        <v>3.9690318092233522E-2</v>
+      </c>
+      <c r="H13">
+        <v>3.1063998292790772E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1.003591251627264</v>
+      </c>
+      <c r="C14">
+        <v>4.1810810724656672E-2</v>
+      </c>
+      <c r="D14">
+        <v>7.5444282756787426E-2</v>
+      </c>
+      <c r="E14">
+        <v>4.1703386457619937E-2</v>
+      </c>
+      <c r="F14">
+        <v>7.8210568386407012E-2</v>
+      </c>
+      <c r="G14">
+        <v>7.1152008473109651E-2</v>
+      </c>
+      <c r="H14">
+        <v>5.7910936523761366E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1.0070385249961189</v>
+      </c>
+      <c r="C15">
+        <v>4.2915103696636522E-2</v>
+      </c>
+      <c r="D15">
+        <v>7.8764176381949269E-2</v>
+      </c>
+      <c r="E15">
+        <v>4.3479850045011398E-2</v>
+      </c>
+      <c r="F15">
+        <v>7.5412595633913893E-2</v>
+      </c>
+      <c r="G15">
+        <v>7.2011560990568046E-2</v>
+      </c>
+      <c r="H15">
+        <v>6.5298195735146467E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>0.94317449424856026</v>
+      </c>
+      <c r="C16">
+        <v>3.743347230456872E-2</v>
+      </c>
+      <c r="D16">
+        <v>6.8539239692100545E-2</v>
+      </c>
+      <c r="E16">
+        <v>3.8404776537416453E-2</v>
+      </c>
+      <c r="F16">
+        <v>6.7289491685300781E-2</v>
+      </c>
+      <c r="G16">
+        <v>6.1528666863547861E-2</v>
+      </c>
+      <c r="H16">
+        <v>4.7151927272539191E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>1.2689549979590189</v>
+      </c>
+      <c r="C17">
+        <v>4.4664037270640618E-2</v>
+      </c>
+      <c r="D17">
+        <v>8.3899406509916327E-2</v>
+      </c>
+      <c r="E17">
+        <v>4.6940305922004009E-2</v>
+      </c>
+      <c r="F17">
+        <v>7.821861225092322E-2</v>
+      </c>
+      <c r="G17">
+        <v>8.6675594127511871E-2</v>
+      </c>
+      <c r="H17">
+        <v>5.7463448404955291E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>1.349875761704193</v>
+      </c>
+      <c r="C18">
+        <v>4.753633934426417E-2</v>
+      </c>
+      <c r="D18">
+        <v>8.4326169085986308E-2</v>
+      </c>
+      <c r="E18">
+        <v>4.3066271277535498E-2</v>
+      </c>
+      <c r="F18">
+        <v>8.5912136833612845E-2</v>
+      </c>
+      <c r="G18">
+        <v>8.0398412386930102E-2</v>
+      </c>
+      <c r="H18">
+        <v>5.5647597620965723E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>1.3362065324613479</v>
+      </c>
+      <c r="C19">
+        <v>4.8805563210103382E-2</v>
+      </c>
+      <c r="D19">
+        <v>8.6880009926717697E-2</v>
+      </c>
+      <c r="E19">
+        <v>4.9721049303481417E-2</v>
+      </c>
+      <c r="F19">
+        <v>9.4083804794127757E-2</v>
+      </c>
+      <c r="G19">
+        <v>8.7609422898526204E-2</v>
+      </c>
+      <c r="H19">
+        <v>6.4008476390022733E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <f>B2/$B2</f>
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <f t="shared" ref="C24:D24" si="0">C2/$B2</f>
+        <v>4.8471272535359107E-2</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>7.5297783514488917E-2</v>
+      </c>
+      <c r="E24">
+        <f t="shared" ref="E24:H24" si="1">E2/$B2</f>
+        <v>3.5927017083364321E-2</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>4.7906312835161932E-2</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>8.6997630765659265E-2</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>2.8495052438584346E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <f t="shared" ref="B25:C41" si="2">B3/$B3</f>
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="2"/>
+        <v>5.2175664487454282E-2</v>
+      </c>
+      <c r="D25">
+        <f t="shared" ref="D25:H25" si="3">D3/$B3</f>
+        <v>7.3175882537938081E-2</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="3"/>
+        <v>3.3264156372241067E-2</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>4.6636044353321228E-2</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="3"/>
+        <v>9.0969556825135717E-2</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="3"/>
+        <v>2.8882268702606141E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="2"/>
+        <v>5.753689926550256E-2</v>
+      </c>
+      <c r="D26">
+        <f t="shared" ref="D26:H26" si="4">D4/$B4</f>
+        <v>8.715176280523293E-2</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="4"/>
+        <v>3.5276285640154351E-2</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="4"/>
+        <v>4.6554619744010164E-2</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="4"/>
+        <v>8.7386923786090268E-2</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="4"/>
+        <v>2.763193500252639E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="2"/>
+        <v>4.7427178717996843E-2</v>
+      </c>
+      <c r="D27">
+        <f t="shared" ref="D27:H27" si="5">D5/$B5</f>
+        <v>9.268107417097321E-2</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="5"/>
+        <v>3.8962357551911304E-2</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="5"/>
+        <v>6.6445724416575633E-2</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="5"/>
+        <v>5.9914744354099291E-2</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="5"/>
+        <v>3.9249496432245751E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="2"/>
+        <v>5.2185261308695031E-2</v>
+      </c>
+      <c r="D28">
+        <f t="shared" ref="D28:H28" si="6">D6/$B6</f>
+        <v>9.1543011154788967E-2</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="6"/>
+        <v>3.9293898519527935E-2</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="6"/>
+        <v>6.6230094526599129E-2</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="6"/>
+        <v>6.1597489597192086E-2</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="6"/>
+        <v>3.9852879318417501E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="2"/>
+        <v>4.6529830265473637E-2</v>
+      </c>
+      <c r="D29">
+        <f t="shared" ref="D29:H29" si="7">D7/$B7</f>
+        <v>7.9435123041207228E-2</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="7"/>
+        <v>4.2820097411780493E-2</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="7"/>
+        <v>4.8308950674223722E-2</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="7"/>
+        <v>7.0895910144644553E-2</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="7"/>
+        <v>2.9987511891042416E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="2"/>
+        <v>5.3654177770046975E-2</v>
+      </c>
+      <c r="D30">
+        <f t="shared" ref="D30:H30" si="8">D8/$B8</f>
+        <v>8.3993546019806103E-2</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="8"/>
+        <v>4.6626960452139599E-2</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="8"/>
+        <v>7.4414145801997247E-2</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="8"/>
+        <v>6.462130204958956E-2</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="8"/>
+        <v>4.4726948931557594E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="2"/>
+        <v>5.2744964188015941E-2</v>
+      </c>
+      <c r="D31">
+        <f t="shared" ref="D31:H31" si="9">D9/$B9</f>
+        <v>9.1332875988826723E-2</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="9"/>
+        <v>4.7775134364775547E-2</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="9"/>
+        <v>7.3225448822892267E-2</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="9"/>
+        <v>6.5237441246494735E-2</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="9"/>
+        <v>4.2138576641448079E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="2"/>
+        <v>5.0808951906897513E-2</v>
+      </c>
+      <c r="D32">
+        <f t="shared" ref="D32:H32" si="10">D10/$B10</f>
+        <v>8.3845791415056548E-2</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="10"/>
+        <v>4.7896934852345571E-2</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="10"/>
+        <v>7.6843673476786958E-2</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="10"/>
+        <v>6.6552226844550672E-2</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="10"/>
+        <v>4.4289881250821251E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="2"/>
+        <v>5.271995862977287E-2</v>
+      </c>
+      <c r="D33">
+        <f t="shared" ref="D33:H33" si="11">D11/$B11</f>
+        <v>7.2557184240636535E-2</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="11"/>
+        <v>5.0258636899140563E-2</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="11"/>
+        <v>8.693659353837753E-2</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="11"/>
+        <v>7.2650686863643815E-2</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="11"/>
+        <v>6.4568858770737805E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="2"/>
+        <v>5.0284067037034551E-2</v>
+      </c>
+      <c r="D34">
+        <f t="shared" ref="D34:H34" si="12">D12/$B12</f>
+        <v>7.5923219433383315E-2</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="12"/>
+        <v>4.9355345480945077E-2</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="12"/>
+        <v>8.3750577288333211E-2</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="12"/>
+        <v>6.9941735125671187E-2</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="12"/>
+        <v>5.2712367249949316E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="2"/>
+        <v>5.3977085350121759E-2</v>
+      </c>
+      <c r="D35">
+        <f t="shared" ref="D35:H35" si="13">D13/$B13</f>
+        <v>8.841155450207433E-2</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="13"/>
+        <v>4.8196993446542283E-2</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="13"/>
+        <v>8.8211286631313959E-2</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="13"/>
+        <v>7.0327693600063537E-2</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="13"/>
+        <v>5.5042626487686764E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="2"/>
+        <v>4.1661194890711642E-2</v>
+      </c>
+      <c r="D36">
+        <f t="shared" ref="D36:H36" si="14">D14/$B14</f>
+        <v>7.517431288331676E-2</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="14"/>
+        <v>4.1554155030746186E-2</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="14"/>
+        <v>7.7930699634530684E-2</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="14"/>
+        <v>7.0897398076897211E-2</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="14"/>
+        <v>5.7703707988548318E-4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="2"/>
+        <v>4.2615155856924061E-2</v>
+      </c>
+      <c r="D37">
+        <f t="shared" ref="D37:H37" si="15">D15/$B15</f>
+        <v>7.8213667528015202E-2</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="15"/>
+        <v>4.3175955006467072E-2</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="15"/>
+        <v>7.4885512085254666E-2</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="15"/>
+        <v>7.1508248396798507E-2</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="15"/>
+        <v>6.4841805069372222E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="2"/>
+        <v>3.9688808945573181E-2</v>
+      </c>
+      <c r="D38">
+        <f t="shared" ref="D38:H38" si="16">D16/$B16</f>
+        <v>7.2668673835064507E-2</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="16"/>
+        <v>4.0718633478330067E-2</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="16"/>
+        <v>7.1343629514611942E-2</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="16"/>
+        <v>6.5235719624255284E-2</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="16"/>
+        <v>4.9992793019817364E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="2"/>
+        <v>3.5197495058909137E-2</v>
+      </c>
+      <c r="D39">
+        <f t="shared" ref="D39:H39" si="17">D17/$B17</f>
+        <v>6.6116928216414086E-2</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="17"/>
+        <v>3.6991308594475435E-2</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="17"/>
+        <v>6.1640178238573991E-2</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="17"/>
+        <v>6.8304702898779296E-2</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="17"/>
+        <v>4.5284071143089567E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="2"/>
+        <v>3.5215344028587066E-2</v>
+      </c>
+      <c r="D40">
+        <f t="shared" ref="D40:H40" si="18">D18/$B18</f>
+        <v>6.2469577925842665E-2</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="18"/>
+        <v>3.1903877748841965E-2</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="18"/>
+        <v>6.3644476974051581E-2</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="18"/>
+        <v>5.955986074261279E-2</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="18"/>
+        <v>4.1224236481371938E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="2"/>
+        <v>3.6525463709716724E-2</v>
+      </c>
+      <c r="D41">
+        <f t="shared" ref="D41:H41" si="19">D19/$B19</f>
+        <v>6.5019896113425749E-2</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="19"/>
+        <v>3.7210601875963874E-2</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="19"/>
+        <v>7.0411124709008482E-2</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="19"/>
+        <v>6.5565779518489561E-2</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="19"/>
+        <v>4.7903130867139572E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/proteomics/volume_size_across_compartment_Rosemary_NH4_limitation_v2.xlsx
+++ b/data/proteomics/volume_size_across_compartment_Rosemary_NH4_limitation_v2.xlsx
@@ -535,40 +535,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5216809007133775</v>
+        <v>0.5216809007133781</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4769684679962733</v>
+        <v>0.4769684679962734</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4955760349940507</v>
+        <v>0.4955760349940506</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3931105192359032</v>
+        <v>0.3931105192359026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.41260246092853</v>
+        <v>0.4126024609285298</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5771677796630974</v>
+        <v>0.5771677796630983</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5979680544289927</v>
+        <v>0.5979680544289928</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5145316142675039</v>
+        <v>0.5145316142675036</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5237126928475411</v>
+        <v>0.5237126928475407</v>
       </c>
       <c r="L2" t="n">
-        <v>0.559621379444229</v>
+        <v>0.5596213794442285</v>
       </c>
       <c r="M2" t="n">
-        <v>0.556169426249124</v>
+        <v>0.5561694262491248</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5643625727006313</v>
+        <v>0.5643625727006305</v>
       </c>
       <c r="O2" t="n">
         <v>1.003591251627263</v>
@@ -577,16 +577,16 @@
         <v>1.007038524996121</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9431744942485613</v>
+        <v>0.9431744942485611</v>
       </c>
       <c r="R2" t="n">
-        <v>1.268954997959021</v>
+        <v>1.268954997959019</v>
       </c>
       <c r="S2" t="n">
         <v>1.349875761704192</v>
       </c>
       <c r="T2" t="n">
-        <v>1.336206532461348</v>
+        <v>1.336206532461347</v>
       </c>
     </row>
     <row r="3">
@@ -605,7 +605,7 @@
         <v>0.001251087432563556</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001129289074246758</v>
+        <v>0.001129289074246759</v>
       </c>
       <c r="F3" t="n">
         <v>0.001002140553597519</v>
@@ -614,7 +614,7 @@
         <v>0.001041135671339215</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009333324967470363</v>
+        <v>0.0009333324967470362</v>
       </c>
       <c r="I3" t="n">
         <v>0.001311823358583556</v>
@@ -623,10 +623,10 @@
         <v>0.001083998113460815</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001206541460260439</v>
+        <v>0.001206541460260438</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00128250273665894</v>
+        <v>0.001282502736658941</v>
       </c>
       <c r="M3" t="n">
         <v>0.001256820027737965</v>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0008741687319571383</v>
+        <v>0.0008741687319571382</v>
       </c>
       <c r="D4" t="n">
         <v>0.0008074599409869479</v>
@@ -672,13 +672,13 @@
         <v>0.0008581465688309836</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008145403158988128</v>
+        <v>0.000814540315898813</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008517442446959937</v>
+        <v>0.0008517442446959935</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008725942137095183</v>
+        <v>0.0008725942137095188</v>
       </c>
       <c r="I4" t="n">
         <v>0.001235246266824286</v>
@@ -690,7 +690,7 @@
         <v>0.001014354494266107</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001183436165546783</v>
+        <v>0.001183436165546782</v>
       </c>
       <c r="M4" t="n">
         <v>0.001223654975188363</v>
@@ -705,7 +705,7 @@
         <v>0.002022179705322244</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002045656496334062</v>
+        <v>0.002045656496334061</v>
       </c>
       <c r="R4" t="n">
         <v>0.002390734275881163</v>
@@ -791,55 +791,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3059797381717771</v>
+        <v>0.3059797381717774</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2810077369380477</v>
+        <v>0.2810077369380482</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2947282768547801</v>
+        <v>0.2947282768547796</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2314773302606147</v>
+        <v>0.2314773302606148</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2455508140171149</v>
+        <v>0.2455508140171152</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3293033144088326</v>
+        <v>0.3293033144088313</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3458118218316983</v>
+        <v>0.3458118218316981</v>
       </c>
       <c r="J6" t="n">
         <v>0.302336404624255</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3005588484065491</v>
+        <v>0.3005588484065487</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3090007872468594</v>
+        <v>0.3090007872468593</v>
       </c>
       <c r="M6" t="n">
         <v>0.3122897137102826</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3134834026986358</v>
+        <v>0.3134834026986363</v>
       </c>
       <c r="O6" t="n">
         <v>0.5639857784356532</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5678304997106747</v>
+        <v>0.5678304997106746</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5487243817797296</v>
+        <v>0.5487243817797304</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7589202747211462</v>
+        <v>0.7589202747211461</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8201641211301683</v>
+        <v>0.8201641211301682</v>
       </c>
       <c r="T6" t="n">
         <v>0.7741979601311868</v>
@@ -855,49 +855,49 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.674420314437807</v>
+        <v>0.674420314437808</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6152096060663304</v>
+        <v>0.6152096060663301</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6298742399652117</v>
+        <v>0.6298742399652122</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5221122862500751</v>
+        <v>0.5221122862500753</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5527945761810208</v>
+        <v>0.5527945761810193</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7523027531461463</v>
+        <v>0.752302753146147</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8005220388485721</v>
+        <v>0.8005220388485718</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6830876819151381</v>
+        <v>0.6830876819151366</v>
       </c>
       <c r="K7" t="n">
         <v>0.692216860905392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.800910647116277</v>
+        <v>0.8009106471162786</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7774359296731652</v>
+        <v>0.7774359296731654</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7655441311337504</v>
+        <v>0.76554413113375</v>
       </c>
       <c r="O7" t="n">
-        <v>1.566262375120504</v>
+        <v>1.566262375120505</v>
       </c>
       <c r="P7" t="n">
-        <v>1.565960937760685</v>
+        <v>1.565960937760687</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.522733603813839</v>
+        <v>1.52273360381384</v>
       </c>
       <c r="R7" t="n">
         <v>2.152409749044962</v>
@@ -906,7 +906,7 @@
         <v>2.257748735439358</v>
       </c>
       <c r="T7" t="n">
-        <v>2.222150261026405</v>
+        <v>2.222150261026401</v>
       </c>
     </row>
     <row r="8">
@@ -922,55 +922,55 @@
         <v>0.3244746526585782</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2866423737727968</v>
+        <v>0.2866423737727969</v>
       </c>
       <c r="E8" t="n">
         <v>0.2788327981304657</v>
       </c>
       <c r="F8" t="n">
-        <v>0.24678451999743</v>
+        <v>0.2467845199974297</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2551384454210683</v>
+        <v>0.2551384454210684</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3869190450973521</v>
+        <v>0.3869190450973518</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3807188592851362</v>
+        <v>0.3807188592851359</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3304304344291123</v>
+        <v>0.330430434429112</v>
       </c>
       <c r="K8" t="n">
         <v>0.330804509371276</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3236235345885699</v>
+        <v>0.3236235345885701</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3292863362551239</v>
+        <v>0.3292863362551235</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3215322174380016</v>
+        <v>0.3215322174380019</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6217249597239213</v>
+        <v>0.6217249597239209</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6176170768101754</v>
+        <v>0.6176170768101757</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6095370693827071</v>
+        <v>0.6095370693827075</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8599770121380084</v>
+        <v>0.8599770121380086</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9561697891533916</v>
+        <v>0.9561697891533919</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8859234514953053</v>
+        <v>0.885923451495306</v>
       </c>
     </row>
     <row r="9">
@@ -986,16 +986,16 @@
         <v>0.1018344970754371</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09500550076582552</v>
+        <v>0.09500550076582551</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08662816483852856</v>
+        <v>0.08662816483852855</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07621756979313228</v>
+        <v>0.07621756979313229</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0805973805394621</v>
+        <v>0.08059738053946207</v>
       </c>
       <c r="H9" t="n">
         <v>0.1157248510346111</v>
@@ -1004,22 +1004,22 @@
         <v>0.1105201273561455</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09664941002444151</v>
+        <v>0.0966494100244415</v>
       </c>
       <c r="K9" t="n">
         <v>0.1001543362025172</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08983019100216064</v>
+        <v>0.08983019100216065</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08957151193742506</v>
+        <v>0.08957151193742505</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07700398077014169</v>
+        <v>0.0770039807701417</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1796545649658059</v>
+        <v>0.179654564965806</v>
       </c>
       <c r="P9" t="n">
         <v>0.1713563778754203</v>
@@ -1120,7 +1120,7 @@
         <v>0.1099763394444485</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09808345730099703</v>
+        <v>0.09808345730099705</v>
       </c>
       <c r="G11" t="n">
         <v>0.1005421342982784</v>
@@ -1132,10 +1132,10 @@
         <v>0.1563110051080617</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1345131566141795</v>
+        <v>0.1345131566141796</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1373929738887599</v>
+        <v>0.13739297388876</v>
       </c>
       <c r="L11" t="n">
         <v>0.1200863018213852</v>
@@ -1153,7 +1153,7 @@
         <v>0.2477774214880019</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2513041015207317</v>
+        <v>0.2513041015207316</v>
       </c>
       <c r="R11" t="n">
         <v>0.3582874022569124</v>
@@ -1175,31 +1175,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03661573016203502</v>
+        <v>0.03661573016203496</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03319341291824938</v>
+        <v>0.0331934129182494</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03273638017898346</v>
+        <v>0.03273638017898348</v>
       </c>
       <c r="F12" t="n">
         <v>0.03038793374970474</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03355886864476986</v>
+        <v>0.0335588686447699</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03291355735044125</v>
+        <v>0.03291355735044124</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04993554413072922</v>
+        <v>0.04993554413072917</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04228986996042203</v>
+        <v>0.04228986996042209</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04475671142734251</v>
+        <v>0.04475671142734254</v>
       </c>
       <c r="L12" t="n">
         <v>0.05150944201058793</v>
@@ -1208,25 +1208,25 @@
         <v>0.0479742562322552</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05128340850969378</v>
+        <v>0.05128340850969379</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0797341998979884</v>
+        <v>0.07973419989798836</v>
       </c>
       <c r="P12" t="n">
-        <v>0.08124902627258181</v>
+        <v>0.08124902627258189</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07787174701674468</v>
+        <v>0.07787174701674469</v>
       </c>
       <c r="R12" t="n">
-        <v>0.09243011071226187</v>
+        <v>0.09243011071226175</v>
       </c>
       <c r="S12" t="n">
         <v>0.09937742984834656</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1030537358957392</v>
+        <v>0.1030537358957393</v>
       </c>
     </row>
     <row r="13">
@@ -1239,37 +1239,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.005049118025665232</v>
+        <v>0.005049118025665233</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004394490135591379</v>
+        <v>0.004394490135591378</v>
       </c>
       <c r="E13" t="n">
         <v>0.004545089439899939</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004705228658975349</v>
+        <v>0.00470522865897535</v>
       </c>
       <c r="G13" t="n">
         <v>0.005466796679180395</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0041119551599477</v>
+        <v>0.004111955159947699</v>
       </c>
       <c r="I13" t="n">
         <v>0.008331749184548477</v>
       </c>
       <c r="J13" t="n">
-        <v>0.006705473885157678</v>
+        <v>0.006705473885157677</v>
       </c>
       <c r="K13" t="n">
-        <v>0.007561135582411533</v>
+        <v>0.007561135582411532</v>
       </c>
       <c r="L13" t="n">
-        <v>0.008718885598009424</v>
+        <v>0.008718885598009426</v>
       </c>
       <c r="M13" t="n">
-        <v>0.007607491039339358</v>
+        <v>0.007607491039339359</v>
       </c>
       <c r="N13" t="n">
         <v>0.008764417056238809</v>
@@ -1284,10 +1284,10 @@
         <v>0.01129449410935769</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0102387998648556</v>
+        <v>0.01023879986485559</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0108725582319312</v>
+        <v>0.01087255823193119</v>
       </c>
       <c r="T13" t="n">
         <v>0.0122298136716976</v>
@@ -1309,16 +1309,16 @@
         <v>0.02488614675726864</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02851390840384986</v>
+        <v>0.02851390840384987</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01864412285172572</v>
+        <v>0.01864412285172573</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02153176724016595</v>
+        <v>0.02153176724016596</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02685551882242426</v>
+        <v>0.02685551882242425</v>
       </c>
       <c r="I14" t="n">
         <v>0.03208348429314235</v>
@@ -1330,28 +1330,28 @@
         <v>0.02660929302392249</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02950321597263616</v>
+        <v>0.02950321597263617</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02796646071346002</v>
+        <v>0.02796646071346003</v>
       </c>
       <c r="N14" t="n">
         <v>0.03046264675507623</v>
       </c>
       <c r="O14" t="n">
-        <v>0.04181081072465666</v>
+        <v>0.04181081072465667</v>
       </c>
       <c r="P14" t="n">
-        <v>0.04291510369663652</v>
+        <v>0.04291510369663654</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.03743347230456871</v>
+        <v>0.03743347230456872</v>
       </c>
       <c r="R14" t="n">
         <v>0.04466403727064062</v>
       </c>
       <c r="S14" t="n">
-        <v>0.04753633934426417</v>
+        <v>0.04753633934426415</v>
       </c>
       <c r="T14" t="n">
         <v>0.04880556321010339</v>
@@ -1367,19 +1367,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003812816599286286</v>
+        <v>0.003812816599286285</v>
       </c>
       <c r="D15" t="n">
         <v>0.003705792189397861</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003923022057734843</v>
+        <v>0.003923022057734842</v>
       </c>
       <c r="F15" t="n">
-        <v>0.003097662792991799</v>
+        <v>0.0030976627929918</v>
       </c>
       <c r="G15" t="n">
-        <v>0.003390836161339783</v>
+        <v>0.003390836161339784</v>
       </c>
       <c r="H15" t="n">
         <v>0.007042050315566639</v>
@@ -1388,22 +1388,22 @@
         <v>0.00716550631679311</v>
       </c>
       <c r="J15" t="n">
-        <v>0.006207707033002465</v>
+        <v>0.006207707033002466</v>
       </c>
       <c r="K15" t="n">
-        <v>0.005661779695231677</v>
+        <v>0.005661779695231678</v>
       </c>
       <c r="L15" t="n">
         <v>0.005948138029819547</v>
       </c>
       <c r="M15" t="n">
-        <v>0.005491708360268058</v>
+        <v>0.005491708360268059</v>
       </c>
       <c r="N15" t="n">
         <v>0.006106169692350783</v>
       </c>
       <c r="O15" t="n">
-        <v>0.009028701124745495</v>
+        <v>0.009028701124745494</v>
       </c>
       <c r="P15" t="n">
         <v>0.0105713992162711</v>
@@ -1431,49 +1431,49 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.005712600841827732</v>
+        <v>0.005712600841827734</v>
       </c>
       <c r="D16" t="n">
-        <v>0.005421618131276168</v>
+        <v>0.005421618131276169</v>
       </c>
       <c r="E16" t="n">
         <v>0.005124411632473768</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005435608453828109</v>
+        <v>0.005435608453828108</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005552460055708857</v>
+        <v>0.005552460055708858</v>
       </c>
       <c r="H16" t="n">
-        <v>0.004732830538987281</v>
+        <v>0.00473283053898728</v>
       </c>
       <c r="I16" t="n">
         <v>0.008275398215146628</v>
       </c>
       <c r="J16" t="n">
-        <v>0.006774819309301443</v>
+        <v>0.006774819309301442</v>
       </c>
       <c r="K16" t="n">
         <v>0.007244622197151865</v>
       </c>
       <c r="L16" t="n">
-        <v>0.008861363455180262</v>
+        <v>0.008861363455180264</v>
       </c>
       <c r="M16" t="n">
-        <v>0.00854389903207008</v>
+        <v>0.008543899032070078</v>
       </c>
       <c r="N16" t="n">
         <v>0.009004211516962006</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01338165463131713</v>
+        <v>0.01338165463131712</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01306321330370544</v>
+        <v>0.01306321330370543</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01286004652863197</v>
+        <v>0.01286004652863196</v>
       </c>
       <c r="R16" t="n">
         <v>0.01540950775474595</v>
@@ -1482,7 +1482,7 @@
         <v>0.01580657355591384</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01704402158098473</v>
+        <v>0.01704402158098474</v>
       </c>
     </row>
     <row r="17">
@@ -1495,58 +1495,58 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.008435572441337276</v>
+        <v>0.004681257980298449</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00675168029985166</v>
+        <v>0.003565421697960222</v>
       </c>
       <c r="E17" t="n">
-        <v>0.007078975116142588</v>
+        <v>0.003753034575357972</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006790131971749828</v>
+        <v>0.003382527880898953</v>
       </c>
       <c r="G17" t="n">
-        <v>0.007867796209051533</v>
+        <v>0.003707618210425618</v>
       </c>
       <c r="H17" t="n">
-        <v>0.006818147431868003</v>
+        <v>0.003814003674793596</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01223084240646462</v>
+        <v>0.005823372495245289</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01000420164235806</v>
+        <v>0.004912093381638569</v>
       </c>
       <c r="K17" t="n">
-        <v>0.009008085030795521</v>
+        <v>0.003290899132391376</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01226754784731512</v>
+        <v>0.005735802174095194</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01094078369384533</v>
+        <v>0.005473914323963424</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01225739201225836</v>
+        <v>0.005592339099503455</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01265238279548674</v>
+        <v>0.004771970529911557</v>
       </c>
       <c r="P17" t="n">
-        <v>0.01631006091967923</v>
+        <v>0.008943046285670725</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01554605619437725</v>
+        <v>0.008098476293101776</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0165020453768771</v>
+        <v>0.01000658933129396</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01657324103404058</v>
+        <v>0.01044815084225277</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01830828423212106</v>
+        <v>0.01043960635570267</v>
       </c>
     </row>
     <row r="18">
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.007443395672678017</v>
+        <v>0.007443395672678019</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00654660053293808</v>
+        <v>0.006546600532938079</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006313395272579767</v>
+        <v>0.006313395272579768</v>
       </c>
       <c r="F18" t="n">
-        <v>0.006037952564738819</v>
+        <v>0.006037952564738816</v>
       </c>
       <c r="G18" t="n">
         <v>0.006628872311452039</v>
       </c>
       <c r="H18" t="n">
-        <v>0.006030287112052417</v>
+        <v>0.006030287112052418</v>
       </c>
       <c r="I18" t="n">
-        <v>0.009793894302960118</v>
+        <v>0.009793894302960116</v>
       </c>
       <c r="J18" t="n">
-        <v>0.008080082426028675</v>
+        <v>0.008080082426028671</v>
       </c>
       <c r="K18" t="n">
-        <v>0.009067461585017544</v>
+        <v>0.009067461585017549</v>
       </c>
       <c r="L18" t="n">
         <v>0.01016044041851465</v>
       </c>
       <c r="M18" t="n">
-        <v>0.009722657632836851</v>
+        <v>0.009722657632836857</v>
       </c>
       <c r="N18" t="n">
         <v>0.01008333486938331</v>
@@ -1610,7 +1610,7 @@
         <v>0.02408388022697337</v>
       </c>
       <c r="T18" t="n">
-        <v>0.02484464946209347</v>
+        <v>0.02484464946209348</v>
       </c>
     </row>
     <row r="19">
@@ -1623,40 +1623,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.005026669736446983</v>
+        <v>0.005026669736446982</v>
       </c>
       <c r="D19" t="n">
-        <v>0.004519991787833755</v>
+        <v>0.004519991787833756</v>
       </c>
       <c r="E19" t="n">
-        <v>0.004650416166567028</v>
+        <v>0.004650416166567029</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00463200705470165</v>
+        <v>0.004632007054701646</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00480680558695471</v>
+        <v>0.004806805586954711</v>
       </c>
       <c r="H19" t="n">
-        <v>0.005001973599284326</v>
+        <v>0.005001973599284327</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00727903239274048</v>
+        <v>0.007279032392740483</v>
       </c>
       <c r="J19" t="n">
         <v>0.006397770808286394</v>
       </c>
       <c r="K19" t="n">
-        <v>0.006388401998568687</v>
+        <v>0.006388401998568684</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007530972041957382</v>
+        <v>0.007530972041957377</v>
       </c>
       <c r="M19" t="n">
-        <v>0.00726335759696508</v>
+        <v>0.007263357596965083</v>
       </c>
       <c r="N19" t="n">
-        <v>0.007618070080118962</v>
+        <v>0.007618070080118965</v>
       </c>
       <c r="O19" t="n">
         <v>0.0114686967913749</v>
@@ -1668,13 +1668,13 @@
         <v>0.01145677756159373</v>
       </c>
       <c r="R19" t="n">
-        <v>0.01444466999713028</v>
+        <v>0.01444466999713029</v>
       </c>
       <c r="S19" t="n">
-        <v>0.01486261021990095</v>
+        <v>0.01486261021990096</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01505131658364078</v>
+        <v>0.01505131658364077</v>
       </c>
     </row>
     <row r="20">
@@ -1690,13 +1690,13 @@
         <v>0.01439008675920186</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01254529804881725</v>
+        <v>0.01254529804881726</v>
       </c>
       <c r="E20" t="n">
         <v>0.01395444048221669</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01286564209019561</v>
+        <v>0.0128656420901956</v>
       </c>
       <c r="G20" t="n">
         <v>0.01394436266123397</v>
@@ -1705,7 +1705,7 @@
         <v>0.01776449821700896</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02080394931722171</v>
+        <v>0.02080394931722172</v>
       </c>
       <c r="J20" t="n">
         <v>0.01792844159990109</v>
@@ -1714,7 +1714,7 @@
         <v>0.01832311476897562</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02239033721602806</v>
+        <v>0.02239033721602808</v>
       </c>
       <c r="M20" t="n">
         <v>0.02251252602155649</v>
@@ -1723,19 +1723,19 @@
         <v>0.02028504530507214</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04361099094122151</v>
+        <v>0.0436109909412215</v>
       </c>
       <c r="P20" t="n">
-        <v>0.04265496736654479</v>
+        <v>0.04265496736654477</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.04084420843985978</v>
+        <v>0.04084420843985979</v>
       </c>
       <c r="R20" t="n">
-        <v>0.05264107071099634</v>
+        <v>0.05264107071099635</v>
       </c>
       <c r="S20" t="n">
-        <v>0.04893222006956956</v>
+        <v>0.04893222006956955</v>
       </c>
       <c r="T20" t="n">
         <v>0.05601116535852404</v>
@@ -1836,13 +1836,13 @@
         <v>0.002609143681042045</v>
       </c>
       <c r="J22" t="n">
-        <v>0.002327622918269024</v>
+        <v>0.002327622918269023</v>
       </c>
       <c r="K22" t="n">
-        <v>0.002335238073920166</v>
+        <v>0.002335238073920165</v>
       </c>
       <c r="L22" t="n">
-        <v>0.002729764962314759</v>
+        <v>0.00272976496231476</v>
       </c>
       <c r="M22" t="n">
         <v>0.002641204495354088</v>
@@ -1851,10 +1851,10 @@
         <v>0.002872123249523663</v>
       </c>
       <c r="O22" t="n">
-        <v>0.004155333641574649</v>
+        <v>0.004155333641574648</v>
       </c>
       <c r="P22" t="n">
-        <v>0.004314340649881362</v>
+        <v>0.004314340649881361</v>
       </c>
       <c r="Q22" t="n">
         <v>0.00400590106790256</v>
@@ -1879,46 +1879,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.06544895927897283</v>
+        <v>0.06544895927897286</v>
       </c>
       <c r="D23" t="n">
         <v>0.05344226526081741</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04835437420598978</v>
+        <v>0.04835437420598979</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0421272284448451</v>
+        <v>0.04212722844484509</v>
       </c>
       <c r="G23" t="n">
-        <v>0.04064635918773631</v>
+        <v>0.04064635918773633</v>
       </c>
       <c r="H23" t="n">
         <v>0.1018017020070821</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08292055708383923</v>
+        <v>0.08292055708383926</v>
       </c>
       <c r="J23" t="n">
-        <v>0.06928222519676554</v>
+        <v>0.06928222519676557</v>
       </c>
       <c r="K23" t="n">
         <v>0.06503827189428044</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06003812759753002</v>
+        <v>0.06003812759753003</v>
       </c>
       <c r="M23" t="n">
-        <v>0.06602394251820769</v>
+        <v>0.06602394251820767</v>
       </c>
       <c r="N23" t="n">
-        <v>0.06067101690685924</v>
+        <v>0.06067101690685925</v>
       </c>
       <c r="O23" t="n">
         <v>0.1245721472587214</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1291345038462924</v>
+        <v>0.1291345038462925</v>
       </c>
       <c r="Q23" t="n">
         <v>0.1210540611101786</v>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0002960735886797674</v>
+        <v>0.0002960735886797675</v>
       </c>
       <c r="D24" t="n">
         <v>0.0003056165462516994</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0003650838090279751</v>
+        <v>0.0003650838090279752</v>
       </c>
       <c r="F24" t="n">
         <v>0.0003193923381672009</v>
@@ -1988,7 +1988,7 @@
         <v>0.0009996345155749984</v>
       </c>
       <c r="R24" t="n">
-        <v>0.001130360403149471</v>
+        <v>0.00113036040314947</v>
       </c>
       <c r="S24" t="n">
         <v>0.001257474704243686</v>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.003981689962999591</v>
+        <v>0.003981689962999592</v>
       </c>
       <c r="D25" t="n">
-        <v>0.003635622454831857</v>
+        <v>0.003635622454831856</v>
       </c>
       <c r="E25" t="n">
-        <v>0.003778346057862444</v>
+        <v>0.003778346057862445</v>
       </c>
       <c r="F25" t="n">
         <v>0.003419780777906692</v>
@@ -2022,37 +2022,37 @@
         <v>0.003702096024915826</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00513337003000971</v>
+        <v>0.005133370030009709</v>
       </c>
       <c r="I25" t="n">
-        <v>0.005293615894974279</v>
+        <v>0.005293615894974278</v>
       </c>
       <c r="J25" t="n">
         <v>0.004605492990943175</v>
       </c>
       <c r="K25" t="n">
-        <v>0.004880605178564208</v>
+        <v>0.004880605178564207</v>
       </c>
       <c r="L25" t="n">
-        <v>0.00571721884839224</v>
+        <v>0.005717218848392241</v>
       </c>
       <c r="M25" t="n">
-        <v>0.005586169686724364</v>
+        <v>0.005586169686724362</v>
       </c>
       <c r="N25" t="n">
-        <v>0.005615593304517421</v>
+        <v>0.005615593304517419</v>
       </c>
       <c r="O25" t="n">
         <v>0.00989733917260684</v>
       </c>
       <c r="P25" t="n">
-        <v>0.009746145370303915</v>
+        <v>0.009746145370303912</v>
       </c>
       <c r="Q25" t="n">
         <v>0.008991249072953926</v>
       </c>
       <c r="R25" t="n">
-        <v>0.01108635701980848</v>
+        <v>0.01108635701980849</v>
       </c>
       <c r="S25" t="n">
         <v>0.01136859001210947</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.003572379925020587</v>
+        <v>0.003572379925020586</v>
       </c>
       <c r="D26" t="n">
         <v>0.003290862127722241</v>
@@ -2080,13 +2080,13 @@
         <v>0.003175276113531483</v>
       </c>
       <c r="F26" t="n">
-        <v>0.00348033784760929</v>
+        <v>0.003480337847609291</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00350861650889362</v>
+        <v>0.003508616508893621</v>
       </c>
       <c r="H26" t="n">
-        <v>0.002870652405661035</v>
+        <v>0.002870652405661034</v>
       </c>
       <c r="I26" t="n">
         <v>0.005333984981971954</v>
@@ -2098,25 +2098,25 @@
         <v>0.004869362592362368</v>
       </c>
       <c r="L26" t="n">
-        <v>0.005731137234644757</v>
+        <v>0.005731137234644756</v>
       </c>
       <c r="M26" t="n">
-        <v>0.005336940010454465</v>
+        <v>0.005336940010454466</v>
       </c>
       <c r="N26" t="n">
-        <v>0.005624705573409331</v>
+        <v>0.005624705573409332</v>
       </c>
       <c r="O26" t="n">
-        <v>0.008118724733919711</v>
+        <v>0.008118724733919712</v>
       </c>
       <c r="P26" t="n">
-        <v>0.007894529086869176</v>
+        <v>0.007894529086869174</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.008127006922679607</v>
+        <v>0.008127006922679609</v>
       </c>
       <c r="R26" t="n">
-        <v>0.009381868413133078</v>
+        <v>0.00938186841313308</v>
       </c>
       <c r="S26" t="n">
         <v>0.01006147872595065</v>
@@ -2135,49 +2135,49 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02363190616199327</v>
+        <v>0.02363190616199328</v>
       </c>
       <c r="D27" t="n">
         <v>0.0203446764789837</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02206476918498531</v>
+        <v>0.02206476918498529</v>
       </c>
       <c r="F27" t="n">
         <v>0.02133382831723831</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02154735531605345</v>
+        <v>0.02154735531605346</v>
       </c>
       <c r="H27" t="n">
-        <v>0.02928489587149748</v>
+        <v>0.02928489587149747</v>
       </c>
       <c r="I27" t="n">
-        <v>0.03493389407902207</v>
+        <v>0.03493389407902206</v>
       </c>
       <c r="J27" t="n">
-        <v>0.02972842407248852</v>
+        <v>0.02972842407248851</v>
       </c>
       <c r="K27" t="n">
-        <v>0.02890109739348917</v>
+        <v>0.02890109739348916</v>
       </c>
       <c r="L27" t="n">
         <v>0.03988912484342511</v>
       </c>
       <c r="M27" t="n">
-        <v>0.03828791478626143</v>
+        <v>0.03828791478626144</v>
       </c>
       <c r="N27" t="n">
         <v>0.03883627107657939</v>
       </c>
       <c r="O27" t="n">
-        <v>0.08964175956440454</v>
+        <v>0.08964175956440451</v>
       </c>
       <c r="P27" t="n">
-        <v>0.09504129227029805</v>
+        <v>0.09504129227029801</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.08807653087278287</v>
+        <v>0.08807653087278289</v>
       </c>
       <c r="R27" t="n">
         <v>0.1329163296625813</v>
@@ -2199,25 +2199,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0009601396901303172</v>
+        <v>0.0009601396901303175</v>
       </c>
       <c r="D28" t="n">
         <v>0.0008917878293514123</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001005887284232088</v>
+        <v>0.001005887284232087</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0008748548515545568</v>
+        <v>0.0008748548515545567</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0009119071443270727</v>
+        <v>0.0009119071443270725</v>
       </c>
       <c r="H28" t="n">
         <v>0.0008759844238974661</v>
       </c>
       <c r="I28" t="n">
-        <v>0.001237888951396374</v>
+        <v>0.001237888951396373</v>
       </c>
       <c r="J28" t="n">
         <v>0.001061281711893008</v>
@@ -2238,7 +2238,7 @@
         <v>0.002078787827943519</v>
       </c>
       <c r="P28" t="n">
-        <v>0.001977947660649412</v>
+        <v>0.001977947660649413</v>
       </c>
       <c r="Q28" t="n">
         <v>0.001918595285612787</v>
@@ -2250,7 +2250,7 @@
         <v>0.002292231620168414</v>
       </c>
       <c r="T28" t="n">
-        <v>0.002443063803981782</v>
+        <v>0.002443063803981783</v>
       </c>
     </row>
     <row r="29">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.04178468371230531</v>
+        <v>0.0417846837123053</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04029921482308036</v>
+        <v>0.04029921482308035</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04284121689574149</v>
+        <v>0.04284121689574148</v>
       </c>
       <c r="F29" t="n">
         <v>0.03434279818144118</v>
@@ -2278,16 +2278,16 @@
         <v>0.03972404405320799</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03318192913057328</v>
+        <v>0.03318192913057326</v>
       </c>
       <c r="I29" t="n">
-        <v>0.04728805586905932</v>
+        <v>0.04728805586905933</v>
       </c>
       <c r="J29" t="n">
-        <v>0.04019107653238922</v>
+        <v>0.04019107653238923</v>
       </c>
       <c r="K29" t="n">
-        <v>0.04374562272135332</v>
+        <v>0.04374562272135329</v>
       </c>
       <c r="L29" t="n">
         <v>0.04906111308521011</v>
@@ -2296,7 +2296,7 @@
         <v>0.04626134440966503</v>
       </c>
       <c r="N29" t="n">
-        <v>0.04968702694724266</v>
+        <v>0.04968702694724268</v>
       </c>
       <c r="O29" t="n">
         <v>0.07300693916132671</v>
@@ -2305,16 +2305,16 @@
         <v>0.07431737936769228</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.07129962323660159</v>
+        <v>0.07129962323660161</v>
       </c>
       <c r="R29" t="n">
-        <v>0.08311022178751409</v>
+        <v>0.08311022178751405</v>
       </c>
       <c r="S29" t="n">
-        <v>0.08415552651775413</v>
+        <v>0.08415552651775415</v>
       </c>
       <c r="T29" t="n">
-        <v>0.09293840875741978</v>
+        <v>0.09293840875741974</v>
       </c>
     </row>
     <row r="30">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.536217811625104e-05</v>
+        <v>6.536217811625103e-05</v>
       </c>
       <c r="D30" t="n">
         <v>5.696548566341211e-05</v>
@@ -2351,13 +2351,13 @@
         <v>6.326455087601082e-05</v>
       </c>
       <c r="K30" t="n">
-        <v>5.613516580507902e-05</v>
+        <v>5.613516580507901e-05</v>
       </c>
       <c r="L30" t="n">
         <v>6.351550964717175e-05</v>
       </c>
       <c r="M30" t="n">
-        <v>7.13601757394949e-05</v>
+        <v>7.136017573949492e-05</v>
       </c>
       <c r="N30" t="n">
         <v>6.729598909199773e-05</v>
@@ -2415,10 +2415,10 @@
         <v>1.656392258703981e-05</v>
       </c>
       <c r="K31" t="n">
-        <v>1.686142517659898e-05</v>
+        <v>1.686142517659899e-05</v>
       </c>
       <c r="L31" t="n">
-        <v>1.888976555242161e-05</v>
+        <v>1.88897655524216e-05</v>
       </c>
       <c r="M31" t="n">
         <v>1.853632812113721e-05</v>
@@ -2433,7 +2433,7 @@
         <v>3.020715256220784e-05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.812234172670426e-05</v>
+        <v>2.812234172670427e-05</v>
       </c>
       <c r="R31" t="n">
         <v>3.331726499246351e-05</v>
@@ -2455,49 +2455,49 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.05967304959223332</v>
+        <v>0.05967304959223335</v>
       </c>
       <c r="D32" t="n">
-        <v>0.05516122588708289</v>
+        <v>0.05516122588708292</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07066063246716911</v>
+        <v>0.07066063246716912</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0510157198685279</v>
+        <v>0.05101571986852792</v>
       </c>
       <c r="G32" t="n">
-        <v>0.05412844437019201</v>
+        <v>0.05412844437019203</v>
       </c>
       <c r="H32" t="n">
-        <v>0.07575494814067367</v>
+        <v>0.0757549481406737</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07830483392638533</v>
+        <v>0.07830483392638532</v>
       </c>
       <c r="J32" t="n">
-        <v>0.06769507343211757</v>
+        <v>0.0676950734321176</v>
       </c>
       <c r="K32" t="n">
-        <v>0.06815147656362597</v>
+        <v>0.06815147656362594</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08207355011330549</v>
+        <v>0.0820735501133055</v>
       </c>
       <c r="M32" t="n">
-        <v>0.08317156084404084</v>
+        <v>0.08317156084404088</v>
       </c>
       <c r="N32" t="n">
-        <v>0.07779299447583217</v>
+        <v>0.0777929944758322</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1686633202522351</v>
+        <v>0.168663320252235</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1605582191046246</v>
+        <v>0.1605582191046247</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.1637301235937188</v>
+        <v>0.1637301235937187</v>
       </c>
       <c r="R32" t="n">
         <v>0.2370010763956215</v>
@@ -2519,58 +2519,58 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.03928141552555951</v>
+        <v>0.03928141552555952</v>
       </c>
       <c r="D33" t="n">
         <v>0.03490258858839559</v>
       </c>
       <c r="E33" t="n">
-        <v>0.04319032505375929</v>
+        <v>0.04319032505375928</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03643390519069255</v>
+        <v>0.03643390519069256</v>
       </c>
       <c r="G33" t="n">
-        <v>0.03777087168327377</v>
+        <v>0.03777087168327378</v>
       </c>
       <c r="H33" t="n">
         <v>0.04584739359295859</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0502254572980556</v>
+        <v>0.05022545729805558</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04699365211822476</v>
+        <v>0.04699365211822475</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04391110520591249</v>
+        <v>0.0439111052059125</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04060455153333406</v>
+        <v>0.04060455153333408</v>
       </c>
       <c r="M33" t="n">
         <v>0.0422261733912512</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04989617235525269</v>
+        <v>0.04989617235525267</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0754442827567874</v>
+        <v>0.07544428275678744</v>
       </c>
       <c r="P33" t="n">
-        <v>0.07876417638194923</v>
+        <v>0.07876417638194927</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.06853923969210057</v>
+        <v>0.06853923969210053</v>
       </c>
       <c r="R33" t="n">
-        <v>0.08389940650991629</v>
+        <v>0.08389940650991633</v>
       </c>
       <c r="S33" t="n">
-        <v>0.08432616908598632</v>
+        <v>0.08432616908598631</v>
       </c>
       <c r="T33" t="n">
-        <v>0.08688000992671772</v>
+        <v>0.08688000992671771</v>
       </c>
     </row>
     <row r="34">
@@ -2586,13 +2586,13 @@
         <v>0.00210258112423081</v>
       </c>
       <c r="D34" t="n">
-        <v>0.001836922371714554</v>
+        <v>0.001836922371714553</v>
       </c>
       <c r="E34" t="n">
         <v>0.001862962321709572</v>
       </c>
       <c r="F34" t="n">
-        <v>0.001654208977858668</v>
+        <v>0.001654208977858669</v>
       </c>
       <c r="G34" t="n">
         <v>0.001777972575455845</v>
@@ -2607,34 +2607,34 @@
         <v>0.002488780392150594</v>
       </c>
       <c r="K34" t="n">
-        <v>0.002521425927899795</v>
+        <v>0.002521425927899796</v>
       </c>
       <c r="L34" t="n">
-        <v>0.002942290564688176</v>
+        <v>0.002942290564688174</v>
       </c>
       <c r="M34" t="n">
-        <v>0.002809841862328544</v>
+        <v>0.002809841862328543</v>
       </c>
       <c r="N34" t="n">
-        <v>0.002826058497224957</v>
+        <v>0.002826058497224958</v>
       </c>
       <c r="O34" t="n">
         <v>0.00521768518509613</v>
       </c>
       <c r="P34" t="n">
-        <v>0.005031621094921959</v>
+        <v>0.005031621094921961</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.00463342746889736</v>
+        <v>0.004633427468897363</v>
       </c>
       <c r="R34" t="n">
-        <v>0.006726304927452117</v>
+        <v>0.006726304927452114</v>
       </c>
       <c r="S34" t="n">
-        <v>0.006865083366614178</v>
+        <v>0.00686508336661418</v>
       </c>
       <c r="T34" t="n">
-        <v>0.00671213655136438</v>
+        <v>0.006712136551364381</v>
       </c>
     </row>
     <row r="35">
@@ -2689,7 +2689,7 @@
         <v>0.003645004130948816</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.003193086741053776</v>
+        <v>0.003193086741053777</v>
       </c>
       <c r="R35" t="n">
         <v>0.003850733355482474</v>
@@ -2711,16 +2711,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.003140770600787807</v>
+        <v>0.003140770600787806</v>
       </c>
       <c r="D36" t="n">
-        <v>0.002819705211409489</v>
+        <v>0.00281970521140949</v>
       </c>
       <c r="E36" t="n">
         <v>0.002880650284996926</v>
       </c>
       <c r="F36" t="n">
-        <v>0.00269769098370607</v>
+        <v>0.002697690983706071</v>
       </c>
       <c r="G36" t="n">
         <v>0.002740712646266431</v>
@@ -2747,7 +2747,7 @@
         <v>0.004027616956137037</v>
       </c>
       <c r="O36" t="n">
-        <v>0.006872496922405302</v>
+        <v>0.006872496922405303</v>
       </c>
       <c r="P36" t="n">
         <v>0.007375429434640457</v>
@@ -2759,10 +2759,10 @@
         <v>0.008351025821890814</v>
       </c>
       <c r="S36" t="n">
-        <v>0.009213512599590206</v>
+        <v>0.009213512599590202</v>
       </c>
       <c r="T36" t="n">
-        <v>0.009510761419686169</v>
+        <v>0.009510761419686171</v>
       </c>
     </row>
     <row r="37">
@@ -2781,28 +2781,28 @@
         <v>0.01586595370405629</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01748208176686525</v>
+        <v>0.01748208176686526</v>
       </c>
       <c r="F37" t="n">
         <v>0.01531651260788678</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01621275922863313</v>
+        <v>0.01621275922863314</v>
       </c>
       <c r="H37" t="n">
         <v>0.02471438054811493</v>
       </c>
       <c r="I37" t="n">
-        <v>0.02788143282550356</v>
+        <v>0.02788143282550355</v>
       </c>
       <c r="J37" t="n">
-        <v>0.02458181700655485</v>
+        <v>0.02458181700655486</v>
       </c>
       <c r="K37" t="n">
-        <v>0.02508423273066514</v>
+        <v>0.02508423273066513</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02812580771048365</v>
+        <v>0.02812580771048367</v>
       </c>
       <c r="M37" t="n">
         <v>0.02744993417846454</v>
@@ -2811,13 +2811,13 @@
         <v>0.02720057921792603</v>
       </c>
       <c r="O37" t="n">
-        <v>0.04170338645761996</v>
+        <v>0.04170338645761994</v>
       </c>
       <c r="P37" t="n">
-        <v>0.04347985004501138</v>
+        <v>0.0434798500450114</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.03840477653741647</v>
+        <v>0.03840477653741646</v>
       </c>
       <c r="R37" t="n">
         <v>0.04694030592200402</v>
@@ -2826,7 +2826,7 @@
         <v>0.04306627127753549</v>
       </c>
       <c r="T37" t="n">
-        <v>0.04972104930348145</v>
+        <v>0.04972104930348142</v>
       </c>
     </row>
     <row r="38">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.00111997981158652</v>
+        <v>0.001119979811586521</v>
       </c>
       <c r="D38" t="n">
         <v>0.00104820183045174</v>
@@ -2848,7 +2848,7 @@
         <v>0.001111413095985852</v>
       </c>
       <c r="F38" t="n">
-        <v>0.000918189041813628</v>
+        <v>0.0009181890418136278</v>
       </c>
       <c r="G38" t="n">
         <v>0.00093411747423178</v>
@@ -2857,7 +2857,7 @@
         <v>0.0008915528447191771</v>
       </c>
       <c r="I38" t="n">
-        <v>0.001311187395852362</v>
+        <v>0.001311187395852363</v>
       </c>
       <c r="J38" t="n">
         <v>0.001093542379639255</v>
@@ -2872,7 +2872,7 @@
         <v>0.001272144682034951</v>
       </c>
       <c r="N38" t="n">
-        <v>0.001333482776760409</v>
+        <v>0.00133348277676041</v>
       </c>
       <c r="O38" t="n">
         <v>0.002016445597492914</v>
@@ -2884,7 +2884,7 @@
         <v>0.002149605687876302</v>
       </c>
       <c r="R38" t="n">
-        <v>0.002522371882809762</v>
+        <v>0.002522371882809761</v>
       </c>
       <c r="S38" t="n">
         <v>0.00254902802101099</v>
@@ -2921,7 +2921,7 @@
         <v>0.0004001379483768973</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0005698991651439697</v>
+        <v>0.0005698991651439698</v>
       </c>
       <c r="J39" t="n">
         <v>0.0004729548580341696</v>
@@ -2930,16 +2930,16 @@
         <v>0.0004676195310665344</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0005738753293783107</v>
+        <v>0.0005738753293783108</v>
       </c>
       <c r="M39" t="n">
         <v>0.0005475429341050075</v>
       </c>
       <c r="N39" t="n">
-        <v>0.0005819366799929223</v>
+        <v>0.0005819366799929222</v>
       </c>
       <c r="O39" t="n">
-        <v>0.0008356076791109799</v>
+        <v>0.0008356076791109801</v>
       </c>
       <c r="P39" t="n">
         <v>0.000907574292150649</v>
@@ -2967,22 +2967,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0003639057570049175</v>
+        <v>0.0003639057570049176</v>
       </c>
       <c r="D40" t="n">
         <v>0.0002801590814539433</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0003029347150350594</v>
+        <v>0.0003029347150350595</v>
       </c>
       <c r="F40" t="n">
         <v>0.0002686408341916116</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0002912700619111126</v>
+        <v>0.0002912700619111125</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0003299408215584417</v>
+        <v>0.0003299408215584418</v>
       </c>
       <c r="I40" t="n">
         <v>0.0004538768502562573</v>
@@ -2991,7 +2991,7 @@
         <v>0.0003979916844135054</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0003797094505343364</v>
+        <v>0.0003797094505343365</v>
       </c>
       <c r="L40" t="n">
         <v>0.0004614202781300067</v>
@@ -3018,7 +3018,7 @@
         <v>0.0009378254605716714</v>
       </c>
       <c r="T40" t="n">
-        <v>0.0009606794398254191</v>
+        <v>0.000960679439825419</v>
       </c>
     </row>
     <row r="41">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.000717672500986763</v>
+        <v>0.0007176725009867631</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0005821637252449532</v>
+        <v>0.0005821637252449531</v>
       </c>
       <c r="E41" t="n">
         <v>0.0006093154879078816</v>
@@ -3046,28 +3046,28 @@
         <v>0.0005915019507909177</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0009476508048630646</v>
+        <v>0.0009476508048630645</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0008824410898727283</v>
+        <v>0.0008824410898727281</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0007473456657593528</v>
+        <v>0.0007473456657593529</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0007678154551806889</v>
+        <v>0.000767815455180689</v>
       </c>
       <c r="L41" t="n">
         <v>0.001036935394352836</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0008752540743390141</v>
+        <v>0.0008752540743390142</v>
       </c>
       <c r="N41" t="n">
         <v>0.0008690463726857524</v>
       </c>
       <c r="O41" t="n">
-        <v>0.00141036533210558</v>
+        <v>0.001410365332105579</v>
       </c>
       <c r="P41" t="n">
         <v>0.001490115268707816</v>
@@ -3101,7 +3101,7 @@
         <v>0.000491209738695646</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0005201759213330667</v>
+        <v>0.0005201759213330668</v>
       </c>
       <c r="F42" t="n">
         <v>0.0004894624595332362</v>
@@ -3168,7 +3168,7 @@
         <v>0.001338310871670054</v>
       </c>
       <c r="F43" t="n">
-        <v>0.001261226372592402</v>
+        <v>0.001261226372592401</v>
       </c>
       <c r="G43" t="n">
         <v>0.00138154392196514</v>
@@ -3183,7 +3183,7 @@
         <v>0.001766939356805425</v>
       </c>
       <c r="K43" t="n">
-        <v>0.001963481392945995</v>
+        <v>0.001963481392945996</v>
       </c>
       <c r="L43" t="n">
         <v>0.002237763593613615</v>
@@ -3195,10 +3195,10 @@
         <v>0.00222716145488672</v>
       </c>
       <c r="O43" t="n">
-        <v>0.003879069652252632</v>
+        <v>0.003879069652252631</v>
       </c>
       <c r="P43" t="n">
-        <v>0.003863080667579024</v>
+        <v>0.003863080667579025</v>
       </c>
       <c r="Q43" t="n">
         <v>0.003948739065758635</v>
@@ -3207,10 +3207,10 @@
         <v>0.0042772897227513</v>
       </c>
       <c r="S43" t="n">
-        <v>0.004808271716528293</v>
+        <v>0.004808271716528292</v>
       </c>
       <c r="T43" t="n">
-        <v>0.005071815455708678</v>
+        <v>0.005071815455708679</v>
       </c>
     </row>
     <row r="44">
@@ -3226,16 +3226,16 @@
         <v>0.007863010387560413</v>
       </c>
       <c r="D44" t="n">
-        <v>0.006794820646434559</v>
+        <v>0.006794820646434558</v>
       </c>
       <c r="E44" t="n">
-        <v>0.006354037684587708</v>
+        <v>0.006354037684587713</v>
       </c>
       <c r="F44" t="n">
         <v>0.006248399803056122</v>
       </c>
       <c r="G44" t="n">
-        <v>0.006817988388062354</v>
+        <v>0.006817988388062353</v>
       </c>
       <c r="H44" t="n">
         <v>0.006890692390890818</v>
@@ -3247,7 +3247,7 @@
         <v>0.008975019969027165</v>
       </c>
       <c r="K44" t="n">
-        <v>0.009287384909961444</v>
+        <v>0.009287384909961446</v>
       </c>
       <c r="L44" t="n">
         <v>0.0108360700194088</v>
@@ -3265,10 +3265,10 @@
         <v>0.02000063324769512</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.01933386238912674</v>
+        <v>0.01933386238912675</v>
       </c>
       <c r="R44" t="n">
-        <v>0.02244486932264941</v>
+        <v>0.02244486932264942</v>
       </c>
       <c r="S44" t="n">
         <v>0.02500026509404587</v>
@@ -3290,13 +3290,13 @@
         <v>0.0001767306540755206</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0001510826285920629</v>
+        <v>0.000151082628592063</v>
       </c>
       <c r="E45" t="n">
         <v>0.0001568257746080243</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0001410147061403566</v>
+        <v>0.0001410147061403565</v>
       </c>
       <c r="G45" t="n">
         <v>0.0001391817060213013</v>
@@ -3320,7 +3320,7 @@
         <v>0.0002139407444541989</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0002226815983364654</v>
+        <v>0.0002226815983364653</v>
       </c>
       <c r="O45" t="n">
         <v>0.0004133550258707325</v>
@@ -3357,10 +3357,10 @@
         <v>8.077718193948885e-05</v>
       </c>
       <c r="E46" t="n">
-        <v>9.118136161837112e-05</v>
+        <v>9.118136161837113e-05</v>
       </c>
       <c r="F46" t="n">
-        <v>7.656782006564766e-05</v>
+        <v>7.656782006564767e-05</v>
       </c>
       <c r="G46" t="n">
         <v>7.414469706222293e-05</v>
@@ -3369,10 +3369,10 @@
         <v>9.499280868702787e-05</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0001213577333661769</v>
+        <v>0.0001213577333661768</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0001068885442734451</v>
+        <v>0.0001068885442734452</v>
       </c>
       <c r="K46" t="n">
         <v>0.0001097264641272879</v>
@@ -3384,7 +3384,7 @@
         <v>0.0001137642823858088</v>
       </c>
       <c r="N46" t="n">
-        <v>0.0001257164349663787</v>
+        <v>0.0001257164349663786</v>
       </c>
       <c r="O46" t="n">
         <v>0.000180178331457102</v>
@@ -3424,7 +3424,7 @@
         <v>0.0004348858786583529</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0004008232802274767</v>
+        <v>0.0004008232802274768</v>
       </c>
       <c r="G47" t="n">
         <v>0.0004128478197850666</v>
@@ -3442,16 +3442,16 @@
         <v>0.0004238000029943557</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0005692890954966685</v>
+        <v>0.0005692890954966684</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0005500931388743395</v>
+        <v>0.0005500931388743396</v>
       </c>
       <c r="N47" t="n">
         <v>0.0005910172556355501</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0008008864797214392</v>
+        <v>0.0008008864797214393</v>
       </c>
       <c r="P47" t="n">
         <v>0.0008084034408457065</v>
@@ -3463,7 +3463,7 @@
         <v>0.0008748776651254892</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009828141149986493</v>
+        <v>0.0009828141149986495</v>
       </c>
       <c r="T47" t="n">
         <v>0.000994752408337187</v>
@@ -3482,7 +3482,7 @@
         <v>0.005196952653723204</v>
       </c>
       <c r="D48" t="n">
-        <v>0.004317810306870075</v>
+        <v>0.004317810306870076</v>
       </c>
       <c r="E48" t="n">
         <v>0.004087420486340369</v>
@@ -3494,7 +3494,7 @@
         <v>0.003874030105241913</v>
       </c>
       <c r="H48" t="n">
-        <v>0.004060990896287202</v>
+        <v>0.004060990896287203</v>
       </c>
       <c r="I48" t="n">
         <v>0.005417238023809207</v>
@@ -3503,19 +3503,19 @@
         <v>0.004527036907750805</v>
       </c>
       <c r="K48" t="n">
-        <v>0.005270317267512577</v>
+        <v>0.005270317267512578</v>
       </c>
       <c r="L48" t="n">
         <v>0.005499479180724023</v>
       </c>
       <c r="M48" t="n">
-        <v>0.005520992334913804</v>
+        <v>0.005520992334913802</v>
       </c>
       <c r="N48" t="n">
         <v>0.005562590273690458</v>
       </c>
       <c r="O48" t="n">
-        <v>0.009682878421946121</v>
+        <v>0.009682878421946123</v>
       </c>
       <c r="P48" t="n">
         <v>0.01027431101665551</v>
@@ -3622,19 +3622,19 @@
         <v>0.0002489035518655286</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0003090577667611848</v>
+        <v>0.0003090577667611847</v>
       </c>
       <c r="I50" t="n">
         <v>0.0003844610978247171</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0003451993875627503</v>
+        <v>0.0003451993875627504</v>
       </c>
       <c r="K50" t="n">
         <v>0.0003335932732388534</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0004266752941893006</v>
+        <v>0.0004266752941893007</v>
       </c>
       <c r="M50" t="n">
         <v>0.0004240489692019076</v>
@@ -3646,13 +3646,13 @@
         <v>0.0007961864659021018</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0008095112106981517</v>
+        <v>0.0008095112106981516</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0008080718311665693</v>
+        <v>0.0008080718311665691</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0009993840860593865</v>
+        <v>0.0009993840860593867</v>
       </c>
       <c r="S50" t="n">
         <v>0.001079928289086057</v>
@@ -3680,37 +3680,37 @@
         <v>0.02588499389940942</v>
       </c>
       <c r="F51" t="n">
-        <v>0.02568907614003456</v>
+        <v>0.02568907614003457</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0256487391438894</v>
+        <v>0.02564873914388941</v>
       </c>
       <c r="H51" t="n">
-        <v>0.03427805167718021</v>
+        <v>0.0342780516771802</v>
       </c>
       <c r="I51" t="n">
         <v>0.04417315381836269</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0375509073547002</v>
+        <v>0.03755090735470019</v>
       </c>
       <c r="K51" t="n">
-        <v>0.03701110946390408</v>
+        <v>0.03701110946390407</v>
       </c>
       <c r="L51" t="n">
-        <v>0.0524455556859118</v>
+        <v>0.05244555568591178</v>
       </c>
       <c r="M51" t="n">
         <v>0.05025188799216815</v>
       </c>
       <c r="N51" t="n">
-        <v>0.04702021221348655</v>
+        <v>0.04702021221348656</v>
       </c>
       <c r="O51" t="n">
         <v>0.1234318284247891</v>
       </c>
       <c r="P51" t="n">
-        <v>0.1234401651413854</v>
+        <v>0.1234401651413855</v>
       </c>
       <c r="Q51" t="n">
         <v>0.122887891811818</v>
@@ -3719,10 +3719,10 @@
         <v>0.1893245025981536</v>
       </c>
       <c r="S51" t="n">
-        <v>0.2041678729973969</v>
+        <v>0.2041678729973968</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1951052889672891</v>
+        <v>0.1951052889672892</v>
       </c>
     </row>
     <row r="52">
@@ -3735,19 +3735,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.0007283473450843273</v>
+        <v>0.0007283473450843272</v>
       </c>
       <c r="D52" t="n">
         <v>0.0006612943781374029</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0006656865350080062</v>
+        <v>0.0006656865350080063</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0006567142805552538</v>
+        <v>0.0006567142805552541</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0006968050461698422</v>
+        <v>0.0006968050461698421</v>
       </c>
       <c r="H52" t="n">
         <v>0.0008606509931428723</v>
@@ -3768,16 +3768,16 @@
         <v>0.001129441734019896</v>
       </c>
       <c r="N52" t="n">
-        <v>0.001211040212533432</v>
+        <v>0.001211040212533433</v>
       </c>
       <c r="O52" t="n">
-        <v>0.001874182164528961</v>
+        <v>0.001874182164528962</v>
       </c>
       <c r="P52" t="n">
-        <v>0.001879419888623998</v>
+        <v>0.001879419888623997</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.001653089448397335</v>
+        <v>0.001653089448397336</v>
       </c>
       <c r="R52" t="n">
         <v>0.001950279422570903</v>
@@ -3820,7 +3820,7 @@
         <v>0.0001423072559419482</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0001157727660977517</v>
+        <v>0.0001157727660977516</v>
       </c>
       <c r="K53" t="n">
         <v>0.0001225655482989715</v>
@@ -3832,10 +3832,10 @@
         <v>0.0001386756320171677</v>
       </c>
       <c r="N53" t="n">
-        <v>0.0001459136599087846</v>
+        <v>0.0001459136599087845</v>
       </c>
       <c r="O53" t="n">
-        <v>0.0002014720441216711</v>
+        <v>0.000201472044121671</v>
       </c>
       <c r="P53" t="n">
         <v>0.0002172032504963772</v>
@@ -3863,16 +3863,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.05857290472854742</v>
+        <v>0.05857290472854743</v>
       </c>
       <c r="D54" t="n">
-        <v>0.05324004902531079</v>
+        <v>0.05324004902531077</v>
       </c>
       <c r="E54" t="n">
-        <v>0.05431422790656239</v>
+        <v>0.05431422790656237</v>
       </c>
       <c r="F54" t="n">
-        <v>0.03979857311804828</v>
+        <v>0.03979857311804829</v>
       </c>
       <c r="G54" t="n">
         <v>0.0457588751304696</v>
@@ -3884,19 +3884,19 @@
         <v>0.05936039204495634</v>
       </c>
       <c r="J54" t="n">
-        <v>0.04803864427597394</v>
+        <v>0.04803864427597396</v>
       </c>
       <c r="K54" t="n">
-        <v>0.04842644127848793</v>
+        <v>0.04842644127848794</v>
       </c>
       <c r="L54" t="n">
-        <v>0.0518825615991347</v>
+        <v>0.05188256159913471</v>
       </c>
       <c r="M54" t="n">
-        <v>0.05306251231184316</v>
+        <v>0.05306251231184315</v>
       </c>
       <c r="N54" t="n">
-        <v>0.05516057509214908</v>
+        <v>0.05516057509214907</v>
       </c>
       <c r="O54" t="n">
         <v>0.1260878639115785</v>
@@ -3911,10 +3911,10 @@
         <v>0.1726253688074165</v>
       </c>
       <c r="S54" t="n">
-        <v>0.1857152921141936</v>
+        <v>0.1857152921141935</v>
       </c>
       <c r="T54" t="n">
-        <v>0.1847289625567464</v>
+        <v>0.1847289625567463</v>
       </c>
     </row>
     <row r="55">
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.009288482532161057</v>
+        <v>0.009288482532161061</v>
       </c>
       <c r="D55" t="n">
-        <v>0.008125054819074272</v>
+        <v>0.008125054819074273</v>
       </c>
       <c r="E55" t="n">
         <v>0.008606380281014528</v>
@@ -3960,10 +3960,10 @@
         <v>0.01246312469582261</v>
       </c>
       <c r="N55" t="n">
-        <v>0.01231265745520274</v>
+        <v>0.01231265745520275</v>
       </c>
       <c r="O55" t="n">
-        <v>0.01999558321850471</v>
+        <v>0.0199955832185047</v>
       </c>
       <c r="P55" t="n">
         <v>0.01957882412444081</v>
@@ -3978,7 +3978,7 @@
         <v>0.02508809410281049</v>
       </c>
       <c r="T55" t="n">
-        <v>0.02507412836736542</v>
+        <v>0.02507412836736543</v>
       </c>
     </row>
     <row r="56">
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.02499180842970413</v>
+        <v>0.02499180842970414</v>
       </c>
       <c r="D56" t="n">
         <v>0.02224392262860989</v>
@@ -4006,16 +4006,16 @@
         <v>0.02732669998920395</v>
       </c>
       <c r="H56" t="n">
-        <v>0.02788236979849583</v>
+        <v>0.02788236979849584</v>
       </c>
       <c r="I56" t="n">
-        <v>0.04449728198721576</v>
+        <v>0.04449728198721575</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03767680838830525</v>
+        <v>0.03767680838830524</v>
       </c>
       <c r="K56" t="n">
-        <v>0.04024400716482525</v>
+        <v>0.04024400716482526</v>
       </c>
       <c r="L56" t="n">
         <v>0.04865157640012904</v>
@@ -4024,7 +4024,7 @@
         <v>0.04657951051848525</v>
       </c>
       <c r="N56" t="n">
-        <v>0.0497831486644811</v>
+        <v>0.04978314866448109</v>
       </c>
       <c r="O56" t="n">
         <v>0.07821056838640705</v>
@@ -4033,16 +4033,16 @@
         <v>0.07541259563391391</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.06728949168530078</v>
+        <v>0.0672894916853008</v>
       </c>
       <c r="R56" t="n">
         <v>0.07821861225092321</v>
       </c>
       <c r="S56" t="n">
-        <v>0.08591213683361291</v>
+        <v>0.08591213683361289</v>
       </c>
       <c r="T56" t="n">
-        <v>0.09408380479412777</v>
+        <v>0.0940838047941278</v>
       </c>
     </row>
     <row r="57">
@@ -4055,28 +4055,28 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.0005770779651762076</v>
+        <v>0.0005770779651762075</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0005081994516022106</v>
+        <v>0.0005081994516022107</v>
       </c>
       <c r="E57" t="n">
         <v>0.0006306169691337961</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0005007545161437509</v>
+        <v>0.0005007545161437507</v>
       </c>
       <c r="G57" t="n">
         <v>0.0005349898807271909</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0005305149327596838</v>
+        <v>0.0005305149327596837</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0006970657295114213</v>
+        <v>0.0006970657295114212</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0006684414624699765</v>
+        <v>0.0006684414624699764</v>
       </c>
       <c r="K57" t="n">
         <v>0.0006276659944181313</v>
@@ -4122,16 +4122,16 @@
         <v>0.0009449344400139658</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0008757557971306017</v>
+        <v>0.0008757557971306018</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0008917637030961148</v>
+        <v>0.0008917637030961151</v>
       </c>
       <c r="F58" t="n">
         <v>0.0008308097029911027</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0009107220242241222</v>
+        <v>0.0009107220242241219</v>
       </c>
       <c r="H58" t="n">
         <v>0.0007002533414524414</v>
@@ -4149,19 +4149,19 @@
         <v>0.001240191814229775</v>
       </c>
       <c r="M58" t="n">
-        <v>0.001175523830842079</v>
+        <v>0.001175523830842078</v>
       </c>
       <c r="N58" t="n">
         <v>0.001289292632663305</v>
       </c>
       <c r="O58" t="n">
-        <v>0.001866120463139621</v>
+        <v>0.00186612046313962</v>
       </c>
       <c r="P58" t="n">
         <v>0.001824965079939083</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.001914809230054279</v>
+        <v>0.001914809230054278</v>
       </c>
       <c r="R58" t="n">
         <v>0.002028772208119279</v>
@@ -4170,7 +4170,7 @@
         <v>0.002296044901218367</v>
       </c>
       <c r="T58" t="n">
-        <v>0.002276435420181714</v>
+        <v>0.002276435420181715</v>
       </c>
     </row>
     <row r="59">
@@ -4186,13 +4186,13 @@
         <v>0.001180121261484723</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0008442368034814512</v>
+        <v>0.0008442368034814513</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001075644154997985</v>
+        <v>0.001075644154997986</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0007995786060417853</v>
+        <v>0.0007995786060417852</v>
       </c>
       <c r="G59" t="n">
         <v>0.001097625630007409</v>
@@ -4207,10 +4207,10 @@
         <v>0.001511603196314317</v>
       </c>
       <c r="K59" t="n">
-        <v>0.001371025215133861</v>
+        <v>0.001371025215133862</v>
       </c>
       <c r="L59" t="n">
-        <v>0.001626969334149027</v>
+        <v>0.001626969334149028</v>
       </c>
       <c r="M59" t="n">
         <v>0.001634280570144979</v>
@@ -4231,10 +4231,10 @@
         <v>0.003241969737141661</v>
       </c>
       <c r="S59" t="n">
-        <v>0.002641397387394245</v>
+        <v>0.002641397387394246</v>
       </c>
       <c r="T59" t="n">
-        <v>0.003035403841779181</v>
+        <v>0.00303540384177918</v>
       </c>
     </row>
     <row r="60">
@@ -4265,7 +4265,7 @@
         <v>0.02169225338579572</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0289471840791505</v>
+        <v>0.02894718407915049</v>
       </c>
       <c r="J60" t="n">
         <v>0.02555353229455078</v>
@@ -4274,7 +4274,7 @@
         <v>0.02545778221877915</v>
       </c>
       <c r="L60" t="n">
-        <v>0.02835323971042891</v>
+        <v>0.02835323971042892</v>
       </c>
       <c r="M60" t="n">
         <v>0.02738291211541331</v>
@@ -4283,22 +4283,22 @@
         <v>0.03019592117095573</v>
       </c>
       <c r="O60" t="n">
-        <v>0.04158486248730464</v>
+        <v>0.04158486248730465</v>
       </c>
       <c r="P60" t="n">
         <v>0.04054302690714037</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.04287597446048184</v>
+        <v>0.04287597446048185</v>
       </c>
       <c r="R60" t="n">
-        <v>0.05120131045905077</v>
+        <v>0.05120131045905076</v>
       </c>
       <c r="S60" t="n">
-        <v>0.05216372175998282</v>
+        <v>0.05216372175998283</v>
       </c>
       <c r="T60" t="n">
-        <v>0.05446448215993897</v>
+        <v>0.05446448215993896</v>
       </c>
     </row>
     <row r="61">
@@ -4314,10 +4314,10 @@
         <v>0.0006061197106397691</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0006515413288554952</v>
+        <v>0.0006515413288554953</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0004978298575038123</v>
+        <v>0.0004978298575038122</v>
       </c>
       <c r="F61" t="n">
         <v>0.0004904757399292254</v>
@@ -4329,19 +4329,19 @@
         <v>0.0006317034413010371</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0007988232553914685</v>
+        <v>0.0007988232553914683</v>
       </c>
       <c r="J61" t="n">
         <v>0.0006765066651379732</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0005948015544907994</v>
+        <v>0.0005948015544907992</v>
       </c>
       <c r="L61" t="n">
-        <v>0.0007342209822745413</v>
+        <v>0.0007342209822745412</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0007098136718420916</v>
+        <v>0.0007098136718420917</v>
       </c>
       <c r="N61" t="n">
         <v>0.0007318263125666763</v>
@@ -4381,7 +4381,7 @@
         <v>1.329227050572132e-05</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0002197722216973953</v>
+        <v>0.0002197722216973954</v>
       </c>
       <c r="F62" t="n">
         <v>5.221971150020664e-06</v>
@@ -4451,13 +4451,13 @@
         <v>0.01720124094090852</v>
       </c>
       <c r="G63" t="n">
-        <v>0.02137908684559434</v>
+        <v>0.02137908684559435</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0245017320531675</v>
+        <v>0.02450173205316751</v>
       </c>
       <c r="I63" t="n">
-        <v>0.02467820436928057</v>
+        <v>0.02467820436928058</v>
       </c>
       <c r="J63" t="n">
         <v>0.02210434191809629</v>
@@ -4469,13 +4469,13 @@
         <v>0.01951875879589951</v>
       </c>
       <c r="M63" t="n">
-        <v>0.02024798030864153</v>
+        <v>0.02024798030864154</v>
       </c>
       <c r="N63" t="n">
         <v>0.02289515688760574</v>
       </c>
       <c r="O63" t="n">
-        <v>0.02498366214116285</v>
+        <v>0.02498366214116286</v>
       </c>
       <c r="P63" t="n">
         <v>0.02487144076926046</v>
@@ -4487,10 +4487,10 @@
         <v>0.02849296838107103</v>
       </c>
       <c r="S63" t="n">
-        <v>0.02853446257747671</v>
+        <v>0.0285344625774767</v>
       </c>
       <c r="T63" t="n">
-        <v>0.02596145898711212</v>
+        <v>0.02596145898711213</v>
       </c>
     </row>
     <row r="64">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6.720313208834166e-05</v>
+        <v>6.720313208834165e-05</v>
       </c>
       <c r="D64" t="n">
         <v>5.913645532120331e-05</v>
@@ -4512,10 +4512,10 @@
         <v>7.361441986057457e-05</v>
       </c>
       <c r="F64" t="n">
-        <v>6.760715154160402e-05</v>
+        <v>6.760715154160403e-05</v>
       </c>
       <c r="G64" t="n">
-        <v>7.395304277678057e-05</v>
+        <v>7.395304277678059e-05</v>
       </c>
       <c r="H64" t="n">
         <v>8.477539560702336e-05</v>
@@ -4524,10 +4524,10 @@
         <v>0.0001083870505709137</v>
       </c>
       <c r="J64" t="n">
-        <v>9.475518504317732e-05</v>
+        <v>9.475518504317734e-05</v>
       </c>
       <c r="K64" t="n">
-        <v>9.330011942754318e-05</v>
+        <v>9.330011942754319e-05</v>
       </c>
       <c r="L64" t="n">
         <v>0.0001179808655334539</v>
@@ -4536,7 +4536,7 @@
         <v>0.0001163481268553569</v>
       </c>
       <c r="N64" t="n">
-        <v>0.0001202272452395046</v>
+        <v>0.0001202272452395045</v>
       </c>
       <c r="O64" t="n">
         <v>0.0002500441313901368</v>
@@ -4545,7 +4545,7 @@
         <v>0.0002541545556738676</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.0002133279948857404</v>
+        <v>0.0002133279948857403</v>
       </c>
       <c r="R64" t="n">
         <v>0.0002787787574952359</v>
@@ -4554,7 +4554,7 @@
         <v>0.0003274137150955893</v>
       </c>
       <c r="T64" t="n">
-        <v>0.0003160617576427602</v>
+        <v>0.0003160617576427603</v>
       </c>
     </row>
     <row r="65">
@@ -4576,7 +4576,7 @@
         <v>0.0433068652002379</v>
       </c>
       <c r="F65" t="n">
-        <v>0.02355311626292639</v>
+        <v>0.02355311626292638</v>
       </c>
       <c r="G65" t="n">
         <v>0.02541527579482097</v>
@@ -4591,7 +4591,7 @@
         <v>0.03356672595524037</v>
       </c>
       <c r="K65" t="n">
-        <v>0.03485424593576003</v>
+        <v>0.03485424593576004</v>
       </c>
       <c r="L65" t="n">
         <v>0.04065687760020305</v>
@@ -4600,10 +4600,10 @@
         <v>0.03889945469571278</v>
       </c>
       <c r="N65" t="n">
-        <v>0.03969031809223352</v>
+        <v>0.03969031809223353</v>
       </c>
       <c r="O65" t="n">
-        <v>0.07115200847310968</v>
+        <v>0.07115200847310967</v>
       </c>
       <c r="P65" t="n">
         <v>0.07201156099056806</v>
@@ -4612,13 +4612,13 @@
         <v>0.06152866686354787</v>
       </c>
       <c r="R65" t="n">
-        <v>0.08667559412751187</v>
+        <v>0.08667559412751188</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0803984123869301</v>
+        <v>0.08039841238693013</v>
       </c>
       <c r="T65" t="n">
-        <v>0.0876094228985262</v>
+        <v>0.08760942289852619</v>
       </c>
     </row>
     <row r="66">
@@ -4652,7 +4652,7 @@
         <v>0.002552324109944717</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0021672872622784</v>
+        <v>0.002167287262278399</v>
       </c>
       <c r="K66" t="n">
         <v>0.002169068974417476</v>
@@ -4670,19 +4670,19 @@
         <v>0.004134299667395341</v>
       </c>
       <c r="P66" t="n">
-        <v>0.003955970073544151</v>
+        <v>0.003955970073544152</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.004062988145373159</v>
+        <v>0.00406298814537316</v>
       </c>
       <c r="R66" t="n">
         <v>0.00485885759215433</v>
       </c>
       <c r="S66" t="n">
-        <v>0.004745925798865115</v>
+        <v>0.004745925798865116</v>
       </c>
       <c r="T66" t="n">
-        <v>0.004631458325474398</v>
+        <v>0.004631458325474399</v>
       </c>
     </row>
     <row r="67">
@@ -4704,7 +4704,7 @@
         <v>8.351978109109367e-05</v>
       </c>
       <c r="F67" t="n">
-        <v>7.423247885592182e-05</v>
+        <v>7.423247885592181e-05</v>
       </c>
       <c r="G67" t="n">
         <v>7.981421193171109e-05</v>
@@ -4713,7 +4713,7 @@
         <v>7.27661636548983e-05</v>
       </c>
       <c r="I67" t="n">
-        <v>9.140683859755845e-05</v>
+        <v>9.140683859755842e-05</v>
       </c>
       <c r="J67" t="n">
         <v>7.687315996281983e-05</v>
@@ -4722,16 +4722,16 @@
         <v>8.504274041685125e-05</v>
       </c>
       <c r="L67" t="n">
-        <v>8.906058359306194e-05</v>
+        <v>8.906058359306196e-05</v>
       </c>
       <c r="M67" t="n">
-        <v>8.183669800176502e-05</v>
+        <v>8.183669800176504e-05</v>
       </c>
       <c r="N67" t="n">
         <v>9.299289647050584e-05</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0001170291077615544</v>
+        <v>0.0001170291077615545</v>
       </c>
       <c r="P67" t="n">
         <v>0.0001254851618496425</v>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.0002896224806174816</v>
+        <v>0.0002896224806174815</v>
       </c>
       <c r="D68" t="n">
         <v>0.0002708195441140243</v>
@@ -4792,25 +4792,25 @@
         <v>0.0004011282476338992</v>
       </c>
       <c r="N68" t="n">
-        <v>0.0004122643205398079</v>
+        <v>0.0004122643205398078</v>
       </c>
       <c r="O68" t="n">
         <v>0.0006699775071638696</v>
       </c>
       <c r="P68" t="n">
-        <v>0.000661724424155169</v>
+        <v>0.0006617244241551689</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.0006028718809485267</v>
+        <v>0.0006028718809485268</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0007349740373265299</v>
+        <v>0.00073497403732653</v>
       </c>
       <c r="S68" t="n">
         <v>0.0007281199876061773</v>
       </c>
       <c r="T68" t="n">
-        <v>0.0007917876059387474</v>
+        <v>0.0007917876059387475</v>
       </c>
     </row>
     <row r="69">
@@ -4823,40 +4823,40 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.00046332819572116</v>
+        <v>0.0004633281957211601</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0003878346035619254</v>
+        <v>0.0003878346035619255</v>
       </c>
       <c r="E69" t="n">
         <v>0.0003691162204705686</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0003858966361778565</v>
+        <v>0.0003858966361778564</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0003914605559053412</v>
+        <v>0.0003914605559053413</v>
       </c>
       <c r="H69" t="n">
-        <v>0.000571848570574346</v>
+        <v>0.0005718485705743459</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0007169978103621083</v>
+        <v>0.0007169978103621082</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0006173166494182951</v>
+        <v>0.000617316649418295</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0005895233196005975</v>
+        <v>0.0005895233196005974</v>
       </c>
       <c r="L69" t="n">
         <v>0.000678597998307159</v>
       </c>
       <c r="M69" t="n">
-        <v>0.0006765252513353319</v>
+        <v>0.000676525251335332</v>
       </c>
       <c r="N69" t="n">
-        <v>0.0006789334868333879</v>
+        <v>0.0006789334868333878</v>
       </c>
       <c r="O69" t="n">
         <v>0.00119829761041941</v>
@@ -4868,7 +4868,7 @@
         <v>0.00122225495870886</v>
       </c>
       <c r="R69" t="n">
-        <v>0.001741458081799373</v>
+        <v>0.001741458081799374</v>
       </c>
       <c r="S69" t="n">
         <v>0.001938964157824213</v>
@@ -4963,43 +4963,43 @@
         <v>0.02583514108216511</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02716203481263801</v>
+        <v>0.027162034812638</v>
       </c>
       <c r="H71" t="n">
         <v>0.03111701673858734</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0409838897924537</v>
+        <v>0.04098388979245371</v>
       </c>
       <c r="J71" t="n">
-        <v>0.03548762131640577</v>
+        <v>0.03548762131640576</v>
       </c>
       <c r="K71" t="n">
         <v>0.03518885671478111</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0383261420774786</v>
+        <v>0.03832614207747861</v>
       </c>
       <c r="M71" t="n">
-        <v>0.03631767426350425</v>
+        <v>0.03631767426350423</v>
       </c>
       <c r="N71" t="n">
-        <v>0.04107934716655569</v>
+        <v>0.04107934716655568</v>
       </c>
       <c r="O71" t="n">
-        <v>0.05098796133209234</v>
+        <v>0.05098796133209233</v>
       </c>
       <c r="P71" t="n">
         <v>0.04950386691641318</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.05030968973282349</v>
+        <v>0.05030968973282347</v>
       </c>
       <c r="R71" t="n">
-        <v>0.05941786776200266</v>
+        <v>0.05941786776200265</v>
       </c>
       <c r="S71" t="n">
-        <v>0.06170427167824288</v>
+        <v>0.06170427167824289</v>
       </c>
       <c r="T71" t="n">
         <v>0.06345394063655223</v>
@@ -5018,28 +5018,28 @@
         <v>0.00591158834100603</v>
       </c>
       <c r="D72" t="n">
-        <v>0.005472875132470742</v>
+        <v>0.005472875132470743</v>
       </c>
       <c r="E72" t="n">
         <v>0.005511764138566286</v>
       </c>
       <c r="F72" t="n">
-        <v>0.005085026790918367</v>
+        <v>0.005085026790918366</v>
       </c>
       <c r="G72" t="n">
-        <v>0.004998769476485135</v>
+        <v>0.004998769476485134</v>
       </c>
       <c r="H72" t="n">
-        <v>0.005508254499132775</v>
+        <v>0.005508254499132774</v>
       </c>
       <c r="I72" t="n">
-        <v>0.008001641833302882</v>
+        <v>0.00800164183330288</v>
       </c>
       <c r="J72" t="n">
-        <v>0.006580810548816611</v>
+        <v>0.006580810548816608</v>
       </c>
       <c r="K72" t="n">
-        <v>0.007134338908588693</v>
+        <v>0.007134338908588691</v>
       </c>
       <c r="L72" t="n">
         <v>0.008694522567118982</v>
@@ -5048,7 +5048,7 @@
         <v>0.007893679741714149</v>
       </c>
       <c r="N72" t="n">
-        <v>0.007831675228281947</v>
+        <v>0.007831675228281949</v>
       </c>
       <c r="O72" t="n">
         <v>0.01693006799742993</v>
@@ -5063,7 +5063,7 @@
         <v>0.02098053184294878</v>
       </c>
       <c r="S72" t="n">
-        <v>0.01786028529217654</v>
+        <v>0.01786028529217653</v>
       </c>
       <c r="T72" t="n">
         <v>0.0228535014861386</v>
@@ -5085,19 +5085,19 @@
         <v>0.003948926664927192</v>
       </c>
       <c r="E73" t="n">
-        <v>0.003863875210915712</v>
+        <v>0.003863875210915713</v>
       </c>
       <c r="F73" t="n">
         <v>0.003472595378495141</v>
       </c>
       <c r="G73" t="n">
-        <v>0.003679093583206078</v>
+        <v>0.003679093583206077</v>
       </c>
       <c r="H73" t="n">
         <v>0.00464156987783138</v>
       </c>
       <c r="I73" t="n">
-        <v>0.005631865492481018</v>
+        <v>0.005631865492481019</v>
       </c>
       <c r="J73" t="n">
         <v>0.004579218404045468</v>
@@ -5106,13 +5106,13 @@
         <v>0.004998269425899777</v>
       </c>
       <c r="L73" t="n">
-        <v>0.005718246501388789</v>
+        <v>0.005718246501388787</v>
       </c>
       <c r="M73" t="n">
-        <v>0.005561617956951356</v>
+        <v>0.005561617956951358</v>
       </c>
       <c r="N73" t="n">
-        <v>0.005600036112992703</v>
+        <v>0.005600036112992702</v>
       </c>
       <c r="O73" t="n">
         <v>0.008197363018726646</v>
@@ -5121,7 +5121,7 @@
         <v>0.008804474124274582</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.007883030648410668</v>
+        <v>0.007883030648410666</v>
       </c>
       <c r="R73" t="n">
         <v>0.009547762731302216</v>
@@ -5130,7 +5130,7 @@
         <v>0.009471961914342483</v>
       </c>
       <c r="T73" t="n">
-        <v>0.009674581438692566</v>
+        <v>0.009674581438692565</v>
       </c>
     </row>
     <row r="74">
@@ -5143,19 +5143,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.003858859539032478</v>
+        <v>0.003858859539032477</v>
       </c>
       <c r="D74" t="n">
-        <v>0.003562513883515147</v>
+        <v>0.003562513883515146</v>
       </c>
       <c r="E74" t="n">
-        <v>0.00376342054437429</v>
+        <v>0.003763420544374291</v>
       </c>
       <c r="F74" t="n">
         <v>0.003122341169767977</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00325776940762117</v>
+        <v>0.003257769407621171</v>
       </c>
       <c r="H74" t="n">
         <v>0.005372201779939284</v>
@@ -5173,22 +5173,22 @@
         <v>0.00505596427887427</v>
       </c>
       <c r="M74" t="n">
-        <v>0.005112668978965527</v>
+        <v>0.005112668978965528</v>
       </c>
       <c r="N74" t="n">
-        <v>0.005341484148739252</v>
+        <v>0.005341484148739251</v>
       </c>
       <c r="O74" t="n">
         <v>0.009208051192570841</v>
       </c>
       <c r="P74" t="n">
-        <v>0.009170267449414222</v>
+        <v>0.00917026744941422</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.008048153330755897</v>
+        <v>0.008048153330755899</v>
       </c>
       <c r="R74" t="n">
-        <v>0.01071296148858976</v>
+        <v>0.01071296148858977</v>
       </c>
       <c r="S74" t="n">
         <v>0.01011398523060772</v>
@@ -5210,7 +5210,7 @@
         <v>1.148246810327173e-05</v>
       </c>
       <c r="D75" t="n">
-        <v>9.98819746069028e-06</v>
+        <v>9.988197460690279e-06</v>
       </c>
       <c r="E75" t="n">
         <v>1.130601136845054e-05</v>
@@ -5249,7 +5249,7 @@
         <v>1.692836404161228e-05</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.001018967822441e-05</v>
+        <v>2.00101896782244e-05</v>
       </c>
       <c r="R75" t="n">
         <v>1.784007663937982e-05</v>
@@ -5258,7 +5258,7 @@
         <v>2.312921799998797e-05</v>
       </c>
       <c r="T75" t="n">
-        <v>2.570642314378747e-05</v>
+        <v>2.570642314378748e-05</v>
       </c>
     </row>
     <row r="76">
@@ -5271,19 +5271,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.002855748211611106</v>
+        <v>0.002855748211611104</v>
       </c>
       <c r="D76" t="n">
         <v>0.002517184897131888</v>
       </c>
       <c r="E76" t="n">
-        <v>0.00239878281086061</v>
+        <v>0.002398782810860611</v>
       </c>
       <c r="F76" t="n">
         <v>0.002331037972674157</v>
       </c>
       <c r="G76" t="n">
-        <v>0.002338450902102357</v>
+        <v>0.002338450902102356</v>
       </c>
       <c r="H76" t="n">
         <v>0.002088608802357396</v>
@@ -5313,7 +5313,7 @@
         <v>0.006356555675617169</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.006116334800148482</v>
+        <v>0.006116334800148484</v>
       </c>
       <c r="R76" t="n">
         <v>0.007216108406888671</v>
@@ -5335,13 +5335,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7.658163187702156e-05</v>
+        <v>7.658163187702155e-05</v>
       </c>
       <c r="D77" t="n">
         <v>7.619584172118826e-05</v>
       </c>
       <c r="E77" t="n">
-        <v>6.905081099163797e-05</v>
+        <v>6.905081099163798e-05</v>
       </c>
       <c r="F77" t="n">
         <v>7.975822148057266e-05</v>
@@ -5377,13 +5377,13 @@
         <v>0.000285275949322136</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.0003251508966190126</v>
+        <v>0.0003251508966190125</v>
       </c>
       <c r="R77" t="n">
         <v>0.0003698002029785356</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0004230812038241612</v>
+        <v>0.0004230812038241611</v>
       </c>
       <c r="T77" t="n">
         <v>0.0003644749434877759</v>
@@ -5478,7 +5478,7 @@
         <v>0.0001199724246250904</v>
       </c>
       <c r="H79" t="n">
-        <v>8.977885100380975e-05</v>
+        <v>8.977885100380976e-05</v>
       </c>
       <c r="I79" t="n">
         <v>0.0001675499112394927</v>
@@ -5511,7 +5511,7 @@
         <v>0.0003050483196752891</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0003015831509391795</v>
+        <v>0.0003015831509391796</v>
       </c>
       <c r="T79" t="n">
         <v>0.0003080833499369033</v>
@@ -5533,13 +5533,13 @@
         <v>0.0002729345580055002</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0002743595057757287</v>
+        <v>0.0002743595057757288</v>
       </c>
       <c r="F80" t="n">
         <v>0.0002773450507326296</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0002925014035649999</v>
+        <v>0.0002925014035649998</v>
       </c>
       <c r="H80" t="n">
         <v>0.0003539100093949758</v>
@@ -5597,7 +5597,7 @@
         <v>0.0001568711143642637</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0001587643346957275</v>
+        <v>0.0001587643346957276</v>
       </c>
       <c r="F81" t="n">
         <v>0.0001188043199283739</v>
@@ -5609,13 +5609,13 @@
         <v>0.0001466113139045273</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0001655952826083398</v>
+        <v>0.0001655952826083399</v>
       </c>
       <c r="J81" t="n">
         <v>0.0001425239076559735</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0001485275694328215</v>
+        <v>0.0001485275694328214</v>
       </c>
       <c r="L81" t="n">
         <v>0.0001646050592459658</v>
@@ -5624,13 +5624,13 @@
         <v>0.0001633215648078686</v>
       </c>
       <c r="N81" t="n">
-        <v>0.0001801567229749179</v>
+        <v>0.0001801567229749178</v>
       </c>
       <c r="O81" t="n">
         <v>0.000258478308731706</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0002725668321110857</v>
+        <v>0.0002725668321110856</v>
       </c>
       <c r="Q81" t="n">
         <v>0.000216434770140497</v>
@@ -5639,7 +5639,7 @@
         <v>0.0002992909408363227</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002886783249889443</v>
+        <v>0.0002886783249889444</v>
       </c>
       <c r="T81" t="n">
         <v>0.0003129869239210119</v>
@@ -5688,7 +5688,7 @@
         <v>0.0002931700704963746</v>
       </c>
       <c r="N82" t="n">
-        <v>0.0003106399829279077</v>
+        <v>0.0003106399829279076</v>
       </c>
       <c r="O82" t="n">
         <v>0.0005791093652376137</v>
@@ -5700,10 +5700,10 @@
         <v>0.0004715192727253919</v>
       </c>
       <c r="R82" t="n">
-        <v>0.0005746344840495529</v>
+        <v>0.0005746344840495528</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0005564759762096572</v>
+        <v>0.0005564759762096573</v>
       </c>
       <c r="T82" t="n">
         <v>0.0006400847639002273</v>
@@ -5725,7 +5725,7 @@
         <v>0.004506007106331803</v>
       </c>
       <c r="E83" t="n">
-        <v>0.004454924966412116</v>
+        <v>0.004454924966412117</v>
       </c>
       <c r="F83" t="n">
         <v>0.005285177143953464</v>
@@ -5746,7 +5746,7 @@
         <v>0.008862321715640139</v>
       </c>
       <c r="L83" t="n">
-        <v>0.011346519002305</v>
+        <v>0.01134651900230501</v>
       </c>
       <c r="M83" t="n">
         <v>0.01151387063228431</v>
@@ -5758,7 +5758,7 @@
         <v>0.02108879396683409</v>
       </c>
       <c r="P83" t="n">
-        <v>0.02270046034455986</v>
+        <v>0.02270046034455987</v>
       </c>
       <c r="Q83" t="n">
         <v>0.0190386351649628</v>
@@ -5792,7 +5792,7 @@
         <v>0.0009577743596968522</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0008997746952792312</v>
+        <v>0.0008997746952792311</v>
       </c>
       <c r="G84" t="n">
         <v>0.0009694055827760408</v>
@@ -5807,7 +5807,7 @@
         <v>0.001562045860004699</v>
       </c>
       <c r="K84" t="n">
-        <v>0.001467961263609143</v>
+        <v>0.001467961263609142</v>
       </c>
       <c r="L84" t="n">
         <v>0.001867550217090584</v>
@@ -5822,7 +5822,7 @@
         <v>0.004054232182882252</v>
       </c>
       <c r="P84" t="n">
-        <v>0.00394160507185337</v>
+        <v>0.003941605071853369</v>
       </c>
       <c r="Q84" t="n">
         <v>0.003484121236049804</v>
@@ -5859,13 +5859,13 @@
         <v>0.0035558582133289</v>
       </c>
       <c r="G85" t="n">
-        <v>0.004310401491244084</v>
+        <v>0.004310401491244083</v>
       </c>
       <c r="H85" t="n">
         <v>0.003100232797072038</v>
       </c>
       <c r="I85" t="n">
-        <v>0.006614308741110702</v>
+        <v>0.006614308741110701</v>
       </c>
       <c r="J85" t="n">
         <v>0.005261331634382558</v>
@@ -5874,19 +5874,19 @@
         <v>0.005910522868272709</v>
       </c>
       <c r="L85" t="n">
-        <v>0.006769288866730987</v>
+        <v>0.006769288866730986</v>
       </c>
       <c r="M85" t="n">
         <v>0.00569626224108662</v>
       </c>
       <c r="N85" t="n">
-        <v>0.006911721816082954</v>
+        <v>0.006911721816082953</v>
       </c>
       <c r="O85" t="n">
-        <v>0.008260093950944927</v>
+        <v>0.008260093950944925</v>
       </c>
       <c r="P85" t="n">
-        <v>0.00774501056342385</v>
+        <v>0.007745010563423849</v>
       </c>
       <c r="Q85" t="n">
         <v>0.007884043777323282</v>
@@ -5895,10 +5895,10 @@
         <v>0.006963051169506447</v>
       </c>
       <c r="S85" t="n">
-        <v>0.006668479741154326</v>
+        <v>0.006668479741154325</v>
       </c>
       <c r="T85" t="n">
-        <v>0.008381917546987605</v>
+        <v>0.008381917546987604</v>
       </c>
     </row>
     <row r="86">
@@ -5917,10 +5917,10 @@
         <v>0.000466625396598411</v>
       </c>
       <c r="E86" t="n">
-        <v>0.0004583549288985006</v>
+        <v>0.0004583549288985007</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0004195312567306146</v>
+        <v>0.0004195312567306145</v>
       </c>
       <c r="G86" t="n">
         <v>0.0004408540326352081</v>
@@ -5929,19 +5929,19 @@
         <v>0.0005127973469333791</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0007002107399513153</v>
+        <v>0.0007002107399513152</v>
       </c>
       <c r="J86" t="n">
         <v>0.0006187911198732316</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0005957052440573665</v>
+        <v>0.0005957052440573666</v>
       </c>
       <c r="L86" t="n">
-        <v>0.0006785816912652621</v>
+        <v>0.0006785816912652622</v>
       </c>
       <c r="M86" t="n">
-        <v>0.0006725833698511504</v>
+        <v>0.0006725833698511503</v>
       </c>
       <c r="N86" t="n">
         <v>0.000730144239209097</v>
@@ -6042,7 +6042,7 @@
         <v>0.00870783520619991</v>
       </c>
       <c r="D88" t="n">
-        <v>0.008116964410070416</v>
+        <v>0.008116964410070414</v>
       </c>
       <c r="E88" t="n">
         <v>0.0093758027677012</v>
@@ -6051,10 +6051,10 @@
         <v>0.007986650505213799</v>
       </c>
       <c r="G88" t="n">
-        <v>0.009318147037737416</v>
+        <v>0.009318147037737418</v>
       </c>
       <c r="H88" t="n">
-        <v>0.007917772554059581</v>
+        <v>0.007917772554059579</v>
       </c>
       <c r="I88" t="n">
         <v>0.01284959218027198</v>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.0005392109507018496</v>
+        <v>0.0005392109507018495</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0004717256551576487</v>
+        <v>0.0004717256551576486</v>
       </c>
       <c r="E90" t="n">
         <v>0.0005995721524307948</v>
@@ -6182,10 +6182,10 @@
         <v>0.0004989308641313566</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0005015234822413138</v>
+        <v>0.0005015234822413136</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0006496322593720389</v>
+        <v>0.0006496322593720387</v>
       </c>
       <c r="J90" t="n">
         <v>0.0006290927455933049</v>
@@ -6194,10 +6194,10 @@
         <v>0.0005850455472596548</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0006551002120700135</v>
+        <v>0.0006551002120700136</v>
       </c>
       <c r="M90" t="n">
-        <v>0.0006954301821555452</v>
+        <v>0.0006954301821555453</v>
       </c>
       <c r="N90" t="n">
         <v>0.0006790115696505156</v>
@@ -6212,7 +6212,7 @@
         <v>0.001150661058439015</v>
       </c>
       <c r="R90" t="n">
-        <v>0.001220141357218769</v>
+        <v>0.001220141357218768</v>
       </c>
       <c r="S90" t="n">
         <v>0.001454559672401229</v>
@@ -6234,10 +6234,10 @@
         <v>3.303502857378957e-05</v>
       </c>
       <c r="D91" t="n">
-        <v>2.794863291993596e-05</v>
+        <v>2.794863291993597e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>3.046755499874787e-05</v>
+        <v>3.046755499874788e-05</v>
       </c>
       <c r="F91" t="n">
         <v>2.635200530601556e-05</v>
@@ -6252,7 +6252,7 @@
         <v>3.669041953988034e-05</v>
       </c>
       <c r="J91" t="n">
-        <v>3.026133856932021e-05</v>
+        <v>3.026133856932022e-05</v>
       </c>
       <c r="K91" t="n">
         <v>3.203148754749245e-05</v>
@@ -6261,7 +6261,7 @@
         <v>4.234130835879529e-05</v>
       </c>
       <c r="M91" t="n">
-        <v>4.095923290986501e-05</v>
+        <v>4.095923290986502e-05</v>
       </c>
       <c r="N91" t="n">
         <v>4.319490356070431e-05</v>
@@ -6273,10 +6273,10 @@
         <v>6.370576545466061e-05</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.550676677193373e-05</v>
+        <v>5.550676677193372e-05</v>
       </c>
       <c r="R91" t="n">
-        <v>7.631463801772467e-05</v>
+        <v>7.631463801772466e-05</v>
       </c>
       <c r="S91" t="n">
         <v>6.847682072770906e-05</v>
@@ -6298,13 +6298,13 @@
         <v>0.0002420094178200132</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0002170311398949466</v>
+        <v>0.0002170311398949467</v>
       </c>
       <c r="E92" t="n">
         <v>0.0002212119913315144</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0002006251282465114</v>
+        <v>0.0002006251282465115</v>
       </c>
       <c r="G92" t="n">
         <v>0.0002214256611316447</v>
@@ -6343,7 +6343,7 @@
         <v>0.0007806100577805832</v>
       </c>
       <c r="S92" t="n">
-        <v>0.0006892387582958308</v>
+        <v>0.000689238758295831</v>
       </c>
       <c r="T92" t="n">
         <v>0.0007778957398805565</v>
@@ -6444,7 +6444,7 @@
         <v>0.001155123068489884</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0009579376896422716</v>
+        <v>0.0009579376896422715</v>
       </c>
       <c r="K94" t="n">
         <v>0.001072934180125792</v>
@@ -6465,7 +6465,7 @@
         <v>0.001776095454893245</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.001523972816235017</v>
+        <v>0.001523972816235016</v>
       </c>
       <c r="R94" t="n">
         <v>0.002004638173650223</v>
@@ -6511,7 +6511,7 @@
         <v>0.001320725973201811</v>
       </c>
       <c r="K95" t="n">
-        <v>0.001396576441378234</v>
+        <v>0.001396576441378233</v>
       </c>
       <c r="L95" t="n">
         <v>0.001538037086567562</v>
@@ -6532,7 +6532,7 @@
         <v>0.001606839614141372</v>
       </c>
       <c r="R95" t="n">
-        <v>0.002015101849013545</v>
+        <v>0.002015101849013546</v>
       </c>
       <c r="S95" t="n">
         <v>0.001698296646146561</v>
@@ -6551,16 +6551,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.0005484323598017881</v>
+        <v>0.000548432359801788</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0004468424794750305</v>
+        <v>0.0004468424794750306</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0004380495068834314</v>
+        <v>0.0004380495068834315</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0004413682976343704</v>
+        <v>0.0004413682976343705</v>
       </c>
       <c r="G96" t="n">
         <v>0.0004971125578609572</v>
@@ -6569,34 +6569,34 @@
         <v>0.0007222300877987053</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0008245818733173216</v>
+        <v>0.0008245818733173217</v>
       </c>
       <c r="J96" t="n">
         <v>0.0007635328440068612</v>
       </c>
       <c r="K96" t="n">
-        <v>0.0007719817187753405</v>
+        <v>0.0007719817187753406</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0009035727868920771</v>
+        <v>0.0009035727868920772</v>
       </c>
       <c r="M96" t="n">
         <v>0.0008764307449400536</v>
       </c>
       <c r="N96" t="n">
-        <v>0.0009190582775236463</v>
+        <v>0.0009190582775236461</v>
       </c>
       <c r="O96" t="n">
         <v>0.001705439855194314</v>
       </c>
       <c r="P96" t="n">
-        <v>0.001516198584674411</v>
+        <v>0.00151619858467441</v>
       </c>
       <c r="Q96" t="n">
         <v>0.001486549729015858</v>
       </c>
       <c r="R96" t="n">
-        <v>0.001958621922117702</v>
+        <v>0.001958621922117703</v>
       </c>
       <c r="S96" t="n">
         <v>0.001970513469315935</v>
@@ -6618,16 +6618,16 @@
         <v>7.701167169960175e-05</v>
       </c>
       <c r="D97" t="n">
-        <v>8.104075655804425e-05</v>
+        <v>8.104075655804424e-05</v>
       </c>
       <c r="E97" t="n">
-        <v>7.256548044418694e-05</v>
+        <v>7.256548044418695e-05</v>
       </c>
       <c r="F97" t="n">
         <v>7.622686634854478e-05</v>
       </c>
       <c r="G97" t="n">
-        <v>8.064627535203272e-05</v>
+        <v>8.064627535203273e-05</v>
       </c>
       <c r="H97" t="n">
         <v>7.260925328747123e-05</v>
@@ -6642,7 +6642,7 @@
         <v>0.0001054507779651953</v>
       </c>
       <c r="L97" t="n">
-        <v>0.0001487846301531954</v>
+        <v>0.0001487846301531955</v>
       </c>
       <c r="M97" t="n">
         <v>0.0001364525827404441</v>
@@ -6679,13 +6679,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.0001808350778486647</v>
+        <v>0.0001808350778486648</v>
       </c>
       <c r="D98" t="n">
         <v>0.0001718924813051544</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0001649559660628178</v>
+        <v>0.0001649559660628179</v>
       </c>
       <c r="F98" t="n">
         <v>0.0001841309052624612</v>
@@ -6694,7 +6694,7 @@
         <v>0.0001787952269374826</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0002156467132180186</v>
+        <v>0.0002156467132180187</v>
       </c>
       <c r="I98" t="n">
         <v>0.0002941728033252369</v>
@@ -6703,7 +6703,7 @@
         <v>0.0002374653927649974</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0002510997440461437</v>
+        <v>0.0002510997440461436</v>
       </c>
       <c r="L98" t="n">
         <v>0.0003189446216440611</v>
@@ -6715,22 +6715,22 @@
         <v>0.0003219204796648441</v>
       </c>
       <c r="O98" t="n">
-        <v>0.0005564044943689389</v>
+        <v>0.000556404494368939</v>
       </c>
       <c r="P98" t="n">
-        <v>0.0005853360449993805</v>
+        <v>0.0005853360449993807</v>
       </c>
       <c r="Q98" t="n">
         <v>0.0005265538925808735</v>
       </c>
       <c r="R98" t="n">
-        <v>0.0006518565227318971</v>
+        <v>0.0006518565227318972</v>
       </c>
       <c r="S98" t="n">
         <v>0.000615149070053512</v>
       </c>
       <c r="T98" t="n">
-        <v>0.0006668033571970915</v>
+        <v>0.0006668033571970913</v>
       </c>
     </row>
     <row r="99">
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8.704711364973073e-05</v>
+        <v>8.704711364973072e-05</v>
       </c>
       <c r="D99" t="n">
         <v>7.579090925858129e-05</v>
@@ -6752,7 +6752,7 @@
         <v>9.656937524371245e-05</v>
       </c>
       <c r="F99" t="n">
-        <v>9.365582743305199e-05</v>
+        <v>9.365582743305198e-05</v>
       </c>
       <c r="G99" t="n">
         <v>9.62005825567072e-05</v>
@@ -6764,13 +6764,13 @@
         <v>0.0001656440504978349</v>
       </c>
       <c r="J99" t="n">
-        <v>0.0001497115232754683</v>
+        <v>0.0001497115232754684</v>
       </c>
       <c r="K99" t="n">
         <v>0.0001386015078837818</v>
       </c>
       <c r="L99" t="n">
-        <v>0.0001643956793533565</v>
+        <v>0.0001643956793533564</v>
       </c>
       <c r="M99" t="n">
         <v>0.0001584900834957547</v>
@@ -6794,7 +6794,7 @@
         <v>0.0003268819658070942</v>
       </c>
       <c r="T99" t="n">
-        <v>0.0003344510887496724</v>
+        <v>0.0003344510887496723</v>
       </c>
     </row>
     <row r="100">
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.000423177113898953</v>
+        <v>0.0004231771138989529</v>
       </c>
       <c r="D100" t="n">
         <v>0.0003793465581696168</v>
@@ -6819,7 +6819,7 @@
         <v>0.0003563266228121634</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0003545382326522412</v>
+        <v>0.0003545382326522413</v>
       </c>
       <c r="H100" t="n">
         <v>0.0004377629325855748</v>
@@ -6828,7 +6828,7 @@
         <v>0.0005521566328917952</v>
       </c>
       <c r="J100" t="n">
-        <v>0.0004684235170160269</v>
+        <v>0.000468423517016027</v>
       </c>
       <c r="K100" t="n">
         <v>0.0004654911258274828</v>
@@ -6840,10 +6840,10 @@
         <v>0.0005236529395144842</v>
       </c>
       <c r="N100" t="n">
-        <v>0.0005653204023816143</v>
+        <v>0.0005653204023816145</v>
       </c>
       <c r="O100" t="n">
-        <v>0.0008829934578995643</v>
+        <v>0.0008829934578995642</v>
       </c>
       <c r="P100" t="n">
         <v>0.0008759370355471241</v>
@@ -6871,13 +6871,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.0005148097991461039</v>
+        <v>0.000514809799146104</v>
       </c>
       <c r="D101" t="n">
         <v>0.0005059353880968008</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0004684685064736216</v>
+        <v>0.0004684685064736215</v>
       </c>
       <c r="F101" t="n">
         <v>0.0003725797737103704</v>
@@ -6886,10 +6886,10 @@
         <v>0.0004446589937113733</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0003936241574469447</v>
+        <v>0.0003936241574469448</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0006765232233377166</v>
+        <v>0.0006765232233377168</v>
       </c>
       <c r="J101" t="n">
         <v>0.0005281283995391038</v>
@@ -6898,7 +6898,7 @@
         <v>0.0006213107411406873</v>
       </c>
       <c r="L101" t="n">
-        <v>0.0006838931965741704</v>
+        <v>0.0006838931965741703</v>
       </c>
       <c r="M101" t="n">
         <v>0.0007218665513508001</v>
@@ -6922,7 +6922,7 @@
         <v>0.001323644940541444</v>
       </c>
       <c r="T101" t="n">
-        <v>0.001434770892768381</v>
+        <v>0.001434770892768382</v>
       </c>
     </row>
     <row r="102">
@@ -6959,25 +6959,25 @@
         <v>0.005212749995645417</v>
       </c>
       <c r="K102" t="n">
-        <v>0.00510662924736902</v>
+        <v>0.005106629247369019</v>
       </c>
       <c r="L102" t="n">
-        <v>0.00565070780874631</v>
+        <v>0.005650707808746309</v>
       </c>
       <c r="M102" t="n">
         <v>0.005395045018860396</v>
       </c>
       <c r="N102" t="n">
-        <v>0.005372424297664287</v>
+        <v>0.005372424297664286</v>
       </c>
       <c r="O102" t="n">
-        <v>0.01005945311592489</v>
+        <v>0.0100594531159249</v>
       </c>
       <c r="P102" t="n">
         <v>0.009672649091345355</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.007200974759195215</v>
+        <v>0.007200974759195216</v>
       </c>
       <c r="R102" t="n">
         <v>0.01271129314764806</v>
@@ -7041,10 +7041,10 @@
         <v>0.0002828299400506825</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.0002928754704679277</v>
+        <v>0.0002928754704679278</v>
       </c>
       <c r="R103" t="n">
-        <v>0.0003778738134815902</v>
+        <v>0.0003778738134815903</v>
       </c>
       <c r="S103" t="n">
         <v>0.0003483257266093061</v>
@@ -7081,7 +7081,7 @@
         <v>0.0002306745161648559</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0003745247389744516</v>
+        <v>0.0003745247389744517</v>
       </c>
       <c r="J104" t="n">
         <v>0.0003187553514866948</v>
@@ -7102,19 +7102,19 @@
         <v>0.0005819078942641007</v>
       </c>
       <c r="P104" t="n">
-        <v>0.0005807431175099125</v>
+        <v>0.0005807431175099124</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.0005514187192513978</v>
+        <v>0.000551418719251398</v>
       </c>
       <c r="R104" t="n">
-        <v>0.0006149388012945307</v>
+        <v>0.0006149388012945306</v>
       </c>
       <c r="S104" t="n">
         <v>0.0006168579429813346</v>
       </c>
       <c r="T104" t="n">
-        <v>0.0007103882863493944</v>
+        <v>0.0007103882863493943</v>
       </c>
     </row>
     <row r="105">
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.0003281195260737335</v>
+        <v>0.0003281195260737334</v>
       </c>
       <c r="D105" t="n">
         <v>0.0002992334864261158</v>
@@ -7139,10 +7139,10 @@
         <v>0.0002711204103280613</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0002843057261366183</v>
+        <v>0.0002843057261366184</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0002937350389962246</v>
+        <v>0.0002937350389962245</v>
       </c>
       <c r="I105" t="n">
         <v>0.0004309743791230669</v>
@@ -7160,13 +7160,13 @@
         <v>0.00041097819110799</v>
       </c>
       <c r="N105" t="n">
-        <v>0.0004352813924060796</v>
+        <v>0.0004352813924060797</v>
       </c>
       <c r="O105" t="n">
         <v>0.0006138876562689627</v>
       </c>
       <c r="P105" t="n">
-        <v>0.0006859380279745258</v>
+        <v>0.0006859380279745259</v>
       </c>
       <c r="Q105" t="n">
         <v>0.0006079043915093755</v>
@@ -7203,7 +7203,7 @@
         <v>0.000468587409488516</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0005223190404285562</v>
+        <v>0.0005223190404285563</v>
       </c>
       <c r="H106" t="n">
         <v>0.0005744933669933773</v>
@@ -7215,10 +7215,10 @@
         <v>0.0006357353647402054</v>
       </c>
       <c r="K106" t="n">
-        <v>0.0006361350558831928</v>
+        <v>0.0006361350558831927</v>
       </c>
       <c r="L106" t="n">
-        <v>0.0006975126028247368</v>
+        <v>0.0006975126028247367</v>
       </c>
       <c r="M106" t="n">
         <v>0.0007085769844078783</v>
@@ -7258,10 +7258,10 @@
         <v>0.0001203949576113875</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0001039714513592692</v>
+        <v>0.0001039714513592693</v>
       </c>
       <c r="E107" t="n">
-        <v>8.275764508310723e-05</v>
+        <v>8.275764508310722e-05</v>
       </c>
       <c r="F107" t="n">
         <v>0.0001105674924716778</v>
@@ -7328,19 +7328,19 @@
         <v>0.001511376326740963</v>
       </c>
       <c r="F108" t="n">
-        <v>0.001378596432646691</v>
+        <v>0.00137859643264669</v>
       </c>
       <c r="G108" t="n">
         <v>0.001444830131909845</v>
       </c>
       <c r="H108" t="n">
-        <v>0.001663990918669541</v>
+        <v>0.00166399091866954</v>
       </c>
       <c r="I108" t="n">
         <v>0.002059701171953409</v>
       </c>
       <c r="J108" t="n">
-        <v>0.001825634799248106</v>
+        <v>0.001825634799248105</v>
       </c>
       <c r="K108" t="n">
         <v>0.001842983141750745</v>
@@ -7355,13 +7355,13 @@
         <v>0.002159379518076259</v>
       </c>
       <c r="O108" t="n">
-        <v>0.003172511747497063</v>
+        <v>0.003172511747497062</v>
       </c>
       <c r="P108" t="n">
         <v>0.003357961804295501</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.003082666717881194</v>
+        <v>0.003082666717881193</v>
       </c>
       <c r="R108" t="n">
         <v>0.003779187269129662</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.000509017456725107</v>
+        <v>0.0005090174567251069</v>
       </c>
       <c r="D110" t="n">
         <v>0.0004652649040581745</v>
@@ -7486,7 +7486,7 @@
         <v>0.001055216403329197</v>
       </c>
       <c r="P110" t="n">
-        <v>0.001161792543355036</v>
+        <v>0.001161792543355035</v>
       </c>
       <c r="Q110" t="n">
         <v>0.0008645508298559274</v>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.007147848405644122</v>
+        <v>0.007147848405644123</v>
       </c>
       <c r="D111" t="n">
-        <v>0.006530013923308906</v>
+        <v>0.006530013923308905</v>
       </c>
       <c r="E111" t="n">
         <v>0.006737260256479563</v>
@@ -7523,19 +7523,19 @@
         <v>0.005652538325049849</v>
       </c>
       <c r="G111" t="n">
-        <v>0.006064454686206187</v>
+        <v>0.006064454686206185</v>
       </c>
       <c r="H111" t="n">
-        <v>0.007214653678758311</v>
+        <v>0.007214653678758307</v>
       </c>
       <c r="I111" t="n">
-        <v>0.008791239177832396</v>
+        <v>0.008791239177832397</v>
       </c>
       <c r="J111" t="n">
-        <v>0.007365134961187588</v>
+        <v>0.007365134961187587</v>
       </c>
       <c r="K111" t="n">
-        <v>0.007696000366660277</v>
+        <v>0.007696000366660278</v>
       </c>
       <c r="L111" t="n">
         <v>0.008531112633392924</v>
@@ -7562,7 +7562,7 @@
         <v>0.01596738982076322</v>
       </c>
       <c r="T111" t="n">
-        <v>0.01592855732443636</v>
+        <v>0.01592855732443635</v>
       </c>
     </row>
     <row r="112">
@@ -7575,19 +7575,19 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.0005462515712837933</v>
+        <v>0.0005462515712837932</v>
       </c>
       <c r="D112" t="n">
-        <v>0.0004774197466258875</v>
+        <v>0.0004774197466258876</v>
       </c>
       <c r="E112" t="n">
         <v>0.0006043427719283416</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0004740470611210125</v>
+        <v>0.0004740470611210126</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0005040043478129773</v>
+        <v>0.0005040043478129772</v>
       </c>
       <c r="H112" t="n">
         <v>0.0005086751465523831</v>
@@ -7596,10 +7596,10 @@
         <v>0.0006598873882081577</v>
       </c>
       <c r="J112" t="n">
-        <v>0.0006362950144766721</v>
+        <v>0.000636295014476672</v>
       </c>
       <c r="K112" t="n">
-        <v>0.0005948713730393359</v>
+        <v>0.000594871373039336</v>
       </c>
       <c r="L112" t="n">
         <v>0.0006676143735352389</v>
@@ -7617,7 +7617,7 @@
         <v>0.001045698333829123</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.001171191905468555</v>
+        <v>0.001171191905468556</v>
       </c>
       <c r="R112" t="n">
         <v>0.001241955291913951</v>
@@ -7648,7 +7648,7 @@
         <v>8.280865218580709e-05</v>
       </c>
       <c r="F113" t="n">
-        <v>7.565264779590263e-05</v>
+        <v>7.565264779590264e-05</v>
       </c>
       <c r="G113" t="n">
         <v>7.48769002934442e-05</v>
@@ -7715,10 +7715,10 @@
         <v>5.261395280240512e-05</v>
       </c>
       <c r="G114" t="n">
-        <v>5.042760941476643e-05</v>
+        <v>5.042760941476644e-05</v>
       </c>
       <c r="H114" t="n">
-        <v>8.585300278822268e-05</v>
+        <v>8.585300278822269e-05</v>
       </c>
       <c r="I114" t="n">
         <v>7.864422016270533e-05</v>
@@ -7730,7 +7730,7 @@
         <v>7.283201563832664e-05</v>
       </c>
       <c r="L114" t="n">
-        <v>8.157936311453009e-05</v>
+        <v>8.157936311453007e-05</v>
       </c>
       <c r="M114" t="n">
         <v>8.846380209521194e-05</v>
@@ -7776,7 +7776,7 @@
         <v>0.001037536273876655</v>
       </c>
       <c r="F115" t="n">
-        <v>0.00099906195723479</v>
+        <v>0.0009990619572347898</v>
       </c>
       <c r="G115" t="n">
         <v>0.001038747981050774</v>
@@ -7791,7 +7791,7 @@
         <v>0.001380778166489826</v>
       </c>
       <c r="K115" t="n">
-        <v>0.001403785110581797</v>
+        <v>0.001403785110581796</v>
       </c>
       <c r="L115" t="n">
         <v>0.001762556040017662</v>
@@ -7876,13 +7876,13 @@
         <v>0.0005924630684149527</v>
       </c>
       <c r="R116" t="n">
-        <v>0.0006492516222633955</v>
+        <v>0.0006492516222633954</v>
       </c>
       <c r="S116" t="n">
         <v>0.0006594607850583615</v>
       </c>
       <c r="T116" t="n">
-        <v>0.0007669408186580522</v>
+        <v>0.0007669408186580523</v>
       </c>
     </row>
     <row r="117">
@@ -7968,7 +7968,7 @@
         <v>2.607339466893031e-05</v>
       </c>
       <c r="F118" t="n">
-        <v>3.102408228519346e-05</v>
+        <v>3.102408228519345e-05</v>
       </c>
       <c r="G118" t="n">
         <v>2.998009329252379e-05</v>
@@ -7977,7 +7977,7 @@
         <v>2.909157938992634e-05</v>
       </c>
       <c r="I118" t="n">
-        <v>5.125573469826685e-05</v>
+        <v>5.125573469826686e-05</v>
       </c>
       <c r="J118" t="n">
         <v>4.602646479555879e-05</v>
@@ -7989,7 +7989,7 @@
         <v>5.024265045365883e-05</v>
       </c>
       <c r="M118" t="n">
-        <v>5.26356345096262e-05</v>
+        <v>5.263563450962619e-05</v>
       </c>
       <c r="N118" t="n">
         <v>5.554544091376503e-05</v>
@@ -8023,22 +8023,22 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.0008374511892421999</v>
+        <v>0.0008374511892421997</v>
       </c>
       <c r="D119" t="n">
-        <v>0.0007057024568883136</v>
+        <v>0.0007057024568883135</v>
       </c>
       <c r="E119" t="n">
         <v>0.0007760414324597531</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0008854474032033802</v>
+        <v>0.0008854474032033803</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0009385091090253417</v>
+        <v>0.0009385091090253415</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0009041365314913683</v>
+        <v>0.0009041365314913682</v>
       </c>
       <c r="I119" t="n">
         <v>0.001579205010724203</v>
@@ -8047,13 +8047,13 @@
         <v>0.001348083700130227</v>
       </c>
       <c r="K119" t="n">
-        <v>0.001408710299861892</v>
+        <v>0.001408710299861893</v>
       </c>
       <c r="L119" t="n">
         <v>0.001668597086511535</v>
       </c>
       <c r="M119" t="n">
-        <v>0.001533844657351755</v>
+        <v>0.001533844657351756</v>
       </c>
       <c r="N119" t="n">
         <v>0.001706667776595202</v>
@@ -8087,16 +8087,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.08294435941061663</v>
+        <v>0.08294435941061665</v>
       </c>
       <c r="D120" t="n">
         <v>0.07244715071478684</v>
       </c>
       <c r="E120" t="n">
-        <v>0.07671815958582948</v>
+        <v>0.07671815958582949</v>
       </c>
       <c r="F120" t="n">
-        <v>0.07302167194658783</v>
+        <v>0.07302167194658785</v>
       </c>
       <c r="G120" t="n">
         <v>0.07399650220444437</v>
@@ -8114,7 +8114,7 @@
         <v>0.1056934808324097</v>
       </c>
       <c r="L120" t="n">
-        <v>0.152542185921069</v>
+        <v>0.1525421859210691</v>
       </c>
       <c r="M120" t="n">
         <v>0.1478156520677522</v>
@@ -8123,22 +8123,22 @@
         <v>0.1372769812164505</v>
       </c>
       <c r="O120" t="n">
-        <v>0.3631557318321336</v>
+        <v>0.3631557318321335</v>
       </c>
       <c r="P120" t="n">
         <v>0.3622728467840045</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.3366920965255813</v>
+        <v>0.3366920965255814</v>
       </c>
       <c r="R120" t="n">
-        <v>0.544470831207703</v>
+        <v>0.5444708312077031</v>
       </c>
       <c r="S120" t="n">
-        <v>0.5759239926054918</v>
+        <v>0.5759239926054915</v>
       </c>
       <c r="T120" t="n">
-        <v>0.5645843964217836</v>
+        <v>0.5645843964217835</v>
       </c>
     </row>
     <row r="121">
@@ -8221,13 +8221,13 @@
         <v>0.0001005766095714286</v>
       </c>
       <c r="E122" t="n">
-        <v>9.683241931202645e-05</v>
+        <v>9.683241931202646e-05</v>
       </c>
       <c r="F122" t="n">
-        <v>9.336942671152425e-05</v>
+        <v>9.336942671152424e-05</v>
       </c>
       <c r="G122" t="n">
-        <v>9.700381777678583e-05</v>
+        <v>9.700381777678582e-05</v>
       </c>
       <c r="H122" t="n">
         <v>6.444175435842752e-05</v>
@@ -8248,7 +8248,7 @@
         <v>0.0001133082436819777</v>
       </c>
       <c r="N122" t="n">
-        <v>0.0001414580864127322</v>
+        <v>0.0001414580864127321</v>
       </c>
       <c r="O122" t="n">
         <v>0.0001634599540315375</v>
@@ -8285,10 +8285,10 @@
         <v>0.003433297728151166</v>
       </c>
       <c r="E123" t="n">
-        <v>0.003533748019788138</v>
+        <v>0.003533748019788139</v>
       </c>
       <c r="F123" t="n">
-        <v>0.00294882252699109</v>
+        <v>0.002948822526991089</v>
       </c>
       <c r="G123" t="n">
         <v>0.003054973716370517</v>
@@ -8303,13 +8303,13 @@
         <v>0.004213765123830884</v>
       </c>
       <c r="K123" t="n">
-        <v>0.00419173777408448</v>
+        <v>0.004191737774084481</v>
       </c>
       <c r="L123" t="n">
         <v>0.005015183497732232</v>
       </c>
       <c r="M123" t="n">
-        <v>0.004480007275639679</v>
+        <v>0.004480007275639681</v>
       </c>
       <c r="N123" t="n">
         <v>0.00490965492978022</v>
@@ -8318,7 +8318,7 @@
         <v>0.008199627325934856</v>
       </c>
       <c r="P123" t="n">
-        <v>0.008452697600896977</v>
+        <v>0.008452697600896978</v>
       </c>
       <c r="Q123" t="n">
         <v>0.009383636265620223</v>
@@ -8373,7 +8373,7 @@
         <v>0.002227931083909796</v>
       </c>
       <c r="M124" t="n">
-        <v>0.00234336773060925</v>
+        <v>0.002343367730609251</v>
       </c>
       <c r="N124" t="n">
         <v>0.00234432522969461</v>
@@ -8385,7 +8385,7 @@
         <v>0.003846416694744855</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.00297414587674308</v>
+        <v>0.002974145876743081</v>
       </c>
       <c r="R124" t="n">
         <v>0.003818410215955781</v>
@@ -8443,7 +8443,7 @@
         <v>0.005347422089636876</v>
       </c>
       <c r="O125" t="n">
-        <v>0.007723229612201963</v>
+        <v>0.007723229612201965</v>
       </c>
       <c r="P125" t="n">
         <v>0.008097523801534201</v>
@@ -8477,7 +8477,7 @@
         <v>7.61832913938599e-05</v>
       </c>
       <c r="E126" t="n">
-        <v>6.984882314639063e-05</v>
+        <v>6.984882314639062e-05</v>
       </c>
       <c r="F126" t="n">
         <v>8.099354807239215e-05</v>
@@ -8538,7 +8538,7 @@
         <v>0.0003341776578469771</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0002947399868782469</v>
+        <v>0.0002947399868782468</v>
       </c>
       <c r="E127" t="n">
         <v>0.0002587802709785501</v>
@@ -8547,7 +8547,7 @@
         <v>0.0003191228624974081</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0003228298492788282</v>
+        <v>0.0003228298492788283</v>
       </c>
       <c r="H127" t="n">
         <v>0.0003097559130749407</v>
@@ -8559,7 +8559,7 @@
         <v>0.0004478897516809736</v>
       </c>
       <c r="K127" t="n">
-        <v>0.0004808507830728366</v>
+        <v>0.0004808507830728365</v>
       </c>
       <c r="L127" t="n">
         <v>0.0005766476522944178</v>
@@ -8577,7 +8577,7 @@
         <v>0.001033917156256942</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.00113997456900021</v>
+        <v>0.001139974569000209</v>
       </c>
       <c r="R127" t="n">
         <v>0.001354100336958297</v>
@@ -8586,7 +8586,7 @@
         <v>0.001432423578940734</v>
       </c>
       <c r="T127" t="n">
-        <v>0.001441582478889106</v>
+        <v>0.001441582478889107</v>
       </c>
     </row>
     <row r="128">
@@ -8614,7 +8614,7 @@
         <v>0.0007949861284293209</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0005788121959783459</v>
+        <v>0.0005788121959783458</v>
       </c>
       <c r="I128" t="n">
         <v>0.001090662804698195</v>
@@ -8623,7 +8623,7 @@
         <v>0.0008439556200055046</v>
       </c>
       <c r="K128" t="n">
-        <v>0.0009637269702751815</v>
+        <v>0.0009637269702751817</v>
       </c>
       <c r="L128" t="n">
         <v>0.001043186885857015</v>
@@ -8666,10 +8666,10 @@
         <v>0.0002836671988360609</v>
       </c>
       <c r="D129" t="n">
-        <v>0.0002364355398638174</v>
+        <v>0.0002364355398638173</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0002384822229516348</v>
+        <v>0.0002384822229516347</v>
       </c>
       <c r="F129" t="n">
         <v>0.00021546268793467</v>
@@ -8678,7 +8678,7 @@
         <v>0.0002167103776823667</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0002843712783910106</v>
+        <v>0.0002843712783910105</v>
       </c>
       <c r="I129" t="n">
         <v>0.0003781142538314995</v>
@@ -8693,22 +8693,22 @@
         <v>0.0003765201396395068</v>
       </c>
       <c r="M129" t="n">
-        <v>0.0003542130558630514</v>
+        <v>0.0003542130558630515</v>
       </c>
       <c r="N129" t="n">
-        <v>0.0003635452266774499</v>
+        <v>0.0003635452266774498</v>
       </c>
       <c r="O129" t="n">
-        <v>0.0006140476376906024</v>
+        <v>0.0006140476376906025</v>
       </c>
       <c r="P129" t="n">
-        <v>0.0006103948064226453</v>
+        <v>0.0006103948064226452</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.0006760158205681157</v>
+        <v>0.0006760158205681158</v>
       </c>
       <c r="R129" t="n">
-        <v>0.0008661138138434084</v>
+        <v>0.0008661138138434085</v>
       </c>
       <c r="S129" t="n">
         <v>0.0008763401449718079</v>
@@ -8742,7 +8742,7 @@
         <v>0.0001889567661646296</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0001811583334806759</v>
+        <v>0.0001811583334806758</v>
       </c>
       <c r="I130" t="n">
         <v>0.0002828623328330711</v>
@@ -8766,7 +8766,7 @@
         <v>0.0005032180095659545</v>
       </c>
       <c r="P130" t="n">
-        <v>0.0005143332813676094</v>
+        <v>0.0005143332813676093</v>
       </c>
       <c r="Q130" t="n">
         <v>0.0004815063007408813</v>
@@ -8775,10 +8775,10 @@
         <v>0.0006195055794507304</v>
       </c>
       <c r="S130" t="n">
-        <v>0.0005930251422931645</v>
+        <v>0.0005930251422931644</v>
       </c>
       <c r="T130" t="n">
-        <v>0.0006181830083405932</v>
+        <v>0.0006181830083405933</v>
       </c>
     </row>
     <row r="131">
@@ -8797,19 +8797,19 @@
         <v>0.0003719655846756468</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0003911675795254287</v>
+        <v>0.0003911675795254288</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0003877323243535501</v>
+        <v>0.00038773232435355</v>
       </c>
       <c r="G131" t="n">
         <v>0.0004071351563649744</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0003954544500542532</v>
+        <v>0.0003954544500542531</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0005970426026338271</v>
+        <v>0.0005970426026338269</v>
       </c>
       <c r="J131" t="n">
         <v>0.0005076960394431194</v>
@@ -8821,7 +8821,7 @@
         <v>0.0006497051065133891</v>
       </c>
       <c r="M131" t="n">
-        <v>0.0006331856630348602</v>
+        <v>0.00063318566303486</v>
       </c>
       <c r="N131" t="n">
         <v>0.0006653381405512702</v>
@@ -8833,7 +8833,7 @@
         <v>0.001027326335436446</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.00104423979471078</v>
+        <v>0.001044239794710779</v>
       </c>
       <c r="R131" t="n">
         <v>0.001279003625796201</v>
@@ -8891,10 +8891,10 @@
         <v>0.0003872843139111436</v>
       </c>
       <c r="O132" t="n">
-        <v>0.0006076135811136491</v>
+        <v>0.000607613581113649</v>
       </c>
       <c r="P132" t="n">
-        <v>0.0006277066171719668</v>
+        <v>0.0006277066171719665</v>
       </c>
       <c r="Q132" t="n">
         <v>0.0006321351751211766</v>
@@ -8928,10 +8928,10 @@
         <v>0.00453044603107151</v>
       </c>
       <c r="F133" t="n">
-        <v>0.004946411591386994</v>
+        <v>0.004946411591386993</v>
       </c>
       <c r="G133" t="n">
-        <v>0.005366816874833896</v>
+        <v>0.005366816874833897</v>
       </c>
       <c r="H133" t="n">
         <v>0.005107404369321484</v>
@@ -9004,7 +9004,7 @@
         <v>1.33219437242415e-05</v>
       </c>
       <c r="J134" t="n">
-        <v>1.179705885810154e-05</v>
+        <v>1.179705885810155e-05</v>
       </c>
       <c r="K134" t="n">
         <v>9.577847415904517e-06</v>
@@ -9016,7 +9016,7 @@
         <v>1.409286831441157e-05</v>
       </c>
       <c r="N134" t="n">
-        <v>1.449712576945149e-05</v>
+        <v>1.449712576945148e-05</v>
       </c>
       <c r="O134" t="n">
         <v>1.263812129707981e-05</v>
@@ -9056,7 +9056,7 @@
         <v>9.797921758509899e-05</v>
       </c>
       <c r="F135" t="n">
-        <v>6.877796220409667e-05</v>
+        <v>6.877796220409668e-05</v>
       </c>
       <c r="G135" t="n">
         <v>7.820272408018849e-05</v>
@@ -9071,7 +9071,7 @@
         <v>9.003486421357502e-05</v>
       </c>
       <c r="K135" t="n">
-        <v>9.022922387731304e-05</v>
+        <v>9.022922387731306e-05</v>
       </c>
       <c r="L135" t="n">
         <v>0.0001185008957910504</v>
@@ -9089,13 +9089,13 @@
         <v>0.0002379470581590378</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.0002369660470445204</v>
+        <v>0.0002369660470445203</v>
       </c>
       <c r="R135" t="n">
         <v>0.0002908111372404711</v>
       </c>
       <c r="S135" t="n">
-        <v>0.0002868133134086002</v>
+        <v>0.0002868133134086001</v>
       </c>
       <c r="T135" t="n">
         <v>0.0003034399261225309</v>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3.984140385409661e-05</v>
+        <v>3.984140385409662e-05</v>
       </c>
       <c r="D138" t="n">
         <v>3.715961333039431e-05</v>
@@ -9248,25 +9248,25 @@
         <v>2.917419740295242e-05</v>
       </c>
       <c r="F138" t="n">
-        <v>3.76284869934375e-05</v>
+        <v>3.762848699343751e-05</v>
       </c>
       <c r="G138" t="n">
         <v>3.924275058133753e-05</v>
       </c>
       <c r="H138" t="n">
-        <v>3.288404754335539e-05</v>
+        <v>3.28840475433554e-05</v>
       </c>
       <c r="I138" t="n">
         <v>5.615126011644947e-05</v>
       </c>
       <c r="J138" t="n">
-        <v>4.201461271103691e-05</v>
+        <v>4.201461271103692e-05</v>
       </c>
       <c r="K138" t="n">
         <v>4.868407987707679e-05</v>
       </c>
       <c r="L138" t="n">
-        <v>5.72652502153265e-05</v>
+        <v>5.726525021532649e-05</v>
       </c>
       <c r="M138" t="n">
         <v>4.188488593922221e-05</v>
@@ -9315,22 +9315,22 @@
         <v>2.616333229675459e-05</v>
       </c>
       <c r="G139" t="n">
-        <v>2.827222748311833e-05</v>
+        <v>2.827222748311832e-05</v>
       </c>
       <c r="H139" t="n">
         <v>2.7021572002866e-05</v>
       </c>
       <c r="I139" t="n">
-        <v>4.085095622685301e-05</v>
+        <v>4.085095622685302e-05</v>
       </c>
       <c r="J139" t="n">
         <v>3.164702132123839e-05</v>
       </c>
       <c r="K139" t="n">
-        <v>3.464555468065137e-05</v>
+        <v>3.464555468065138e-05</v>
       </c>
       <c r="L139" t="n">
-        <v>3.972424983017392e-05</v>
+        <v>3.972424983017393e-05</v>
       </c>
       <c r="M139" t="n">
         <v>2.912079709059454e-05</v>
@@ -9354,7 +9354,7 @@
         <v>7.788555778846933e-05</v>
       </c>
       <c r="T139" t="n">
-        <v>7.829605240254976e-05</v>
+        <v>7.829605240254974e-05</v>
       </c>
     </row>
     <row r="140">

--- a/data/proteomics/volume_size_across_compartment_Rosemary_NH4_limitation_v2.xlsx
+++ b/data/proteomics/volume_size_across_compartment_Rosemary_NH4_limitation_v2.xlsx
@@ -535,37 +535,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5216809007133781</v>
+        <v>0.5216809007133776</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4769684679962734</v>
+        <v>0.4769684679962738</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4955760349940506</v>
+        <v>0.4955760349940507</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3931105192359026</v>
+        <v>0.3931105192359032</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4126024609285298</v>
+        <v>0.4126024609285293</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5771677796630983</v>
+        <v>0.5771677796630987</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5979680544289928</v>
+        <v>0.5979680544289935</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5145316142675036</v>
+        <v>0.5145316142675039</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5237126928475407</v>
+        <v>0.523712692847541</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5596213794442285</v>
+        <v>0.5596213794442295</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5561694262491248</v>
+        <v>0.5561694262491246</v>
       </c>
       <c r="N2" t="n">
         <v>0.5643625727006305</v>
@@ -574,19 +574,19 @@
         <v>1.003591251627263</v>
       </c>
       <c r="P2" t="n">
-        <v>1.007038524996121</v>
+        <v>1.00703852499612</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9431744942485611</v>
+        <v>0.943174494248561</v>
       </c>
       <c r="R2" t="n">
         <v>1.268954997959019</v>
       </c>
       <c r="S2" t="n">
-        <v>1.349875761704192</v>
+        <v>1.349875761704194</v>
       </c>
       <c r="T2" t="n">
-        <v>1.336206532461347</v>
+        <v>1.336206532461349</v>
       </c>
     </row>
     <row r="3">
@@ -620,7 +620,7 @@
         <v>0.001311823358583556</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001083998113460815</v>
+        <v>0.001083998113460814</v>
       </c>
       <c r="K3" t="n">
         <v>0.001206541460260438</v>
@@ -638,7 +638,7 @@
         <v>0.00177001969155968</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001821413848389597</v>
+        <v>0.001821413848389598</v>
       </c>
       <c r="Q3" t="n">
         <v>0.001763168397826595</v>
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0008741687319571382</v>
+        <v>0.0008741687319571379</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008074599409869479</v>
+        <v>0.0008074599409869483</v>
       </c>
       <c r="E4" t="n">
         <v>0.0008581465688309836</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000814540315898813</v>
+        <v>0.0008145403158988128</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008517442446959935</v>
+        <v>0.0008517442446959936</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008725942137095188</v>
+        <v>0.0008725942137095186</v>
       </c>
       <c r="I4" t="n">
         <v>0.001235246266824286</v>
@@ -705,13 +705,13 @@
         <v>0.002022179705322244</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002045656496334061</v>
+        <v>0.002045656496334062</v>
       </c>
       <c r="R4" t="n">
         <v>0.002390734275881163</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00284641807427786</v>
+        <v>0.002846418074277858</v>
       </c>
       <c r="T4" t="n">
         <v>0.002696512095604279</v>
@@ -791,55 +791,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3059797381717774</v>
+        <v>0.3059797381717771</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2810077369380482</v>
+        <v>0.281007736938048</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2947282768547796</v>
+        <v>0.2947282768547801</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2314773302606148</v>
+        <v>0.2314773302606146</v>
       </c>
       <c r="G6" t="n">
         <v>0.2455508140171152</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3293033144088313</v>
+        <v>0.3293033144088323</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3458118218316981</v>
+        <v>0.3458118218316984</v>
       </c>
       <c r="J6" t="n">
         <v>0.302336404624255</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3005588484065487</v>
+        <v>0.3005588484065486</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3090007872468593</v>
+        <v>0.3090007872468595</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3122897137102826</v>
+        <v>0.3122897137102825</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3134834026986363</v>
+        <v>0.3134834026986355</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5639857784356532</v>
+        <v>0.5639857784356533</v>
       </c>
       <c r="P6" t="n">
         <v>0.5678304997106746</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5487243817797304</v>
+        <v>0.5487243817797302</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7589202747211461</v>
+        <v>0.7589202747211448</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8201641211301682</v>
+        <v>0.8201641211301661</v>
       </c>
       <c r="T6" t="n">
         <v>0.7741979601311868</v>
@@ -855,58 +855,58 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.674420314437808</v>
+        <v>0.6744203144378083</v>
       </c>
       <c r="D7" t="n">
         <v>0.6152096060663301</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6298742399652122</v>
+        <v>0.629874239965211</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5221122862500753</v>
+        <v>0.5221122862500754</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5527945761810193</v>
+        <v>0.5527945761810198</v>
       </c>
       <c r="H7" t="n">
-        <v>0.752302753146147</v>
+        <v>0.7523027531461471</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8005220388485718</v>
+        <v>0.8005220388485711</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6830876819151366</v>
+        <v>0.6830876819151378</v>
       </c>
       <c r="K7" t="n">
-        <v>0.692216860905392</v>
+        <v>0.6922168609053919</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8009106471162786</v>
+        <v>0.8009106471162772</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7774359296731654</v>
+        <v>0.7774359296731642</v>
       </c>
       <c r="N7" t="n">
-        <v>0.76554413113375</v>
+        <v>0.7655441311337494</v>
       </c>
       <c r="O7" t="n">
         <v>1.566262375120505</v>
       </c>
       <c r="P7" t="n">
-        <v>1.565960937760687</v>
+        <v>1.565960937760685</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.52273360381384</v>
+        <v>1.522733603813841</v>
       </c>
       <c r="R7" t="n">
-        <v>2.152409749044962</v>
+        <v>2.152409749044963</v>
       </c>
       <c r="S7" t="n">
-        <v>2.257748735439358</v>
+        <v>2.257748735439359</v>
       </c>
       <c r="T7" t="n">
-        <v>2.222150261026401</v>
+        <v>2.222150261026406</v>
       </c>
     </row>
     <row r="8">
@@ -922,55 +922,55 @@
         <v>0.3244746526585782</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2866423737727969</v>
+        <v>0.2866423737727971</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2788327981304657</v>
+        <v>0.2788327981304656</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2467845199974297</v>
+        <v>0.2467845199974298</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2551384454210684</v>
+        <v>0.2551384454210683</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3869190450973518</v>
+        <v>0.3869190450973516</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3807188592851359</v>
+        <v>0.3807188592851358</v>
       </c>
       <c r="J8" t="n">
-        <v>0.330430434429112</v>
+        <v>0.3304304344291121</v>
       </c>
       <c r="K8" t="n">
         <v>0.330804509371276</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3236235345885701</v>
+        <v>0.3236235345885697</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3292863362551235</v>
+        <v>0.329286336255124</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3215322174380019</v>
+        <v>0.3215322174380015</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6217249597239209</v>
+        <v>0.6217249597239208</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6176170768101757</v>
+        <v>0.6176170768101755</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6095370693827075</v>
+        <v>0.6095370693827069</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8599770121380086</v>
+        <v>0.8599770121380085</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9561697891533919</v>
+        <v>0.9561697891533907</v>
       </c>
       <c r="T8" t="n">
-        <v>0.885923451495306</v>
+        <v>0.8859234514953058</v>
       </c>
     </row>
     <row r="9">
@@ -986,16 +986,16 @@
         <v>0.1018344970754371</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09500550076582551</v>
+        <v>0.09500550076582553</v>
       </c>
       <c r="E9" t="n">
         <v>0.08662816483852855</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07621756979313229</v>
+        <v>0.07621756979313228</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08059738053946207</v>
+        <v>0.08059738053946204</v>
       </c>
       <c r="H9" t="n">
         <v>0.1157248510346111</v>
@@ -1004,7 +1004,7 @@
         <v>0.1105201273561455</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0966494100244415</v>
+        <v>0.09664941002444148</v>
       </c>
       <c r="K9" t="n">
         <v>0.1001543362025172</v>
@@ -1013,7 +1013,7 @@
         <v>0.08983019100216065</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08957151193742505</v>
+        <v>0.08957151193742507</v>
       </c>
       <c r="N9" t="n">
         <v>0.0770039807701417</v>
@@ -1120,7 +1120,7 @@
         <v>0.1099763394444485</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09808345730099705</v>
+        <v>0.09808345730099706</v>
       </c>
       <c r="G11" t="n">
         <v>0.1005421342982784</v>
@@ -1162,7 +1162,7 @@
         <v>0.4363055828050145</v>
       </c>
       <c r="T11" t="n">
-        <v>0.369362268005803</v>
+        <v>0.3693622680058031</v>
       </c>
     </row>
     <row r="12">
@@ -1175,58 +1175,58 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03661573016203496</v>
+        <v>0.03661573016203498</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0331934129182494</v>
+        <v>0.03319341291824942</v>
       </c>
       <c r="E12" t="n">
         <v>0.03273638017898348</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03038793374970474</v>
+        <v>0.03038793374970473</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0335588686447699</v>
+        <v>0.03355886864476988</v>
       </c>
       <c r="H12" t="n">
         <v>0.03291355735044124</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04993554413072917</v>
+        <v>0.04993554413072915</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04228986996042209</v>
+        <v>0.04228986996042206</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04475671142734254</v>
+        <v>0.04475671142734255</v>
       </c>
       <c r="L12" t="n">
         <v>0.05150944201058793</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0479742562322552</v>
+        <v>0.04797425623225519</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05128340850969379</v>
+        <v>0.0512834085096938</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07973419989798836</v>
+        <v>0.07973419989798837</v>
       </c>
       <c r="P12" t="n">
         <v>0.08124902627258189</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07787174701674469</v>
+        <v>0.07787174701674474</v>
       </c>
       <c r="R12" t="n">
-        <v>0.09243011071226175</v>
+        <v>0.09243011071226179</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09937742984834656</v>
+        <v>0.09937742984834658</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1030537358957393</v>
+        <v>0.1030537358957392</v>
       </c>
     </row>
     <row r="13">
@@ -1242,37 +1242,37 @@
         <v>0.005049118025665233</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004394490135591378</v>
+        <v>0.004394490135591379</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004545089439899939</v>
+        <v>0.00454508943989994</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00470522865897535</v>
+        <v>0.004705228658975349</v>
       </c>
       <c r="G13" t="n">
         <v>0.005466796679180395</v>
       </c>
       <c r="H13" t="n">
-        <v>0.004111955159947699</v>
+        <v>0.0041119551599477</v>
       </c>
       <c r="I13" t="n">
         <v>0.008331749184548477</v>
       </c>
       <c r="J13" t="n">
-        <v>0.006705473885157677</v>
+        <v>0.006705473885157678</v>
       </c>
       <c r="K13" t="n">
-        <v>0.007561135582411532</v>
+        <v>0.007561135582411531</v>
       </c>
       <c r="L13" t="n">
-        <v>0.008718885598009426</v>
+        <v>0.008718885598009428</v>
       </c>
       <c r="M13" t="n">
         <v>0.007607491039339359</v>
       </c>
       <c r="N13" t="n">
-        <v>0.008764417056238809</v>
+        <v>0.008764417056238807</v>
       </c>
       <c r="O13" t="n">
         <v>0.0116590875381931</v>
@@ -1287,7 +1287,7 @@
         <v>0.01023879986485559</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01087255823193119</v>
+        <v>0.0108725582319312</v>
       </c>
       <c r="T13" t="n">
         <v>0.0122298136716976</v>
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02528653711496976</v>
+        <v>0.02528653711496977</v>
       </c>
       <c r="D14" t="n">
         <v>0.02488614675726864</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02851390840384987</v>
+        <v>0.02851390840384985</v>
       </c>
       <c r="F14" t="n">
         <v>0.01864412285172573</v>
@@ -1318,13 +1318,13 @@
         <v>0.02153176724016596</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02685551882242425</v>
+        <v>0.02685551882242424</v>
       </c>
       <c r="I14" t="n">
         <v>0.03208348429314235</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02713895156814151</v>
+        <v>0.0271389515681415</v>
       </c>
       <c r="K14" t="n">
         <v>0.02660929302392249</v>
@@ -1333,28 +1333,28 @@
         <v>0.02950321597263617</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02796646071346003</v>
+        <v>0.02796646071346001</v>
       </c>
       <c r="N14" t="n">
         <v>0.03046264675507623</v>
       </c>
       <c r="O14" t="n">
-        <v>0.04181081072465667</v>
+        <v>0.04181081072465669</v>
       </c>
       <c r="P14" t="n">
         <v>0.04291510369663654</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.03743347230456872</v>
+        <v>0.03743347230456871</v>
       </c>
       <c r="R14" t="n">
-        <v>0.04466403727064062</v>
+        <v>0.04466403727064063</v>
       </c>
       <c r="S14" t="n">
-        <v>0.04753633934426415</v>
+        <v>0.04753633934426416</v>
       </c>
       <c r="T14" t="n">
-        <v>0.04880556321010339</v>
+        <v>0.04880556321010336</v>
       </c>
     </row>
     <row r="15">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003812816599286285</v>
+        <v>0.003812816599286284</v>
       </c>
       <c r="D15" t="n">
         <v>0.003705792189397861</v>
@@ -1382,7 +1382,7 @@
         <v>0.003390836161339784</v>
       </c>
       <c r="H15" t="n">
-        <v>0.007042050315566639</v>
+        <v>0.007042050315566638</v>
       </c>
       <c r="I15" t="n">
         <v>0.00716550631679311</v>
@@ -1391,19 +1391,19 @@
         <v>0.006207707033002466</v>
       </c>
       <c r="K15" t="n">
-        <v>0.005661779695231678</v>
+        <v>0.005661779695231677</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005948138029819547</v>
+        <v>0.005948138029819546</v>
       </c>
       <c r="M15" t="n">
         <v>0.005491708360268059</v>
       </c>
       <c r="N15" t="n">
-        <v>0.006106169692350783</v>
+        <v>0.006106169692350782</v>
       </c>
       <c r="O15" t="n">
-        <v>0.009028701124745494</v>
+        <v>0.009028701124745495</v>
       </c>
       <c r="P15" t="n">
         <v>0.0105713992162711</v>
@@ -1431,37 +1431,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.005712600841827734</v>
+        <v>0.005712600841827732</v>
       </c>
       <c r="D16" t="n">
         <v>0.005421618131276169</v>
       </c>
       <c r="E16" t="n">
-        <v>0.005124411632473768</v>
+        <v>0.005124411632473769</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005435608453828108</v>
+        <v>0.005435608453828109</v>
       </c>
       <c r="G16" t="n">
         <v>0.005552460055708858</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00473283053898728</v>
+        <v>0.004732830538987282</v>
       </c>
       <c r="I16" t="n">
         <v>0.008275398215146628</v>
       </c>
       <c r="J16" t="n">
-        <v>0.006774819309301442</v>
+        <v>0.006774819309301443</v>
       </c>
       <c r="K16" t="n">
         <v>0.007244622197151865</v>
       </c>
       <c r="L16" t="n">
-        <v>0.008861363455180264</v>
+        <v>0.008861363455180267</v>
       </c>
       <c r="M16" t="n">
-        <v>0.008543899032070078</v>
+        <v>0.00854389903207008</v>
       </c>
       <c r="N16" t="n">
         <v>0.009004211516962006</v>
@@ -1476,13 +1476,13 @@
         <v>0.01286004652863196</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01540950775474595</v>
+        <v>0.01540950775474596</v>
       </c>
       <c r="S16" t="n">
         <v>0.01580657355591384</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01704402158098474</v>
+        <v>0.01704402158098473</v>
       </c>
     </row>
     <row r="17">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.004681257980298449</v>
+        <v>0.00468125798029845</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003565421697960222</v>
+        <v>0.003565421697960223</v>
       </c>
       <c r="E17" t="n">
         <v>0.003753034575357972</v>
@@ -1507,40 +1507,40 @@
         <v>0.003382527880898953</v>
       </c>
       <c r="G17" t="n">
-        <v>0.003707618210425618</v>
+        <v>0.003707618210425617</v>
       </c>
       <c r="H17" t="n">
         <v>0.003814003674793596</v>
       </c>
       <c r="I17" t="n">
-        <v>0.005823372495245289</v>
+        <v>0.005823372495245287</v>
       </c>
       <c r="J17" t="n">
-        <v>0.004912093381638569</v>
+        <v>0.004912093381638568</v>
       </c>
       <c r="K17" t="n">
         <v>0.003290899132391376</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005735802174095194</v>
+        <v>0.005735802174095195</v>
       </c>
       <c r="M17" t="n">
-        <v>0.005473914323963424</v>
+        <v>0.005473914323963421</v>
       </c>
       <c r="N17" t="n">
-        <v>0.005592339099503455</v>
+        <v>0.005592339099503459</v>
       </c>
       <c r="O17" t="n">
-        <v>0.004771970529911557</v>
+        <v>0.004771970529911556</v>
       </c>
       <c r="P17" t="n">
-        <v>0.008943046285670725</v>
+        <v>0.008943046285670719</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.008098476293101776</v>
+        <v>0.008098476293101774</v>
       </c>
       <c r="R17" t="n">
-        <v>0.01000658933129396</v>
+        <v>0.01000658933129395</v>
       </c>
       <c r="S17" t="n">
         <v>0.01044815084225277</v>
@@ -1559,28 +1559,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.007443395672678019</v>
+        <v>0.007443395672678018</v>
       </c>
       <c r="D18" t="n">
-        <v>0.006546600532938079</v>
+        <v>0.006546600532938078</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006313395272579768</v>
+        <v>0.006313395272579767</v>
       </c>
       <c r="F18" t="n">
-        <v>0.006037952564738816</v>
+        <v>0.006037952564738817</v>
       </c>
       <c r="G18" t="n">
-        <v>0.006628872311452039</v>
+        <v>0.006628872311452037</v>
       </c>
       <c r="H18" t="n">
-        <v>0.006030287112052418</v>
+        <v>0.006030287112052417</v>
       </c>
       <c r="I18" t="n">
         <v>0.009793894302960116</v>
       </c>
       <c r="J18" t="n">
-        <v>0.008080082426028671</v>
+        <v>0.008080082426028673</v>
       </c>
       <c r="K18" t="n">
         <v>0.009067461585017549</v>
@@ -1610,7 +1610,7 @@
         <v>0.02408388022697337</v>
       </c>
       <c r="T18" t="n">
-        <v>0.02484464946209348</v>
+        <v>0.02484464946209347</v>
       </c>
     </row>
     <row r="19">
@@ -1629,34 +1629,34 @@
         <v>0.004519991787833756</v>
       </c>
       <c r="E19" t="n">
-        <v>0.004650416166567029</v>
+        <v>0.004650416166567028</v>
       </c>
       <c r="F19" t="n">
         <v>0.004632007054701646</v>
       </c>
       <c r="G19" t="n">
-        <v>0.004806805586954711</v>
+        <v>0.004806805586954712</v>
       </c>
       <c r="H19" t="n">
         <v>0.005001973599284327</v>
       </c>
       <c r="I19" t="n">
-        <v>0.007279032392740483</v>
+        <v>0.007279032392740479</v>
       </c>
       <c r="J19" t="n">
-        <v>0.006397770808286394</v>
+        <v>0.006397770808286391</v>
       </c>
       <c r="K19" t="n">
-        <v>0.006388401998568684</v>
+        <v>0.006388401998568687</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007530972041957377</v>
+        <v>0.007530972041957378</v>
       </c>
       <c r="M19" t="n">
-        <v>0.007263357596965083</v>
+        <v>0.00726335759696508</v>
       </c>
       <c r="N19" t="n">
-        <v>0.007618070080118965</v>
+        <v>0.007618070080118959</v>
       </c>
       <c r="O19" t="n">
         <v>0.0114686967913749</v>
@@ -1668,10 +1668,10 @@
         <v>0.01145677756159373</v>
       </c>
       <c r="R19" t="n">
-        <v>0.01444466999713029</v>
+        <v>0.01444466999713028</v>
       </c>
       <c r="S19" t="n">
-        <v>0.01486261021990096</v>
+        <v>0.01486261021990095</v>
       </c>
       <c r="T19" t="n">
         <v>0.01505131658364077</v>
@@ -1687,16 +1687,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01439008675920186</v>
+        <v>0.01439008675920187</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01254529804881726</v>
+        <v>0.01254529804881725</v>
       </c>
       <c r="E20" t="n">
         <v>0.01395444048221669</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0128656420901956</v>
+        <v>0.01286564209019561</v>
       </c>
       <c r="G20" t="n">
         <v>0.01394436266123397</v>
@@ -1705,40 +1705,40 @@
         <v>0.01776449821700896</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02080394931722172</v>
+        <v>0.02080394931722171</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01792844159990109</v>
+        <v>0.01792844159990108</v>
       </c>
       <c r="K20" t="n">
         <v>0.01832311476897562</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02239033721602808</v>
+        <v>0.02239033721602806</v>
       </c>
       <c r="M20" t="n">
         <v>0.02251252602155649</v>
       </c>
       <c r="N20" t="n">
-        <v>0.02028504530507214</v>
+        <v>0.02028504530507213</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0436109909412215</v>
+        <v>0.04361099094122149</v>
       </c>
       <c r="P20" t="n">
         <v>0.04265496736654477</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.04084420843985979</v>
+        <v>0.04084420843985977</v>
       </c>
       <c r="R20" t="n">
-        <v>0.05264107071099635</v>
+        <v>0.05264107071099634</v>
       </c>
       <c r="S20" t="n">
-        <v>0.04893222006956955</v>
+        <v>0.04893222006956954</v>
       </c>
       <c r="T20" t="n">
-        <v>0.05601116535852404</v>
+        <v>0.05601116535852405</v>
       </c>
     </row>
     <row r="21">
@@ -1836,7 +1836,7 @@
         <v>0.002609143681042045</v>
       </c>
       <c r="J22" t="n">
-        <v>0.002327622918269023</v>
+        <v>0.002327622918269024</v>
       </c>
       <c r="K22" t="n">
         <v>0.002335238073920165</v>
@@ -1845,7 +1845,7 @@
         <v>0.00272976496231476</v>
       </c>
       <c r="M22" t="n">
-        <v>0.002641204495354088</v>
+        <v>0.002641204495354089</v>
       </c>
       <c r="N22" t="n">
         <v>0.002872123249523663</v>
@@ -1854,13 +1854,13 @@
         <v>0.004155333641574648</v>
       </c>
       <c r="P22" t="n">
-        <v>0.004314340649881361</v>
+        <v>0.004314340649881362</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.00400590106790256</v>
+        <v>0.004005901067902559</v>
       </c>
       <c r="R22" t="n">
-        <v>0.005105864786075024</v>
+        <v>0.005105864786075022</v>
       </c>
       <c r="S22" t="n">
         <v>0.005051898804130198</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.06544895927897286</v>
+        <v>0.06544895927897283</v>
       </c>
       <c r="D23" t="n">
-        <v>0.05344226526081741</v>
+        <v>0.0534422652608174</v>
       </c>
       <c r="E23" t="n">
         <v>0.04835437420598979</v>
@@ -1891,7 +1891,7 @@
         <v>0.04212722844484509</v>
       </c>
       <c r="G23" t="n">
-        <v>0.04064635918773633</v>
+        <v>0.04064635918773631</v>
       </c>
       <c r="H23" t="n">
         <v>0.1018017020070821</v>
@@ -1900,19 +1900,19 @@
         <v>0.08292055708383926</v>
       </c>
       <c r="J23" t="n">
-        <v>0.06928222519676557</v>
+        <v>0.06928222519676554</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06503827189428044</v>
+        <v>0.06503827189428042</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06003812759753003</v>
+        <v>0.06003812759753002</v>
       </c>
       <c r="M23" t="n">
         <v>0.06602394251820767</v>
       </c>
       <c r="N23" t="n">
-        <v>0.06067101690685925</v>
+        <v>0.06067101690685924</v>
       </c>
       <c r="O23" t="n">
         <v>0.1245721472587214</v>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0002960735886797675</v>
+        <v>0.0002960735886797674</v>
       </c>
       <c r="D24" t="n">
         <v>0.0003056165462516994</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0003650838090279752</v>
+        <v>0.0003650838090279751</v>
       </c>
       <c r="F24" t="n">
         <v>0.0003193923381672009</v>
@@ -1958,7 +1958,7 @@
         <v>0.000294966065360185</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0004172351128721647</v>
+        <v>0.0004172351128721648</v>
       </c>
       <c r="I24" t="n">
         <v>0.0005670029983989803</v>
@@ -1970,13 +1970,13 @@
         <v>0.0004583174489436459</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0005291002864420677</v>
+        <v>0.0005291002864420676</v>
       </c>
       <c r="M24" t="n">
         <v>0.0005646461396192717</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0005272754254156419</v>
+        <v>0.0005272754254156417</v>
       </c>
       <c r="O24" t="n">
         <v>0.001001765132372118</v>
@@ -1985,13 +1985,13 @@
         <v>0.001002464709202405</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0009996345155749984</v>
+        <v>0.0009996345155749982</v>
       </c>
       <c r="R24" t="n">
         <v>0.00113036040314947</v>
       </c>
       <c r="S24" t="n">
-        <v>0.001257474704243686</v>
+        <v>0.001257474704243687</v>
       </c>
       <c r="T24" t="n">
         <v>0.001255203598807323</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.003981689962999592</v>
+        <v>0.003981689962999591</v>
       </c>
       <c r="D25" t="n">
         <v>0.003635622454831856</v>
@@ -2016,16 +2016,16 @@
         <v>0.003778346057862445</v>
       </c>
       <c r="F25" t="n">
-        <v>0.003419780777906692</v>
+        <v>0.003419780777906693</v>
       </c>
       <c r="G25" t="n">
-        <v>0.003702096024915826</v>
+        <v>0.003702096024915824</v>
       </c>
       <c r="H25" t="n">
         <v>0.005133370030009709</v>
       </c>
       <c r="I25" t="n">
-        <v>0.005293615894974278</v>
+        <v>0.005293615894974277</v>
       </c>
       <c r="J25" t="n">
         <v>0.004605492990943175</v>
@@ -2037,16 +2037,16 @@
         <v>0.005717218848392241</v>
       </c>
       <c r="M25" t="n">
-        <v>0.005586169686724362</v>
+        <v>0.005586169686724365</v>
       </c>
       <c r="N25" t="n">
-        <v>0.005615593304517419</v>
+        <v>0.005615593304517421</v>
       </c>
       <c r="O25" t="n">
-        <v>0.00989733917260684</v>
+        <v>0.009897339172606842</v>
       </c>
       <c r="P25" t="n">
-        <v>0.009746145370303912</v>
+        <v>0.00974614537030391</v>
       </c>
       <c r="Q25" t="n">
         <v>0.008991249072953926</v>
@@ -2071,37 +2071,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.003572379925020586</v>
+        <v>0.003572379925020587</v>
       </c>
       <c r="D26" t="n">
         <v>0.003290862127722241</v>
       </c>
       <c r="E26" t="n">
-        <v>0.003175276113531483</v>
+        <v>0.003175276113531482</v>
       </c>
       <c r="F26" t="n">
         <v>0.003480337847609291</v>
       </c>
       <c r="G26" t="n">
-        <v>0.003508616508893621</v>
+        <v>0.00350861650889362</v>
       </c>
       <c r="H26" t="n">
-        <v>0.002870652405661034</v>
+        <v>0.002870652405661035</v>
       </c>
       <c r="I26" t="n">
-        <v>0.005333984981971954</v>
+        <v>0.005333984981971955</v>
       </c>
       <c r="J26" t="n">
-        <v>0.004343037244887173</v>
+        <v>0.004343037244887172</v>
       </c>
       <c r="K26" t="n">
-        <v>0.004869362592362368</v>
+        <v>0.004869362592362369</v>
       </c>
       <c r="L26" t="n">
-        <v>0.005731137234644756</v>
+        <v>0.005731137234644757</v>
       </c>
       <c r="M26" t="n">
-        <v>0.005336940010454466</v>
+        <v>0.005336940010454465</v>
       </c>
       <c r="N26" t="n">
         <v>0.005624705573409332</v>
@@ -2110,16 +2110,16 @@
         <v>0.008118724733919712</v>
       </c>
       <c r="P26" t="n">
-        <v>0.007894529086869174</v>
+        <v>0.007894529086869176</v>
       </c>
       <c r="Q26" t="n">
         <v>0.008127006922679609</v>
       </c>
       <c r="R26" t="n">
-        <v>0.00938186841313308</v>
+        <v>0.009381868413133081</v>
       </c>
       <c r="S26" t="n">
-        <v>0.01006147872595065</v>
+        <v>0.01006147872595064</v>
       </c>
       <c r="T26" t="n">
         <v>0.0112525675673088</v>
@@ -2135,31 +2135,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02363190616199328</v>
+        <v>0.02363190616199327</v>
       </c>
       <c r="D27" t="n">
         <v>0.0203446764789837</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02206476918498529</v>
+        <v>0.0220647691849853</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02133382831723831</v>
+        <v>0.0213338283172383</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02154735531605346</v>
+        <v>0.02154735531605345</v>
       </c>
       <c r="H27" t="n">
-        <v>0.02928489587149747</v>
+        <v>0.02928489587149748</v>
       </c>
       <c r="I27" t="n">
-        <v>0.03493389407902206</v>
+        <v>0.03493389407902207</v>
       </c>
       <c r="J27" t="n">
         <v>0.02972842407248851</v>
       </c>
       <c r="K27" t="n">
-        <v>0.02890109739348916</v>
+        <v>0.02890109739348917</v>
       </c>
       <c r="L27" t="n">
         <v>0.03988912484342511</v>
@@ -2171,13 +2171,13 @@
         <v>0.03883627107657939</v>
       </c>
       <c r="O27" t="n">
-        <v>0.08964175956440451</v>
+        <v>0.08964175956440446</v>
       </c>
       <c r="P27" t="n">
-        <v>0.09504129227029801</v>
+        <v>0.09504129227029803</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.08807653087278289</v>
+        <v>0.08807653087278294</v>
       </c>
       <c r="R27" t="n">
         <v>0.1329163296625813</v>
@@ -2186,7 +2186,7 @@
         <v>0.1445893913710392</v>
       </c>
       <c r="T27" t="n">
-        <v>0.140710549349797</v>
+        <v>0.1407105493497969</v>
       </c>
     </row>
     <row r="28">
@@ -2199,25 +2199,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0009601396901303175</v>
+        <v>0.0009601396901303173</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0008917878293514123</v>
+        <v>0.0008917878293514126</v>
       </c>
       <c r="E28" t="n">
         <v>0.001005887284232087</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0008748548515545567</v>
+        <v>0.0008748548515545568</v>
       </c>
       <c r="G28" t="n">
         <v>0.0009119071443270725</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0008759844238974661</v>
+        <v>0.0008759844238974662</v>
       </c>
       <c r="I28" t="n">
-        <v>0.001237888951396373</v>
+        <v>0.001237888951396374</v>
       </c>
       <c r="J28" t="n">
         <v>0.001061281711893008</v>
@@ -2226,7 +2226,7 @@
         <v>0.001091706714391585</v>
       </c>
       <c r="L28" t="n">
-        <v>0.00122532468596344</v>
+        <v>0.001225324685963441</v>
       </c>
       <c r="M28" t="n">
         <v>0.001254621874208841</v>
@@ -2238,7 +2238,7 @@
         <v>0.002078787827943519</v>
       </c>
       <c r="P28" t="n">
-        <v>0.001977947660649413</v>
+        <v>0.001977947660649412</v>
       </c>
       <c r="Q28" t="n">
         <v>0.001918595285612787</v>
@@ -2247,10 +2247,10 @@
         <v>0.002265381791223839</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002292231620168414</v>
+        <v>0.002292231620168415</v>
       </c>
       <c r="T28" t="n">
-        <v>0.002443063803981783</v>
+        <v>0.002443063803981782</v>
       </c>
     </row>
     <row r="29">
@@ -2263,28 +2263,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0417846837123053</v>
+        <v>0.04178468371230531</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04029921482308035</v>
+        <v>0.04029921482308037</v>
       </c>
       <c r="E29" t="n">
         <v>0.04284121689574148</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03434279818144118</v>
+        <v>0.0343427981814412</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03972404405320799</v>
+        <v>0.03972404405320798</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03318192913057326</v>
+        <v>0.03318192913057327</v>
       </c>
       <c r="I29" t="n">
-        <v>0.04728805586905933</v>
+        <v>0.04728805586905934</v>
       </c>
       <c r="J29" t="n">
-        <v>0.04019107653238923</v>
+        <v>0.0401910765323892</v>
       </c>
       <c r="K29" t="n">
         <v>0.04374562272135329</v>
@@ -2293,28 +2293,28 @@
         <v>0.04906111308521011</v>
       </c>
       <c r="M29" t="n">
-        <v>0.04626134440966503</v>
+        <v>0.04626134440966502</v>
       </c>
       <c r="N29" t="n">
-        <v>0.04968702694724268</v>
+        <v>0.04968702694724266</v>
       </c>
       <c r="O29" t="n">
-        <v>0.07300693916132671</v>
+        <v>0.07300693916132668</v>
       </c>
       <c r="P29" t="n">
         <v>0.07431737936769228</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.07129962323660161</v>
+        <v>0.07129962323660163</v>
       </c>
       <c r="R29" t="n">
-        <v>0.08311022178751405</v>
+        <v>0.08311022178751414</v>
       </c>
       <c r="S29" t="n">
-        <v>0.08415552651775415</v>
+        <v>0.08415552651775413</v>
       </c>
       <c r="T29" t="n">
-        <v>0.09293840875741974</v>
+        <v>0.09293840875741972</v>
       </c>
     </row>
     <row r="30">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.536217811625103e-05</v>
+        <v>6.536217811625104e-05</v>
       </c>
       <c r="D30" t="n">
         <v>5.696548566341211e-05</v>
@@ -2348,7 +2348,7 @@
         <v>6.941510683550844e-05</v>
       </c>
       <c r="J30" t="n">
-        <v>6.326455087601082e-05</v>
+        <v>6.326455087601081e-05</v>
       </c>
       <c r="K30" t="n">
         <v>5.613516580507901e-05</v>
@@ -2357,7 +2357,7 @@
         <v>6.351550964717175e-05</v>
       </c>
       <c r="M30" t="n">
-        <v>7.136017573949492e-05</v>
+        <v>7.13601757394949e-05</v>
       </c>
       <c r="N30" t="n">
         <v>6.729598909199773e-05</v>
@@ -2439,7 +2439,7 @@
         <v>3.331726499246351e-05</v>
       </c>
       <c r="S31" t="n">
-        <v>2.959878246107162e-05</v>
+        <v>2.959878246107163e-05</v>
       </c>
       <c r="T31" t="n">
         <v>3.675402781604053e-05</v>
@@ -2455,31 +2455,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.05967304959223335</v>
+        <v>0.05967304959223334</v>
       </c>
       <c r="D32" t="n">
-        <v>0.05516122588708292</v>
+        <v>0.05516122588708289</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07066063246716912</v>
+        <v>0.07066063246716911</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05101571986852792</v>
+        <v>0.05101571986852788</v>
       </c>
       <c r="G32" t="n">
-        <v>0.05412844437019203</v>
+        <v>0.05412844437019202</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0757549481406737</v>
+        <v>0.07575494814067366</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07830483392638532</v>
+        <v>0.07830483392638535</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0676950734321176</v>
+        <v>0.06769507343211757</v>
       </c>
       <c r="K32" t="n">
-        <v>0.06815147656362594</v>
+        <v>0.06815147656362593</v>
       </c>
       <c r="L32" t="n">
         <v>0.0820735501133055</v>
@@ -2488,19 +2488,19 @@
         <v>0.08317156084404088</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0777929944758322</v>
+        <v>0.07779299447583216</v>
       </c>
       <c r="O32" t="n">
         <v>0.168663320252235</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1605582191046247</v>
+        <v>0.1605582191046246</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.1637301235937187</v>
+        <v>0.1637301235937188</v>
       </c>
       <c r="R32" t="n">
-        <v>0.2370010763956215</v>
+        <v>0.2370010763956214</v>
       </c>
       <c r="S32" t="n">
         <v>0.247474117027106</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.03928141552555952</v>
+        <v>0.03928141552555954</v>
       </c>
       <c r="D33" t="n">
         <v>0.03490258858839559</v>
@@ -2537,40 +2537,40 @@
         <v>0.04584739359295859</v>
       </c>
       <c r="I33" t="n">
-        <v>0.05022545729805558</v>
+        <v>0.0502254572980556</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04699365211822475</v>
+        <v>0.04699365211822474</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0439111052059125</v>
+        <v>0.04391110520591249</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04060455153333408</v>
+        <v>0.04060455153333407</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0422261733912512</v>
+        <v>0.04222617339125118</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04989617235525267</v>
+        <v>0.04989617235525266</v>
       </c>
       <c r="O33" t="n">
-        <v>0.07544428275678744</v>
+        <v>0.0754442827567874</v>
       </c>
       <c r="P33" t="n">
         <v>0.07876417638194927</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.06853923969210053</v>
+        <v>0.06853923969210055</v>
       </c>
       <c r="R33" t="n">
-        <v>0.08389940650991633</v>
+        <v>0.08389940650991629</v>
       </c>
       <c r="S33" t="n">
         <v>0.08432616908598631</v>
       </c>
       <c r="T33" t="n">
-        <v>0.08688000992671771</v>
+        <v>0.0868800099267177</v>
       </c>
     </row>
     <row r="34">
@@ -2595,13 +2595,13 @@
         <v>0.001654208977858669</v>
       </c>
       <c r="G34" t="n">
-        <v>0.001777972575455845</v>
+        <v>0.001777972575455846</v>
       </c>
       <c r="H34" t="n">
         <v>0.002084177877093493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.002933287248525037</v>
+        <v>0.002933287248525036</v>
       </c>
       <c r="J34" t="n">
         <v>0.002488780392150594</v>
@@ -2610,7 +2610,7 @@
         <v>0.002521425927899796</v>
       </c>
       <c r="L34" t="n">
-        <v>0.002942290564688174</v>
+        <v>0.002942290564688175</v>
       </c>
       <c r="M34" t="n">
         <v>0.002809841862328543</v>
@@ -2619,22 +2619,22 @@
         <v>0.002826058497224958</v>
       </c>
       <c r="O34" t="n">
-        <v>0.00521768518509613</v>
+        <v>0.005217685185096129</v>
       </c>
       <c r="P34" t="n">
-        <v>0.005031621094921961</v>
+        <v>0.005031621094921959</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.004633427468897363</v>
+        <v>0.00463342746889736</v>
       </c>
       <c r="R34" t="n">
-        <v>0.006726304927452114</v>
+        <v>0.006726304927452116</v>
       </c>
       <c r="S34" t="n">
-        <v>0.00686508336661418</v>
+        <v>0.006865083366614178</v>
       </c>
       <c r="T34" t="n">
-        <v>0.006712136551364381</v>
+        <v>0.006712136551364382</v>
       </c>
     </row>
     <row r="35">
@@ -2683,13 +2683,13 @@
         <v>0.001780555778188278</v>
       </c>
       <c r="O35" t="n">
-        <v>0.00361147436818957</v>
+        <v>0.003611474368189569</v>
       </c>
       <c r="P35" t="n">
         <v>0.003645004130948816</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.003193086741053777</v>
+        <v>0.003193086741053776</v>
       </c>
       <c r="R35" t="n">
         <v>0.003850733355482474</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.003140770600787806</v>
+        <v>0.003140770600787807</v>
       </c>
       <c r="D36" t="n">
         <v>0.00281970521140949</v>
@@ -2726,40 +2726,40 @@
         <v>0.002740712646266431</v>
       </c>
       <c r="H36" t="n">
-        <v>0.002418928181212141</v>
+        <v>0.00241892818121214</v>
       </c>
       <c r="I36" t="n">
         <v>0.004110386844249587</v>
       </c>
       <c r="J36" t="n">
-        <v>0.003570742073707007</v>
+        <v>0.003570742073707008</v>
       </c>
       <c r="K36" t="n">
         <v>0.003613381540449738</v>
       </c>
       <c r="L36" t="n">
-        <v>0.00409994143041147</v>
+        <v>0.004099941430411471</v>
       </c>
       <c r="M36" t="n">
         <v>0.003851570371646665</v>
       </c>
       <c r="N36" t="n">
-        <v>0.004027616956137037</v>
+        <v>0.004027616956137036</v>
       </c>
       <c r="O36" t="n">
-        <v>0.006872496922405303</v>
+        <v>0.006872496922405301</v>
       </c>
       <c r="P36" t="n">
-        <v>0.007375429434640457</v>
+        <v>0.007375429434640456</v>
       </c>
       <c r="Q36" t="n">
         <v>0.007302751047231808</v>
       </c>
       <c r="R36" t="n">
-        <v>0.008351025821890814</v>
+        <v>0.008351025821890816</v>
       </c>
       <c r="S36" t="n">
-        <v>0.009213512599590202</v>
+        <v>0.009213512599590206</v>
       </c>
       <c r="T36" t="n">
         <v>0.009510761419686171</v>
@@ -2778,7 +2778,7 @@
         <v>0.01874243863199443</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01586595370405629</v>
+        <v>0.0158659537040563</v>
       </c>
       <c r="E37" t="n">
         <v>0.01748208176686526</v>
@@ -2790,19 +2790,19 @@
         <v>0.01621275922863314</v>
       </c>
       <c r="H37" t="n">
-        <v>0.02471438054811493</v>
+        <v>0.02471438054811492</v>
       </c>
       <c r="I37" t="n">
-        <v>0.02788143282550355</v>
+        <v>0.02788143282550356</v>
       </c>
       <c r="J37" t="n">
-        <v>0.02458181700655486</v>
+        <v>0.02458181700655485</v>
       </c>
       <c r="K37" t="n">
         <v>0.02508423273066513</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02812580771048367</v>
+        <v>0.02812580771048365</v>
       </c>
       <c r="M37" t="n">
         <v>0.02744993417846454</v>
@@ -2811,10 +2811,10 @@
         <v>0.02720057921792603</v>
       </c>
       <c r="O37" t="n">
-        <v>0.04170338645761994</v>
+        <v>0.04170338645761996</v>
       </c>
       <c r="P37" t="n">
-        <v>0.0434798500450114</v>
+        <v>0.04347985004501139</v>
       </c>
       <c r="Q37" t="n">
         <v>0.03840477653741646</v>
@@ -2826,7 +2826,7 @@
         <v>0.04306627127753549</v>
       </c>
       <c r="T37" t="n">
-        <v>0.04972104930348142</v>
+        <v>0.04972104930348143</v>
       </c>
     </row>
     <row r="38">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001119979811586521</v>
+        <v>0.00111997981158652</v>
       </c>
       <c r="D38" t="n">
         <v>0.00104820183045174</v>
@@ -2848,16 +2848,16 @@
         <v>0.001111413095985852</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0009181890418136278</v>
+        <v>0.0009181890418136279</v>
       </c>
       <c r="G38" t="n">
-        <v>0.00093411747423178</v>
+        <v>0.0009341174742317801</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0008915528447191771</v>
+        <v>0.0008915528447191772</v>
       </c>
       <c r="I38" t="n">
-        <v>0.001311187395852363</v>
+        <v>0.001311187395852362</v>
       </c>
       <c r="J38" t="n">
         <v>0.001093542379639255</v>
@@ -2884,7 +2884,7 @@
         <v>0.002149605687876302</v>
       </c>
       <c r="R38" t="n">
-        <v>0.002522371882809761</v>
+        <v>0.002522371882809762</v>
       </c>
       <c r="S38" t="n">
         <v>0.00254902802101099</v>
@@ -2915,7 +2915,7 @@
         <v>0.0004153652726398151</v>
       </c>
       <c r="G39" t="n">
-        <v>0.000388625607693216</v>
+        <v>0.0003886256076932159</v>
       </c>
       <c r="H39" t="n">
         <v>0.0004001379483768973</v>
@@ -2927,7 +2927,7 @@
         <v>0.0004729548580341696</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0004676195310665344</v>
+        <v>0.0004676195310665343</v>
       </c>
       <c r="L39" t="n">
         <v>0.0005738753293783108</v>
@@ -2942,7 +2942,7 @@
         <v>0.0008356076791109801</v>
       </c>
       <c r="P39" t="n">
-        <v>0.000907574292150649</v>
+        <v>0.0009075742921506491</v>
       </c>
       <c r="Q39" t="n">
         <v>0.0008815389454429107</v>
@@ -2973,13 +2973,13 @@
         <v>0.0002801590814539433</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0003029347150350595</v>
+        <v>0.0003029347150350594</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0002686408341916116</v>
+        <v>0.0002686408341916115</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0002912700619111125</v>
+        <v>0.0002912700619111126</v>
       </c>
       <c r="H40" t="n">
         <v>0.0003299408215584418</v>
@@ -2988,7 +2988,7 @@
         <v>0.0004538768502562573</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0003979916844135054</v>
+        <v>0.0003979916844135055</v>
       </c>
       <c r="K40" t="n">
         <v>0.0003797094505343365</v>
@@ -3000,16 +3000,16 @@
         <v>0.0004290058857576306</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0004444842415552417</v>
+        <v>0.0004444842415552418</v>
       </c>
       <c r="O40" t="n">
-        <v>0.000719415550425733</v>
+        <v>0.0007194155504257333</v>
       </c>
       <c r="P40" t="n">
-        <v>0.0007048667687519836</v>
+        <v>0.0007048667687519835</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0007614144461801881</v>
+        <v>0.0007614144461801879</v>
       </c>
       <c r="R40" t="n">
         <v>0.0009606343116023746</v>
@@ -3018,7 +3018,7 @@
         <v>0.0009378254605716714</v>
       </c>
       <c r="T40" t="n">
-        <v>0.000960679439825419</v>
+        <v>0.0009606794398254191</v>
       </c>
     </row>
     <row r="41">
@@ -3031,28 +3031,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0007176725009867631</v>
+        <v>0.000717672500986763</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0005821637252449531</v>
+        <v>0.0005821637252449533</v>
       </c>
       <c r="E41" t="n">
         <v>0.0006093154879078816</v>
       </c>
       <c r="F41" t="n">
-        <v>0.000577935967025965</v>
+        <v>0.0005779359670259649</v>
       </c>
       <c r="G41" t="n">
         <v>0.0005915019507909177</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0009476508048630645</v>
+        <v>0.0009476508048630646</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0008824410898727281</v>
+        <v>0.0008824410898727284</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0007473456657593529</v>
+        <v>0.0007473456657593528</v>
       </c>
       <c r="K41" t="n">
         <v>0.000767815455180689</v>
@@ -3064,7 +3064,7 @@
         <v>0.0008752540743390142</v>
       </c>
       <c r="N41" t="n">
-        <v>0.0008690463726857524</v>
+        <v>0.0008690463726857523</v>
       </c>
       <c r="O41" t="n">
         <v>0.001410365332105579</v>
@@ -3095,13 +3095,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0006493572351318268</v>
+        <v>0.0006493572351318267</v>
       </c>
       <c r="D42" t="n">
-        <v>0.000491209738695646</v>
+        <v>0.0004912097386956461</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0005201759213330668</v>
+        <v>0.0005201759213330667</v>
       </c>
       <c r="F42" t="n">
         <v>0.0004894624595332362</v>
@@ -3110,19 +3110,19 @@
         <v>0.0005137720214202067</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0006999381801553096</v>
+        <v>0.0006999381801553095</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0007344291052171246</v>
+        <v>0.0007344291052171247</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0006102484615524504</v>
+        <v>0.0006102484615524505</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0006298000302696462</v>
+        <v>0.0006298000302696463</v>
       </c>
       <c r="L42" t="n">
-        <v>0.0008791805517163138</v>
+        <v>0.0008791805517163137</v>
       </c>
       <c r="M42" t="n">
         <v>0.0007081828034723708</v>
@@ -3143,7 +3143,7 @@
         <v>0.001235177384246955</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001210571453382411</v>
+        <v>0.001210571453382412</v>
       </c>
       <c r="T42" t="n">
         <v>0.001215611748998546</v>
@@ -3174,7 +3174,7 @@
         <v>0.00138154392196514</v>
       </c>
       <c r="H43" t="n">
-        <v>0.001756812364982077</v>
+        <v>0.001756812364982076</v>
       </c>
       <c r="I43" t="n">
         <v>0.002184495304047338</v>
@@ -3183,7 +3183,7 @@
         <v>0.001766939356805425</v>
       </c>
       <c r="K43" t="n">
-        <v>0.001963481392945996</v>
+        <v>0.001963481392945995</v>
       </c>
       <c r="L43" t="n">
         <v>0.002237763593613615</v>
@@ -3192,22 +3192,22 @@
         <v>0.002139123113656401</v>
       </c>
       <c r="N43" t="n">
-        <v>0.00222716145488672</v>
+        <v>0.002227161454886719</v>
       </c>
       <c r="O43" t="n">
-        <v>0.003879069652252631</v>
+        <v>0.003879069652252633</v>
       </c>
       <c r="P43" t="n">
-        <v>0.003863080667579025</v>
+        <v>0.003863080667579023</v>
       </c>
       <c r="Q43" t="n">
         <v>0.003948739065758635</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0042772897227513</v>
+        <v>0.004277289722751301</v>
       </c>
       <c r="S43" t="n">
-        <v>0.004808271716528292</v>
+        <v>0.004808271716528291</v>
       </c>
       <c r="T43" t="n">
         <v>0.005071815455708679</v>
@@ -3226,10 +3226,10 @@
         <v>0.007863010387560413</v>
       </c>
       <c r="D44" t="n">
-        <v>0.006794820646434558</v>
+        <v>0.00679482064643456</v>
       </c>
       <c r="E44" t="n">
-        <v>0.006354037684587713</v>
+        <v>0.00635403768458771</v>
       </c>
       <c r="F44" t="n">
         <v>0.006248399803056122</v>
@@ -3238,13 +3238,13 @@
         <v>0.006817988388062353</v>
       </c>
       <c r="H44" t="n">
-        <v>0.006890692390890818</v>
+        <v>0.00689069239089082</v>
       </c>
       <c r="I44" t="n">
         <v>0.01035079939910132</v>
       </c>
       <c r="J44" t="n">
-        <v>0.008975019969027165</v>
+        <v>0.008975019969027168</v>
       </c>
       <c r="K44" t="n">
         <v>0.009287384909961446</v>
@@ -3259,13 +3259,13 @@
         <v>0.01049926516432097</v>
       </c>
       <c r="O44" t="n">
-        <v>0.01899610877904079</v>
+        <v>0.0189961087790408</v>
       </c>
       <c r="P44" t="n">
         <v>0.02000063324769512</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.01933386238912675</v>
+        <v>0.01933386238912674</v>
       </c>
       <c r="R44" t="n">
         <v>0.02244486932264942</v>
@@ -3274,7 +3274,7 @@
         <v>0.02500026509404587</v>
       </c>
       <c r="T44" t="n">
-        <v>0.02603926928490411</v>
+        <v>0.0260392692849041</v>
       </c>
     </row>
     <row r="45">
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0001767306540755206</v>
+        <v>0.0001767306540755205</v>
       </c>
       <c r="D45" t="n">
         <v>0.000151082628592063</v>
@@ -3296,7 +3296,7 @@
         <v>0.0001568257746080243</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0001410147061403565</v>
+        <v>0.0001410147061403566</v>
       </c>
       <c r="G45" t="n">
         <v>0.0001391817060213013</v>
@@ -3320,7 +3320,7 @@
         <v>0.0002139407444541989</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0002226815983364653</v>
+        <v>0.0002226815983364654</v>
       </c>
       <c r="O45" t="n">
         <v>0.0004133550258707325</v>
@@ -3360,7 +3360,7 @@
         <v>9.118136161837113e-05</v>
       </c>
       <c r="F46" t="n">
-        <v>7.656782006564767e-05</v>
+        <v>7.656782006564766e-05</v>
       </c>
       <c r="G46" t="n">
         <v>7.414469706222293e-05</v>
@@ -3372,7 +3372,7 @@
         <v>0.0001213577333661768</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0001068885442734452</v>
+        <v>0.0001068885442734451</v>
       </c>
       <c r="K46" t="n">
         <v>0.0001097264641272879</v>
@@ -3384,7 +3384,7 @@
         <v>0.0001137642823858088</v>
       </c>
       <c r="N46" t="n">
-        <v>0.0001257164349663786</v>
+        <v>0.0001257164349663787</v>
       </c>
       <c r="O46" t="n">
         <v>0.000180178331457102</v>
@@ -3402,7 +3402,7 @@
         <v>0.0001613517757607435</v>
       </c>
       <c r="T46" t="n">
-        <v>0.0002072032203985273</v>
+        <v>0.0002072032203985272</v>
       </c>
     </row>
     <row r="47">
@@ -3427,7 +3427,7 @@
         <v>0.0004008232802274768</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0004128478197850666</v>
+        <v>0.0004128478197850665</v>
       </c>
       <c r="H47" t="n">
         <v>0.0004508554071086186</v>
@@ -3448,19 +3448,19 @@
         <v>0.0005500931388743396</v>
       </c>
       <c r="N47" t="n">
-        <v>0.0005910172556355501</v>
+        <v>0.0005910172556355499</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0008008864797214393</v>
+        <v>0.0008008864797214392</v>
       </c>
       <c r="P47" t="n">
         <v>0.0008084034408457065</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0008024723857798309</v>
+        <v>0.0008024723857798311</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0008748776651254892</v>
+        <v>0.0008748776651254893</v>
       </c>
       <c r="S47" t="n">
         <v>0.0009828141149986495</v>
@@ -3494,22 +3494,22 @@
         <v>0.003874030105241913</v>
       </c>
       <c r="H48" t="n">
-        <v>0.004060990896287203</v>
+        <v>0.004060990896287202</v>
       </c>
       <c r="I48" t="n">
-        <v>0.005417238023809207</v>
+        <v>0.005417238023809208</v>
       </c>
       <c r="J48" t="n">
-        <v>0.004527036907750805</v>
+        <v>0.004527036907750804</v>
       </c>
       <c r="K48" t="n">
         <v>0.005270317267512578</v>
       </c>
       <c r="L48" t="n">
-        <v>0.005499479180724023</v>
+        <v>0.005499479180724022</v>
       </c>
       <c r="M48" t="n">
-        <v>0.005520992334913802</v>
+        <v>0.005520992334913803</v>
       </c>
       <c r="N48" t="n">
         <v>0.005562590273690458</v>
@@ -3518,7 +3518,7 @@
         <v>0.009682878421946123</v>
       </c>
       <c r="P48" t="n">
-        <v>0.01027431101665551</v>
+        <v>0.0102743110166555</v>
       </c>
       <c r="Q48" t="n">
         <v>0.008825209887677071</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0003012805972378639</v>
+        <v>0.0003012805972378638</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0002555088121314011</v>
+        <v>0.0002555088121314012</v>
       </c>
       <c r="E50" t="n">
         <v>0.0002743745032590484</v>
@@ -3628,28 +3628,28 @@
         <v>0.0003844610978247171</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0003451993875627504</v>
+        <v>0.0003451993875627503</v>
       </c>
       <c r="K50" t="n">
         <v>0.0003335932732388534</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0004266752941893007</v>
+        <v>0.0004266752941893008</v>
       </c>
       <c r="M50" t="n">
         <v>0.0004240489692019076</v>
       </c>
       <c r="N50" t="n">
-        <v>0.0004089335118390941</v>
+        <v>0.0004089335118390939</v>
       </c>
       <c r="O50" t="n">
         <v>0.0007961864659021018</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0008095112106981516</v>
+        <v>0.0008095112106981515</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0008080718311665691</v>
+        <v>0.0008080718311665692</v>
       </c>
       <c r="R50" t="n">
         <v>0.0009993840860593867</v>
@@ -3671,37 +3671,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.02963435017940521</v>
+        <v>0.0296343501794052</v>
       </c>
       <c r="D51" t="n">
         <v>0.02600229489078499</v>
       </c>
       <c r="E51" t="n">
-        <v>0.02588499389940942</v>
+        <v>0.02588499389940941</v>
       </c>
       <c r="F51" t="n">
         <v>0.02568907614003457</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02564873914388941</v>
+        <v>0.0256487391438894</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0342780516771802</v>
+        <v>0.03427805167718021</v>
       </c>
       <c r="I51" t="n">
-        <v>0.04417315381836269</v>
+        <v>0.04417315381836271</v>
       </c>
       <c r="J51" t="n">
-        <v>0.03755090735470019</v>
+        <v>0.03755090735470021</v>
       </c>
       <c r="K51" t="n">
-        <v>0.03701110946390407</v>
+        <v>0.03701110946390408</v>
       </c>
       <c r="L51" t="n">
-        <v>0.05244555568591178</v>
+        <v>0.05244555568591179</v>
       </c>
       <c r="M51" t="n">
-        <v>0.05025188799216815</v>
+        <v>0.05025188799216816</v>
       </c>
       <c r="N51" t="n">
         <v>0.04702021221348656</v>
@@ -3716,13 +3716,13 @@
         <v>0.122887891811818</v>
       </c>
       <c r="R51" t="n">
-        <v>0.1893245025981536</v>
+        <v>0.1893245025981537</v>
       </c>
       <c r="S51" t="n">
         <v>0.2041678729973968</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1951052889672892</v>
+        <v>0.1951052889672891</v>
       </c>
     </row>
     <row r="52">
@@ -3735,22 +3735,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.0007283473450843272</v>
+        <v>0.0007283473450843273</v>
       </c>
       <c r="D52" t="n">
         <v>0.0006612943781374029</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0006656865350080063</v>
+        <v>0.0006656865350080062</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0006567142805552541</v>
+        <v>0.0006567142805552539</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0006968050461698421</v>
+        <v>0.0006968050461698422</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0008606509931428723</v>
+        <v>0.0008606509931428724</v>
       </c>
       <c r="I52" t="n">
         <v>0.001149160480263709</v>
@@ -3777,7 +3777,7 @@
         <v>0.001879419888623997</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.001653089448397336</v>
+        <v>0.001653089448397335</v>
       </c>
       <c r="R52" t="n">
         <v>0.001950279422570903</v>
@@ -3826,7 +3826,7 @@
         <v>0.0001225655482989715</v>
       </c>
       <c r="L53" t="n">
-        <v>0.0001390022797621929</v>
+        <v>0.000139002279762193</v>
       </c>
       <c r="M53" t="n">
         <v>0.0001386756320171677</v>
@@ -3835,13 +3835,13 @@
         <v>0.0001459136599087845</v>
       </c>
       <c r="O53" t="n">
-        <v>0.000201472044121671</v>
+        <v>0.0002014720441216711</v>
       </c>
       <c r="P53" t="n">
         <v>0.0002172032504963772</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.0001991031771334228</v>
+        <v>0.0001991031771334227</v>
       </c>
       <c r="R53" t="n">
         <v>0.0002212594216522949</v>
@@ -3863,16 +3863,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.05857290472854743</v>
+        <v>0.05857290472854741</v>
       </c>
       <c r="D54" t="n">
-        <v>0.05324004902531077</v>
+        <v>0.05324004902531078</v>
       </c>
       <c r="E54" t="n">
-        <v>0.05431422790656237</v>
+        <v>0.0543142279065624</v>
       </c>
       <c r="F54" t="n">
-        <v>0.03979857311804829</v>
+        <v>0.03979857311804828</v>
       </c>
       <c r="G54" t="n">
         <v>0.0457588751304696</v>
@@ -3881,19 +3881,19 @@
         <v>0.0533808367748307</v>
       </c>
       <c r="I54" t="n">
-        <v>0.05936039204495634</v>
+        <v>0.05936039204495635</v>
       </c>
       <c r="J54" t="n">
-        <v>0.04803864427597396</v>
+        <v>0.04803864427597392</v>
       </c>
       <c r="K54" t="n">
-        <v>0.04842644127848794</v>
+        <v>0.04842644127848793</v>
       </c>
       <c r="L54" t="n">
-        <v>0.05188256159913471</v>
+        <v>0.0518825615991347</v>
       </c>
       <c r="M54" t="n">
-        <v>0.05306251231184315</v>
+        <v>0.0530625123118432</v>
       </c>
       <c r="N54" t="n">
         <v>0.05516057509214907</v>
@@ -3911,7 +3911,7 @@
         <v>0.1726253688074165</v>
       </c>
       <c r="S54" t="n">
-        <v>0.1857152921141935</v>
+        <v>0.1857152921141936</v>
       </c>
       <c r="T54" t="n">
         <v>0.1847289625567463</v>
@@ -3927,13 +3927,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.009288482532161061</v>
+        <v>0.009288482532161059</v>
       </c>
       <c r="D55" t="n">
-        <v>0.008125054819074273</v>
+        <v>0.008125054819074272</v>
       </c>
       <c r="E55" t="n">
-        <v>0.008606380281014528</v>
+        <v>0.008606380281014526</v>
       </c>
       <c r="F55" t="n">
         <v>0.008372308787847607</v>
@@ -3960,7 +3960,7 @@
         <v>0.01246312469582261</v>
       </c>
       <c r="N55" t="n">
-        <v>0.01231265745520275</v>
+        <v>0.01231265745520274</v>
       </c>
       <c r="O55" t="n">
         <v>0.0199955832185047</v>
@@ -3975,7 +3975,7 @@
         <v>0.02403707548585926</v>
       </c>
       <c r="S55" t="n">
-        <v>0.02508809410281049</v>
+        <v>0.0250880941028105</v>
       </c>
       <c r="T55" t="n">
         <v>0.02507412836736543</v>
@@ -3994,37 +3994,37 @@
         <v>0.02499180842970414</v>
       </c>
       <c r="D56" t="n">
-        <v>0.02224392262860989</v>
+        <v>0.02224392262860988</v>
       </c>
       <c r="E56" t="n">
-        <v>0.02307135386339231</v>
+        <v>0.02307135386339232</v>
       </c>
       <c r="F56" t="n">
-        <v>0.02612051322640579</v>
+        <v>0.0261205132264058</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02732669998920395</v>
+        <v>0.02732669998920394</v>
       </c>
       <c r="H56" t="n">
-        <v>0.02788236979849584</v>
+        <v>0.02788236979849583</v>
       </c>
       <c r="I56" t="n">
-        <v>0.04449728198721575</v>
+        <v>0.04449728198721577</v>
       </c>
       <c r="J56" t="n">
         <v>0.03767680838830524</v>
       </c>
       <c r="K56" t="n">
-        <v>0.04024400716482526</v>
+        <v>0.04024400716482524</v>
       </c>
       <c r="L56" t="n">
         <v>0.04865157640012904</v>
       </c>
       <c r="M56" t="n">
-        <v>0.04657951051848525</v>
+        <v>0.04657951051848528</v>
       </c>
       <c r="N56" t="n">
-        <v>0.04978314866448109</v>
+        <v>0.0497831486644811</v>
       </c>
       <c r="O56" t="n">
         <v>0.07821056838640705</v>
@@ -4036,10 +4036,10 @@
         <v>0.0672894916853008</v>
       </c>
       <c r="R56" t="n">
-        <v>0.07821861225092321</v>
+        <v>0.07821861225092325</v>
       </c>
       <c r="S56" t="n">
-        <v>0.08591213683361289</v>
+        <v>0.08591213683361287</v>
       </c>
       <c r="T56" t="n">
         <v>0.0940838047941278</v>
@@ -4067,7 +4067,7 @@
         <v>0.0005007545161437507</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0005349898807271909</v>
+        <v>0.000534989880727191</v>
       </c>
       <c r="H57" t="n">
         <v>0.0005305149327596837</v>
@@ -4091,7 +4091,7 @@
         <v>0.0007254573583040019</v>
       </c>
       <c r="O57" t="n">
-        <v>0.001191058425090083</v>
+        <v>0.001191058425090082</v>
       </c>
       <c r="P57" t="n">
         <v>0.001096560622799685</v>
@@ -4122,16 +4122,16 @@
         <v>0.0009449344400139658</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0008757557971306018</v>
+        <v>0.0008757557971306016</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0008917637030961151</v>
+        <v>0.000891763703096115</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0008308097029911027</v>
+        <v>0.0008308097029911026</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0009107220242241219</v>
+        <v>0.000910722024224122</v>
       </c>
       <c r="H58" t="n">
         <v>0.0007002533414524414</v>
@@ -4143,13 +4143,13 @@
         <v>0.001013346273851311</v>
       </c>
       <c r="K58" t="n">
-        <v>0.001047867855902679</v>
+        <v>0.00104786785590268</v>
       </c>
       <c r="L58" t="n">
         <v>0.001240191814229775</v>
       </c>
       <c r="M58" t="n">
-        <v>0.001175523830842078</v>
+        <v>0.001175523830842079</v>
       </c>
       <c r="N58" t="n">
         <v>0.001289292632663305</v>
@@ -4158,7 +4158,7 @@
         <v>0.00186612046313962</v>
       </c>
       <c r="P58" t="n">
-        <v>0.001824965079939083</v>
+        <v>0.001824965079939084</v>
       </c>
       <c r="Q58" t="n">
         <v>0.001914809230054278</v>
@@ -4186,13 +4186,13 @@
         <v>0.001180121261484723</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0008442368034814513</v>
+        <v>0.0008442368034814512</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001075644154997986</v>
+        <v>0.001075644154997985</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0007995786060417852</v>
+        <v>0.0007995786060417853</v>
       </c>
       <c r="G59" t="n">
         <v>0.001097625630007409</v>
@@ -4207,7 +4207,7 @@
         <v>0.001511603196314317</v>
       </c>
       <c r="K59" t="n">
-        <v>0.001371025215133862</v>
+        <v>0.001371025215133861</v>
       </c>
       <c r="L59" t="n">
         <v>0.001626969334149028</v>
@@ -4234,7 +4234,7 @@
         <v>0.002641397387394246</v>
       </c>
       <c r="T59" t="n">
-        <v>0.00303540384177918</v>
+        <v>0.003035403841779181</v>
       </c>
     </row>
     <row r="60">
@@ -4292,10 +4292,10 @@
         <v>0.04287597446048185</v>
       </c>
       <c r="R60" t="n">
-        <v>0.05120131045905076</v>
+        <v>0.05120131045905078</v>
       </c>
       <c r="S60" t="n">
-        <v>0.05216372175998283</v>
+        <v>0.05216372175998284</v>
       </c>
       <c r="T60" t="n">
         <v>0.05446448215993896</v>
@@ -4317,34 +4317,34 @@
         <v>0.0006515413288554953</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0004978298575038122</v>
+        <v>0.0004978298575038123</v>
       </c>
       <c r="F61" t="n">
         <v>0.0004904757399292254</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0004970455142231163</v>
+        <v>0.0004970455142231162</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0006317034413010371</v>
+        <v>0.0006317034413010372</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0007988232553914683</v>
+        <v>0.0007988232553914685</v>
       </c>
       <c r="J61" t="n">
         <v>0.0006765066651379732</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0005948015544907992</v>
+        <v>0.0005948015544907995</v>
       </c>
       <c r="L61" t="n">
-        <v>0.0007342209822745412</v>
+        <v>0.0007342209822745413</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0007098136718420917</v>
+        <v>0.0007098136718420916</v>
       </c>
       <c r="N61" t="n">
-        <v>0.0007318263125666763</v>
+        <v>0.0007318263125666764</v>
       </c>
       <c r="O61" t="n">
         <v>0.001077214113257938</v>
@@ -4356,7 +4356,7 @@
         <v>0.001184529465228846</v>
       </c>
       <c r="R61" t="n">
-        <v>0.001486466088547341</v>
+        <v>0.00148646608854734</v>
       </c>
       <c r="S61" t="n">
         <v>0.001608054909930285</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.02610803419415911</v>
+        <v>0.02610803419415912</v>
       </c>
       <c r="D63" t="n">
         <v>0.02580979820618974</v>
@@ -4448,7 +4448,7 @@
         <v>0.02577269670636673</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01720124094090852</v>
+        <v>0.01720124094090853</v>
       </c>
       <c r="G63" t="n">
         <v>0.02137908684559435</v>
@@ -4457,7 +4457,7 @@
         <v>0.02450173205316751</v>
       </c>
       <c r="I63" t="n">
-        <v>0.02467820436928058</v>
+        <v>0.02467820436928057</v>
       </c>
       <c r="J63" t="n">
         <v>0.02210434191809629</v>
@@ -4487,7 +4487,7 @@
         <v>0.02849296838107103</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0285344625774767</v>
+        <v>0.02853446257747671</v>
       </c>
       <c r="T63" t="n">
         <v>0.02596145898711213</v>
@@ -4503,28 +4503,28 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6.720313208834165e-05</v>
+        <v>6.720313208834166e-05</v>
       </c>
       <c r="D64" t="n">
         <v>5.913645532120331e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>7.361441986057457e-05</v>
+        <v>7.361441986057459e-05</v>
       </c>
       <c r="F64" t="n">
-        <v>6.760715154160403e-05</v>
+        <v>6.760715154160402e-05</v>
       </c>
       <c r="G64" t="n">
-        <v>7.395304277678059e-05</v>
+        <v>7.39530427767806e-05</v>
       </c>
       <c r="H64" t="n">
-        <v>8.477539560702336e-05</v>
+        <v>8.477539560702339e-05</v>
       </c>
       <c r="I64" t="n">
         <v>0.0001083870505709137</v>
       </c>
       <c r="J64" t="n">
-        <v>9.475518504317734e-05</v>
+        <v>9.475518504317732e-05</v>
       </c>
       <c r="K64" t="n">
         <v>9.330011942754319e-05</v>
@@ -4545,7 +4545,7 @@
         <v>0.0002541545556738676</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.0002133279948857403</v>
+        <v>0.0002133279948857404</v>
       </c>
       <c r="R64" t="n">
         <v>0.0002787787574952359</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.04538500237775901</v>
+        <v>0.04538500237775899</v>
       </c>
       <c r="D65" t="n">
         <v>0.04338961015318493</v>
@@ -4585,37 +4585,37 @@
         <v>0.04091883504537901</v>
       </c>
       <c r="I65" t="n">
-        <v>0.03864147426126141</v>
+        <v>0.0386414742612614</v>
       </c>
       <c r="J65" t="n">
         <v>0.03356672595524037</v>
       </c>
       <c r="K65" t="n">
-        <v>0.03485424593576004</v>
+        <v>0.03485424593576003</v>
       </c>
       <c r="L65" t="n">
-        <v>0.04065687760020305</v>
+        <v>0.04065687760020306</v>
       </c>
       <c r="M65" t="n">
         <v>0.03889945469571278</v>
       </c>
       <c r="N65" t="n">
-        <v>0.03969031809223353</v>
+        <v>0.03969031809223352</v>
       </c>
       <c r="O65" t="n">
         <v>0.07115200847310967</v>
       </c>
       <c r="P65" t="n">
-        <v>0.07201156099056806</v>
+        <v>0.07201156099056805</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.06152866686354787</v>
+        <v>0.06152866686354786</v>
       </c>
       <c r="R65" t="n">
         <v>0.08667559412751188</v>
       </c>
       <c r="S65" t="n">
-        <v>0.08039841238693013</v>
+        <v>0.0803984123869301</v>
       </c>
       <c r="T65" t="n">
         <v>0.08760942289852619</v>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.001750738048166454</v>
+        <v>0.001750738048166453</v>
       </c>
       <c r="D66" t="n">
         <v>0.001537607569649404</v>
@@ -4652,7 +4652,7 @@
         <v>0.002552324109944717</v>
       </c>
       <c r="J66" t="n">
-        <v>0.002167287262278399</v>
+        <v>0.0021672872622784</v>
       </c>
       <c r="K66" t="n">
         <v>0.002169068974417476</v>
@@ -4673,13 +4673,13 @@
         <v>0.003955970073544152</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.00406298814537316</v>
+        <v>0.004062988145373158</v>
       </c>
       <c r="R66" t="n">
-        <v>0.00485885759215433</v>
+        <v>0.004858857592154329</v>
       </c>
       <c r="S66" t="n">
-        <v>0.004745925798865116</v>
+        <v>0.004745925798865114</v>
       </c>
       <c r="T66" t="n">
         <v>0.004631458325474399</v>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9.386591861321949e-05</v>
+        <v>9.386591861321948e-05</v>
       </c>
       <c r="D67" t="n">
         <v>8.62703769457975e-05</v>
@@ -4704,7 +4704,7 @@
         <v>8.351978109109367e-05</v>
       </c>
       <c r="F67" t="n">
-        <v>7.423247885592181e-05</v>
+        <v>7.423247885592182e-05</v>
       </c>
       <c r="G67" t="n">
         <v>7.981421193171109e-05</v>
@@ -4713,7 +4713,7 @@
         <v>7.27661636548983e-05</v>
       </c>
       <c r="I67" t="n">
-        <v>9.140683859755842e-05</v>
+        <v>9.140683859755845e-05</v>
       </c>
       <c r="J67" t="n">
         <v>7.687315996281983e-05</v>
@@ -4728,10 +4728,10 @@
         <v>8.183669800176504e-05</v>
       </c>
       <c r="N67" t="n">
-        <v>9.299289647050584e-05</v>
+        <v>9.299289647050583e-05</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0001170291077615545</v>
+        <v>0.0001170291077615544</v>
       </c>
       <c r="P67" t="n">
         <v>0.0001254851618496425</v>
@@ -4777,7 +4777,7 @@
         <v>0.000291441084853131</v>
       </c>
       <c r="I68" t="n">
-        <v>0.000416464126257296</v>
+        <v>0.0004164641262572959</v>
       </c>
       <c r="J68" t="n">
         <v>0.0003311326045180553</v>
@@ -4792,25 +4792,25 @@
         <v>0.0004011282476338992</v>
       </c>
       <c r="N68" t="n">
-        <v>0.0004122643205398078</v>
+        <v>0.0004122643205398079</v>
       </c>
       <c r="O68" t="n">
         <v>0.0006699775071638696</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0006617244241551689</v>
+        <v>0.000661724424155169</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.0006028718809485268</v>
+        <v>0.0006028718809485267</v>
       </c>
       <c r="R68" t="n">
         <v>0.00073497403732653</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0007281199876061773</v>
+        <v>0.0007281199876061774</v>
       </c>
       <c r="T68" t="n">
-        <v>0.0007917876059387475</v>
+        <v>0.0007917876059387474</v>
       </c>
     </row>
     <row r="69">
@@ -4826,28 +4826,28 @@
         <v>0.0004633281957211601</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0003878346035619255</v>
+        <v>0.0003878346035619254</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0003691162204705686</v>
+        <v>0.0003691162204705687</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0003858966361778564</v>
+        <v>0.0003858966361778565</v>
       </c>
       <c r="G69" t="n">
         <v>0.0003914605559053413</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0005718485705743459</v>
+        <v>0.000571848570574346</v>
       </c>
       <c r="I69" t="n">
         <v>0.0007169978103621082</v>
       </c>
       <c r="J69" t="n">
-        <v>0.000617316649418295</v>
+        <v>0.0006173166494182951</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0005895233196005974</v>
+        <v>0.0005895233196005975</v>
       </c>
       <c r="L69" t="n">
         <v>0.000678597998307159</v>
@@ -4856,7 +4856,7 @@
         <v>0.000676525251335332</v>
       </c>
       <c r="N69" t="n">
-        <v>0.0006789334868333878</v>
+        <v>0.0006789334868333879</v>
       </c>
       <c r="O69" t="n">
         <v>0.00119829761041941</v>
@@ -4868,7 +4868,7 @@
         <v>0.00122225495870886</v>
       </c>
       <c r="R69" t="n">
-        <v>0.001741458081799374</v>
+        <v>0.001741458081799373</v>
       </c>
       <c r="S69" t="n">
         <v>0.001938964157824213</v>
@@ -4963,7 +4963,7 @@
         <v>0.02583514108216511</v>
       </c>
       <c r="G71" t="n">
-        <v>0.027162034812638</v>
+        <v>0.02716203481263801</v>
       </c>
       <c r="H71" t="n">
         <v>0.03111701673858734</v>
@@ -4978,13 +4978,13 @@
         <v>0.03518885671478111</v>
       </c>
       <c r="L71" t="n">
-        <v>0.03832614207747861</v>
+        <v>0.0383261420774786</v>
       </c>
       <c r="M71" t="n">
-        <v>0.03631767426350423</v>
+        <v>0.03631767426350425</v>
       </c>
       <c r="N71" t="n">
-        <v>0.04107934716655568</v>
+        <v>0.04107934716655569</v>
       </c>
       <c r="O71" t="n">
         <v>0.05098796133209233</v>
@@ -4999,7 +4999,7 @@
         <v>0.05941786776200265</v>
       </c>
       <c r="S71" t="n">
-        <v>0.06170427167824289</v>
+        <v>0.06170427167824288</v>
       </c>
       <c r="T71" t="n">
         <v>0.06345394063655223</v>
@@ -5018,37 +5018,37 @@
         <v>0.00591158834100603</v>
       </c>
       <c r="D72" t="n">
-        <v>0.005472875132470743</v>
+        <v>0.005472875132470742</v>
       </c>
       <c r="E72" t="n">
         <v>0.005511764138566286</v>
       </c>
       <c r="F72" t="n">
-        <v>0.005085026790918366</v>
+        <v>0.005085026790918367</v>
       </c>
       <c r="G72" t="n">
-        <v>0.004998769476485134</v>
+        <v>0.004998769476485135</v>
       </c>
       <c r="H72" t="n">
-        <v>0.005508254499132774</v>
+        <v>0.005508254499132775</v>
       </c>
       <c r="I72" t="n">
-        <v>0.00800164183330288</v>
+        <v>0.008001641833302882</v>
       </c>
       <c r="J72" t="n">
-        <v>0.006580810548816608</v>
+        <v>0.006580810548816609</v>
       </c>
       <c r="K72" t="n">
-        <v>0.007134338908588691</v>
+        <v>0.007134338908588693</v>
       </c>
       <c r="L72" t="n">
-        <v>0.008694522567118982</v>
+        <v>0.00869452256711898</v>
       </c>
       <c r="M72" t="n">
         <v>0.007893679741714149</v>
       </c>
       <c r="N72" t="n">
-        <v>0.007831675228281949</v>
+        <v>0.007831675228281947</v>
       </c>
       <c r="O72" t="n">
         <v>0.01693006799742993</v>
@@ -5063,10 +5063,10 @@
         <v>0.02098053184294878</v>
       </c>
       <c r="S72" t="n">
-        <v>0.01786028529217653</v>
+        <v>0.01786028529217654</v>
       </c>
       <c r="T72" t="n">
-        <v>0.0228535014861386</v>
+        <v>0.02285350148613859</v>
       </c>
     </row>
     <row r="73">
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.00422951719064272</v>
+        <v>0.004229517190642719</v>
       </c>
       <c r="D73" t="n">
         <v>0.003948926664927192</v>
@@ -5091,43 +5091,43 @@
         <v>0.003472595378495141</v>
       </c>
       <c r="G73" t="n">
-        <v>0.003679093583206077</v>
+        <v>0.003679093583206078</v>
       </c>
       <c r="H73" t="n">
         <v>0.00464156987783138</v>
       </c>
       <c r="I73" t="n">
-        <v>0.005631865492481019</v>
+        <v>0.005631865492481018</v>
       </c>
       <c r="J73" t="n">
-        <v>0.004579218404045468</v>
+        <v>0.004579218404045467</v>
       </c>
       <c r="K73" t="n">
-        <v>0.004998269425899777</v>
+        <v>0.004998269425899779</v>
       </c>
       <c r="L73" t="n">
-        <v>0.005718246501388787</v>
+        <v>0.005718246501388786</v>
       </c>
       <c r="M73" t="n">
         <v>0.005561617956951358</v>
       </c>
       <c r="N73" t="n">
-        <v>0.005600036112992702</v>
+        <v>0.005600036112992703</v>
       </c>
       <c r="O73" t="n">
-        <v>0.008197363018726646</v>
+        <v>0.008197363018726644</v>
       </c>
       <c r="P73" t="n">
         <v>0.008804474124274582</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.007883030648410666</v>
+        <v>0.00788303064841067</v>
       </c>
       <c r="R73" t="n">
-        <v>0.009547762731302216</v>
+        <v>0.009547762731302215</v>
       </c>
       <c r="S73" t="n">
-        <v>0.009471961914342483</v>
+        <v>0.009471961914342485</v>
       </c>
       <c r="T73" t="n">
         <v>0.009674581438692565</v>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.003858859539032477</v>
+        <v>0.003858859539032478</v>
       </c>
       <c r="D74" t="n">
-        <v>0.003562513883515146</v>
+        <v>0.003562513883515147</v>
       </c>
       <c r="E74" t="n">
         <v>0.003763420544374291</v>
@@ -5161,7 +5161,7 @@
         <v>0.005372201779939284</v>
       </c>
       <c r="I74" t="n">
-        <v>0.00532571316294432</v>
+        <v>0.005325713162944321</v>
       </c>
       <c r="J74" t="n">
         <v>0.00459386089997292</v>
@@ -5182,7 +5182,7 @@
         <v>0.009208051192570841</v>
       </c>
       <c r="P74" t="n">
-        <v>0.00917026744941422</v>
+        <v>0.009170267449414222</v>
       </c>
       <c r="Q74" t="n">
         <v>0.008048153330755899</v>
@@ -5194,7 +5194,7 @@
         <v>0.01011398523060772</v>
       </c>
       <c r="T74" t="n">
-        <v>0.01128563330941134</v>
+        <v>0.01128563330941133</v>
       </c>
     </row>
     <row r="75">
@@ -5210,7 +5210,7 @@
         <v>1.148246810327173e-05</v>
       </c>
       <c r="D75" t="n">
-        <v>9.988197460690279e-06</v>
+        <v>9.98819746069028e-06</v>
       </c>
       <c r="E75" t="n">
         <v>1.130601136845054e-05</v>
@@ -5249,7 +5249,7 @@
         <v>1.692836404161228e-05</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.00101896782244e-05</v>
+        <v>2.001018967822441e-05</v>
       </c>
       <c r="R75" t="n">
         <v>1.784007663937982e-05</v>
@@ -5258,7 +5258,7 @@
         <v>2.312921799998797e-05</v>
       </c>
       <c r="T75" t="n">
-        <v>2.570642314378748e-05</v>
+        <v>2.570642314378747e-05</v>
       </c>
     </row>
     <row r="76">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.002855748211611104</v>
+        <v>0.002855748211611105</v>
       </c>
       <c r="D76" t="n">
         <v>0.002517184897131888</v>
@@ -5283,13 +5283,13 @@
         <v>0.002331037972674157</v>
       </c>
       <c r="G76" t="n">
-        <v>0.002338450902102356</v>
+        <v>0.002338450902102357</v>
       </c>
       <c r="H76" t="n">
-        <v>0.002088608802357396</v>
+        <v>0.002088608802357395</v>
       </c>
       <c r="I76" t="n">
-        <v>0.003698490111716686</v>
+        <v>0.003698490111716687</v>
       </c>
       <c r="J76" t="n">
         <v>0.003134867085289426</v>
@@ -5298,28 +5298,28 @@
         <v>0.003229548106693547</v>
       </c>
       <c r="L76" t="n">
-        <v>0.003641234053210944</v>
+        <v>0.003641234053210945</v>
       </c>
       <c r="M76" t="n">
         <v>0.003361145959178447</v>
       </c>
       <c r="N76" t="n">
-        <v>0.003557414601213113</v>
+        <v>0.003557414601213114</v>
       </c>
       <c r="O76" t="n">
         <v>0.005857501615107136</v>
       </c>
       <c r="P76" t="n">
-        <v>0.006356555675617169</v>
+        <v>0.00635655567561717</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.006116334800148484</v>
+        <v>0.006116334800148483</v>
       </c>
       <c r="R76" t="n">
         <v>0.007216108406888671</v>
       </c>
       <c r="S76" t="n">
-        <v>0.007819969584078804</v>
+        <v>0.007819969584078802</v>
       </c>
       <c r="T76" t="n">
         <v>0.008100264409694077</v>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7.658163187702155e-05</v>
+        <v>7.658163187702156e-05</v>
       </c>
       <c r="D77" t="n">
         <v>7.619584172118826e-05</v>
@@ -5350,7 +5350,7 @@
         <v>8.507342557341149e-05</v>
       </c>
       <c r="H77" t="n">
-        <v>7.148972648716797e-05</v>
+        <v>7.148972648716796e-05</v>
       </c>
       <c r="I77" t="n">
         <v>0.0001419318538061084</v>
@@ -5377,13 +5377,13 @@
         <v>0.000285275949322136</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.0003251508966190125</v>
+        <v>0.0003251508966190126</v>
       </c>
       <c r="R77" t="n">
         <v>0.0003698002029785356</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0004230812038241611</v>
+        <v>0.0004230812038241612</v>
       </c>
       <c r="T77" t="n">
         <v>0.0003644749434877759</v>
@@ -5478,7 +5478,7 @@
         <v>0.0001199724246250904</v>
       </c>
       <c r="H79" t="n">
-        <v>8.977885100380976e-05</v>
+        <v>8.977885100380975e-05</v>
       </c>
       <c r="I79" t="n">
         <v>0.0001675499112394927</v>
@@ -5508,7 +5508,7 @@
         <v>0.0002605208863417205</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0003050483196752891</v>
+        <v>0.000305048319675289</v>
       </c>
       <c r="S79" t="n">
         <v>0.0003015831509391796</v>
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.000345266887945053</v>
+        <v>0.0003452668879450531</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0002729345580055002</v>
+        <v>0.0002729345580055003</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0002743595057757288</v>
+        <v>0.0002743595057757287</v>
       </c>
       <c r="F80" t="n">
         <v>0.0002773450507326296</v>
@@ -5545,7 +5545,7 @@
         <v>0.0003539100093949758</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0004831677645039401</v>
+        <v>0.00048316776450394</v>
       </c>
       <c r="J80" t="n">
         <v>0.0004165224557102835</v>
@@ -5566,10 +5566,10 @@
         <v>0.000735340716666861</v>
       </c>
       <c r="P80" t="n">
-        <v>0.0008653060161787569</v>
+        <v>0.000865306016178757</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.0009067664506483244</v>
+        <v>0.0009067664506483246</v>
       </c>
       <c r="R80" t="n">
         <v>0.001163778143326537</v>
@@ -5594,7 +5594,7 @@
         <v>0.0001617649677853665</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0001568711143642637</v>
+        <v>0.0001568711143642636</v>
       </c>
       <c r="E81" t="n">
         <v>0.0001587643346957276</v>
@@ -5615,7 +5615,7 @@
         <v>0.0001425239076559735</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0001485275694328214</v>
+        <v>0.0001485275694328215</v>
       </c>
       <c r="L81" t="n">
         <v>0.0001646050592459658</v>
@@ -5719,13 +5719,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.004965745614155851</v>
+        <v>0.00496574561415585</v>
       </c>
       <c r="D83" t="n">
         <v>0.004506007106331803</v>
       </c>
       <c r="E83" t="n">
-        <v>0.004454924966412117</v>
+        <v>0.004454924966412116</v>
       </c>
       <c r="F83" t="n">
         <v>0.005285177143953464</v>
@@ -5758,7 +5758,7 @@
         <v>0.02108879396683409</v>
       </c>
       <c r="P83" t="n">
-        <v>0.02270046034455987</v>
+        <v>0.02270046034455986</v>
       </c>
       <c r="Q83" t="n">
         <v>0.0190386351649628</v>
@@ -5770,7 +5770,7 @@
         <v>0.02560952748971333</v>
       </c>
       <c r="T83" t="n">
-        <v>0.02586862924910176</v>
+        <v>0.02586862924910177</v>
       </c>
     </row>
     <row r="84">
@@ -5789,10 +5789,10 @@
         <v>0.0008257745720205966</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0009577743596968522</v>
+        <v>0.0009577743596968521</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0008997746952792311</v>
+        <v>0.0008997746952792312</v>
       </c>
       <c r="G84" t="n">
         <v>0.0009694055827760408</v>
@@ -5822,19 +5822,19 @@
         <v>0.004054232182882252</v>
       </c>
       <c r="P84" t="n">
-        <v>0.003941605071853369</v>
+        <v>0.00394160507185337</v>
       </c>
       <c r="Q84" t="n">
         <v>0.003484121236049804</v>
       </c>
       <c r="R84" t="n">
-        <v>0.004415170932562624</v>
+        <v>0.004415170932562623</v>
       </c>
       <c r="S84" t="n">
         <v>0.005316169629355797</v>
       </c>
       <c r="T84" t="n">
-        <v>0.00504525049959036</v>
+        <v>0.005045250499590359</v>
       </c>
     </row>
     <row r="85">
@@ -5929,19 +5929,19 @@
         <v>0.0005127973469333791</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0007002107399513152</v>
+        <v>0.0007002107399513153</v>
       </c>
       <c r="J86" t="n">
         <v>0.0006187911198732316</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0005957052440573666</v>
+        <v>0.0005957052440573665</v>
       </c>
       <c r="L86" t="n">
         <v>0.0006785816912652622</v>
       </c>
       <c r="M86" t="n">
-        <v>0.0006725833698511503</v>
+        <v>0.0006725833698511504</v>
       </c>
       <c r="N86" t="n">
         <v>0.000730144239209097</v>
@@ -6042,7 +6042,7 @@
         <v>0.00870783520619991</v>
       </c>
       <c r="D88" t="n">
-        <v>0.008116964410070414</v>
+        <v>0.008116964410070416</v>
       </c>
       <c r="E88" t="n">
         <v>0.0093758027677012</v>
@@ -6054,7 +6054,7 @@
         <v>0.009318147037737418</v>
       </c>
       <c r="H88" t="n">
-        <v>0.007917772554059579</v>
+        <v>0.007917772554059581</v>
       </c>
       <c r="I88" t="n">
         <v>0.01284959218027198</v>
@@ -6188,7 +6188,7 @@
         <v>0.0006496322593720387</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0006290927455933049</v>
+        <v>0.0006290927455933047</v>
       </c>
       <c r="K90" t="n">
         <v>0.0005850455472596548</v>
@@ -6197,7 +6197,7 @@
         <v>0.0006551002120700136</v>
       </c>
       <c r="M90" t="n">
-        <v>0.0006954301821555453</v>
+        <v>0.0006954301821555452</v>
       </c>
       <c r="N90" t="n">
         <v>0.0006790115696505156</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.0002420094178200132</v>
+        <v>0.0002420094178200133</v>
       </c>
       <c r="D92" t="n">
         <v>0.0002170311398949467</v>
@@ -6304,7 +6304,7 @@
         <v>0.0002212119913315144</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0002006251282465115</v>
+        <v>0.0002006251282465114</v>
       </c>
       <c r="G92" t="n">
         <v>0.0002214256611316447</v>
@@ -6322,7 +6322,7 @@
         <v>0.0002847580151946248</v>
       </c>
       <c r="L92" t="n">
-        <v>0.000356365762642837</v>
+        <v>0.0003563657626428372</v>
       </c>
       <c r="M92" t="n">
         <v>0.0003568566823863595</v>
@@ -6331,16 +6331,16 @@
         <v>0.0003557053572316754</v>
       </c>
       <c r="O92" t="n">
-        <v>0.000621593626104158</v>
+        <v>0.0006215936261041579</v>
       </c>
       <c r="P92" t="n">
-        <v>0.0005466391326850275</v>
+        <v>0.0005466391326850276</v>
       </c>
       <c r="Q92" t="n">
         <v>0.0005742908561919574</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0007806100577805832</v>
+        <v>0.0007806100577805833</v>
       </c>
       <c r="S92" t="n">
         <v>0.000689238758295831</v>
@@ -6432,13 +6432,13 @@
         <v>0.001042945306637311</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0008207180984568261</v>
+        <v>0.0008207180984568263</v>
       </c>
       <c r="G94" t="n">
         <v>0.0009470753771369663</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0006359212337559353</v>
+        <v>0.0006359212337559352</v>
       </c>
       <c r="I94" t="n">
         <v>0.001155123068489884</v>
@@ -6465,7 +6465,7 @@
         <v>0.001776095454893245</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.001523972816235016</v>
+        <v>0.001523972816235017</v>
       </c>
       <c r="R94" t="n">
         <v>0.002004638173650223</v>
@@ -6502,7 +6502,7 @@
         <v>0.001136815110097682</v>
       </c>
       <c r="H95" t="n">
-        <v>0.001434695428067532</v>
+        <v>0.001434695428067531</v>
       </c>
       <c r="I95" t="n">
         <v>0.001530847424523807</v>
@@ -6535,7 +6535,7 @@
         <v>0.002015101849013546</v>
       </c>
       <c r="S95" t="n">
-        <v>0.001698296646146561</v>
+        <v>0.001698296646146562</v>
       </c>
       <c r="T95" t="n">
         <v>0.001824822719678126</v>
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.000548432359801788</v>
+        <v>0.0005484323598017881</v>
       </c>
       <c r="D96" t="n">
         <v>0.0004468424794750306</v>
@@ -6560,7 +6560,7 @@
         <v>0.0004380495068834315</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0004413682976343705</v>
+        <v>0.0004413682976343704</v>
       </c>
       <c r="G96" t="n">
         <v>0.0004971125578609572</v>
@@ -6569,16 +6569,16 @@
         <v>0.0007222300877987053</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0008245818733173217</v>
+        <v>0.0008245818733173216</v>
       </c>
       <c r="J96" t="n">
         <v>0.0007635328440068612</v>
       </c>
       <c r="K96" t="n">
-        <v>0.0007719817187753406</v>
+        <v>0.0007719817187753407</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0009035727868920772</v>
+        <v>0.0009035727868920771</v>
       </c>
       <c r="M96" t="n">
         <v>0.0008764307449400536</v>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7.701167169960175e-05</v>
+        <v>7.701167169960174e-05</v>
       </c>
       <c r="D97" t="n">
-        <v>8.104075655804424e-05</v>
+        <v>8.104075655804425e-05</v>
       </c>
       <c r="E97" t="n">
         <v>7.256548044418695e-05</v>
@@ -6642,7 +6642,7 @@
         <v>0.0001054507779651953</v>
       </c>
       <c r="L97" t="n">
-        <v>0.0001487846301531955</v>
+        <v>0.0001487846301531954</v>
       </c>
       <c r="M97" t="n">
         <v>0.0001364525827404441</v>
@@ -6666,7 +6666,7 @@
         <v>0.0003230218731935015</v>
       </c>
       <c r="T97" t="n">
-        <v>0.0003347933954237593</v>
+        <v>0.0003347933954237592</v>
       </c>
     </row>
     <row r="98">
@@ -6682,10 +6682,10 @@
         <v>0.0001808350778486648</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0001718924813051544</v>
+        <v>0.0001718924813051543</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0001649559660628179</v>
+        <v>0.0001649559660628178</v>
       </c>
       <c r="F98" t="n">
         <v>0.0001841309052624612</v>
@@ -6712,22 +6712,22 @@
         <v>0.0003104585732514793</v>
       </c>
       <c r="N98" t="n">
-        <v>0.0003219204796648441</v>
+        <v>0.000321920479664844</v>
       </c>
       <c r="O98" t="n">
-        <v>0.000556404494368939</v>
+        <v>0.0005564044943689388</v>
       </c>
       <c r="P98" t="n">
-        <v>0.0005853360449993807</v>
+        <v>0.0005853360449993806</v>
       </c>
       <c r="Q98" t="n">
         <v>0.0005265538925808735</v>
       </c>
       <c r="R98" t="n">
-        <v>0.0006518565227318972</v>
+        <v>0.0006518565227318971</v>
       </c>
       <c r="S98" t="n">
-        <v>0.000615149070053512</v>
+        <v>0.0006151490700535121</v>
       </c>
       <c r="T98" t="n">
         <v>0.0006668033571970913</v>
@@ -6746,7 +6746,7 @@
         <v>8.704711364973072e-05</v>
       </c>
       <c r="D99" t="n">
-        <v>7.579090925858129e-05</v>
+        <v>7.579090925858127e-05</v>
       </c>
       <c r="E99" t="n">
         <v>9.656937524371245e-05</v>
@@ -6755,7 +6755,7 @@
         <v>9.365582743305198e-05</v>
       </c>
       <c r="G99" t="n">
-        <v>9.62005825567072e-05</v>
+        <v>9.620058255670721e-05</v>
       </c>
       <c r="H99" t="n">
         <v>0.0001166353899263836</v>
@@ -6770,7 +6770,7 @@
         <v>0.0001386015078837818</v>
       </c>
       <c r="L99" t="n">
-        <v>0.0001643956793533564</v>
+        <v>0.0001643956793533565</v>
       </c>
       <c r="M99" t="n">
         <v>0.0001584900834957547</v>
@@ -6785,7 +6785,7 @@
         <v>0.000290017789956531</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.0002757623812084135</v>
+        <v>0.0002757623812084134</v>
       </c>
       <c r="R99" t="n">
         <v>0.0003503632630264545</v>
@@ -6807,28 +6807,28 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.0004231771138989529</v>
+        <v>0.000423177113898953</v>
       </c>
       <c r="D100" t="n">
         <v>0.0003793465581696168</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0004242372532230605</v>
+        <v>0.0004242372532230604</v>
       </c>
       <c r="F100" t="n">
         <v>0.0003563266228121634</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0003545382326522413</v>
+        <v>0.0003545382326522412</v>
       </c>
       <c r="H100" t="n">
         <v>0.0004377629325855748</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0005521566328917952</v>
+        <v>0.0005521566328917951</v>
       </c>
       <c r="J100" t="n">
-        <v>0.000468423517016027</v>
+        <v>0.0004684235170160269</v>
       </c>
       <c r="K100" t="n">
         <v>0.0004654911258274828</v>
@@ -6843,7 +6843,7 @@
         <v>0.0005653204023816145</v>
       </c>
       <c r="O100" t="n">
-        <v>0.0008829934578995642</v>
+        <v>0.0008829934578995643</v>
       </c>
       <c r="P100" t="n">
         <v>0.0008759370355471241</v>
@@ -6855,7 +6855,7 @@
         <v>0.0009815453833992437</v>
       </c>
       <c r="S100" t="n">
-        <v>0.0009803876243405436</v>
+        <v>0.0009803876243405433</v>
       </c>
       <c r="T100" t="n">
         <v>0.001103597424587455</v>
@@ -6871,13 +6871,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.000514809799146104</v>
+        <v>0.0005148097991461039</v>
       </c>
       <c r="D101" t="n">
         <v>0.0005059353880968008</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0004684685064736215</v>
+        <v>0.0004684685064736216</v>
       </c>
       <c r="F101" t="n">
         <v>0.0003725797737103704</v>
@@ -6889,7 +6889,7 @@
         <v>0.0003936241574469448</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0006765232233377168</v>
+        <v>0.0006765232233377166</v>
       </c>
       <c r="J101" t="n">
         <v>0.0005281283995391038</v>
@@ -6898,7 +6898,7 @@
         <v>0.0006213107411406873</v>
       </c>
       <c r="L101" t="n">
-        <v>0.0006838931965741703</v>
+        <v>0.0006838931965741704</v>
       </c>
       <c r="M101" t="n">
         <v>0.0007218665513508001</v>
@@ -6968,7 +6968,7 @@
         <v>0.005395045018860396</v>
       </c>
       <c r="N102" t="n">
-        <v>0.005372424297664286</v>
+        <v>0.005372424297664287</v>
       </c>
       <c r="O102" t="n">
         <v>0.0100594531159249</v>
@@ -6977,7 +6977,7 @@
         <v>0.009672649091345355</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.007200974759195216</v>
+        <v>0.007200974759195215</v>
       </c>
       <c r="R102" t="n">
         <v>0.01271129314764806</v>
@@ -7014,13 +7014,13 @@
         <v>0.0001183753987228475</v>
       </c>
       <c r="H103" t="n">
-        <v>0.000163821945913131</v>
+        <v>0.0001638219459131309</v>
       </c>
       <c r="I103" t="n">
         <v>0.0001876386813603034</v>
       </c>
       <c r="J103" t="n">
-        <v>0.0001634203544936842</v>
+        <v>0.0001634203544936843</v>
       </c>
       <c r="K103" t="n">
         <v>0.0001646220427507586</v>
@@ -7069,10 +7069,10 @@
         <v>0.0002769263953794417</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0002669034313371819</v>
+        <v>0.000266903431337182</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0002678779259221557</v>
+        <v>0.0002678779259221558</v>
       </c>
       <c r="G104" t="n">
         <v>0.0002765962571633018</v>
@@ -7105,16 +7105,16 @@
         <v>0.0005807431175099124</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.000551418719251398</v>
+        <v>0.0005514187192513978</v>
       </c>
       <c r="R104" t="n">
-        <v>0.0006149388012945306</v>
+        <v>0.0006149388012945307</v>
       </c>
       <c r="S104" t="n">
         <v>0.0006168579429813346</v>
       </c>
       <c r="T104" t="n">
-        <v>0.0007103882863493943</v>
+        <v>0.0007103882863493944</v>
       </c>
     </row>
     <row r="105">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.0003281195260737334</v>
+        <v>0.0003281195260737335</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0002992334864261158</v>
+        <v>0.0002992334864261159</v>
       </c>
       <c r="E105" t="n">
         <v>0.000275117051719068</v>
@@ -7139,13 +7139,13 @@
         <v>0.0002711204103280613</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0002843057261366184</v>
+        <v>0.0002843057261366183</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0002937350389962245</v>
+        <v>0.0002937350389962246</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0004309743791230669</v>
+        <v>0.0004309743791230668</v>
       </c>
       <c r="J105" t="n">
         <v>0.0003776526779766492</v>
@@ -7154,10 +7154,10 @@
         <v>0.0003673730396040664</v>
       </c>
       <c r="L105" t="n">
-        <v>0.0004079886253197027</v>
+        <v>0.0004079886253197026</v>
       </c>
       <c r="M105" t="n">
-        <v>0.00041097819110799</v>
+        <v>0.0004109781911079899</v>
       </c>
       <c r="N105" t="n">
         <v>0.0004352813924060797</v>
@@ -7166,7 +7166,7 @@
         <v>0.0006138876562689627</v>
       </c>
       <c r="P105" t="n">
-        <v>0.0006859380279745259</v>
+        <v>0.0006859380279745258</v>
       </c>
       <c r="Q105" t="n">
         <v>0.0006079043915093755</v>
@@ -7203,7 +7203,7 @@
         <v>0.000468587409488516</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0005223190404285563</v>
+        <v>0.0005223190404285562</v>
       </c>
       <c r="H106" t="n">
         <v>0.0005744933669933773</v>
@@ -7215,10 +7215,10 @@
         <v>0.0006357353647402054</v>
       </c>
       <c r="K106" t="n">
-        <v>0.0006361350558831927</v>
+        <v>0.0006361350558831928</v>
       </c>
       <c r="L106" t="n">
-        <v>0.0006975126028247367</v>
+        <v>0.0006975126028247368</v>
       </c>
       <c r="M106" t="n">
         <v>0.0007085769844078783</v>
@@ -7258,7 +7258,7 @@
         <v>0.0001203949576113875</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0001039714513592693</v>
+        <v>0.0001039714513592692</v>
       </c>
       <c r="E107" t="n">
         <v>8.275764508310722e-05</v>
@@ -7337,22 +7337,22 @@
         <v>0.00166399091866954</v>
       </c>
       <c r="I108" t="n">
-        <v>0.002059701171953409</v>
+        <v>0.002059701171953408</v>
       </c>
       <c r="J108" t="n">
-        <v>0.001825634799248105</v>
+        <v>0.001825634799248106</v>
       </c>
       <c r="K108" t="n">
-        <v>0.001842983141750745</v>
+        <v>0.001842983141750746</v>
       </c>
       <c r="L108" t="n">
         <v>0.002048684847425215</v>
       </c>
       <c r="M108" t="n">
-        <v>0.002012945057390617</v>
+        <v>0.002012945057390616</v>
       </c>
       <c r="N108" t="n">
-        <v>0.002159379518076259</v>
+        <v>0.00215937951807626</v>
       </c>
       <c r="O108" t="n">
         <v>0.003172511747497062</v>
@@ -7367,10 +7367,10 @@
         <v>0.003779187269129662</v>
       </c>
       <c r="S108" t="n">
-        <v>0.003409692303071313</v>
+        <v>0.003409692303071311</v>
       </c>
       <c r="T108" t="n">
-        <v>0.003833816121304411</v>
+        <v>0.00383381612130441</v>
       </c>
     </row>
     <row r="109">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.0005090174567251069</v>
+        <v>0.000509017456725107</v>
       </c>
       <c r="D110" t="n">
         <v>0.0004652649040581745</v>
@@ -7486,7 +7486,7 @@
         <v>0.001055216403329197</v>
       </c>
       <c r="P110" t="n">
-        <v>0.001161792543355035</v>
+        <v>0.001161792543355036</v>
       </c>
       <c r="Q110" t="n">
         <v>0.0008645508298559274</v>
@@ -7511,13 +7511,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.007147848405644123</v>
+        <v>0.007147848405644124</v>
       </c>
       <c r="D111" t="n">
         <v>0.006530013923308905</v>
       </c>
       <c r="E111" t="n">
-        <v>0.006737260256479563</v>
+        <v>0.006737260256479564</v>
       </c>
       <c r="F111" t="n">
         <v>0.005652538325049849</v>
@@ -7526,7 +7526,7 @@
         <v>0.006064454686206185</v>
       </c>
       <c r="H111" t="n">
-        <v>0.007214653678758307</v>
+        <v>0.007214653678758311</v>
       </c>
       <c r="I111" t="n">
         <v>0.008791239177832397</v>
@@ -7535,16 +7535,16 @@
         <v>0.007365134961187587</v>
       </c>
       <c r="K111" t="n">
-        <v>0.007696000366660278</v>
+        <v>0.007696000366660277</v>
       </c>
       <c r="L111" t="n">
-        <v>0.008531112633392924</v>
+        <v>0.008531112633392922</v>
       </c>
       <c r="M111" t="n">
         <v>0.008130492792810622</v>
       </c>
       <c r="N111" t="n">
-        <v>0.008262168682014209</v>
+        <v>0.008262168682014213</v>
       </c>
       <c r="O111" t="n">
         <v>0.01306399765912115</v>
@@ -7587,7 +7587,7 @@
         <v>0.0004740470611210126</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0005040043478129772</v>
+        <v>0.0005040043478129773</v>
       </c>
       <c r="H112" t="n">
         <v>0.0005086751465523831</v>
@@ -7596,7 +7596,7 @@
         <v>0.0006598873882081577</v>
       </c>
       <c r="J112" t="n">
-        <v>0.000636295014476672</v>
+        <v>0.0006362950144766721</v>
       </c>
       <c r="K112" t="n">
         <v>0.000594871373039336</v>
@@ -7706,7 +7706,7 @@
         <v>5.418175824221336e-05</v>
       </c>
       <c r="D114" t="n">
-        <v>5.663931402314569e-05</v>
+        <v>5.663931402314568e-05</v>
       </c>
       <c r="E114" t="n">
         <v>4.636119405373623e-05</v>
@@ -7721,7 +7721,7 @@
         <v>8.585300278822269e-05</v>
       </c>
       <c r="I114" t="n">
-        <v>7.864422016270533e-05</v>
+        <v>7.864422016270534e-05</v>
       </c>
       <c r="J114" t="n">
         <v>6.591663919710182e-05</v>
@@ -7773,10 +7773,10 @@
         <v>0.0010197577509933</v>
       </c>
       <c r="E115" t="n">
-        <v>0.001037536273876655</v>
+        <v>0.001037536273876654</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0009990619572347898</v>
+        <v>0.00099906195723479</v>
       </c>
       <c r="G115" t="n">
         <v>0.001038747981050774</v>
@@ -7791,7 +7791,7 @@
         <v>0.001380778166489826</v>
       </c>
       <c r="K115" t="n">
-        <v>0.001403785110581796</v>
+        <v>0.001403785110581797</v>
       </c>
       <c r="L115" t="n">
         <v>0.001762556040017662</v>
@@ -7834,10 +7834,10 @@
         <v>0.0003446181325606332</v>
       </c>
       <c r="D116" t="n">
-        <v>0.0003085533645825065</v>
+        <v>0.0003085533645825064</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0003239574441846765</v>
+        <v>0.0003239574441846764</v>
       </c>
       <c r="F116" t="n">
         <v>0.0002892075629600128</v>
@@ -7846,7 +7846,7 @@
         <v>0.0003113433482958528</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0003226964778247655</v>
+        <v>0.0003226964778247656</v>
       </c>
       <c r="I116" t="n">
         <v>0.0004150705282411047</v>
@@ -7864,7 +7864,7 @@
         <v>0.0003925575484067068</v>
       </c>
       <c r="N116" t="n">
-        <v>0.0004235862255352092</v>
+        <v>0.0004235862255352091</v>
       </c>
       <c r="O116" t="n">
         <v>0.0006171008020656691</v>
@@ -7873,7 +7873,7 @@
         <v>0.0006203190875769606</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.0005924630684149527</v>
+        <v>0.0005924630684149526</v>
       </c>
       <c r="R116" t="n">
         <v>0.0006492516222633954</v>
@@ -7882,7 +7882,7 @@
         <v>0.0006594607850583615</v>
       </c>
       <c r="T116" t="n">
-        <v>0.0007669408186580523</v>
+        <v>0.000766940818658052</v>
       </c>
     </row>
     <row r="117">
@@ -7907,7 +7907,7 @@
         <v>0.0001453750515334986</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0001133677673913558</v>
+        <v>0.0001133677673913557</v>
       </c>
       <c r="H117" t="n">
         <v>0.000171288110198191</v>
@@ -7919,10 +7919,10 @@
         <v>0.0002205986636869308</v>
       </c>
       <c r="K117" t="n">
-        <v>0.0002598505780225361</v>
+        <v>0.000259850578022536</v>
       </c>
       <c r="L117" t="n">
-        <v>0.0002830954641293459</v>
+        <v>0.000283095464129346</v>
       </c>
       <c r="M117" t="n">
         <v>0.0002666394848199745</v>
@@ -7931,7 +7931,7 @@
         <v>0.0002062096273551532</v>
       </c>
       <c r="O117" t="n">
-        <v>0.0005474047743563915</v>
+        <v>0.0005474047743563914</v>
       </c>
       <c r="P117" t="n">
         <v>0.0005724282905675983</v>
@@ -8023,22 +8023,22 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.0008374511892421997</v>
+        <v>0.0008374511892421998</v>
       </c>
       <c r="D119" t="n">
-        <v>0.0007057024568883135</v>
+        <v>0.0007057024568883136</v>
       </c>
       <c r="E119" t="n">
         <v>0.0007760414324597531</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0008854474032033803</v>
+        <v>0.0008854474032033802</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0009385091090253415</v>
+        <v>0.0009385091090253416</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0009041365314913682</v>
+        <v>0.0009041365314913683</v>
       </c>
       <c r="I119" t="n">
         <v>0.001579205010724203</v>
@@ -8053,10 +8053,10 @@
         <v>0.001668597086511535</v>
       </c>
       <c r="M119" t="n">
-        <v>0.001533844657351756</v>
+        <v>0.001533844657351755</v>
       </c>
       <c r="N119" t="n">
-        <v>0.001706667776595202</v>
+        <v>0.001706667776595201</v>
       </c>
       <c r="O119" t="n">
         <v>0.002485102313413088</v>
@@ -8087,19 +8087,19 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.08294435941061665</v>
+        <v>0.08294435941061667</v>
       </c>
       <c r="D120" t="n">
         <v>0.07244715071478684</v>
       </c>
       <c r="E120" t="n">
-        <v>0.07671815958582949</v>
+        <v>0.07671815958582948</v>
       </c>
       <c r="F120" t="n">
-        <v>0.07302167194658785</v>
+        <v>0.07302167194658782</v>
       </c>
       <c r="G120" t="n">
-        <v>0.07399650220444437</v>
+        <v>0.07399650220444438</v>
       </c>
       <c r="H120" t="n">
         <v>0.1052170263830711</v>
@@ -8114,7 +8114,7 @@
         <v>0.1056934808324097</v>
       </c>
       <c r="L120" t="n">
-        <v>0.1525421859210691</v>
+        <v>0.152542185921069</v>
       </c>
       <c r="M120" t="n">
         <v>0.1478156520677522</v>
@@ -8138,7 +8138,7 @@
         <v>0.5759239926054915</v>
       </c>
       <c r="T120" t="n">
-        <v>0.5645843964217835</v>
+        <v>0.5645843964217834</v>
       </c>
     </row>
     <row r="121">
@@ -8230,7 +8230,7 @@
         <v>9.700381777678582e-05</v>
       </c>
       <c r="H122" t="n">
-        <v>6.444175435842752e-05</v>
+        <v>6.444175435842753e-05</v>
       </c>
       <c r="I122" t="n">
         <v>0.0001208756126330559</v>
@@ -8245,10 +8245,10 @@
         <v>0.0001254752240059063</v>
       </c>
       <c r="M122" t="n">
-        <v>0.0001133082436819777</v>
+        <v>0.0001133082436819778</v>
       </c>
       <c r="N122" t="n">
-        <v>0.0001414580864127321</v>
+        <v>0.0001414580864127322</v>
       </c>
       <c r="O122" t="n">
         <v>0.0001634599540315375</v>
@@ -8288,7 +8288,7 @@
         <v>0.003533748019788139</v>
       </c>
       <c r="F123" t="n">
-        <v>0.002948822526991089</v>
+        <v>0.00294882252699109</v>
       </c>
       <c r="G123" t="n">
         <v>0.003054973716370517</v>
@@ -8297,7 +8297,7 @@
         <v>0.003577567405704181</v>
       </c>
       <c r="I123" t="n">
-        <v>0.004737435951652457</v>
+        <v>0.004737435951652458</v>
       </c>
       <c r="J123" t="n">
         <v>0.004213765123830884</v>
@@ -8306,7 +8306,7 @@
         <v>0.004191737774084481</v>
       </c>
       <c r="L123" t="n">
-        <v>0.005015183497732232</v>
+        <v>0.005015183497732233</v>
       </c>
       <c r="M123" t="n">
         <v>0.004480007275639681</v>
@@ -8318,7 +8318,7 @@
         <v>0.008199627325934856</v>
       </c>
       <c r="P123" t="n">
-        <v>0.008452697600896978</v>
+        <v>0.008452697600896977</v>
       </c>
       <c r="Q123" t="n">
         <v>0.009383636265620223</v>
@@ -8373,13 +8373,13 @@
         <v>0.002227931083909796</v>
       </c>
       <c r="M124" t="n">
-        <v>0.002343367730609251</v>
+        <v>0.00234336773060925</v>
       </c>
       <c r="N124" t="n">
-        <v>0.00234432522969461</v>
+        <v>0.002344325229694611</v>
       </c>
       <c r="O124" t="n">
-        <v>0.003602182383823798</v>
+        <v>0.003602182383823797</v>
       </c>
       <c r="P124" t="n">
         <v>0.003846416694744855</v>
@@ -8413,7 +8413,7 @@
         <v>0.00364061851595127</v>
       </c>
       <c r="E125" t="n">
-        <v>0.003334963984193435</v>
+        <v>0.003334963984193434</v>
       </c>
       <c r="F125" t="n">
         <v>0.003582132138181014</v>
@@ -8428,13 +8428,13 @@
         <v>0.005302572990986082</v>
       </c>
       <c r="J125" t="n">
-        <v>0.004217126843982003</v>
+        <v>0.004217126843982001</v>
       </c>
       <c r="K125" t="n">
         <v>0.00482352229059526</v>
       </c>
       <c r="L125" t="n">
-        <v>0.005411799257794388</v>
+        <v>0.005411799257794389</v>
       </c>
       <c r="M125" t="n">
         <v>0.004888420028105881</v>
@@ -8443,7 +8443,7 @@
         <v>0.005347422089636876</v>
       </c>
       <c r="O125" t="n">
-        <v>0.007723229612201965</v>
+        <v>0.007723229612201963</v>
       </c>
       <c r="P125" t="n">
         <v>0.008097523801534201</v>
@@ -8452,7 +8452,7 @@
         <v>0.007843068793175079</v>
       </c>
       <c r="R125" t="n">
-        <v>0.008485405230374143</v>
+        <v>0.008485405230374145</v>
       </c>
       <c r="S125" t="n">
         <v>0.009047123790318325</v>
@@ -8538,16 +8538,16 @@
         <v>0.0003341776578469771</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0002947399868782468</v>
+        <v>0.0002947399868782469</v>
       </c>
       <c r="E127" t="n">
         <v>0.0002587802709785501</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0003191228624974081</v>
+        <v>0.000319122862497408</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0003228298492788283</v>
+        <v>0.0003228298492788282</v>
       </c>
       <c r="H127" t="n">
         <v>0.0003097559130749407</v>
@@ -8580,13 +8580,13 @@
         <v>0.001139974569000209</v>
       </c>
       <c r="R127" t="n">
-        <v>0.001354100336958297</v>
+        <v>0.001354100336958298</v>
       </c>
       <c r="S127" t="n">
         <v>0.001432423578940734</v>
       </c>
       <c r="T127" t="n">
-        <v>0.001441582478889107</v>
+        <v>0.001441582478889106</v>
       </c>
     </row>
     <row r="128">
@@ -8614,7 +8614,7 @@
         <v>0.0007949861284293209</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0005788121959783458</v>
+        <v>0.0005788121959783459</v>
       </c>
       <c r="I128" t="n">
         <v>0.001090662804698195</v>
@@ -8623,7 +8623,7 @@
         <v>0.0008439556200055046</v>
       </c>
       <c r="K128" t="n">
-        <v>0.0009637269702751817</v>
+        <v>0.0009637269702751815</v>
       </c>
       <c r="L128" t="n">
         <v>0.001043186885857015</v>
@@ -8666,7 +8666,7 @@
         <v>0.0002836671988360609</v>
       </c>
       <c r="D129" t="n">
-        <v>0.0002364355398638173</v>
+        <v>0.0002364355398638174</v>
       </c>
       <c r="E129" t="n">
         <v>0.0002384822229516347</v>
@@ -8678,7 +8678,7 @@
         <v>0.0002167103776823667</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0002843712783910105</v>
+        <v>0.0002843712783910106</v>
       </c>
       <c r="I129" t="n">
         <v>0.0003781142538314995</v>
@@ -8687,7 +8687,7 @@
         <v>0.0003235393319982524</v>
       </c>
       <c r="K129" t="n">
-        <v>0.0003156363727811173</v>
+        <v>0.0003156363727811172</v>
       </c>
       <c r="L129" t="n">
         <v>0.0003765201396395068</v>
@@ -8702,7 +8702,7 @@
         <v>0.0006140476376906025</v>
       </c>
       <c r="P129" t="n">
-        <v>0.0006103948064226452</v>
+        <v>0.0006103948064226453</v>
       </c>
       <c r="Q129" t="n">
         <v>0.0006760158205681158</v>
@@ -8739,16 +8739,16 @@
         <v>0.0001837895131469715</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0001889567661646296</v>
+        <v>0.0001889567661646297</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0001811583334806758</v>
+        <v>0.0001811583334806759</v>
       </c>
       <c r="I130" t="n">
         <v>0.0002828623328330711</v>
       </c>
       <c r="J130" t="n">
-        <v>0.0002422348512885662</v>
+        <v>0.0002422348512885661</v>
       </c>
       <c r="K130" t="n">
         <v>0.000264208326532129</v>
@@ -8766,19 +8766,19 @@
         <v>0.0005032180095659545</v>
       </c>
       <c r="P130" t="n">
-        <v>0.0005143332813676093</v>
+        <v>0.0005143332813676094</v>
       </c>
       <c r="Q130" t="n">
         <v>0.0004815063007408813</v>
       </c>
       <c r="R130" t="n">
-        <v>0.0006195055794507304</v>
+        <v>0.0006195055794507305</v>
       </c>
       <c r="S130" t="n">
         <v>0.0005930251422931644</v>
       </c>
       <c r="T130" t="n">
-        <v>0.0006181830083405933</v>
+        <v>0.0006181830083405932</v>
       </c>
     </row>
     <row r="131">
@@ -8791,13 +8791,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.0004098282715403446</v>
+        <v>0.0004098282715403447</v>
       </c>
       <c r="D131" t="n">
         <v>0.0003719655846756468</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0003911675795254288</v>
+        <v>0.0003911675795254287</v>
       </c>
       <c r="F131" t="n">
         <v>0.00038773232435355</v>
@@ -8812,16 +8812,16 @@
         <v>0.0005970426026338269</v>
       </c>
       <c r="J131" t="n">
-        <v>0.0005076960394431194</v>
+        <v>0.0005076960394431193</v>
       </c>
       <c r="K131" t="n">
         <v>0.0005226102825393457</v>
       </c>
       <c r="L131" t="n">
-        <v>0.0006497051065133891</v>
+        <v>0.000649705106513389</v>
       </c>
       <c r="M131" t="n">
-        <v>0.00063318566303486</v>
+        <v>0.0006331856630348601</v>
       </c>
       <c r="N131" t="n">
         <v>0.0006653381405512702</v>
@@ -8833,10 +8833,10 @@
         <v>0.001027326335436446</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.001044239794710779</v>
+        <v>0.00104423979471078</v>
       </c>
       <c r="R131" t="n">
-        <v>0.001279003625796201</v>
+        <v>0.0012790036257962</v>
       </c>
       <c r="S131" t="n">
         <v>0.001236341242380846</v>
@@ -8876,7 +8876,7 @@
         <v>0.0003833325408872984</v>
       </c>
       <c r="J132" t="n">
-        <v>0.000317217455294705</v>
+        <v>0.0003172174552947051</v>
       </c>
       <c r="K132" t="n">
         <v>0.00032461456573768</v>
@@ -8900,10 +8900,10 @@
         <v>0.0006321351751211766</v>
       </c>
       <c r="R132" t="n">
-        <v>0.0007406336390682554</v>
+        <v>0.0007406336390682555</v>
       </c>
       <c r="S132" t="n">
-        <v>0.0007890901791257756</v>
+        <v>0.0007890901791257755</v>
       </c>
       <c r="T132" t="n">
         <v>0.0007755771346502321</v>
@@ -8928,10 +8928,10 @@
         <v>0.00453044603107151</v>
       </c>
       <c r="F133" t="n">
-        <v>0.004946411591386993</v>
+        <v>0.004946411591386994</v>
       </c>
       <c r="G133" t="n">
-        <v>0.005366816874833897</v>
+        <v>0.005366816874833896</v>
       </c>
       <c r="H133" t="n">
         <v>0.005107404369321484</v>
@@ -8995,7 +8995,7 @@
         <v>1.044860789430714e-05</v>
       </c>
       <c r="G134" t="n">
-        <v>1.104254080964704e-05</v>
+        <v>1.104254080964705e-05</v>
       </c>
       <c r="H134" t="n">
         <v>1.454756455273593e-05</v>
@@ -9004,7 +9004,7 @@
         <v>1.33219437242415e-05</v>
       </c>
       <c r="J134" t="n">
-        <v>1.179705885810155e-05</v>
+        <v>1.179705885810154e-05</v>
       </c>
       <c r="K134" t="n">
         <v>9.577847415904517e-06</v>
@@ -9016,7 +9016,7 @@
         <v>1.409286831441157e-05</v>
       </c>
       <c r="N134" t="n">
-        <v>1.449712576945148e-05</v>
+        <v>1.449712576945149e-05</v>
       </c>
       <c r="O134" t="n">
         <v>1.263812129707981e-05</v>
@@ -9034,7 +9034,7 @@
         <v>1.543914967820906e-05</v>
       </c>
       <c r="T134" t="n">
-        <v>2.074225799857105e-05</v>
+        <v>2.074225799857104e-05</v>
       </c>
     </row>
     <row r="135">
@@ -9062,13 +9062,13 @@
         <v>7.820272408018849e-05</v>
       </c>
       <c r="H135" t="n">
-        <v>7.722665167844125e-05</v>
+        <v>7.722665167844127e-05</v>
       </c>
       <c r="I135" t="n">
         <v>0.0001045199426009159</v>
       </c>
       <c r="J135" t="n">
-        <v>9.003486421357502e-05</v>
+        <v>9.003486421357501e-05</v>
       </c>
       <c r="K135" t="n">
         <v>9.022922387731306e-05</v>
@@ -9083,7 +9083,7 @@
         <v>0.0001258380609405097</v>
       </c>
       <c r="O135" t="n">
-        <v>0.0002211602638222907</v>
+        <v>0.0002211602638222908</v>
       </c>
       <c r="P135" t="n">
         <v>0.0002379470581590378</v>
@@ -9092,7 +9092,7 @@
         <v>0.0002369660470445203</v>
       </c>
       <c r="R135" t="n">
-        <v>0.0002908111372404711</v>
+        <v>0.000290811137240471</v>
       </c>
       <c r="S135" t="n">
         <v>0.0002868133134086001</v>
@@ -9181,13 +9181,13 @@
         <v>5.987897606895392e-05</v>
       </c>
       <c r="E137" t="n">
-        <v>7.592792195923593e-05</v>
+        <v>7.592792195923595e-05</v>
       </c>
       <c r="F137" t="n">
-        <v>9.067798318112058e-05</v>
+        <v>9.06779831811206e-05</v>
       </c>
       <c r="G137" t="n">
-        <v>9.26398038954789e-05</v>
+        <v>9.263980389547892e-05</v>
       </c>
       <c r="H137" t="n">
         <v>9.253281528359185e-05</v>
@@ -9196,7 +9196,7 @@
         <v>0.0001165642505054719</v>
       </c>
       <c r="J137" t="n">
-        <v>8.399193914626369e-05</v>
+        <v>8.399193914626368e-05</v>
       </c>
       <c r="K137" t="n">
         <v>0.0001128028122691764</v>
@@ -9220,7 +9220,7 @@
         <v>0.0001531627684869459</v>
       </c>
       <c r="R137" t="n">
-        <v>0.0001778793132019594</v>
+        <v>0.0001778793132019595</v>
       </c>
       <c r="S137" t="n">
         <v>0.0001665894922312595</v>
@@ -9242,13 +9242,13 @@
         <v>3.984140385409662e-05</v>
       </c>
       <c r="D138" t="n">
-        <v>3.715961333039431e-05</v>
+        <v>3.715961333039432e-05</v>
       </c>
       <c r="E138" t="n">
         <v>2.917419740295242e-05</v>
       </c>
       <c r="F138" t="n">
-        <v>3.762848699343751e-05</v>
+        <v>3.76284869934375e-05</v>
       </c>
       <c r="G138" t="n">
         <v>3.924275058133753e-05</v>
@@ -9260,13 +9260,13 @@
         <v>5.615126011644947e-05</v>
       </c>
       <c r="J138" t="n">
-        <v>4.201461271103692e-05</v>
+        <v>4.201461271103691e-05</v>
       </c>
       <c r="K138" t="n">
         <v>4.868407987707679e-05</v>
       </c>
       <c r="L138" t="n">
-        <v>5.726525021532649e-05</v>
+        <v>5.72652502153265e-05</v>
       </c>
       <c r="M138" t="n">
         <v>4.188488593922221e-05</v>
@@ -9275,7 +9275,7 @@
         <v>5.424859735813813e-05</v>
       </c>
       <c r="O138" t="n">
-        <v>8.578213519121597e-05</v>
+        <v>8.578213519121596e-05</v>
       </c>
       <c r="P138" t="n">
         <v>6.457694283470354e-05</v>
@@ -9321,22 +9321,22 @@
         <v>2.7021572002866e-05</v>
       </c>
       <c r="I139" t="n">
-        <v>4.085095622685302e-05</v>
+        <v>4.085095622685301e-05</v>
       </c>
       <c r="J139" t="n">
         <v>3.164702132123839e-05</v>
       </c>
       <c r="K139" t="n">
-        <v>3.464555468065138e-05</v>
+        <v>3.464555468065137e-05</v>
       </c>
       <c r="L139" t="n">
-        <v>3.972424983017393e-05</v>
+        <v>3.972424983017392e-05</v>
       </c>
       <c r="M139" t="n">
         <v>2.912079709059454e-05</v>
       </c>
       <c r="N139" t="n">
-        <v>4.059252126957839e-05</v>
+        <v>4.05925212695784e-05</v>
       </c>
       <c r="O139" t="n">
         <v>6.880220346458619e-05</v>
@@ -9348,13 +9348,13 @@
         <v>7.053963119870861e-05</v>
       </c>
       <c r="R139" t="n">
-        <v>5.235914051958047e-05</v>
+        <v>5.235914051958046e-05</v>
       </c>
       <c r="S139" t="n">
         <v>7.788555778846933e-05</v>
       </c>
       <c r="T139" t="n">
-        <v>7.829605240254974e-05</v>
+        <v>7.829605240254976e-05</v>
       </c>
     </row>
     <row r="140">

--- a/data/proteomics/volume_size_across_compartment_Rosemary_NH4_limitation_v2.xlsx
+++ b/data/proteomics/volume_size_across_compartment_Rosemary_NH4_limitation_v2.xlsx
@@ -535,58 +535,58 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5216809007133776</v>
+        <v>0.5216809007133777</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4769684679962738</v>
+        <v>0.4769684679962741</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4955760349940507</v>
+        <v>0.495576034994051</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3931105192359032</v>
+        <v>0.3931105192359028</v>
       </c>
       <c r="G2" t="n">
         <v>0.4126024609285293</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5771677796630987</v>
+        <v>0.5771677796630981</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5979680544289935</v>
+        <v>0.5979680544289933</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5145316142675039</v>
+        <v>0.5145316142675037</v>
       </c>
       <c r="K2" t="n">
-        <v>0.523712692847541</v>
+        <v>0.5237126928475406</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5596213794442295</v>
+        <v>0.5596213794442294</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5561694262491246</v>
+        <v>0.5561694262491252</v>
       </c>
       <c r="N2" t="n">
         <v>0.5643625727006305</v>
       </c>
       <c r="O2" t="n">
-        <v>1.003591251627263</v>
+        <v>1.003591251627262</v>
       </c>
       <c r="P2" t="n">
         <v>1.00703852499612</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.943174494248561</v>
+        <v>0.9431744942485611</v>
       </c>
       <c r="R2" t="n">
         <v>1.268954997959019</v>
       </c>
       <c r="S2" t="n">
-        <v>1.349875761704194</v>
+        <v>1.349875761704193</v>
       </c>
       <c r="T2" t="n">
-        <v>1.336206532461349</v>
+        <v>1.336206532461348</v>
       </c>
     </row>
     <row r="3">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.001315346070136692</v>
+        <v>0.001315346070136693</v>
       </c>
       <c r="D3" t="n">
         <v>0.001251087432563556</v>
@@ -620,7 +620,7 @@
         <v>0.001311823358583556</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001083998113460814</v>
+        <v>0.001083998113460815</v>
       </c>
       <c r="K3" t="n">
         <v>0.001206541460260438</v>
@@ -638,7 +638,7 @@
         <v>0.00177001969155968</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001821413848389598</v>
+        <v>0.001821413848389597</v>
       </c>
       <c r="Q3" t="n">
         <v>0.001763168397826595</v>
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0008741687319571379</v>
+        <v>0.0008741687319571383</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008074599409869483</v>
+        <v>0.0008074599409869479</v>
       </c>
       <c r="E4" t="n">
         <v>0.0008581465688309836</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008145403158988128</v>
+        <v>0.000814540315898813</v>
       </c>
       <c r="G4" t="n">
         <v>0.0008517442446959936</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008725942137095186</v>
+        <v>0.0008725942137095187</v>
       </c>
       <c r="I4" t="n">
         <v>0.001235246266824286</v>
@@ -702,7 +702,7 @@
         <v>0.001988242490895574</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002022179705322244</v>
+        <v>0.002022179705322243</v>
       </c>
       <c r="Q4" t="n">
         <v>0.002045656496334062</v>
@@ -711,7 +711,7 @@
         <v>0.002390734275881163</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002846418074277858</v>
+        <v>0.00284641807427786</v>
       </c>
       <c r="T4" t="n">
         <v>0.002696512095604279</v>
@@ -794,55 +794,55 @@
         <v>0.3059797381717771</v>
       </c>
       <c r="D6" t="n">
-        <v>0.281007736938048</v>
+        <v>0.2810077369380481</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2947282768547801</v>
+        <v>0.2947282768547799</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2314773302606146</v>
+        <v>0.2314773302606145</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2455508140171152</v>
+        <v>0.2455508140171151</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3293033144088323</v>
+        <v>0.3293033144088321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3458118218316984</v>
+        <v>0.3458118218316987</v>
       </c>
       <c r="J6" t="n">
-        <v>0.302336404624255</v>
+        <v>0.3023364046242545</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3005588484065486</v>
+        <v>0.3005588484065489</v>
       </c>
       <c r="L6" t="n">
         <v>0.3090007872468595</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3122897137102825</v>
+        <v>0.3122897137102826</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3134834026986355</v>
+        <v>0.3134834026986362</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5639857784356533</v>
+        <v>0.5639857784356536</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5678304997106746</v>
+        <v>0.5678304997106745</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5487243817797302</v>
+        <v>0.5487243817797299</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7589202747211448</v>
+        <v>0.758920274721146</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8201641211301661</v>
+        <v>0.8201641211301671</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7741979601311868</v>
+        <v>0.7741979601311886</v>
       </c>
     </row>
     <row r="7">
@@ -855,46 +855,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6744203144378083</v>
+        <v>0.674420314437808</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6152096060663301</v>
+        <v>0.6152096060663299</v>
       </c>
       <c r="E7" t="n">
-        <v>0.629874239965211</v>
+        <v>0.6298742399652116</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5221122862500754</v>
+        <v>0.5221122862500759</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5527945761810198</v>
+        <v>0.5527945761810206</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7523027531461471</v>
+        <v>0.7523027531461467</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8005220388485711</v>
+        <v>0.8005220388485724</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6830876819151378</v>
+        <v>0.6830876819151369</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6922168609053919</v>
+        <v>0.692216860905392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8009106471162772</v>
+        <v>0.8009106471162774</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7774359296731642</v>
+        <v>0.777435929673165</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7655441311337494</v>
+        <v>0.76554413113375</v>
       </c>
       <c r="O7" t="n">
-        <v>1.566262375120505</v>
+        <v>1.566262375120506</v>
       </c>
       <c r="P7" t="n">
-        <v>1.565960937760685</v>
+        <v>1.565960937760687</v>
       </c>
       <c r="Q7" t="n">
         <v>1.522733603813841</v>
@@ -903,10 +903,10 @@
         <v>2.152409749044963</v>
       </c>
       <c r="S7" t="n">
-        <v>2.257748735439359</v>
+        <v>2.257748735439358</v>
       </c>
       <c r="T7" t="n">
-        <v>2.222150261026406</v>
+        <v>2.222150261026404</v>
       </c>
     </row>
     <row r="8">
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.3244746526585782</v>
+        <v>0.3244746526585783</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2866423737727971</v>
+        <v>0.2866423737727969</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2788327981304656</v>
+        <v>0.2788327981304658</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2467845199974298</v>
+        <v>0.2467845199974299</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2551384454210683</v>
+        <v>0.2551384454210684</v>
       </c>
       <c r="H8" t="n">
         <v>0.3869190450973516</v>
@@ -943,34 +943,34 @@
         <v>0.3304304344291121</v>
       </c>
       <c r="K8" t="n">
-        <v>0.330804509371276</v>
+        <v>0.3308045093712763</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3236235345885697</v>
+        <v>0.3236235345885701</v>
       </c>
       <c r="M8" t="n">
-        <v>0.329286336255124</v>
+        <v>0.3292863362551236</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3215322174380015</v>
+        <v>0.3215322174380017</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6217249597239208</v>
+        <v>0.6217249597239214</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6176170768101755</v>
+        <v>0.6176170768101757</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6095370693827069</v>
+        <v>0.6095370693827071</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8599770121380085</v>
+        <v>0.8599770121380079</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9561697891533907</v>
+        <v>0.9561697891533913</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8859234514953058</v>
+        <v>0.8859234514953063</v>
       </c>
     </row>
     <row r="9">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1018344970754371</v>
+        <v>0.1018344970754372</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09500550076582553</v>
+        <v>0.09500550076582551</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08662816483852855</v>
+        <v>0.08662816483852853</v>
       </c>
       <c r="F9" t="n">
         <v>0.07621756979313228</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08059738053946204</v>
+        <v>0.08059738053946207</v>
       </c>
       <c r="H9" t="n">
         <v>0.1157248510346111</v>
@@ -1004,7 +1004,7 @@
         <v>0.1105201273561455</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09664941002444148</v>
+        <v>0.0966494100244415</v>
       </c>
       <c r="K9" t="n">
         <v>0.1001543362025172</v>
@@ -1013,10 +1013,10 @@
         <v>0.08983019100216065</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08957151193742507</v>
+        <v>0.08957151193742505</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0770039807701417</v>
+        <v>0.07700398077014171</v>
       </c>
       <c r="O9" t="n">
         <v>0.179654564965806</v>
@@ -1025,13 +1025,13 @@
         <v>0.1713563778754203</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1912716087407241</v>
+        <v>0.191271608740724</v>
       </c>
       <c r="R9" t="n">
         <v>0.2722666981267455</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2998168788279474</v>
+        <v>0.2998168788279476</v>
       </c>
       <c r="T9" t="n">
         <v>0.2666462512275095</v>
@@ -1120,7 +1120,7 @@
         <v>0.1099763394444485</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09808345730099706</v>
+        <v>0.09808345730099705</v>
       </c>
       <c r="G11" t="n">
         <v>0.1005421342982784</v>
@@ -1135,7 +1135,7 @@
         <v>0.1345131566141796</v>
       </c>
       <c r="K11" t="n">
-        <v>0.13739297388876</v>
+        <v>0.1373929738887599</v>
       </c>
       <c r="L11" t="n">
         <v>0.1200863018213852</v>
@@ -1159,7 +1159,7 @@
         <v>0.3582874022569124</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4363055828050145</v>
+        <v>0.4363055828050146</v>
       </c>
       <c r="T11" t="n">
         <v>0.3693622680058031</v>
@@ -1178,10 +1178,10 @@
         <v>0.03661573016203498</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03319341291824942</v>
+        <v>0.03319341291824938</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03273638017898348</v>
+        <v>0.03273638017898347</v>
       </c>
       <c r="F12" t="n">
         <v>0.03038793374970473</v>
@@ -1196,34 +1196,34 @@
         <v>0.04993554413072915</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04228986996042206</v>
+        <v>0.04228986996042209</v>
       </c>
       <c r="K12" t="n">
         <v>0.04475671142734255</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05150944201058793</v>
+        <v>0.05150944201058789</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04797425623225519</v>
+        <v>0.04797425623225522</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0512834085096938</v>
+        <v>0.05128340850969383</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07973419989798837</v>
+        <v>0.07973419989798844</v>
       </c>
       <c r="P12" t="n">
-        <v>0.08124902627258189</v>
+        <v>0.08124902627258183</v>
       </c>
       <c r="Q12" t="n">
         <v>0.07787174701674474</v>
       </c>
       <c r="R12" t="n">
-        <v>0.09243011071226179</v>
+        <v>0.0924301107122618</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09937742984834658</v>
+        <v>0.0993774298483466</v>
       </c>
       <c r="T12" t="n">
         <v>0.1030537358957392</v>
@@ -1245,10 +1245,10 @@
         <v>0.004394490135591379</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00454508943989994</v>
+        <v>0.004545089439899938</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004705228658975349</v>
+        <v>0.00470522865897535</v>
       </c>
       <c r="G13" t="n">
         <v>0.005466796679180395</v>
@@ -1263,16 +1263,16 @@
         <v>0.006705473885157678</v>
       </c>
       <c r="K13" t="n">
-        <v>0.007561135582411531</v>
+        <v>0.007561135582411533</v>
       </c>
       <c r="L13" t="n">
-        <v>0.008718885598009428</v>
+        <v>0.008718885598009424</v>
       </c>
       <c r="M13" t="n">
-        <v>0.007607491039339359</v>
+        <v>0.007607491039339358</v>
       </c>
       <c r="N13" t="n">
-        <v>0.008764417056238807</v>
+        <v>0.008764417056238812</v>
       </c>
       <c r="O13" t="n">
         <v>0.0116590875381931</v>
@@ -1284,7 +1284,7 @@
         <v>0.01129449410935769</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01023879986485559</v>
+        <v>0.0102387998648556</v>
       </c>
       <c r="S13" t="n">
         <v>0.0108725582319312</v>
@@ -1309,7 +1309,7 @@
         <v>0.02488614675726864</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02851390840384985</v>
+        <v>0.02851390840384986</v>
       </c>
       <c r="F14" t="n">
         <v>0.01864412285172573</v>
@@ -1318,7 +1318,7 @@
         <v>0.02153176724016596</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02685551882242424</v>
+        <v>0.02685551882242425</v>
       </c>
       <c r="I14" t="n">
         <v>0.03208348429314235</v>
@@ -1327,34 +1327,34 @@
         <v>0.0271389515681415</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02660929302392249</v>
+        <v>0.0266092930239225</v>
       </c>
       <c r="L14" t="n">
         <v>0.02950321597263617</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02796646071346001</v>
+        <v>0.02796646071346</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03046264675507623</v>
+        <v>0.03046264675507624</v>
       </c>
       <c r="O14" t="n">
         <v>0.04181081072465669</v>
       </c>
       <c r="P14" t="n">
-        <v>0.04291510369663654</v>
+        <v>0.04291510369663653</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.03743347230456871</v>
+        <v>0.03743347230456872</v>
       </c>
       <c r="R14" t="n">
-        <v>0.04466403727064063</v>
+        <v>0.04466403727064061</v>
       </c>
       <c r="S14" t="n">
         <v>0.04753633934426416</v>
       </c>
       <c r="T14" t="n">
-        <v>0.04880556321010336</v>
+        <v>0.04880556321010338</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>0.0030976627929918</v>
       </c>
       <c r="G15" t="n">
-        <v>0.003390836161339784</v>
+        <v>0.003390836161339783</v>
       </c>
       <c r="H15" t="n">
         <v>0.007042050315566638</v>
@@ -1388,13 +1388,13 @@
         <v>0.00716550631679311</v>
       </c>
       <c r="J15" t="n">
-        <v>0.006207707033002466</v>
+        <v>0.006207707033002465</v>
       </c>
       <c r="K15" t="n">
         <v>0.005661779695231677</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005948138029819546</v>
+        <v>0.005948138029819547</v>
       </c>
       <c r="M15" t="n">
         <v>0.005491708360268059</v>
@@ -1434,49 +1434,49 @@
         <v>0.005712600841827732</v>
       </c>
       <c r="D16" t="n">
-        <v>0.005421618131276169</v>
+        <v>0.005421618131276168</v>
       </c>
       <c r="E16" t="n">
-        <v>0.005124411632473769</v>
+        <v>0.005124411632473768</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005435608453828109</v>
+        <v>0.005435608453828108</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005552460055708858</v>
+        <v>0.005552460055708857</v>
       </c>
       <c r="H16" t="n">
-        <v>0.004732830538987282</v>
+        <v>0.004732830538987281</v>
       </c>
       <c r="I16" t="n">
-        <v>0.008275398215146628</v>
+        <v>0.008275398215146629</v>
       </c>
       <c r="J16" t="n">
-        <v>0.006774819309301443</v>
+        <v>0.006774819309301442</v>
       </c>
       <c r="K16" t="n">
-        <v>0.007244622197151865</v>
+        <v>0.007244622197151864</v>
       </c>
       <c r="L16" t="n">
-        <v>0.008861363455180267</v>
+        <v>0.008861363455180266</v>
       </c>
       <c r="M16" t="n">
-        <v>0.00854389903207008</v>
+        <v>0.008543899032070078</v>
       </c>
       <c r="N16" t="n">
         <v>0.009004211516962006</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01338165463131712</v>
+        <v>0.01338165463131713</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01306321330370543</v>
+        <v>0.01306321330370544</v>
       </c>
       <c r="Q16" t="n">
         <v>0.01286004652863196</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01540950775474596</v>
+        <v>0.01540950775474595</v>
       </c>
       <c r="S16" t="n">
         <v>0.01580657355591384</v>
@@ -1495,52 +1495,52 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.00468125798029845</v>
+        <v>0.004681257980298451</v>
       </c>
       <c r="D17" t="n">
         <v>0.003565421697960223</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003753034575357972</v>
+        <v>0.003753034575357973</v>
       </c>
       <c r="F17" t="n">
-        <v>0.003382527880898953</v>
+        <v>0.003382527880898955</v>
       </c>
       <c r="G17" t="n">
         <v>0.003707618210425617</v>
       </c>
       <c r="H17" t="n">
-        <v>0.003814003674793596</v>
+        <v>0.003814003674793597</v>
       </c>
       <c r="I17" t="n">
         <v>0.005823372495245287</v>
       </c>
       <c r="J17" t="n">
-        <v>0.004912093381638568</v>
+        <v>0.004912093381638569</v>
       </c>
       <c r="K17" t="n">
         <v>0.003290899132391376</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005735802174095195</v>
+        <v>0.005735802174095197</v>
       </c>
       <c r="M17" t="n">
-        <v>0.005473914323963421</v>
+        <v>0.005473914323963424</v>
       </c>
       <c r="N17" t="n">
-        <v>0.005592339099503459</v>
+        <v>0.005592339099503458</v>
       </c>
       <c r="O17" t="n">
         <v>0.004771970529911556</v>
       </c>
       <c r="P17" t="n">
-        <v>0.008943046285670719</v>
+        <v>0.008943046285670725</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.008098476293101774</v>
+        <v>0.008098476293101776</v>
       </c>
       <c r="R17" t="n">
-        <v>0.01000658933129395</v>
+        <v>0.01000658933129396</v>
       </c>
       <c r="S17" t="n">
         <v>0.01044815084225277</v>
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.007443395672678018</v>
+        <v>0.007443395672678017</v>
       </c>
       <c r="D18" t="n">
-        <v>0.006546600532938078</v>
+        <v>0.006546600532938082</v>
       </c>
       <c r="E18" t="n">
         <v>0.006313395272579767</v>
       </c>
       <c r="F18" t="n">
-        <v>0.006037952564738817</v>
+        <v>0.00603795256473882</v>
       </c>
       <c r="G18" t="n">
-        <v>0.006628872311452037</v>
+        <v>0.006628872311452039</v>
       </c>
       <c r="H18" t="n">
         <v>0.006030287112052417</v>
@@ -1580,16 +1580,16 @@
         <v>0.009793894302960116</v>
       </c>
       <c r="J18" t="n">
-        <v>0.008080082426028673</v>
+        <v>0.008080082426028675</v>
       </c>
       <c r="K18" t="n">
-        <v>0.009067461585017549</v>
+        <v>0.009067461585017547</v>
       </c>
       <c r="L18" t="n">
         <v>0.01016044041851465</v>
       </c>
       <c r="M18" t="n">
-        <v>0.009722657632836857</v>
+        <v>0.009722657632836853</v>
       </c>
       <c r="N18" t="n">
         <v>0.01008333486938331</v>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.005026669736446982</v>
+        <v>0.005026669736446984</v>
       </c>
       <c r="D19" t="n">
-        <v>0.004519991787833756</v>
+        <v>0.004519991787833758</v>
       </c>
       <c r="E19" t="n">
         <v>0.004650416166567028</v>
@@ -1635,31 +1635,31 @@
         <v>0.004632007054701646</v>
       </c>
       <c r="G19" t="n">
-        <v>0.004806805586954712</v>
+        <v>0.004806805586954711</v>
       </c>
       <c r="H19" t="n">
-        <v>0.005001973599284327</v>
+        <v>0.005001973599284326</v>
       </c>
       <c r="I19" t="n">
         <v>0.007279032392740479</v>
       </c>
       <c r="J19" t="n">
-        <v>0.006397770808286391</v>
+        <v>0.006397770808286394</v>
       </c>
       <c r="K19" t="n">
-        <v>0.006388401998568687</v>
+        <v>0.006388401998568688</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007530972041957378</v>
+        <v>0.007530972041957376</v>
       </c>
       <c r="M19" t="n">
-        <v>0.00726335759696508</v>
+        <v>0.007263357596965085</v>
       </c>
       <c r="N19" t="n">
-        <v>0.007618070080118959</v>
+        <v>0.007618070080118963</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0114686967913749</v>
+        <v>0.01146869679137489</v>
       </c>
       <c r="P19" t="n">
         <v>0.01171069222763032</v>
@@ -1668,10 +1668,10 @@
         <v>0.01145677756159373</v>
       </c>
       <c r="R19" t="n">
-        <v>0.01444466999713028</v>
+        <v>0.01444466999713029</v>
       </c>
       <c r="S19" t="n">
-        <v>0.01486261021990095</v>
+        <v>0.01486261021990096</v>
       </c>
       <c r="T19" t="n">
         <v>0.01505131658364077</v>
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01439008675920187</v>
+        <v>0.01439008675920186</v>
       </c>
       <c r="D20" t="n">
         <v>0.01254529804881725</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01395444048221669</v>
+        <v>0.01395444048221668</v>
       </c>
       <c r="F20" t="n">
         <v>0.01286564209019561</v>
@@ -1705,37 +1705,37 @@
         <v>0.01776449821700896</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02080394931722171</v>
+        <v>0.0208039493172217</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01792844159990108</v>
+        <v>0.0179284415999011</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01832311476897562</v>
+        <v>0.01832311476897563</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02239033721602806</v>
+        <v>0.02239033721602808</v>
       </c>
       <c r="M20" t="n">
         <v>0.02251252602155649</v>
       </c>
       <c r="N20" t="n">
-        <v>0.02028504530507213</v>
+        <v>0.02028504530507215</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04361099094122149</v>
+        <v>0.04361099094122148</v>
       </c>
       <c r="P20" t="n">
-        <v>0.04265496736654477</v>
+        <v>0.04265496736654476</v>
       </c>
       <c r="Q20" t="n">
         <v>0.04084420843985977</v>
       </c>
       <c r="R20" t="n">
-        <v>0.05264107071099634</v>
+        <v>0.05264107071099636</v>
       </c>
       <c r="S20" t="n">
-        <v>0.04893222006956954</v>
+        <v>0.04893222006956955</v>
       </c>
       <c r="T20" t="n">
         <v>0.05601116535852405</v>
@@ -1833,7 +1833,7 @@
         <v>0.001731485853245787</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002609143681042045</v>
+        <v>0.002609143681042044</v>
       </c>
       <c r="J22" t="n">
         <v>0.002327622918269024</v>
@@ -1845,25 +1845,25 @@
         <v>0.00272976496231476</v>
       </c>
       <c r="M22" t="n">
-        <v>0.002641204495354089</v>
+        <v>0.002641204495354088</v>
       </c>
       <c r="N22" t="n">
         <v>0.002872123249523663</v>
       </c>
       <c r="O22" t="n">
-        <v>0.004155333641574648</v>
+        <v>0.004155333641574649</v>
       </c>
       <c r="P22" t="n">
         <v>0.004314340649881362</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.004005901067902559</v>
+        <v>0.00400590106790256</v>
       </c>
       <c r="R22" t="n">
-        <v>0.005105864786075022</v>
+        <v>0.005105864786075023</v>
       </c>
       <c r="S22" t="n">
-        <v>0.005051898804130198</v>
+        <v>0.0050518988041302</v>
       </c>
       <c r="T22" t="n">
         <v>0.005379530798831744</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.06544895927897283</v>
+        <v>0.06544895927897285</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0534422652608174</v>
+        <v>0.05344226526081738</v>
       </c>
       <c r="E23" t="n">
         <v>0.04835437420598979</v>
@@ -1897,16 +1897,16 @@
         <v>0.1018017020070821</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08292055708383926</v>
+        <v>0.08292055708383925</v>
       </c>
       <c r="J23" t="n">
-        <v>0.06928222519676554</v>
+        <v>0.06928222519676555</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06503827189428042</v>
+        <v>0.06503827189428044</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06003812759753002</v>
+        <v>0.06003812759753003</v>
       </c>
       <c r="M23" t="n">
         <v>0.06602394251820767</v>
@@ -1924,7 +1924,7 @@
         <v>0.1210540611101786</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1688441950469033</v>
+        <v>0.1688441950469032</v>
       </c>
       <c r="S23" t="n">
         <v>0.2171413747250973</v>
@@ -1958,10 +1958,10 @@
         <v>0.000294966065360185</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0004172351128721648</v>
+        <v>0.0004172351128721647</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0005670029983989803</v>
+        <v>0.0005670029983989804</v>
       </c>
       <c r="J24" t="n">
         <v>0.0004730872666516136</v>
@@ -1970,13 +1970,13 @@
         <v>0.0004583174489436459</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0005291002864420676</v>
+        <v>0.0005291002864420678</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0005646461396192717</v>
+        <v>0.0005646461396192719</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0005272754254156417</v>
+        <v>0.0005272754254156419</v>
       </c>
       <c r="O24" t="n">
         <v>0.001001765132372118</v>
@@ -1985,10 +1985,10 @@
         <v>0.001002464709202405</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0009996345155749982</v>
+        <v>0.0009996345155749984</v>
       </c>
       <c r="R24" t="n">
-        <v>0.00113036040314947</v>
+        <v>0.001130360403149471</v>
       </c>
       <c r="S24" t="n">
         <v>0.001257474704243687</v>
@@ -2010,46 +2010,46 @@
         <v>0.003981689962999591</v>
       </c>
       <c r="D25" t="n">
-        <v>0.003635622454831856</v>
+        <v>0.003635622454831857</v>
       </c>
       <c r="E25" t="n">
         <v>0.003778346057862445</v>
       </c>
       <c r="F25" t="n">
-        <v>0.003419780777906693</v>
+        <v>0.003419780777906692</v>
       </c>
       <c r="G25" t="n">
-        <v>0.003702096024915824</v>
+        <v>0.003702096024915825</v>
       </c>
       <c r="H25" t="n">
         <v>0.005133370030009709</v>
       </c>
       <c r="I25" t="n">
-        <v>0.005293615894974277</v>
+        <v>0.005293615894974278</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004605492990943175</v>
+        <v>0.004605492990943173</v>
       </c>
       <c r="K25" t="n">
-        <v>0.004880605178564207</v>
+        <v>0.004880605178564208</v>
       </c>
       <c r="L25" t="n">
         <v>0.005717218848392241</v>
       </c>
       <c r="M25" t="n">
-        <v>0.005586169686724365</v>
+        <v>0.005586169686724364</v>
       </c>
       <c r="N25" t="n">
-        <v>0.005615593304517421</v>
+        <v>0.005615593304517422</v>
       </c>
       <c r="O25" t="n">
-        <v>0.009897339172606842</v>
+        <v>0.00989733917260684</v>
       </c>
       <c r="P25" t="n">
-        <v>0.00974614537030391</v>
+        <v>0.009746145370303912</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.008991249072953926</v>
+        <v>0.008991249072953924</v>
       </c>
       <c r="R25" t="n">
         <v>0.01108635701980849</v>
@@ -2077,16 +2077,16 @@
         <v>0.003290862127722241</v>
       </c>
       <c r="E26" t="n">
-        <v>0.003175276113531482</v>
+        <v>0.003175276113531483</v>
       </c>
       <c r="F26" t="n">
-        <v>0.003480337847609291</v>
+        <v>0.003480337847609292</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00350861650889362</v>
+        <v>0.003508616508893619</v>
       </c>
       <c r="H26" t="n">
-        <v>0.002870652405661035</v>
+        <v>0.002870652405661034</v>
       </c>
       <c r="I26" t="n">
         <v>0.005333984981971955</v>
@@ -2095,31 +2095,31 @@
         <v>0.004343037244887172</v>
       </c>
       <c r="K26" t="n">
-        <v>0.004869362592362369</v>
+        <v>0.004869362592362368</v>
       </c>
       <c r="L26" t="n">
-        <v>0.005731137234644757</v>
+        <v>0.005731137234644756</v>
       </c>
       <c r="M26" t="n">
         <v>0.005336940010454465</v>
       </c>
       <c r="N26" t="n">
-        <v>0.005624705573409332</v>
+        <v>0.005624705573409333</v>
       </c>
       <c r="O26" t="n">
-        <v>0.008118724733919712</v>
+        <v>0.008118724733919711</v>
       </c>
       <c r="P26" t="n">
         <v>0.007894529086869176</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.008127006922679609</v>
+        <v>0.008127006922679607</v>
       </c>
       <c r="R26" t="n">
-        <v>0.009381868413133081</v>
+        <v>0.00938186841313308</v>
       </c>
       <c r="S26" t="n">
-        <v>0.01006147872595064</v>
+        <v>0.01006147872595065</v>
       </c>
       <c r="T26" t="n">
         <v>0.0112525675673088</v>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02363190616199327</v>
+        <v>0.02363190616199328</v>
       </c>
       <c r="D27" t="n">
         <v>0.0203446764789837</v>
@@ -2147,16 +2147,16 @@
         <v>0.0213338283172383</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02154735531605345</v>
+        <v>0.02154735531605346</v>
       </c>
       <c r="H27" t="n">
-        <v>0.02928489587149748</v>
+        <v>0.02928489587149747</v>
       </c>
       <c r="I27" t="n">
         <v>0.03493389407902207</v>
       </c>
       <c r="J27" t="n">
-        <v>0.02972842407248851</v>
+        <v>0.02972842407248852</v>
       </c>
       <c r="K27" t="n">
         <v>0.02890109739348917</v>
@@ -2165,28 +2165,28 @@
         <v>0.03988912484342511</v>
       </c>
       <c r="M27" t="n">
-        <v>0.03828791478626144</v>
+        <v>0.03828791478626145</v>
       </c>
       <c r="N27" t="n">
-        <v>0.03883627107657939</v>
+        <v>0.0388362710765794</v>
       </c>
       <c r="O27" t="n">
-        <v>0.08964175956440446</v>
+        <v>0.08964175956440448</v>
       </c>
       <c r="P27" t="n">
         <v>0.09504129227029803</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.08807653087278294</v>
+        <v>0.0880765308727829</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1329163296625813</v>
+        <v>0.1329163296625812</v>
       </c>
       <c r="S27" t="n">
         <v>0.1445893913710392</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1407105493497969</v>
+        <v>0.140710549349797</v>
       </c>
     </row>
     <row r="28">
@@ -2202,7 +2202,7 @@
         <v>0.0009601396901303173</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0008917878293514126</v>
+        <v>0.0008917878293514123</v>
       </c>
       <c r="E28" t="n">
         <v>0.001005887284232087</v>
@@ -2229,7 +2229,7 @@
         <v>0.001225324685963441</v>
       </c>
       <c r="M28" t="n">
-        <v>0.001254621874208841</v>
+        <v>0.00125462187420884</v>
       </c>
       <c r="N28" t="n">
         <v>0.001249500659015432</v>
@@ -2269,37 +2269,37 @@
         <v>0.04029921482308037</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04284121689574148</v>
+        <v>0.04284121689574149</v>
       </c>
       <c r="F29" t="n">
         <v>0.0343427981814412</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03972404405320798</v>
+        <v>0.03972404405320799</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03318192913057327</v>
+        <v>0.03318192913057326</v>
       </c>
       <c r="I29" t="n">
-        <v>0.04728805586905934</v>
+        <v>0.04728805586905935</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0401910765323892</v>
+        <v>0.04019107653238919</v>
       </c>
       <c r="K29" t="n">
-        <v>0.04374562272135329</v>
+        <v>0.04374562272135332</v>
       </c>
       <c r="L29" t="n">
         <v>0.04906111308521011</v>
       </c>
       <c r="M29" t="n">
-        <v>0.04626134440966502</v>
+        <v>0.04626134440966503</v>
       </c>
       <c r="N29" t="n">
-        <v>0.04968702694724266</v>
+        <v>0.04968702694724269</v>
       </c>
       <c r="O29" t="n">
-        <v>0.07300693916132668</v>
+        <v>0.07300693916132667</v>
       </c>
       <c r="P29" t="n">
         <v>0.07431737936769228</v>
@@ -2308,13 +2308,13 @@
         <v>0.07129962323660163</v>
       </c>
       <c r="R29" t="n">
-        <v>0.08311022178751414</v>
+        <v>0.08311022178751412</v>
       </c>
       <c r="S29" t="n">
-        <v>0.08415552651775413</v>
+        <v>0.08415552651775414</v>
       </c>
       <c r="T29" t="n">
-        <v>0.09293840875741972</v>
+        <v>0.09293840875741978</v>
       </c>
     </row>
     <row r="30">
@@ -2348,13 +2348,13 @@
         <v>6.941510683550844e-05</v>
       </c>
       <c r="J30" t="n">
-        <v>6.326455087601081e-05</v>
+        <v>6.326455087601082e-05</v>
       </c>
       <c r="K30" t="n">
         <v>5.613516580507901e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>6.351550964717175e-05</v>
+        <v>6.351550964717173e-05</v>
       </c>
       <c r="M30" t="n">
         <v>7.13601757394949e-05</v>
@@ -2415,10 +2415,10 @@
         <v>1.656392258703981e-05</v>
       </c>
       <c r="K31" t="n">
-        <v>1.686142517659899e-05</v>
+        <v>1.686142517659898e-05</v>
       </c>
       <c r="L31" t="n">
-        <v>1.88897655524216e-05</v>
+        <v>1.888976555242161e-05</v>
       </c>
       <c r="M31" t="n">
         <v>1.853632812113721e-05</v>
@@ -2433,13 +2433,13 @@
         <v>3.020715256220784e-05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.812234172670427e-05</v>
+        <v>2.812234172670426e-05</v>
       </c>
       <c r="R31" t="n">
         <v>3.331726499246351e-05</v>
       </c>
       <c r="S31" t="n">
-        <v>2.959878246107163e-05</v>
+        <v>2.959878246107162e-05</v>
       </c>
       <c r="T31" t="n">
         <v>3.675402781604053e-05</v>
@@ -2458,52 +2458,52 @@
         <v>0.05967304959223334</v>
       </c>
       <c r="D32" t="n">
-        <v>0.05516122588708289</v>
+        <v>0.05516122588708292</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07066063246716911</v>
+        <v>0.07066063246716914</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05101571986852788</v>
+        <v>0.0510157198685279</v>
       </c>
       <c r="G32" t="n">
-        <v>0.05412844437019202</v>
+        <v>0.05412844437019201</v>
       </c>
       <c r="H32" t="n">
-        <v>0.07575494814067366</v>
+        <v>0.07575494814067367</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07830483392638535</v>
+        <v>0.07830483392638533</v>
       </c>
       <c r="J32" t="n">
-        <v>0.06769507343211757</v>
+        <v>0.06769507343211759</v>
       </c>
       <c r="K32" t="n">
-        <v>0.06815147656362593</v>
+        <v>0.06815147656362594</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0820735501133055</v>
+        <v>0.08207355011330551</v>
       </c>
       <c r="M32" t="n">
-        <v>0.08317156084404088</v>
+        <v>0.08317156084404084</v>
       </c>
       <c r="N32" t="n">
-        <v>0.07779299447583216</v>
+        <v>0.07779299447583217</v>
       </c>
       <c r="O32" t="n">
         <v>0.168663320252235</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1605582191046246</v>
+        <v>0.1605582191046247</v>
       </c>
       <c r="Q32" t="n">
         <v>0.1637301235937188</v>
       </c>
       <c r="R32" t="n">
-        <v>0.2370010763956214</v>
+        <v>0.2370010763956215</v>
       </c>
       <c r="S32" t="n">
-        <v>0.247474117027106</v>
+        <v>0.2474741170271061</v>
       </c>
       <c r="T32" t="n">
         <v>0.2352219645202518</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.03928141552555954</v>
+        <v>0.03928141552555952</v>
       </c>
       <c r="D33" t="n">
         <v>0.03490258858839559</v>
       </c>
       <c r="E33" t="n">
-        <v>0.04319032505375928</v>
+        <v>0.04319032505375929</v>
       </c>
       <c r="F33" t="n">
         <v>0.03643390519069256</v>
@@ -2534,13 +2534,13 @@
         <v>0.03777087168327378</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04584739359295859</v>
+        <v>0.04584739359295858</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0502254572980556</v>
+        <v>0.05022545729805559</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04699365211822474</v>
+        <v>0.04699365211822475</v>
       </c>
       <c r="K33" t="n">
         <v>0.04391110520591249</v>
@@ -2549,25 +2549,25 @@
         <v>0.04060455153333407</v>
       </c>
       <c r="M33" t="n">
-        <v>0.04222617339125118</v>
+        <v>0.0422261733912512</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04989617235525266</v>
+        <v>0.04989617235525268</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0754442827567874</v>
+        <v>0.07544428275678743</v>
       </c>
       <c r="P33" t="n">
-        <v>0.07876417638194927</v>
+        <v>0.07876417638194921</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.06853923969210055</v>
+        <v>0.06853923969210056</v>
       </c>
       <c r="R33" t="n">
-        <v>0.08389940650991629</v>
+        <v>0.0838994065099163</v>
       </c>
       <c r="S33" t="n">
-        <v>0.08432616908598631</v>
+        <v>0.08432616908598632</v>
       </c>
       <c r="T33" t="n">
         <v>0.0868800099267177</v>
@@ -2592,7 +2592,7 @@
         <v>0.001862962321709572</v>
       </c>
       <c r="F34" t="n">
-        <v>0.001654208977858669</v>
+        <v>0.00165420897785867</v>
       </c>
       <c r="G34" t="n">
         <v>0.001777972575455846</v>
@@ -2601,7 +2601,7 @@
         <v>0.002084177877093493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.002933287248525036</v>
+        <v>0.002933287248525037</v>
       </c>
       <c r="J34" t="n">
         <v>0.002488780392150594</v>
@@ -2616,25 +2616,25 @@
         <v>0.002809841862328543</v>
       </c>
       <c r="N34" t="n">
-        <v>0.002826058497224958</v>
+        <v>0.002826058497224957</v>
       </c>
       <c r="O34" t="n">
-        <v>0.005217685185096129</v>
+        <v>0.00521768518509613</v>
       </c>
       <c r="P34" t="n">
-        <v>0.005031621094921959</v>
+        <v>0.005031621094921961</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.00463342746889736</v>
+        <v>0.004633427468897361</v>
       </c>
       <c r="R34" t="n">
-        <v>0.006726304927452116</v>
+        <v>0.006726304927452113</v>
       </c>
       <c r="S34" t="n">
-        <v>0.006865083366614178</v>
+        <v>0.00686508336661418</v>
       </c>
       <c r="T34" t="n">
-        <v>0.006712136551364382</v>
+        <v>0.006712136551364383</v>
       </c>
     </row>
     <row r="35">
@@ -2683,7 +2683,7 @@
         <v>0.001780555778188278</v>
       </c>
       <c r="O35" t="n">
-        <v>0.003611474368189569</v>
+        <v>0.00361147436818957</v>
       </c>
       <c r="P35" t="n">
         <v>0.003645004130948816</v>
@@ -2714,7 +2714,7 @@
         <v>0.003140770600787807</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00281970521140949</v>
+        <v>0.002819705211409488</v>
       </c>
       <c r="E36" t="n">
         <v>0.002880650284996926</v>
@@ -2723,7 +2723,7 @@
         <v>0.002697690983706071</v>
       </c>
       <c r="G36" t="n">
-        <v>0.002740712646266431</v>
+        <v>0.00274071264626643</v>
       </c>
       <c r="H36" t="n">
         <v>0.00241892818121214</v>
@@ -2732,37 +2732,37 @@
         <v>0.004110386844249587</v>
       </c>
       <c r="J36" t="n">
-        <v>0.003570742073707008</v>
+        <v>0.003570742073707007</v>
       </c>
       <c r="K36" t="n">
         <v>0.003613381540449738</v>
       </c>
       <c r="L36" t="n">
-        <v>0.004099941430411471</v>
+        <v>0.00409994143041147</v>
       </c>
       <c r="M36" t="n">
         <v>0.003851570371646665</v>
       </c>
       <c r="N36" t="n">
-        <v>0.004027616956137036</v>
+        <v>0.004027616956137037</v>
       </c>
       <c r="O36" t="n">
-        <v>0.006872496922405301</v>
+        <v>0.006872496922405303</v>
       </c>
       <c r="P36" t="n">
-        <v>0.007375429434640456</v>
+        <v>0.007375429434640457</v>
       </c>
       <c r="Q36" t="n">
         <v>0.007302751047231808</v>
       </c>
       <c r="R36" t="n">
-        <v>0.008351025821890816</v>
+        <v>0.008351025821890814</v>
       </c>
       <c r="S36" t="n">
-        <v>0.009213512599590206</v>
+        <v>0.009213512599590204</v>
       </c>
       <c r="T36" t="n">
-        <v>0.009510761419686171</v>
+        <v>0.009510761419686169</v>
       </c>
     </row>
     <row r="37">
@@ -2778,10 +2778,10 @@
         <v>0.01874243863199443</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0158659537040563</v>
+        <v>0.01586595370405629</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01748208176686526</v>
+        <v>0.01748208176686527</v>
       </c>
       <c r="F37" t="n">
         <v>0.01531651260788678</v>
@@ -2790,19 +2790,19 @@
         <v>0.01621275922863314</v>
       </c>
       <c r="H37" t="n">
-        <v>0.02471438054811492</v>
+        <v>0.02471438054811493</v>
       </c>
       <c r="I37" t="n">
-        <v>0.02788143282550356</v>
+        <v>0.02788143282550355</v>
       </c>
       <c r="J37" t="n">
         <v>0.02458181700655485</v>
       </c>
       <c r="K37" t="n">
-        <v>0.02508423273066513</v>
+        <v>0.02508423273066512</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02812580771048365</v>
+        <v>0.02812580771048366</v>
       </c>
       <c r="M37" t="n">
         <v>0.02744993417846454</v>
@@ -2811,13 +2811,13 @@
         <v>0.02720057921792603</v>
       </c>
       <c r="O37" t="n">
-        <v>0.04170338645761996</v>
+        <v>0.04170338645761994</v>
       </c>
       <c r="P37" t="n">
-        <v>0.04347985004501139</v>
+        <v>0.04347985004501138</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.03840477653741646</v>
+        <v>0.03840477653741647</v>
       </c>
       <c r="R37" t="n">
         <v>0.04694030592200402</v>
@@ -2826,7 +2826,7 @@
         <v>0.04306627127753549</v>
       </c>
       <c r="T37" t="n">
-        <v>0.04972104930348143</v>
+        <v>0.04972104930348144</v>
       </c>
     </row>
     <row r="38">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.00111997981158652</v>
+        <v>0.001119979811586521</v>
       </c>
       <c r="D38" t="n">
         <v>0.00104820183045174</v>
@@ -2848,16 +2848,16 @@
         <v>0.001111413095985852</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0009181890418136279</v>
+        <v>0.0009181890418136278</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0009341174742317801</v>
+        <v>0.00093411747423178</v>
       </c>
       <c r="H38" t="n">
         <v>0.0008915528447191772</v>
       </c>
       <c r="I38" t="n">
-        <v>0.001311187395852362</v>
+        <v>0.001311187395852363</v>
       </c>
       <c r="J38" t="n">
         <v>0.001093542379639255</v>
@@ -2878,19 +2878,19 @@
         <v>0.002016445597492914</v>
       </c>
       <c r="P38" t="n">
-        <v>0.00214105321402657</v>
+        <v>0.002141053214026571</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.002149605687876302</v>
+        <v>0.002149605687876303</v>
       </c>
       <c r="R38" t="n">
-        <v>0.002522371882809762</v>
+        <v>0.002522371882809761</v>
       </c>
       <c r="S38" t="n">
         <v>0.00254902802101099</v>
       </c>
       <c r="T38" t="n">
-        <v>0.002614712431686027</v>
+        <v>0.002614712431686028</v>
       </c>
     </row>
     <row r="39">
@@ -2915,34 +2915,34 @@
         <v>0.0004153652726398151</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0003886256076932159</v>
+        <v>0.000388625607693216</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0004001379483768973</v>
+        <v>0.0004001379483768972</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0005698991651439698</v>
+        <v>0.0005698991651439697</v>
       </c>
       <c r="J39" t="n">
         <v>0.0004729548580341696</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0004676195310665343</v>
+        <v>0.0004676195310665344</v>
       </c>
       <c r="L39" t="n">
         <v>0.0005738753293783108</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0005475429341050075</v>
+        <v>0.0005475429341050076</v>
       </c>
       <c r="N39" t="n">
-        <v>0.0005819366799929222</v>
+        <v>0.0005819366799929223</v>
       </c>
       <c r="O39" t="n">
         <v>0.0008356076791109801</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0009075742921506491</v>
+        <v>0.000907574292150649</v>
       </c>
       <c r="Q39" t="n">
         <v>0.0008815389454429107</v>
@@ -2973,10 +2973,10 @@
         <v>0.0002801590814539433</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0003029347150350594</v>
+        <v>0.0003029347150350595</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0002686408341916115</v>
+        <v>0.0002686408341916116</v>
       </c>
       <c r="G40" t="n">
         <v>0.0002912700619111126</v>
@@ -2988,28 +2988,28 @@
         <v>0.0004538768502562573</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0003979916844135055</v>
+        <v>0.0003979916844135054</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0003797094505343365</v>
+        <v>0.0003797094505343364</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0004614202781300067</v>
+        <v>0.0004614202781300068</v>
       </c>
       <c r="M40" t="n">
         <v>0.0004290058857576306</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0004444842415552418</v>
+        <v>0.0004444842415552416</v>
       </c>
       <c r="O40" t="n">
         <v>0.0007194155504257333</v>
       </c>
       <c r="P40" t="n">
-        <v>0.0007048667687519835</v>
+        <v>0.0007048667687519836</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0007614144461801879</v>
+        <v>0.0007614144461801878</v>
       </c>
       <c r="R40" t="n">
         <v>0.0009606343116023746</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.000717672500986763</v>
+        <v>0.0007176725009867631</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0005821637252449533</v>
+        <v>0.0005821637252449531</v>
       </c>
       <c r="E41" t="n">
         <v>0.0006093154879078816</v>
@@ -3046,25 +3046,25 @@
         <v>0.0005915019507909177</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0009476508048630646</v>
+        <v>0.0009476508048630645</v>
       </c>
       <c r="I41" t="n">
         <v>0.0008824410898727284</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0007473456657593528</v>
+        <v>0.0007473456657593529</v>
       </c>
       <c r="K41" t="n">
-        <v>0.000767815455180689</v>
+        <v>0.0007678154551806891</v>
       </c>
       <c r="L41" t="n">
         <v>0.001036935394352836</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0008752540743390142</v>
+        <v>0.0008752540743390143</v>
       </c>
       <c r="N41" t="n">
-        <v>0.0008690463726857523</v>
+        <v>0.0008690463726857525</v>
       </c>
       <c r="O41" t="n">
         <v>0.001410365332105579</v>
@@ -3079,7 +3079,7 @@
         <v>0.00171824052819977</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001635874904768214</v>
+        <v>0.001635874904768213</v>
       </c>
       <c r="T41" t="n">
         <v>0.001667701275330164</v>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0006493572351318267</v>
+        <v>0.0006493572351318268</v>
       </c>
       <c r="D42" t="n">
         <v>0.0004912097386956461</v>
@@ -3119,7 +3119,7 @@
         <v>0.0006102484615524505</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0006298000302696463</v>
+        <v>0.0006298000302696462</v>
       </c>
       <c r="L42" t="n">
         <v>0.0008791805517163137</v>
@@ -3165,16 +3165,16 @@
         <v>0.001259838610016748</v>
       </c>
       <c r="E43" t="n">
-        <v>0.001338310871670054</v>
+        <v>0.001338310871670053</v>
       </c>
       <c r="F43" t="n">
-        <v>0.001261226372592401</v>
+        <v>0.001261226372592402</v>
       </c>
       <c r="G43" t="n">
         <v>0.00138154392196514</v>
       </c>
       <c r="H43" t="n">
-        <v>0.001756812364982076</v>
+        <v>0.001756812364982077</v>
       </c>
       <c r="I43" t="n">
         <v>0.002184495304047338</v>
@@ -3186,7 +3186,7 @@
         <v>0.001963481392945995</v>
       </c>
       <c r="L43" t="n">
-        <v>0.002237763593613615</v>
+        <v>0.002237763593613616</v>
       </c>
       <c r="M43" t="n">
         <v>0.002139123113656401</v>
@@ -3195,10 +3195,10 @@
         <v>0.002227161454886719</v>
       </c>
       <c r="O43" t="n">
-        <v>0.003879069652252633</v>
+        <v>0.003879069652252632</v>
       </c>
       <c r="P43" t="n">
-        <v>0.003863080667579023</v>
+        <v>0.003863080667579024</v>
       </c>
       <c r="Q43" t="n">
         <v>0.003948739065758635</v>
@@ -3207,10 +3207,10 @@
         <v>0.004277289722751301</v>
       </c>
       <c r="S43" t="n">
-        <v>0.004808271716528291</v>
+        <v>0.004808271716528294</v>
       </c>
       <c r="T43" t="n">
-        <v>0.005071815455708679</v>
+        <v>0.005071815455708677</v>
       </c>
     </row>
     <row r="44">
@@ -3226,25 +3226,25 @@
         <v>0.007863010387560413</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00679482064643456</v>
+        <v>0.006794820646434559</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00635403768458771</v>
+        <v>0.006354037684587709</v>
       </c>
       <c r="F44" t="n">
         <v>0.006248399803056122</v>
       </c>
       <c r="G44" t="n">
-        <v>0.006817988388062353</v>
+        <v>0.006817988388062354</v>
       </c>
       <c r="H44" t="n">
-        <v>0.00689069239089082</v>
+        <v>0.006890692390890819</v>
       </c>
       <c r="I44" t="n">
         <v>0.01035079939910132</v>
       </c>
       <c r="J44" t="n">
-        <v>0.008975019969027168</v>
+        <v>0.008975019969027167</v>
       </c>
       <c r="K44" t="n">
         <v>0.009287384909961446</v>
@@ -3262,7 +3262,7 @@
         <v>0.0189961087790408</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02000063324769512</v>
+        <v>0.02000063324769513</v>
       </c>
       <c r="Q44" t="n">
         <v>0.01933386238912674</v>
@@ -3274,7 +3274,7 @@
         <v>0.02500026509404587</v>
       </c>
       <c r="T44" t="n">
-        <v>0.0260392692849041</v>
+        <v>0.02603926928490411</v>
       </c>
     </row>
     <row r="45">
@@ -3354,13 +3354,13 @@
         <v>8.275588257162259e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>8.077718193948885e-05</v>
+        <v>8.077718193948887e-05</v>
       </c>
       <c r="E46" t="n">
         <v>9.118136161837113e-05</v>
       </c>
       <c r="F46" t="n">
-        <v>7.656782006564766e-05</v>
+        <v>7.656782006564767e-05</v>
       </c>
       <c r="G46" t="n">
         <v>7.414469706222293e-05</v>
@@ -3369,10 +3369,10 @@
         <v>9.499280868702787e-05</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0001213577333661768</v>
+        <v>0.0001213577333661769</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0001068885442734451</v>
+        <v>0.0001068885442734452</v>
       </c>
       <c r="K46" t="n">
         <v>0.0001097264641272879</v>
@@ -3396,13 +3396,13 @@
         <v>0.0001412767395292943</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0001544512321523327</v>
+        <v>0.0001544512321523326</v>
       </c>
       <c r="S46" t="n">
         <v>0.0001613517757607435</v>
       </c>
       <c r="T46" t="n">
-        <v>0.0002072032203985272</v>
+        <v>0.0002072032203985273</v>
       </c>
     </row>
     <row r="47">
@@ -3424,7 +3424,7 @@
         <v>0.0004348858786583529</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0004008232802274768</v>
+        <v>0.0004008232802274767</v>
       </c>
       <c r="G47" t="n">
         <v>0.0004128478197850665</v>
@@ -3442,28 +3442,28 @@
         <v>0.0004238000029943557</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0005692890954966684</v>
+        <v>0.0005692890954966686</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0005500931388743396</v>
+        <v>0.0005500931388743395</v>
       </c>
       <c r="N47" t="n">
-        <v>0.0005910172556355499</v>
+        <v>0.0005910172556355501</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0008008864797214392</v>
+        <v>0.0008008864797214394</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0008084034408457065</v>
+        <v>0.0008084034408457066</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0008024723857798311</v>
+        <v>0.000802472385779831</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0008748776651254893</v>
+        <v>0.0008748776651254892</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009828141149986495</v>
+        <v>0.0009828141149986493</v>
       </c>
       <c r="T47" t="n">
         <v>0.000994752408337187</v>
@@ -3500,13 +3500,13 @@
         <v>0.005417238023809208</v>
       </c>
       <c r="J48" t="n">
-        <v>0.004527036907750804</v>
+        <v>0.004527036907750805</v>
       </c>
       <c r="K48" t="n">
-        <v>0.005270317267512578</v>
+        <v>0.005270317267512577</v>
       </c>
       <c r="L48" t="n">
-        <v>0.005499479180724022</v>
+        <v>0.005499479180724023</v>
       </c>
       <c r="M48" t="n">
         <v>0.005520992334913803</v>
@@ -3518,7 +3518,7 @@
         <v>0.009682878421946123</v>
       </c>
       <c r="P48" t="n">
-        <v>0.0102743110166555</v>
+        <v>0.01027431101665551</v>
       </c>
       <c r="Q48" t="n">
         <v>0.008825209887677071</v>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0003012805972378638</v>
+        <v>0.0003012805972378639</v>
       </c>
       <c r="D50" t="n">
         <v>0.0002555088121314012</v>
@@ -3628,28 +3628,28 @@
         <v>0.0003844610978247171</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0003451993875627503</v>
+        <v>0.0003451993875627504</v>
       </c>
       <c r="K50" t="n">
         <v>0.0003335932732388534</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0004266752941893008</v>
+        <v>0.0004266752941893007</v>
       </c>
       <c r="M50" t="n">
         <v>0.0004240489692019076</v>
       </c>
       <c r="N50" t="n">
-        <v>0.0004089335118390939</v>
+        <v>0.000408933511839094</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0007961864659021018</v>
+        <v>0.0007961864659021017</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0008095112106981515</v>
+        <v>0.0008095112106981516</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0008080718311665692</v>
+        <v>0.0008080718311665691</v>
       </c>
       <c r="R50" t="n">
         <v>0.0009993840860593867</v>
@@ -3674,49 +3674,49 @@
         <v>0.0296343501794052</v>
       </c>
       <c r="D51" t="n">
-        <v>0.02600229489078499</v>
+        <v>0.02600229489078498</v>
       </c>
       <c r="E51" t="n">
-        <v>0.02588499389940941</v>
+        <v>0.02588499389940942</v>
       </c>
       <c r="F51" t="n">
         <v>0.02568907614003457</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0256487391438894</v>
+        <v>0.02564873914388941</v>
       </c>
       <c r="H51" t="n">
-        <v>0.03427805167718021</v>
+        <v>0.0342780516771802</v>
       </c>
       <c r="I51" t="n">
-        <v>0.04417315381836271</v>
+        <v>0.04417315381836268</v>
       </c>
       <c r="J51" t="n">
-        <v>0.03755090735470021</v>
+        <v>0.0375509073547002</v>
       </c>
       <c r="K51" t="n">
-        <v>0.03701110946390408</v>
+        <v>0.03701110946390407</v>
       </c>
       <c r="L51" t="n">
-        <v>0.05244555568591179</v>
+        <v>0.0524455556859118</v>
       </c>
       <c r="M51" t="n">
-        <v>0.05025188799216816</v>
+        <v>0.05025188799216818</v>
       </c>
       <c r="N51" t="n">
-        <v>0.04702021221348656</v>
+        <v>0.04702021221348655</v>
       </c>
       <c r="O51" t="n">
         <v>0.1234318284247891</v>
       </c>
       <c r="P51" t="n">
-        <v>0.1234401651413855</v>
+        <v>0.1234401651413854</v>
       </c>
       <c r="Q51" t="n">
         <v>0.122887891811818</v>
       </c>
       <c r="R51" t="n">
-        <v>0.1893245025981537</v>
+        <v>0.1893245025981536</v>
       </c>
       <c r="S51" t="n">
         <v>0.2041678729973968</v>
@@ -3741,7 +3741,7 @@
         <v>0.0006612943781374029</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0006656865350080062</v>
+        <v>0.0006656865350080063</v>
       </c>
       <c r="F52" t="n">
         <v>0.0006567142805552539</v>
@@ -3750,7 +3750,7 @@
         <v>0.0006968050461698422</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0008606509931428724</v>
+        <v>0.0008606509931428723</v>
       </c>
       <c r="I52" t="n">
         <v>0.001149160480263709</v>
@@ -3768,16 +3768,16 @@
         <v>0.001129441734019896</v>
       </c>
       <c r="N52" t="n">
-        <v>0.001211040212533433</v>
+        <v>0.001211040212533432</v>
       </c>
       <c r="O52" t="n">
-        <v>0.001874182164528962</v>
+        <v>0.001874182164528961</v>
       </c>
       <c r="P52" t="n">
         <v>0.001879419888623997</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.001653089448397335</v>
+        <v>0.001653089448397336</v>
       </c>
       <c r="R52" t="n">
         <v>0.001950279422570903</v>
@@ -3820,16 +3820,16 @@
         <v>0.0001423072559419482</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0001157727660977516</v>
+        <v>0.0001157727660977517</v>
       </c>
       <c r="K53" t="n">
         <v>0.0001225655482989715</v>
       </c>
       <c r="L53" t="n">
-        <v>0.000139002279762193</v>
+        <v>0.0001390022797621929</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0001386756320171677</v>
+        <v>0.0001386756320171678</v>
       </c>
       <c r="N53" t="n">
         <v>0.0001459136599087845</v>
@@ -3841,7 +3841,7 @@
         <v>0.0002172032504963772</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.0001991031771334227</v>
+        <v>0.0001991031771334228</v>
       </c>
       <c r="R53" t="n">
         <v>0.0002212594216522949</v>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.05857290472854741</v>
+        <v>0.05857290472854743</v>
       </c>
       <c r="D54" t="n">
-        <v>0.05324004902531078</v>
+        <v>0.0532400490253108</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0543142279065624</v>
+        <v>0.05431422790656239</v>
       </c>
       <c r="F54" t="n">
         <v>0.03979857311804828</v>
@@ -3878,25 +3878,25 @@
         <v>0.0457588751304696</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0533808367748307</v>
+        <v>0.05338083677483069</v>
       </c>
       <c r="I54" t="n">
-        <v>0.05936039204495635</v>
+        <v>0.05936039204495634</v>
       </c>
       <c r="J54" t="n">
-        <v>0.04803864427597392</v>
+        <v>0.04803864427597394</v>
       </c>
       <c r="K54" t="n">
-        <v>0.04842644127848793</v>
+        <v>0.04842644127848791</v>
       </c>
       <c r="L54" t="n">
-        <v>0.0518825615991347</v>
+        <v>0.05188256159913472</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0530625123118432</v>
+        <v>0.05306251231184315</v>
       </c>
       <c r="N54" t="n">
-        <v>0.05516057509214907</v>
+        <v>0.0551605750921491</v>
       </c>
       <c r="O54" t="n">
         <v>0.1260878639115785</v>
@@ -3911,7 +3911,7 @@
         <v>0.1726253688074165</v>
       </c>
       <c r="S54" t="n">
-        <v>0.1857152921141936</v>
+        <v>0.1857152921141937</v>
       </c>
       <c r="T54" t="n">
         <v>0.1847289625567463</v>
@@ -3930,7 +3930,7 @@
         <v>0.009288482532161059</v>
       </c>
       <c r="D55" t="n">
-        <v>0.008125054819074272</v>
+        <v>0.008125054819074273</v>
       </c>
       <c r="E55" t="n">
         <v>0.008606380281014526</v>
@@ -3939,7 +3939,7 @@
         <v>0.008372308787847607</v>
       </c>
       <c r="G55" t="n">
-        <v>0.008889010598180678</v>
+        <v>0.008889010598180676</v>
       </c>
       <c r="H55" t="n">
         <v>0.01228029484102317</v>
@@ -3963,7 +3963,7 @@
         <v>0.01231265745520274</v>
       </c>
       <c r="O55" t="n">
-        <v>0.0199955832185047</v>
+        <v>0.01999558321850471</v>
       </c>
       <c r="P55" t="n">
         <v>0.01957882412444081</v>
@@ -3991,55 +3991,55 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.02499180842970414</v>
+        <v>0.02499180842970413</v>
       </c>
       <c r="D56" t="n">
-        <v>0.02224392262860988</v>
+        <v>0.02224392262860989</v>
       </c>
       <c r="E56" t="n">
-        <v>0.02307135386339232</v>
+        <v>0.02307135386339231</v>
       </c>
       <c r="F56" t="n">
         <v>0.0261205132264058</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02732669998920394</v>
+        <v>0.02732669998920395</v>
       </c>
       <c r="H56" t="n">
-        <v>0.02788236979849583</v>
+        <v>0.02788236979849584</v>
       </c>
       <c r="I56" t="n">
-        <v>0.04449728198721577</v>
+        <v>0.04449728198721576</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03767680838830524</v>
+        <v>0.03767680838830525</v>
       </c>
       <c r="K56" t="n">
-        <v>0.04024400716482524</v>
+        <v>0.04024400716482526</v>
       </c>
       <c r="L56" t="n">
-        <v>0.04865157640012904</v>
+        <v>0.04865157640012905</v>
       </c>
       <c r="M56" t="n">
-        <v>0.04657951051848528</v>
+        <v>0.04657951051848525</v>
       </c>
       <c r="N56" t="n">
         <v>0.0497831486644811</v>
       </c>
       <c r="O56" t="n">
-        <v>0.07821056838640705</v>
+        <v>0.07821056838640701</v>
       </c>
       <c r="P56" t="n">
         <v>0.07541259563391391</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.0672894916853008</v>
+        <v>0.06728949168530077</v>
       </c>
       <c r="R56" t="n">
-        <v>0.07821861225092325</v>
+        <v>0.07821861225092323</v>
       </c>
       <c r="S56" t="n">
-        <v>0.08591213683361287</v>
+        <v>0.08591213683361289</v>
       </c>
       <c r="T56" t="n">
         <v>0.0940838047941278</v>
@@ -4064,16 +4064,16 @@
         <v>0.0006306169691337961</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0005007545161437507</v>
+        <v>0.0005007545161437509</v>
       </c>
       <c r="G57" t="n">
-        <v>0.000534989880727191</v>
+        <v>0.0005349898807271908</v>
       </c>
       <c r="H57" t="n">
         <v>0.0005305149327596837</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0006970657295114212</v>
+        <v>0.0006970657295114211</v>
       </c>
       <c r="J57" t="n">
         <v>0.0006684414624699764</v>
@@ -4091,7 +4091,7 @@
         <v>0.0007254573583040019</v>
       </c>
       <c r="O57" t="n">
-        <v>0.001191058425090082</v>
+        <v>0.001191058425090083</v>
       </c>
       <c r="P57" t="n">
         <v>0.001096560622799685</v>
@@ -4119,22 +4119,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.0009449344400139658</v>
+        <v>0.0009449344400139659</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0008757557971306016</v>
+        <v>0.0008757557971306015</v>
       </c>
       <c r="E58" t="n">
-        <v>0.000891763703096115</v>
+        <v>0.0008917637030961152</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0008308097029911026</v>
+        <v>0.0008308097029911027</v>
       </c>
       <c r="G58" t="n">
         <v>0.000910722024224122</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0007002533414524414</v>
+        <v>0.0007002533414524415</v>
       </c>
       <c r="I58" t="n">
         <v>0.001203245227154371</v>
@@ -4143,10 +4143,10 @@
         <v>0.001013346273851311</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00104786785590268</v>
+        <v>0.001047867855902679</v>
       </c>
       <c r="L58" t="n">
-        <v>0.001240191814229775</v>
+        <v>0.001240191814229776</v>
       </c>
       <c r="M58" t="n">
         <v>0.001175523830842079</v>
@@ -4158,7 +4158,7 @@
         <v>0.00186612046313962</v>
       </c>
       <c r="P58" t="n">
-        <v>0.001824965079939084</v>
+        <v>0.001824965079939083</v>
       </c>
       <c r="Q58" t="n">
         <v>0.001914809230054278</v>
@@ -4170,7 +4170,7 @@
         <v>0.002296044901218367</v>
       </c>
       <c r="T58" t="n">
-        <v>0.002276435420181715</v>
+        <v>0.002276435420181714</v>
       </c>
     </row>
     <row r="59">
@@ -4189,7 +4189,7 @@
         <v>0.0008442368034814512</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001075644154997985</v>
+        <v>0.001075644154997986</v>
       </c>
       <c r="F59" t="n">
         <v>0.0007995786060417853</v>
@@ -4225,7 +4225,7 @@
         <v>0.002636209887512057</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.002440576700567975</v>
+        <v>0.002440576700567974</v>
       </c>
       <c r="R59" t="n">
         <v>0.003241969737141661</v>
@@ -4265,7 +4265,7 @@
         <v>0.02169225338579572</v>
       </c>
       <c r="I60" t="n">
-        <v>0.02894718407915049</v>
+        <v>0.0289471840791505</v>
       </c>
       <c r="J60" t="n">
         <v>0.02555353229455078</v>
@@ -4292,13 +4292,13 @@
         <v>0.04287597446048185</v>
       </c>
       <c r="R60" t="n">
-        <v>0.05120131045905078</v>
+        <v>0.05120131045905076</v>
       </c>
       <c r="S60" t="n">
-        <v>0.05216372175998284</v>
+        <v>0.05216372175998282</v>
       </c>
       <c r="T60" t="n">
-        <v>0.05446448215993896</v>
+        <v>0.05446448215993897</v>
       </c>
     </row>
     <row r="61">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.0006061197106397691</v>
+        <v>0.0006061197106397692</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0006515413288554953</v>
+        <v>0.0006515413288554954</v>
       </c>
       <c r="E61" t="n">
         <v>0.0004978298575038123</v>
@@ -4323,16 +4323,16 @@
         <v>0.0004904757399292254</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0004970455142231162</v>
+        <v>0.0004970455142231163</v>
       </c>
       <c r="H61" t="n">
         <v>0.0006317034413010372</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0007988232553914685</v>
+        <v>0.0007988232553914683</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0006765066651379732</v>
+        <v>0.0006765066651379731</v>
       </c>
       <c r="K61" t="n">
         <v>0.0005948015544907995</v>
@@ -4341,7 +4341,7 @@
         <v>0.0007342209822745413</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0007098136718420916</v>
+        <v>0.0007098136718420917</v>
       </c>
       <c r="N61" t="n">
         <v>0.0007318263125666764</v>
@@ -4356,13 +4356,13 @@
         <v>0.001184529465228846</v>
       </c>
       <c r="R61" t="n">
-        <v>0.00148646608854734</v>
+        <v>0.001486466088547341</v>
       </c>
       <c r="S61" t="n">
-        <v>0.001608054909930285</v>
+        <v>0.001608054909930286</v>
       </c>
       <c r="T61" t="n">
-        <v>0.001484957532704425</v>
+        <v>0.001484957532704424</v>
       </c>
     </row>
     <row r="62">
@@ -4442,13 +4442,13 @@
         <v>0.02610803419415912</v>
       </c>
       <c r="D63" t="n">
-        <v>0.02580979820618974</v>
+        <v>0.02580979820618973</v>
       </c>
       <c r="E63" t="n">
         <v>0.02577269670636673</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01720124094090853</v>
+        <v>0.01720124094090852</v>
       </c>
       <c r="G63" t="n">
         <v>0.02137908684559435</v>
@@ -4475,7 +4475,7 @@
         <v>0.02289515688760574</v>
       </c>
       <c r="O63" t="n">
-        <v>0.02498366214116286</v>
+        <v>0.02498366214116285</v>
       </c>
       <c r="P63" t="n">
         <v>0.02487144076926046</v>
@@ -4484,13 +4484,13 @@
         <v>0.021470238661894</v>
       </c>
       <c r="R63" t="n">
-        <v>0.02849296838107103</v>
+        <v>0.02849296838107104</v>
       </c>
       <c r="S63" t="n">
-        <v>0.02853446257747671</v>
+        <v>0.02853446257747669</v>
       </c>
       <c r="T63" t="n">
-        <v>0.02596145898711213</v>
+        <v>0.02596145898711212</v>
       </c>
     </row>
     <row r="64">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6.720313208834166e-05</v>
+        <v>6.720313208834165e-05</v>
       </c>
       <c r="D64" t="n">
         <v>5.913645532120331e-05</v>
@@ -4512,19 +4512,19 @@
         <v>7.361441986057459e-05</v>
       </c>
       <c r="F64" t="n">
-        <v>6.760715154160402e-05</v>
+        <v>6.760715154160403e-05</v>
       </c>
       <c r="G64" t="n">
-        <v>7.39530427767806e-05</v>
+        <v>7.395304277678059e-05</v>
       </c>
       <c r="H64" t="n">
-        <v>8.477539560702339e-05</v>
+        <v>8.477539560702338e-05</v>
       </c>
       <c r="I64" t="n">
         <v>0.0001083870505709137</v>
       </c>
       <c r="J64" t="n">
-        <v>9.475518504317732e-05</v>
+        <v>9.475518504317731e-05</v>
       </c>
       <c r="K64" t="n">
         <v>9.330011942754319e-05</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.04538500237775899</v>
+        <v>0.04538500237775901</v>
       </c>
       <c r="D65" t="n">
         <v>0.04338961015318493</v>
@@ -4585,28 +4585,28 @@
         <v>0.04091883504537901</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0386414742612614</v>
+        <v>0.03864147426126141</v>
       </c>
       <c r="J65" t="n">
-        <v>0.03356672595524037</v>
+        <v>0.03356672595524038</v>
       </c>
       <c r="K65" t="n">
         <v>0.03485424593576003</v>
       </c>
       <c r="L65" t="n">
-        <v>0.04065687760020306</v>
+        <v>0.04065687760020305</v>
       </c>
       <c r="M65" t="n">
         <v>0.03889945469571278</v>
       </c>
       <c r="N65" t="n">
-        <v>0.03969031809223352</v>
+        <v>0.03969031809223353</v>
       </c>
       <c r="O65" t="n">
         <v>0.07115200847310967</v>
       </c>
       <c r="P65" t="n">
-        <v>0.07201156099056805</v>
+        <v>0.07201156099056806</v>
       </c>
       <c r="Q65" t="n">
         <v>0.06152866686354786</v>
@@ -4618,7 +4618,7 @@
         <v>0.0803984123869301</v>
       </c>
       <c r="T65" t="n">
-        <v>0.08760942289852619</v>
+        <v>0.0876094228985262</v>
       </c>
     </row>
     <row r="66">
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.001750738048166453</v>
+        <v>0.001750738048166454</v>
       </c>
       <c r="D66" t="n">
         <v>0.001537607569649404</v>
@@ -4649,34 +4649,34 @@
         <v>0.002098101915306448</v>
       </c>
       <c r="I66" t="n">
-        <v>0.002552324109944717</v>
+        <v>0.002552324109944716</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0021672872622784</v>
+        <v>0.002167287262278399</v>
       </c>
       <c r="K66" t="n">
         <v>0.002169068974417476</v>
       </c>
       <c r="L66" t="n">
-        <v>0.002346664005244008</v>
+        <v>0.002346664005244009</v>
       </c>
       <c r="M66" t="n">
         <v>0.002374642599413692</v>
       </c>
       <c r="N66" t="n">
-        <v>0.002367072264646551</v>
+        <v>0.00236707226464655</v>
       </c>
       <c r="O66" t="n">
         <v>0.004134299667395341</v>
       </c>
       <c r="P66" t="n">
-        <v>0.003955970073544152</v>
+        <v>0.003955970073544151</v>
       </c>
       <c r="Q66" t="n">
         <v>0.004062988145373158</v>
       </c>
       <c r="R66" t="n">
-        <v>0.004858857592154329</v>
+        <v>0.00485885759215433</v>
       </c>
       <c r="S66" t="n">
         <v>0.004745925798865114</v>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9.386591861321948e-05</v>
+        <v>9.386591861321949e-05</v>
       </c>
       <c r="D67" t="n">
         <v>8.62703769457975e-05</v>
@@ -4707,7 +4707,7 @@
         <v>7.423247885592182e-05</v>
       </c>
       <c r="G67" t="n">
-        <v>7.981421193171109e-05</v>
+        <v>7.981421193171108e-05</v>
       </c>
       <c r="H67" t="n">
         <v>7.27661636548983e-05</v>
@@ -4728,7 +4728,7 @@
         <v>8.183669800176504e-05</v>
       </c>
       <c r="N67" t="n">
-        <v>9.299289647050583e-05</v>
+        <v>9.299289647050584e-05</v>
       </c>
       <c r="O67" t="n">
         <v>0.0001170291077615544</v>
@@ -4762,7 +4762,7 @@
         <v>0.0002896224806174815</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0002708195441140243</v>
+        <v>0.0002708195441140242</v>
       </c>
       <c r="E68" t="n">
         <v>0.0002641779168121323</v>
@@ -4795,22 +4795,22 @@
         <v>0.0004122643205398079</v>
       </c>
       <c r="O68" t="n">
-        <v>0.0006699775071638696</v>
+        <v>0.0006699775071638695</v>
       </c>
       <c r="P68" t="n">
         <v>0.000661724424155169</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.0006028718809485267</v>
+        <v>0.0006028718809485271</v>
       </c>
       <c r="R68" t="n">
         <v>0.00073497403732653</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0007281199876061774</v>
+        <v>0.0007281199876061773</v>
       </c>
       <c r="T68" t="n">
-        <v>0.0007917876059387474</v>
+        <v>0.0007917876059387475</v>
       </c>
     </row>
     <row r="69">
@@ -4823,25 +4823,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.0004633281957211601</v>
+        <v>0.00046332819572116</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0003878346035619254</v>
+        <v>0.0003878346035619255</v>
       </c>
       <c r="E69" t="n">
         <v>0.0003691162204705687</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0003858966361778565</v>
+        <v>0.0003858966361778564</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0003914605559053413</v>
+        <v>0.0003914605559053412</v>
       </c>
       <c r="H69" t="n">
         <v>0.000571848570574346</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0007169978103621082</v>
+        <v>0.0007169978103621081</v>
       </c>
       <c r="J69" t="n">
         <v>0.0006173166494182951</v>
@@ -4856,7 +4856,7 @@
         <v>0.000676525251335332</v>
       </c>
       <c r="N69" t="n">
-        <v>0.0006789334868333879</v>
+        <v>0.0006789334868333878</v>
       </c>
       <c r="O69" t="n">
         <v>0.00119829761041941</v>
@@ -4969,7 +4969,7 @@
         <v>0.03111701673858734</v>
       </c>
       <c r="I71" t="n">
-        <v>0.04098388979245371</v>
+        <v>0.0409838897924537</v>
       </c>
       <c r="J71" t="n">
         <v>0.03548762131640576</v>
@@ -4978,7 +4978,7 @@
         <v>0.03518885671478111</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0383261420774786</v>
+        <v>0.03832614207747861</v>
       </c>
       <c r="M71" t="n">
         <v>0.03631767426350425</v>
@@ -4987,7 +4987,7 @@
         <v>0.04107934716655569</v>
       </c>
       <c r="O71" t="n">
-        <v>0.05098796133209233</v>
+        <v>0.05098796133209234</v>
       </c>
       <c r="P71" t="n">
         <v>0.04950386691641318</v>
@@ -5033,22 +5033,22 @@
         <v>0.005508254499132775</v>
       </c>
       <c r="I72" t="n">
-        <v>0.008001641833302882</v>
+        <v>0.00800164183330288</v>
       </c>
       <c r="J72" t="n">
         <v>0.006580810548816609</v>
       </c>
       <c r="K72" t="n">
-        <v>0.007134338908588693</v>
+        <v>0.007134338908588692</v>
       </c>
       <c r="L72" t="n">
-        <v>0.00869452256711898</v>
+        <v>0.008694522567118982</v>
       </c>
       <c r="M72" t="n">
         <v>0.007893679741714149</v>
       </c>
       <c r="N72" t="n">
-        <v>0.007831675228281947</v>
+        <v>0.007831675228281949</v>
       </c>
       <c r="O72" t="n">
         <v>0.01693006799742993</v>
@@ -5066,7 +5066,7 @@
         <v>0.01786028529217654</v>
       </c>
       <c r="T72" t="n">
-        <v>0.02285350148613859</v>
+        <v>0.0228535014861386</v>
       </c>
     </row>
     <row r="73">
@@ -5088,19 +5088,19 @@
         <v>0.003863875210915713</v>
       </c>
       <c r="F73" t="n">
-        <v>0.003472595378495141</v>
+        <v>0.00347259537849514</v>
       </c>
       <c r="G73" t="n">
-        <v>0.003679093583206078</v>
+        <v>0.003679093583206077</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00464156987783138</v>
+        <v>0.004641569877831379</v>
       </c>
       <c r="I73" t="n">
-        <v>0.005631865492481018</v>
+        <v>0.00563186549248102</v>
       </c>
       <c r="J73" t="n">
-        <v>0.004579218404045467</v>
+        <v>0.004579218404045468</v>
       </c>
       <c r="K73" t="n">
         <v>0.004998269425899779</v>
@@ -5109,25 +5109,25 @@
         <v>0.005718246501388786</v>
       </c>
       <c r="M73" t="n">
-        <v>0.005561617956951358</v>
+        <v>0.005561617956951356</v>
       </c>
       <c r="N73" t="n">
-        <v>0.005600036112992703</v>
+        <v>0.005600036112992704</v>
       </c>
       <c r="O73" t="n">
-        <v>0.008197363018726644</v>
+        <v>0.008197363018726646</v>
       </c>
       <c r="P73" t="n">
         <v>0.008804474124274582</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.00788303064841067</v>
+        <v>0.007883030648410666</v>
       </c>
       <c r="R73" t="n">
         <v>0.009547762731302215</v>
       </c>
       <c r="S73" t="n">
-        <v>0.009471961914342485</v>
+        <v>0.009471961914342483</v>
       </c>
       <c r="T73" t="n">
         <v>0.009674581438692565</v>
@@ -5146,7 +5146,7 @@
         <v>0.003858859539032478</v>
       </c>
       <c r="D74" t="n">
-        <v>0.003562513883515147</v>
+        <v>0.003562513883515146</v>
       </c>
       <c r="E74" t="n">
         <v>0.003763420544374291</v>
@@ -5161,31 +5161,31 @@
         <v>0.005372201779939284</v>
       </c>
       <c r="I74" t="n">
-        <v>0.005325713162944321</v>
+        <v>0.00532571316294432</v>
       </c>
       <c r="J74" t="n">
-        <v>0.00459386089997292</v>
+        <v>0.004593860899972919</v>
       </c>
       <c r="K74" t="n">
-        <v>0.004332786695136966</v>
+        <v>0.004332786695136967</v>
       </c>
       <c r="L74" t="n">
-        <v>0.00505596427887427</v>
+        <v>0.005055964278874269</v>
       </c>
       <c r="M74" t="n">
-        <v>0.005112668978965528</v>
+        <v>0.005112668978965529</v>
       </c>
       <c r="N74" t="n">
-        <v>0.005341484148739251</v>
+        <v>0.005341484148739253</v>
       </c>
       <c r="O74" t="n">
         <v>0.009208051192570841</v>
       </c>
       <c r="P74" t="n">
-        <v>0.009170267449414222</v>
+        <v>0.009170267449414219</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.008048153330755899</v>
+        <v>0.008048153330755897</v>
       </c>
       <c r="R74" t="n">
         <v>0.01071296148858977</v>
@@ -5194,7 +5194,7 @@
         <v>0.01011398523060772</v>
       </c>
       <c r="T74" t="n">
-        <v>0.01128563330941133</v>
+        <v>0.01128563330941134</v>
       </c>
     </row>
     <row r="75">
@@ -5271,13 +5271,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.002855748211611105</v>
+        <v>0.002855748211611104</v>
       </c>
       <c r="D76" t="n">
         <v>0.002517184897131888</v>
       </c>
       <c r="E76" t="n">
-        <v>0.002398782810860611</v>
+        <v>0.00239878281086061</v>
       </c>
       <c r="F76" t="n">
         <v>0.002331037972674157</v>
@@ -5286,40 +5286,40 @@
         <v>0.002338450902102357</v>
       </c>
       <c r="H76" t="n">
-        <v>0.002088608802357395</v>
+        <v>0.002088608802357396</v>
       </c>
       <c r="I76" t="n">
         <v>0.003698490111716687</v>
       </c>
       <c r="J76" t="n">
-        <v>0.003134867085289426</v>
+        <v>0.003134867085289427</v>
       </c>
       <c r="K76" t="n">
-        <v>0.003229548106693547</v>
+        <v>0.003229548106693548</v>
       </c>
       <c r="L76" t="n">
-        <v>0.003641234053210945</v>
+        <v>0.003641234053210944</v>
       </c>
       <c r="M76" t="n">
         <v>0.003361145959178447</v>
       </c>
       <c r="N76" t="n">
-        <v>0.003557414601213114</v>
+        <v>0.003557414601213113</v>
       </c>
       <c r="O76" t="n">
-        <v>0.005857501615107136</v>
+        <v>0.005857501615107137</v>
       </c>
       <c r="P76" t="n">
         <v>0.00635655567561717</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.006116334800148483</v>
+        <v>0.006116334800148482</v>
       </c>
       <c r="R76" t="n">
         <v>0.007216108406888671</v>
       </c>
       <c r="S76" t="n">
-        <v>0.007819969584078802</v>
+        <v>0.007819969584078804</v>
       </c>
       <c r="T76" t="n">
         <v>0.008100264409694077</v>
@@ -5338,10 +5338,10 @@
         <v>7.658163187702156e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>7.619584172118826e-05</v>
+        <v>7.619584172118827e-05</v>
       </c>
       <c r="E77" t="n">
-        <v>6.905081099163798e-05</v>
+        <v>6.905081099163797e-05</v>
       </c>
       <c r="F77" t="n">
         <v>7.975822148057266e-05</v>
@@ -5350,7 +5350,7 @@
         <v>8.507342557341149e-05</v>
       </c>
       <c r="H77" t="n">
-        <v>7.148972648716796e-05</v>
+        <v>7.148972648716797e-05</v>
       </c>
       <c r="I77" t="n">
         <v>0.0001419318538061084</v>
@@ -5478,7 +5478,7 @@
         <v>0.0001199724246250904</v>
       </c>
       <c r="H79" t="n">
-        <v>8.977885100380975e-05</v>
+        <v>8.977885100380976e-05</v>
       </c>
       <c r="I79" t="n">
         <v>0.0001675499112394927</v>
@@ -5508,13 +5508,13 @@
         <v>0.0002605208863417205</v>
       </c>
       <c r="R79" t="n">
-        <v>0.000305048319675289</v>
+        <v>0.0003050483196752891</v>
       </c>
       <c r="S79" t="n">
         <v>0.0003015831509391796</v>
       </c>
       <c r="T79" t="n">
-        <v>0.0003080833499369033</v>
+        <v>0.0003080833499369034</v>
       </c>
     </row>
     <row r="80">
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.0003452668879450531</v>
+        <v>0.000345266887945053</v>
       </c>
       <c r="D80" t="n">
         <v>0.0002729345580055003</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0002743595057757287</v>
+        <v>0.0002743595057757288</v>
       </c>
       <c r="F80" t="n">
         <v>0.0002773450507326296</v>
@@ -5569,7 +5569,7 @@
         <v>0.000865306016178757</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.0009067664506483246</v>
+        <v>0.0009067664506483244</v>
       </c>
       <c r="R80" t="n">
         <v>0.001163778143326537</v>
@@ -5594,7 +5594,7 @@
         <v>0.0001617649677853665</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0001568711143642636</v>
+        <v>0.0001568711143642637</v>
       </c>
       <c r="E81" t="n">
         <v>0.0001587643346957276</v>
@@ -5630,7 +5630,7 @@
         <v>0.000258478308731706</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0002725668321110856</v>
+        <v>0.0002725668321110857</v>
       </c>
       <c r="Q81" t="n">
         <v>0.000216434770140497</v>
@@ -5639,10 +5639,10 @@
         <v>0.0002992909408363227</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002886783249889444</v>
+        <v>0.0002886783249889443</v>
       </c>
       <c r="T81" t="n">
-        <v>0.0003129869239210119</v>
+        <v>0.0003129869239210118</v>
       </c>
     </row>
     <row r="82">
@@ -5679,7 +5679,7 @@
         <v>0.0002168162986225921</v>
       </c>
       <c r="K82" t="n">
-        <v>0.0002319517297576541</v>
+        <v>0.000231951729757654</v>
       </c>
       <c r="L82" t="n">
         <v>0.0003613411381441987</v>
@@ -5694,19 +5694,19 @@
         <v>0.0005791093652376137</v>
       </c>
       <c r="P82" t="n">
-        <v>0.0006529819573514647</v>
+        <v>0.0006529819573514646</v>
       </c>
       <c r="Q82" t="n">
         <v>0.0004715192727253919</v>
       </c>
       <c r="R82" t="n">
-        <v>0.0005746344840495528</v>
+        <v>0.0005746344840495529</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0005564759762096573</v>
+        <v>0.0005564759762096572</v>
       </c>
       <c r="T82" t="n">
-        <v>0.0006400847639002273</v>
+        <v>0.0006400847639002275</v>
       </c>
     </row>
     <row r="83">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.00496574561415585</v>
+        <v>0.004965745614155851</v>
       </c>
       <c r="D83" t="n">
         <v>0.004506007106331803</v>
@@ -5746,7 +5746,7 @@
         <v>0.008862321715640139</v>
       </c>
       <c r="L83" t="n">
-        <v>0.01134651900230501</v>
+        <v>0.011346519002305</v>
       </c>
       <c r="M83" t="n">
         <v>0.01151387063228431</v>
@@ -5764,7 +5764,7 @@
         <v>0.0190386351649628</v>
       </c>
       <c r="R83" t="n">
-        <v>0.02440528674624765</v>
+        <v>0.02440528674624766</v>
       </c>
       <c r="S83" t="n">
         <v>0.02560952748971333</v>
@@ -5789,7 +5789,7 @@
         <v>0.0008257745720205966</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0009577743596968521</v>
+        <v>0.0009577743596968522</v>
       </c>
       <c r="F84" t="n">
         <v>0.0008997746952792312</v>
@@ -5816,7 +5816,7 @@
         <v>0.00188682300385407</v>
       </c>
       <c r="N84" t="n">
-        <v>0.001808521550999375</v>
+        <v>0.001808521550999376</v>
       </c>
       <c r="O84" t="n">
         <v>0.004054232182882252</v>
@@ -5828,7 +5828,7 @@
         <v>0.003484121236049804</v>
       </c>
       <c r="R84" t="n">
-        <v>0.004415170932562623</v>
+        <v>0.004415170932562624</v>
       </c>
       <c r="S84" t="n">
         <v>0.005316169629355797</v>
@@ -5853,7 +5853,7 @@
         <v>0.003337754884852308</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00345581572373401</v>
+        <v>0.003455815723734011</v>
       </c>
       <c r="F85" t="n">
         <v>0.0035558582133289</v>
@@ -5868,10 +5868,10 @@
         <v>0.006614308741110701</v>
       </c>
       <c r="J85" t="n">
-        <v>0.005261331634382558</v>
+        <v>0.005261331634382559</v>
       </c>
       <c r="K85" t="n">
-        <v>0.005910522868272709</v>
+        <v>0.00591052286827271</v>
       </c>
       <c r="L85" t="n">
         <v>0.006769288866730986</v>
@@ -5880,13 +5880,13 @@
         <v>0.00569626224108662</v>
       </c>
       <c r="N85" t="n">
-        <v>0.006911721816082953</v>
+        <v>0.006911721816082954</v>
       </c>
       <c r="O85" t="n">
-        <v>0.008260093950944925</v>
+        <v>0.008260093950944927</v>
       </c>
       <c r="P85" t="n">
-        <v>0.007745010563423849</v>
+        <v>0.00774501056342385</v>
       </c>
       <c r="Q85" t="n">
         <v>0.007884043777323282</v>
@@ -5895,10 +5895,10 @@
         <v>0.006963051169506447</v>
       </c>
       <c r="S85" t="n">
-        <v>0.006668479741154325</v>
+        <v>0.006668479741154326</v>
       </c>
       <c r="T85" t="n">
-        <v>0.008381917546987604</v>
+        <v>0.008381917546987605</v>
       </c>
     </row>
     <row r="86">
@@ -5917,13 +5917,13 @@
         <v>0.000466625396598411</v>
       </c>
       <c r="E86" t="n">
-        <v>0.0004583549288985007</v>
+        <v>0.0004583549288985006</v>
       </c>
       <c r="F86" t="n">
         <v>0.0004195312567306145</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0004408540326352081</v>
+        <v>0.0004408540326352082</v>
       </c>
       <c r="H86" t="n">
         <v>0.0005127973469333791</v>
@@ -5956,7 +5956,7 @@
         <v>0.001020336973867774</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001294580304057057</v>
+        <v>0.001294580304057058</v>
       </c>
       <c r="S86" t="n">
         <v>0.001327865091382486</v>
@@ -6048,10 +6048,10 @@
         <v>0.0093758027677012</v>
       </c>
       <c r="F88" t="n">
-        <v>0.007986650505213799</v>
+        <v>0.007986650505213798</v>
       </c>
       <c r="G88" t="n">
-        <v>0.009318147037737418</v>
+        <v>0.00931814703773742</v>
       </c>
       <c r="H88" t="n">
         <v>0.007917772554059581</v>
@@ -6087,7 +6087,7 @@
         <v>0.01358692305246828</v>
       </c>
       <c r="S88" t="n">
-        <v>0.01249148247625341</v>
+        <v>0.0124914824762534</v>
       </c>
       <c r="T88" t="n">
         <v>0.01587213603872019</v>
@@ -6182,13 +6182,13 @@
         <v>0.0004989308641313566</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0005015234822413136</v>
+        <v>0.0005015234822413138</v>
       </c>
       <c r="I90" t="n">
         <v>0.0006496322593720387</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0006290927455933047</v>
+        <v>0.0006290927455933049</v>
       </c>
       <c r="K90" t="n">
         <v>0.0005850455472596548</v>
@@ -6206,7 +6206,7 @@
         <v>0.001114425398092645</v>
       </c>
       <c r="P90" t="n">
-        <v>0.001027638819941948</v>
+        <v>0.001027638819941949</v>
       </c>
       <c r="Q90" t="n">
         <v>0.001150661058439015</v>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3.303502857378957e-05</v>
+        <v>3.303502857378959e-05</v>
       </c>
       <c r="D91" t="n">
         <v>2.794863291993597e-05</v>
@@ -6240,7 +6240,7 @@
         <v>3.046755499874788e-05</v>
       </c>
       <c r="F91" t="n">
-        <v>2.635200530601556e-05</v>
+        <v>2.635200530601555e-05</v>
       </c>
       <c r="G91" t="n">
         <v>3.001954033626006e-05</v>
@@ -6252,7 +6252,7 @@
         <v>3.669041953988034e-05</v>
       </c>
       <c r="J91" t="n">
-        <v>3.026133856932022e-05</v>
+        <v>3.026133856932021e-05</v>
       </c>
       <c r="K91" t="n">
         <v>3.203148754749245e-05</v>
@@ -6267,16 +6267,16 @@
         <v>4.319490356070431e-05</v>
       </c>
       <c r="O91" t="n">
-        <v>5.659683737635366e-05</v>
+        <v>5.659683737635367e-05</v>
       </c>
       <c r="P91" t="n">
         <v>6.370576545466061e-05</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.550676677193372e-05</v>
+        <v>5.550676677193373e-05</v>
       </c>
       <c r="R91" t="n">
-        <v>7.631463801772466e-05</v>
+        <v>7.631463801772467e-05</v>
       </c>
       <c r="S91" t="n">
         <v>6.847682072770906e-05</v>
@@ -6322,7 +6322,7 @@
         <v>0.0002847580151946248</v>
       </c>
       <c r="L92" t="n">
-        <v>0.0003563657626428372</v>
+        <v>0.000356365762642837</v>
       </c>
       <c r="M92" t="n">
         <v>0.0003568566823863595</v>
@@ -6340,7 +6340,7 @@
         <v>0.0005742908561919574</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0007806100577805833</v>
+        <v>0.0007806100577805832</v>
       </c>
       <c r="S92" t="n">
         <v>0.000689238758295831</v>
@@ -6404,13 +6404,13 @@
         <v>0.00141227680002631</v>
       </c>
       <c r="R93" t="n">
-        <v>0.003363233379999409</v>
+        <v>0.00336323337999941</v>
       </c>
       <c r="S93" t="n">
         <v>0.005631147717995752</v>
       </c>
       <c r="T93" t="n">
-        <v>0.004226000980218006</v>
+        <v>0.004226000980218005</v>
       </c>
     </row>
     <row r="94">
@@ -6426,22 +6426,22 @@
         <v>0.001134123193772568</v>
       </c>
       <c r="D94" t="n">
-        <v>0.001161229336365993</v>
+        <v>0.001161229336365994</v>
       </c>
       <c r="E94" t="n">
         <v>0.001042945306637311</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0008207180984568263</v>
+        <v>0.000820718098456826</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0009470753771369663</v>
+        <v>0.0009470753771369662</v>
       </c>
       <c r="H94" t="n">
         <v>0.0006359212337559352</v>
       </c>
       <c r="I94" t="n">
-        <v>0.001155123068489884</v>
+        <v>0.001155123068489883</v>
       </c>
       <c r="J94" t="n">
         <v>0.0009579376896422715</v>
@@ -6459,7 +6459,7 @@
         <v>0.00122381058544584</v>
       </c>
       <c r="O94" t="n">
-        <v>0.001814383905365716</v>
+        <v>0.001814383905365715</v>
       </c>
       <c r="P94" t="n">
         <v>0.001776095454893245</v>
@@ -6502,7 +6502,7 @@
         <v>0.001136815110097682</v>
       </c>
       <c r="H95" t="n">
-        <v>0.001434695428067531</v>
+        <v>0.001434695428067532</v>
       </c>
       <c r="I95" t="n">
         <v>0.001530847424523807</v>
@@ -6535,7 +6535,7 @@
         <v>0.002015101849013546</v>
       </c>
       <c r="S95" t="n">
-        <v>0.001698296646146562</v>
+        <v>0.001698296646146561</v>
       </c>
       <c r="T95" t="n">
         <v>0.001824822719678126</v>
@@ -6554,10 +6554,10 @@
         <v>0.0005484323598017881</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0004468424794750306</v>
+        <v>0.0004468424794750305</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0004380495068834315</v>
+        <v>0.0004380495068834314</v>
       </c>
       <c r="F96" t="n">
         <v>0.0004413682976343704</v>
@@ -6566,13 +6566,13 @@
         <v>0.0004971125578609572</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0007222300877987053</v>
+        <v>0.0007222300877987054</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0008245818733173216</v>
+        <v>0.0008245818733173217</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0007635328440068612</v>
+        <v>0.0007635328440068613</v>
       </c>
       <c r="K96" t="n">
         <v>0.0007719817187753407</v>
@@ -6581,10 +6581,10 @@
         <v>0.0009035727868920771</v>
       </c>
       <c r="M96" t="n">
-        <v>0.0008764307449400536</v>
+        <v>0.0008764307449400535</v>
       </c>
       <c r="N96" t="n">
-        <v>0.0009190582775236461</v>
+        <v>0.0009190582775236463</v>
       </c>
       <c r="O96" t="n">
         <v>0.001705439855194314</v>
@@ -6596,7 +6596,7 @@
         <v>0.001486549729015858</v>
       </c>
       <c r="R96" t="n">
-        <v>0.001958621922117703</v>
+        <v>0.001958621922117702</v>
       </c>
       <c r="S96" t="n">
         <v>0.001970513469315935</v>
@@ -6627,7 +6627,7 @@
         <v>7.622686634854478e-05</v>
       </c>
       <c r="G97" t="n">
-        <v>8.064627535203273e-05</v>
+        <v>8.064627535203272e-05</v>
       </c>
       <c r="H97" t="n">
         <v>7.260925328747123e-05</v>
@@ -6642,7 +6642,7 @@
         <v>0.0001054507779651953</v>
       </c>
       <c r="L97" t="n">
-        <v>0.0001487846301531954</v>
+        <v>0.0001487846301531955</v>
       </c>
       <c r="M97" t="n">
         <v>0.0001364525827404441</v>
@@ -6666,7 +6666,7 @@
         <v>0.0003230218731935015</v>
       </c>
       <c r="T97" t="n">
-        <v>0.0003347933954237592</v>
+        <v>0.0003347933954237593</v>
       </c>
     </row>
     <row r="98">
@@ -6682,10 +6682,10 @@
         <v>0.0001808350778486648</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0001718924813051543</v>
+        <v>0.0001718924813051544</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0001649559660628178</v>
+        <v>0.0001649559660628179</v>
       </c>
       <c r="F98" t="n">
         <v>0.0001841309052624612</v>
@@ -6694,7 +6694,7 @@
         <v>0.0001787952269374826</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0002156467132180187</v>
+        <v>0.0002156467132180186</v>
       </c>
       <c r="I98" t="n">
         <v>0.0002941728033252369</v>
@@ -6706,16 +6706,16 @@
         <v>0.0002510997440461436</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0003189446216440611</v>
+        <v>0.0003189446216440612</v>
       </c>
       <c r="M98" t="n">
-        <v>0.0003104585732514793</v>
+        <v>0.0003104585732514792</v>
       </c>
       <c r="N98" t="n">
-        <v>0.000321920479664844</v>
+        <v>0.0003219204796648441</v>
       </c>
       <c r="O98" t="n">
-        <v>0.0005564044943689388</v>
+        <v>0.0005564044943689389</v>
       </c>
       <c r="P98" t="n">
         <v>0.0005853360449993806</v>
@@ -6724,10 +6724,10 @@
         <v>0.0005265538925808735</v>
       </c>
       <c r="R98" t="n">
-        <v>0.0006518565227318971</v>
+        <v>0.0006518565227318972</v>
       </c>
       <c r="S98" t="n">
-        <v>0.0006151490700535121</v>
+        <v>0.0006151490700535118</v>
       </c>
       <c r="T98" t="n">
         <v>0.0006668033571970913</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8.704711364973072e-05</v>
+        <v>8.704711364973073e-05</v>
       </c>
       <c r="D99" t="n">
-        <v>7.579090925858127e-05</v>
+        <v>7.579090925858129e-05</v>
       </c>
       <c r="E99" t="n">
         <v>9.656937524371245e-05</v>
@@ -6755,7 +6755,7 @@
         <v>9.365582743305198e-05</v>
       </c>
       <c r="G99" t="n">
-        <v>9.620058255670721e-05</v>
+        <v>9.62005825567072e-05</v>
       </c>
       <c r="H99" t="n">
         <v>0.0001166353899263836</v>
@@ -6782,19 +6782,19 @@
         <v>0.0002874346084051589</v>
       </c>
       <c r="P99" t="n">
-        <v>0.000290017789956531</v>
+        <v>0.0002900177899565311</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.0002757623812084134</v>
+        <v>0.0002757623812084135</v>
       </c>
       <c r="R99" t="n">
         <v>0.0003503632630264545</v>
       </c>
       <c r="S99" t="n">
-        <v>0.0003268819658070942</v>
+        <v>0.0003268819658070941</v>
       </c>
       <c r="T99" t="n">
-        <v>0.0003344510887496723</v>
+        <v>0.0003344510887496724</v>
       </c>
     </row>
     <row r="100">
@@ -6822,10 +6822,10 @@
         <v>0.0003545382326522412</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0004377629325855748</v>
+        <v>0.0004377629325855749</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0005521566328917951</v>
+        <v>0.0005521566328917952</v>
       </c>
       <c r="J100" t="n">
         <v>0.0004684235170160269</v>
@@ -6840,7 +6840,7 @@
         <v>0.0005236529395144842</v>
       </c>
       <c r="N100" t="n">
-        <v>0.0005653204023816145</v>
+        <v>0.0005653204023816143</v>
       </c>
       <c r="O100" t="n">
         <v>0.0008829934578995643</v>
@@ -6877,10 +6877,10 @@
         <v>0.0005059353880968008</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0004684685064736216</v>
+        <v>0.0004684685064736215</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0003725797737103704</v>
+        <v>0.0003725797737103703</v>
       </c>
       <c r="G101" t="n">
         <v>0.0004446589937113733</v>
@@ -6889,22 +6889,22 @@
         <v>0.0003936241574469448</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0006765232233377166</v>
+        <v>0.0006765232233377169</v>
       </c>
       <c r="J101" t="n">
-        <v>0.0005281283995391038</v>
+        <v>0.0005281283995391037</v>
       </c>
       <c r="K101" t="n">
         <v>0.0006213107411406873</v>
       </c>
       <c r="L101" t="n">
-        <v>0.0006838931965741704</v>
+        <v>0.0006838931965741703</v>
       </c>
       <c r="M101" t="n">
         <v>0.0007218665513508001</v>
       </c>
       <c r="N101" t="n">
-        <v>0.0006342506311464436</v>
+        <v>0.0006342506311464435</v>
       </c>
       <c r="O101" t="n">
         <v>0.001106891036127439</v>
@@ -7014,13 +7014,13 @@
         <v>0.0001183753987228475</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0001638219459131309</v>
+        <v>0.000163821945913131</v>
       </c>
       <c r="I103" t="n">
         <v>0.0001876386813603034</v>
       </c>
       <c r="J103" t="n">
-        <v>0.0001634203544936843</v>
+        <v>0.0001634203544936842</v>
       </c>
       <c r="K103" t="n">
         <v>0.0001646220427507586</v>
@@ -7041,7 +7041,7 @@
         <v>0.0002828299400506825</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.0002928754704679278</v>
+        <v>0.0002928754704679277</v>
       </c>
       <c r="R103" t="n">
         <v>0.0003778738134815903</v>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.000287101285483898</v>
+        <v>0.0002871012854838981</v>
       </c>
       <c r="D104" t="n">
         <v>0.0002769263953794417</v>
@@ -7072,7 +7072,7 @@
         <v>0.000266903431337182</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0002678779259221558</v>
+        <v>0.0002678779259221557</v>
       </c>
       <c r="G104" t="n">
         <v>0.0002765962571633018</v>
@@ -7081,10 +7081,10 @@
         <v>0.0002306745161648559</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0003745247389744517</v>
+        <v>0.0003745247389744516</v>
       </c>
       <c r="J104" t="n">
-        <v>0.0003187553514866948</v>
+        <v>0.0003187553514866947</v>
       </c>
       <c r="K104" t="n">
         <v>0.000332515530818986</v>
@@ -7099,7 +7099,7 @@
         <v>0.0004050102697166751</v>
       </c>
       <c r="O104" t="n">
-        <v>0.0005819078942641007</v>
+        <v>0.0005819078942641008</v>
       </c>
       <c r="P104" t="n">
         <v>0.0005807431175099124</v>
@@ -7130,10 +7130,10 @@
         <v>0.0003281195260737335</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0002992334864261159</v>
+        <v>0.0002992334864261158</v>
       </c>
       <c r="E105" t="n">
-        <v>0.000275117051719068</v>
+        <v>0.0002751170517190681</v>
       </c>
       <c r="F105" t="n">
         <v>0.0002711204103280613</v>
@@ -7142,10 +7142,10 @@
         <v>0.0002843057261366183</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0002937350389962246</v>
+        <v>0.0002937350389962245</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0004309743791230668</v>
+        <v>0.0004309743791230669</v>
       </c>
       <c r="J105" t="n">
         <v>0.0003776526779766492</v>
@@ -7154,7 +7154,7 @@
         <v>0.0003673730396040664</v>
       </c>
       <c r="L105" t="n">
-        <v>0.0004079886253197026</v>
+        <v>0.0004079886253197027</v>
       </c>
       <c r="M105" t="n">
         <v>0.0004109781911079899</v>
@@ -7166,19 +7166,19 @@
         <v>0.0006138876562689627</v>
       </c>
       <c r="P105" t="n">
-        <v>0.0006859380279745258</v>
+        <v>0.0006859380279745259</v>
       </c>
       <c r="Q105" t="n">
         <v>0.0006079043915093755</v>
       </c>
       <c r="R105" t="n">
-        <v>0.0007802910060180881</v>
+        <v>0.000780291006018088</v>
       </c>
       <c r="S105" t="n">
-        <v>0.000744761140575886</v>
+        <v>0.0007447611405758861</v>
       </c>
       <c r="T105" t="n">
-        <v>0.0007318224023714983</v>
+        <v>0.0007318224023714981</v>
       </c>
     </row>
     <row r="106">
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.0005312872006624986</v>
+        <v>0.0005312872006624985</v>
       </c>
       <c r="D106" t="n">
         <v>0.0005025884151891144</v>
@@ -7203,19 +7203,19 @@
         <v>0.000468587409488516</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0005223190404285562</v>
+        <v>0.0005223190404285563</v>
       </c>
       <c r="H106" t="n">
         <v>0.0005744933669933773</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0007480583065481392</v>
+        <v>0.0007480583065481391</v>
       </c>
       <c r="J106" t="n">
         <v>0.0006357353647402054</v>
       </c>
       <c r="K106" t="n">
-        <v>0.0006361350558831928</v>
+        <v>0.0006361350558831927</v>
       </c>
       <c r="L106" t="n">
         <v>0.0006975126028247368</v>
@@ -7258,10 +7258,10 @@
         <v>0.0001203949576113875</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0001039714513592692</v>
+        <v>0.0001039714513592693</v>
       </c>
       <c r="E107" t="n">
-        <v>8.275764508310722e-05</v>
+        <v>8.275764508310723e-05</v>
       </c>
       <c r="F107" t="n">
         <v>0.0001105674924716778</v>
@@ -7337,40 +7337,40 @@
         <v>0.00166399091866954</v>
       </c>
       <c r="I108" t="n">
-        <v>0.002059701171953408</v>
+        <v>0.002059701171953409</v>
       </c>
       <c r="J108" t="n">
-        <v>0.001825634799248106</v>
+        <v>0.001825634799248105</v>
       </c>
       <c r="K108" t="n">
-        <v>0.001842983141750746</v>
+        <v>0.001842983141750745</v>
       </c>
       <c r="L108" t="n">
-        <v>0.002048684847425215</v>
+        <v>0.002048684847425216</v>
       </c>
       <c r="M108" t="n">
         <v>0.002012945057390616</v>
       </c>
       <c r="N108" t="n">
-        <v>0.00215937951807626</v>
+        <v>0.002159379518076259</v>
       </c>
       <c r="O108" t="n">
         <v>0.003172511747497062</v>
       </c>
       <c r="P108" t="n">
-        <v>0.003357961804295501</v>
+        <v>0.0033579618042955</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.003082666717881193</v>
+        <v>0.003082666717881192</v>
       </c>
       <c r="R108" t="n">
-        <v>0.003779187269129662</v>
+        <v>0.003779187269129663</v>
       </c>
       <c r="S108" t="n">
-        <v>0.003409692303071311</v>
+        <v>0.003409692303071313</v>
       </c>
       <c r="T108" t="n">
-        <v>0.00383381612130441</v>
+        <v>0.003833816121304411</v>
       </c>
     </row>
     <row r="109">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.000509017456725107</v>
+        <v>0.0005090174567251069</v>
       </c>
       <c r="D110" t="n">
         <v>0.0004652649040581745</v>
@@ -7486,7 +7486,7 @@
         <v>0.001055216403329197</v>
       </c>
       <c r="P110" t="n">
-        <v>0.001161792543355036</v>
+        <v>0.001161792543355035</v>
       </c>
       <c r="Q110" t="n">
         <v>0.0008645508298559274</v>
@@ -7511,16 +7511,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.007147848405644124</v>
+        <v>0.007147848405644123</v>
       </c>
       <c r="D111" t="n">
-        <v>0.006530013923308905</v>
+        <v>0.006530013923308906</v>
       </c>
       <c r="E111" t="n">
         <v>0.006737260256479564</v>
       </c>
       <c r="F111" t="n">
-        <v>0.005652538325049849</v>
+        <v>0.00565253832504985</v>
       </c>
       <c r="G111" t="n">
         <v>0.006064454686206185</v>
@@ -7535,16 +7535,16 @@
         <v>0.007365134961187587</v>
       </c>
       <c r="K111" t="n">
-        <v>0.007696000366660277</v>
+        <v>0.007696000366660278</v>
       </c>
       <c r="L111" t="n">
-        <v>0.008531112633392922</v>
+        <v>0.008531112633392924</v>
       </c>
       <c r="M111" t="n">
-        <v>0.008130492792810622</v>
+        <v>0.008130492792810624</v>
       </c>
       <c r="N111" t="n">
-        <v>0.008262168682014213</v>
+        <v>0.008262168682014209</v>
       </c>
       <c r="O111" t="n">
         <v>0.01306399765912115</v>
@@ -7581,22 +7581,22 @@
         <v>0.0004774197466258876</v>
       </c>
       <c r="E112" t="n">
-        <v>0.0006043427719283416</v>
+        <v>0.0006043427719283417</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0004740470611210126</v>
+        <v>0.0004740470611210125</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0005040043478129773</v>
+        <v>0.0005040043478129772</v>
       </c>
       <c r="H112" t="n">
         <v>0.0005086751465523831</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0006598873882081577</v>
+        <v>0.0006598873882081576</v>
       </c>
       <c r="J112" t="n">
-        <v>0.0006362950144766721</v>
+        <v>0.000636295014476672</v>
       </c>
       <c r="K112" t="n">
         <v>0.000594871373039336</v>
@@ -7605,10 +7605,10 @@
         <v>0.0006676143735352389</v>
       </c>
       <c r="M112" t="n">
-        <v>0.0007044272265569302</v>
+        <v>0.0007044272265569303</v>
       </c>
       <c r="N112" t="n">
-        <v>0.0006877594739995331</v>
+        <v>0.000687759473999533</v>
       </c>
       <c r="O112" t="n">
         <v>0.001135036464211664</v>
@@ -7617,7 +7617,7 @@
         <v>0.001045698333829123</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.001171191905468556</v>
+        <v>0.001171191905468555</v>
       </c>
       <c r="R112" t="n">
         <v>0.001241955291913951</v>
@@ -7651,7 +7651,7 @@
         <v>7.565264779590264e-05</v>
       </c>
       <c r="G113" t="n">
-        <v>7.48769002934442e-05</v>
+        <v>7.487690029344418e-05</v>
       </c>
       <c r="H113" t="n">
         <v>0.0001284485656628661</v>
@@ -7678,7 +7678,7 @@
         <v>0.0002164514147711673</v>
       </c>
       <c r="P113" t="n">
-        <v>0.0002333809984158051</v>
+        <v>0.000233380998415805</v>
       </c>
       <c r="Q113" t="n">
         <v>0.0002335213746660436</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5.418175824221336e-05</v>
+        <v>5.418175824221337e-05</v>
       </c>
       <c r="D114" t="n">
         <v>5.663931402314568e-05</v>
@@ -7715,13 +7715,13 @@
         <v>5.261395280240512e-05</v>
       </c>
       <c r="G114" t="n">
-        <v>5.042760941476644e-05</v>
+        <v>5.042760941476643e-05</v>
       </c>
       <c r="H114" t="n">
-        <v>8.585300278822269e-05</v>
+        <v>8.585300278822268e-05</v>
       </c>
       <c r="I114" t="n">
-        <v>7.864422016270534e-05</v>
+        <v>7.864422016270533e-05</v>
       </c>
       <c r="J114" t="n">
         <v>6.591663919710182e-05</v>
@@ -7730,7 +7730,7 @@
         <v>7.283201563832664e-05</v>
       </c>
       <c r="L114" t="n">
-        <v>8.157936311453007e-05</v>
+        <v>8.157936311453009e-05</v>
       </c>
       <c r="M114" t="n">
         <v>8.846380209521194e-05</v>
@@ -7748,7 +7748,7 @@
         <v>0.0001473246409846664</v>
       </c>
       <c r="R114" t="n">
-        <v>0.0001925872067486656</v>
+        <v>0.0001925872067486655</v>
       </c>
       <c r="S114" t="n">
         <v>0.000166602639066906</v>
@@ -7773,7 +7773,7 @@
         <v>0.0010197577509933</v>
       </c>
       <c r="E115" t="n">
-        <v>0.001037536273876654</v>
+        <v>0.001037536273876655</v>
       </c>
       <c r="F115" t="n">
         <v>0.00099906195723479</v>
@@ -7815,7 +7815,7 @@
         <v>0.003714974991880551</v>
       </c>
       <c r="S115" t="n">
-        <v>0.003788428533222401</v>
+        <v>0.0037884285332224</v>
       </c>
       <c r="T115" t="n">
         <v>0.003717374288917422</v>
@@ -7834,10 +7834,10 @@
         <v>0.0003446181325606332</v>
       </c>
       <c r="D116" t="n">
-        <v>0.0003085533645825064</v>
+        <v>0.0003085533645825065</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0003239574441846764</v>
+        <v>0.0003239574441846765</v>
       </c>
       <c r="F116" t="n">
         <v>0.0002892075629600128</v>
@@ -7849,7 +7849,7 @@
         <v>0.0003226964778247656</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0004150705282411047</v>
+        <v>0.0004150705282411046</v>
       </c>
       <c r="J116" t="n">
         <v>0.0003451214365192869</v>
@@ -7864,7 +7864,7 @@
         <v>0.0003925575484067068</v>
       </c>
       <c r="N116" t="n">
-        <v>0.0004235862255352091</v>
+        <v>0.0004235862255352092</v>
       </c>
       <c r="O116" t="n">
         <v>0.0006171008020656691</v>
@@ -7873,7 +7873,7 @@
         <v>0.0006203190875769606</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.0005924630684149526</v>
+        <v>0.0005924630684149528</v>
       </c>
       <c r="R116" t="n">
         <v>0.0006492516222633954</v>
@@ -7882,7 +7882,7 @@
         <v>0.0006594607850583615</v>
       </c>
       <c r="T116" t="n">
-        <v>0.000766940818658052</v>
+        <v>0.0007669408186580522</v>
       </c>
     </row>
     <row r="117">
@@ -7907,7 +7907,7 @@
         <v>0.0001453750515334986</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0001133677673913557</v>
+        <v>0.0001133677673913558</v>
       </c>
       <c r="H117" t="n">
         <v>0.000171288110198191</v>
@@ -7919,10 +7919,10 @@
         <v>0.0002205986636869308</v>
       </c>
       <c r="K117" t="n">
-        <v>0.000259850578022536</v>
+        <v>0.0002598505780225361</v>
       </c>
       <c r="L117" t="n">
-        <v>0.000283095464129346</v>
+        <v>0.0002830954641293459</v>
       </c>
       <c r="M117" t="n">
         <v>0.0002666394848199745</v>
@@ -7931,7 +7931,7 @@
         <v>0.0002062096273551532</v>
       </c>
       <c r="O117" t="n">
-        <v>0.0005474047743563914</v>
+        <v>0.0005474047743563915</v>
       </c>
       <c r="P117" t="n">
         <v>0.0005724282905675983</v>
@@ -7943,7 +7943,7 @@
         <v>0.0007196959365290616</v>
       </c>
       <c r="S117" t="n">
-        <v>0.000881335348135572</v>
+        <v>0.0008813353481355721</v>
       </c>
       <c r="T117" t="n">
         <v>0.0009433717042739697</v>
@@ -7968,7 +7968,7 @@
         <v>2.607339466893031e-05</v>
       </c>
       <c r="F118" t="n">
-        <v>3.102408228519345e-05</v>
+        <v>3.102408228519346e-05</v>
       </c>
       <c r="G118" t="n">
         <v>2.998009329252379e-05</v>
@@ -7977,7 +7977,7 @@
         <v>2.909157938992634e-05</v>
       </c>
       <c r="I118" t="n">
-        <v>5.125573469826686e-05</v>
+        <v>5.125573469826685e-05</v>
       </c>
       <c r="J118" t="n">
         <v>4.602646479555879e-05</v>
@@ -7989,7 +7989,7 @@
         <v>5.024265045365883e-05</v>
       </c>
       <c r="M118" t="n">
-        <v>5.263563450962619e-05</v>
+        <v>5.26356345096262e-05</v>
       </c>
       <c r="N118" t="n">
         <v>5.554544091376503e-05</v>
@@ -8001,7 +8001,7 @@
         <v>9.532959798594227e-05</v>
       </c>
       <c r="Q118" t="n">
-        <v>9.547683253804425e-05</v>
+        <v>9.547683253804422e-05</v>
       </c>
       <c r="R118" t="n">
         <v>0.0001226006110813631</v>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.0008374511892421998</v>
+        <v>0.0008374511892421999</v>
       </c>
       <c r="D119" t="n">
-        <v>0.0007057024568883136</v>
+        <v>0.0007057024568883135</v>
       </c>
       <c r="E119" t="n">
         <v>0.0007760414324597531</v>
@@ -8035,13 +8035,13 @@
         <v>0.0008854474032033802</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0009385091090253416</v>
+        <v>0.0009385091090253418</v>
       </c>
       <c r="H119" t="n">
         <v>0.0009041365314913683</v>
       </c>
       <c r="I119" t="n">
-        <v>0.001579205010724203</v>
+        <v>0.001579205010724202</v>
       </c>
       <c r="J119" t="n">
         <v>0.001348083700130227</v>
@@ -8087,22 +8087,22 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.08294435941061667</v>
+        <v>0.08294435941061666</v>
       </c>
       <c r="D120" t="n">
         <v>0.07244715071478684</v>
       </c>
       <c r="E120" t="n">
-        <v>0.07671815958582948</v>
+        <v>0.07671815958582952</v>
       </c>
       <c r="F120" t="n">
-        <v>0.07302167194658782</v>
+        <v>0.07302167194658785</v>
       </c>
       <c r="G120" t="n">
-        <v>0.07399650220444438</v>
+        <v>0.07399650220444437</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1052170263830711</v>
+        <v>0.105217026383071</v>
       </c>
       <c r="I120" t="n">
         <v>0.1280073206437392</v>
@@ -8129,13 +8129,13 @@
         <v>0.3622728467840045</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.3366920965255814</v>
+        <v>0.3366920965255812</v>
       </c>
       <c r="R120" t="n">
-        <v>0.5444708312077031</v>
+        <v>0.544470831207703</v>
       </c>
       <c r="S120" t="n">
-        <v>0.5759239926054915</v>
+        <v>0.5759239926054918</v>
       </c>
       <c r="T120" t="n">
         <v>0.5645843964217834</v>
@@ -8224,13 +8224,13 @@
         <v>9.683241931202646e-05</v>
       </c>
       <c r="F122" t="n">
-        <v>9.336942671152424e-05</v>
+        <v>9.336942671152425e-05</v>
       </c>
       <c r="G122" t="n">
         <v>9.700381777678582e-05</v>
       </c>
       <c r="H122" t="n">
-        <v>6.444175435842753e-05</v>
+        <v>6.444175435842752e-05</v>
       </c>
       <c r="I122" t="n">
         <v>0.0001208756126330559</v>
@@ -8245,7 +8245,7 @@
         <v>0.0001254752240059063</v>
       </c>
       <c r="M122" t="n">
-        <v>0.0001133082436819778</v>
+        <v>0.0001133082436819777</v>
       </c>
       <c r="N122" t="n">
         <v>0.0001414580864127322</v>
@@ -8288,7 +8288,7 @@
         <v>0.003533748019788139</v>
       </c>
       <c r="F123" t="n">
-        <v>0.00294882252699109</v>
+        <v>0.002948822526991089</v>
       </c>
       <c r="G123" t="n">
         <v>0.003054973716370517</v>
@@ -8297,7 +8297,7 @@
         <v>0.003577567405704181</v>
       </c>
       <c r="I123" t="n">
-        <v>0.004737435951652458</v>
+        <v>0.004737435951652457</v>
       </c>
       <c r="J123" t="n">
         <v>0.004213765123830884</v>
@@ -8306,10 +8306,10 @@
         <v>0.004191737774084481</v>
       </c>
       <c r="L123" t="n">
-        <v>0.005015183497732233</v>
+        <v>0.005015183497732232</v>
       </c>
       <c r="M123" t="n">
-        <v>0.004480007275639681</v>
+        <v>0.004480007275639679</v>
       </c>
       <c r="N123" t="n">
         <v>0.00490965492978022</v>
@@ -8376,7 +8376,7 @@
         <v>0.00234336773060925</v>
       </c>
       <c r="N124" t="n">
-        <v>0.002344325229694611</v>
+        <v>0.00234432522969461</v>
       </c>
       <c r="O124" t="n">
         <v>0.003602182383823797</v>
@@ -8385,7 +8385,7 @@
         <v>0.003846416694744855</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.002974145876743081</v>
+        <v>0.00297414587674308</v>
       </c>
       <c r="R124" t="n">
         <v>0.003818410215955781</v>
@@ -8413,7 +8413,7 @@
         <v>0.00364061851595127</v>
       </c>
       <c r="E125" t="n">
-        <v>0.003334963984193434</v>
+        <v>0.003334963984193435</v>
       </c>
       <c r="F125" t="n">
         <v>0.003582132138181014</v>
@@ -8428,13 +8428,13 @@
         <v>0.005302572990986082</v>
       </c>
       <c r="J125" t="n">
-        <v>0.004217126843982001</v>
+        <v>0.004217126843982003</v>
       </c>
       <c r="K125" t="n">
         <v>0.00482352229059526</v>
       </c>
       <c r="L125" t="n">
-        <v>0.005411799257794389</v>
+        <v>0.005411799257794388</v>
       </c>
       <c r="M125" t="n">
         <v>0.004888420028105881</v>
@@ -8443,7 +8443,7 @@
         <v>0.005347422089636876</v>
       </c>
       <c r="O125" t="n">
-        <v>0.007723229612201963</v>
+        <v>0.007723229612201964</v>
       </c>
       <c r="P125" t="n">
         <v>0.008097523801534201</v>
@@ -8452,7 +8452,7 @@
         <v>0.007843068793175079</v>
       </c>
       <c r="R125" t="n">
-        <v>0.008485405230374145</v>
+        <v>0.008485405230374143</v>
       </c>
       <c r="S125" t="n">
         <v>0.009047123790318325</v>
@@ -8477,7 +8477,7 @@
         <v>7.61832913938599e-05</v>
       </c>
       <c r="E126" t="n">
-        <v>6.984882314639062e-05</v>
+        <v>6.984882314639063e-05</v>
       </c>
       <c r="F126" t="n">
         <v>8.099354807239215e-05</v>
@@ -8510,7 +8510,7 @@
         <v>0.0002307100277549754</v>
       </c>
       <c r="P126" t="n">
-        <v>0.0001442337197691568</v>
+        <v>0.0001442337197691567</v>
       </c>
       <c r="Q126" t="n">
         <v>0.0002312874930300865</v>
@@ -8544,13 +8544,13 @@
         <v>0.0002587802709785501</v>
       </c>
       <c r="F127" t="n">
-        <v>0.000319122862497408</v>
+        <v>0.0003191228624974081</v>
       </c>
       <c r="G127" t="n">
         <v>0.0003228298492788282</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0003097559130749407</v>
+        <v>0.0003097559130749406</v>
       </c>
       <c r="I127" t="n">
         <v>0.0005329165062810001</v>
@@ -8559,13 +8559,13 @@
         <v>0.0004478897516809736</v>
       </c>
       <c r="K127" t="n">
-        <v>0.0004808507830728365</v>
+        <v>0.0004808507830728366</v>
       </c>
       <c r="L127" t="n">
         <v>0.0005766476522944178</v>
       </c>
       <c r="M127" t="n">
-        <v>0.0005477158417101017</v>
+        <v>0.0005477158417101016</v>
       </c>
       <c r="N127" t="n">
         <v>0.0005624510555085067</v>
@@ -8666,7 +8666,7 @@
         <v>0.0002836671988360609</v>
       </c>
       <c r="D129" t="n">
-        <v>0.0002364355398638174</v>
+        <v>0.0002364355398638173</v>
       </c>
       <c r="E129" t="n">
         <v>0.0002384822229516347</v>
@@ -8678,7 +8678,7 @@
         <v>0.0002167103776823667</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0002843712783910106</v>
+        <v>0.0002843712783910105</v>
       </c>
       <c r="I129" t="n">
         <v>0.0003781142538314995</v>
@@ -8739,7 +8739,7 @@
         <v>0.0001837895131469715</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0001889567661646297</v>
+        <v>0.0001889567661646296</v>
       </c>
       <c r="H130" t="n">
         <v>0.0001811583334806759</v>
@@ -8766,16 +8766,16 @@
         <v>0.0005032180095659545</v>
       </c>
       <c r="P130" t="n">
-        <v>0.0005143332813676094</v>
+        <v>0.0005143332813676093</v>
       </c>
       <c r="Q130" t="n">
         <v>0.0004815063007408813</v>
       </c>
       <c r="R130" t="n">
-        <v>0.0006195055794507305</v>
+        <v>0.0006195055794507304</v>
       </c>
       <c r="S130" t="n">
-        <v>0.0005930251422931644</v>
+        <v>0.0005930251422931645</v>
       </c>
       <c r="T130" t="n">
         <v>0.0006181830083405932</v>
@@ -8800,28 +8800,28 @@
         <v>0.0003911675795254287</v>
       </c>
       <c r="F131" t="n">
-        <v>0.00038773232435355</v>
+        <v>0.0003877323243535501</v>
       </c>
       <c r="G131" t="n">
         <v>0.0004071351563649744</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0003954544500542531</v>
+        <v>0.0003954544500542532</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0005970426026338269</v>
+        <v>0.0005970426026338271</v>
       </c>
       <c r="J131" t="n">
-        <v>0.0005076960394431193</v>
+        <v>0.0005076960394431194</v>
       </c>
       <c r="K131" t="n">
         <v>0.0005226102825393457</v>
       </c>
       <c r="L131" t="n">
-        <v>0.000649705106513389</v>
+        <v>0.0006497051065133891</v>
       </c>
       <c r="M131" t="n">
-        <v>0.0006331856630348601</v>
+        <v>0.0006331856630348602</v>
       </c>
       <c r="N131" t="n">
         <v>0.0006653381405512702</v>
@@ -8836,7 +8836,7 @@
         <v>0.00104423979471078</v>
       </c>
       <c r="R131" t="n">
-        <v>0.0012790036257962</v>
+        <v>0.001279003625796201</v>
       </c>
       <c r="S131" t="n">
         <v>0.001236341242380846</v>
@@ -8870,7 +8870,7 @@
         <v>0.0002474034297589365</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0002593264301543935</v>
+        <v>0.0002593264301543934</v>
       </c>
       <c r="I132" t="n">
         <v>0.0003833325408872984</v>
@@ -8894,7 +8894,7 @@
         <v>0.000607613581113649</v>
       </c>
       <c r="P132" t="n">
-        <v>0.0006277066171719665</v>
+        <v>0.0006277066171719668</v>
       </c>
       <c r="Q132" t="n">
         <v>0.0006321351751211766</v>
@@ -8928,7 +8928,7 @@
         <v>0.00453044603107151</v>
       </c>
       <c r="F133" t="n">
-        <v>0.004946411591386994</v>
+        <v>0.004946411591386993</v>
       </c>
       <c r="G133" t="n">
         <v>0.005366816874833896</v>
@@ -8937,7 +8937,7 @@
         <v>0.005107404369321484</v>
       </c>
       <c r="I133" t="n">
-        <v>0.008417793333523787</v>
+        <v>0.008417793333523783</v>
       </c>
       <c r="J133" t="n">
         <v>0.007289189782693875</v>
@@ -8946,10 +8946,10 @@
         <v>0.007044396425886384</v>
       </c>
       <c r="L133" t="n">
-        <v>0.009244010188467199</v>
+        <v>0.009244010188467197</v>
       </c>
       <c r="M133" t="n">
-        <v>0.009689482060003222</v>
+        <v>0.009689482060003226</v>
       </c>
       <c r="N133" t="n">
         <v>0.008846914022983319</v>
@@ -8995,7 +8995,7 @@
         <v>1.044860789430714e-05</v>
       </c>
       <c r="G134" t="n">
-        <v>1.104254080964705e-05</v>
+        <v>1.104254080964704e-05</v>
       </c>
       <c r="H134" t="n">
         <v>1.454756455273593e-05</v>
@@ -9016,7 +9016,7 @@
         <v>1.409286831441157e-05</v>
       </c>
       <c r="N134" t="n">
-        <v>1.449712576945149e-05</v>
+        <v>1.449712576945148e-05</v>
       </c>
       <c r="O134" t="n">
         <v>1.263812129707981e-05</v>
@@ -9034,7 +9034,7 @@
         <v>1.543914967820906e-05</v>
       </c>
       <c r="T134" t="n">
-        <v>2.074225799857104e-05</v>
+        <v>2.074225799857105e-05</v>
       </c>
     </row>
     <row r="135">
@@ -9062,13 +9062,13 @@
         <v>7.820272408018849e-05</v>
       </c>
       <c r="H135" t="n">
-        <v>7.722665167844127e-05</v>
+        <v>7.722665167844125e-05</v>
       </c>
       <c r="I135" t="n">
         <v>0.0001045199426009159</v>
       </c>
       <c r="J135" t="n">
-        <v>9.003486421357501e-05</v>
+        <v>9.003486421357502e-05</v>
       </c>
       <c r="K135" t="n">
         <v>9.022922387731306e-05</v>
@@ -9083,16 +9083,16 @@
         <v>0.0001258380609405097</v>
       </c>
       <c r="O135" t="n">
-        <v>0.0002211602638222908</v>
+        <v>0.0002211602638222907</v>
       </c>
       <c r="P135" t="n">
         <v>0.0002379470581590378</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.0002369660470445203</v>
+        <v>0.0002369660470445204</v>
       </c>
       <c r="R135" t="n">
-        <v>0.000290811137240471</v>
+        <v>0.0002908111372404711</v>
       </c>
       <c r="S135" t="n">
         <v>0.0002868133134086001</v>
@@ -9181,13 +9181,13 @@
         <v>5.987897606895392e-05</v>
       </c>
       <c r="E137" t="n">
-        <v>7.592792195923595e-05</v>
+        <v>7.592792195923593e-05</v>
       </c>
       <c r="F137" t="n">
         <v>9.06779831811206e-05</v>
       </c>
       <c r="G137" t="n">
-        <v>9.263980389547892e-05</v>
+        <v>9.26398038954789e-05</v>
       </c>
       <c r="H137" t="n">
         <v>9.253281528359185e-05</v>
@@ -9196,7 +9196,7 @@
         <v>0.0001165642505054719</v>
       </c>
       <c r="J137" t="n">
-        <v>8.399193914626368e-05</v>
+        <v>8.399193914626369e-05</v>
       </c>
       <c r="K137" t="n">
         <v>0.0001128028122691764</v>
@@ -9214,13 +9214,13 @@
         <v>0.0001818846517113032</v>
       </c>
       <c r="P137" t="n">
-        <v>0.0001871961942871278</v>
+        <v>0.0001871961942871277</v>
       </c>
       <c r="Q137" t="n">
         <v>0.0001531627684869459</v>
       </c>
       <c r="R137" t="n">
-        <v>0.0001778793132019595</v>
+        <v>0.0001778793132019594</v>
       </c>
       <c r="S137" t="n">
         <v>0.0001665894922312595</v>
@@ -9257,13 +9257,13 @@
         <v>3.28840475433554e-05</v>
       </c>
       <c r="I138" t="n">
-        <v>5.615126011644947e-05</v>
+        <v>5.615126011644948e-05</v>
       </c>
       <c r="J138" t="n">
         <v>4.201461271103691e-05</v>
       </c>
       <c r="K138" t="n">
-        <v>4.868407987707679e-05</v>
+        <v>4.868407987707678e-05</v>
       </c>
       <c r="L138" t="n">
         <v>5.72652502153265e-05</v>
@@ -9321,10 +9321,10 @@
         <v>2.7021572002866e-05</v>
       </c>
       <c r="I139" t="n">
-        <v>4.085095622685301e-05</v>
+        <v>4.085095622685302e-05</v>
       </c>
       <c r="J139" t="n">
-        <v>3.164702132123839e-05</v>
+        <v>3.16470213212384e-05</v>
       </c>
       <c r="K139" t="n">
         <v>3.464555468065137e-05</v>
@@ -9336,7 +9336,7 @@
         <v>2.912079709059454e-05</v>
       </c>
       <c r="N139" t="n">
-        <v>4.05925212695784e-05</v>
+        <v>4.059252126957839e-05</v>
       </c>
       <c r="O139" t="n">
         <v>6.880220346458619e-05</v>
@@ -9345,7 +9345,7 @@
         <v>5.083278630743579e-05</v>
       </c>
       <c r="Q139" t="n">
-        <v>7.053963119870861e-05</v>
+        <v>7.053963119870863e-05</v>
       </c>
       <c r="R139" t="n">
         <v>5.235914051958046e-05</v>
@@ -9354,7 +9354,7 @@
         <v>7.788555778846933e-05</v>
       </c>
       <c r="T139" t="n">
-        <v>7.829605240254976e-05</v>
+        <v>7.829605240254974e-05</v>
       </c>
     </row>
     <row r="140">
